--- a/Bons/paliers.xlsx
+++ b/Bons/paliers.xlsx
@@ -26,20 +26,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D54B33"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,9 +55,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,14 +428,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,346 +447,571 @@
           <t>Palier</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Prize 1</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Prize 2</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Prize 3</t>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cadeau 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Image 1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cadeau 2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Image 2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cadeau 3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Image 3</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Soundbar Xiaomi 2.1 ch (Black)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TV AZATECH 50" 50H2</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TV Hisense 43" 4K UHD + Apple AirPods Pro 3</t>
+      <c r="B2" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>vivo Y04 6.7" 64Go ROM + 4GB</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAAAAQQDAQAAAAAAAAAAAAAAAAIDBAcFBggB/8QAUhAAAQMCAwMFCQkMCgEFAAAAAQACAwQRBQYhBxIxE0FRYbEIVXFzdIGSstEUFyI2cpGTwdIYIyYnMjM1Q1JjdaEVFjRCRWJkgoPwJERUosLx/8QAGwEAAQUBAQAAAAAAAAAAAAAAAAECBAUGAwf/xAA3EQACAQIEAgYHCAMBAAAAAAAAAQIDEQQSITEFQTJRcYGx8AYTImGRodEUFSMzNEKywTVS4VP/2gAMAwEAAhEDEQA/AOkUIQgDU9oOe6TIuBCrlj5epmO5BCDbePSegBUPV7bc5Vc7pG1sNKy9wyKMAAeErOd0RUPfmTDqck7jILgdZJVXVFJSUGCxYhVO5U7olMW9ZpLiWxMPWd17yeZo6SusUrXIk5ScrI3On2tZ4qheHEJ5WjnZBcfPZOO2sZ1YbPxSRvhjA+pVXSZhqZ6svfJIQDoGuLWtHUAdArBwWtpcQZAK9zqqkkeIpAT98jJ4EO4kHgL8DbmS3QjjNK9zJja1nLvs70G+xK99rOPfZ3oN9i1zFcIlwrG6jDiTM+GTca5o/OA6tIHWCD51FdC6OQse1zHtNiHCxHhCdZHHNLrNt99nOPfV3oN9i999nONv0q70G+xafuI3EWQZ31m4++znHvqfQHsSmbWM4vcGjFbX5yxth1nRaZZJlbu0dUf3Lh8+iGkOUm3a5nvfxzzidW6iwOWqrHjQvjgDnHrtb4IUkZ62yEaU+J/Rx+xbFsxwKHDsg4bJGwCStjFTM4cXl2ov4BYLcWUzQOAVjSwEJQUpPVmVxfpHWp15U6NNZYu13fWxVv8AXfbMf/TYn9HH7Ef122030p8Rt4qNWw2nHQF7LHHTxGSThzDnJ6E54Cn1s5L0kxNruEfn9Sn67aDtjw6hlrKuPEIaeIFz3mFlmgcSsNT7cNolVUw08FfUyzT25NjY2Evv0aK28VnjqqeWGoa18crDG5nNukWI+ZVzhWSMKy/i5rqaaonkZcRNlcLR342sNTZP+6KkpRUHpz9xJwnpRCrCbqxtJdG19foeO2l7W2flGtH/ABxpA2p7VW/lSVvmjj9izUzi4lRXhWS4DR5yfyEj6Q13vBfP6mP99bakP1lb6EfsSTtg2n0/3x76wtbqQYWO/kApbmplzbG44pfuGi9pv5HePHaj3ivmWRsk27Ozdi7cBx6COnxCTSGZg3RIR/dLeYq7Vxe2MUG0rAq+AbkskgLiOctc3X5iu0BwWXxVB4erKk+Rp8NWVemqi5ghCFGJIIKEFAHOfdCj8LaLydva5VHXtlxXK9ZDEQZKSoilIJ/V7jo7+AOc2/RvK3e6E+N1F5O3/wCypyhqpaPEHTQv3Xh7hqAQQdCCDoQRoQdCF2SvGxCbyzua5SVZonPY+ICVpI+EL7vMdOnrWy5VnqKvEqenZcCWVp8DWkOJ8AAUx+XsNxaQTNpZ6ZzuIhkvH5g4EjwXWzZdwSkwYOMMbjM8WdJJq63R1BCTHyqR5Gdw/MxwTPrMakpW1YiZyZjJ3TbcDbg8xFlAzbjn9aMyVGK+5W0olDWiMO3jZotcnnJUKcB9ZMf857Unk0+2tyLmdrEMxpJZophjSDGEohE3U3P/AGGp8Ue0KU5iYqW2oanxZ7QmvYfDpIuLIDAdnWAH/QxeqtjEYWD2es/Fxl8/6CLsWxhmquqcvYXYYHEUl6+b978RsMDQXE2AFyTzLXsRruVeX8GDRg+tZPHKrkom0zD8KT4T+odC1KsqN5xAOgVhhaeZ5mU2Mlml6mOy3I9XUF5Oqx79Sn36lNlquItRVkLBKK0IzmppzFKLdUgsRnJCkQ3Rpl0anuj1TTo05SO8ZmsYg3dznl7rkd6zF2UFxzizd3OeXfGO9Zi7GHBYbirvip93gj0ThDvhIPt8WCEIVYWoIKEFAHOfdCH8LqLydva5U7ByVLSVuJTtD2QSCONjuD5XXIv1ANc49NgOdXD3Qx/C+i8nb2uVQGmOJ5dxCiiNpoKkVgH7TA1zHn/bvNceoOPMu37SG0nU1MZSYpPUVTpZAZdeLh/23gC37AcTjfDERIbOeI3xuN90n8lzT0X0I67qr6asmw1z4nM3X8LjjY8degrYMrunqsRp4tQHPEj+pjSCSewdZSJnWUVbU3ofCmmP71/anA3RM07t8yuPPM8//IqS0Cy7EAac1NOapTgmnN04JAIrwotYLUFT4s9oU1wsoldph9R4s9oSS2Hw6SLq2eA+9rl3yCL1VsZG6C52gAuT1LA7Oh+LPLvkEXYslj9Q6lweTdPwpPgDzq0pe0oxRi8XaE6k3ybNTxKuNRPNOTrI7TqHMsM9xJT9S+790cBomN1aKmlFWRl4L9z3Y3YpO6nt0ILQV0zHW4wWFJLLp8sSSEZhykRyxIczqUkt1SSzVKpD1I1HHW7uc8udcjvWYuwQuQcxi2cct+Mf6zF18sZxN3xMu7wR6bwV3wUO/wAWCEIVcXAIKEFAHOHdDm2cKLydva5UvBUS01Xy8EjopY5C5j2Gxab8QVb2395OeA0kkNYwDX/IPaqddcPk6d4ld47EGe7Jz20mIvMk+GQGXi58O9GD1lrTujzALNYLHT0bC2nibFv6utxPhK6SyFheFUGSMKjw+npuRnhZJvgC9Q4t1c48+vsVH5/bh9HtGxSDDmxxwskG8yK24ySwLwLdBTYyTdrDqkWoptkKidvRyG/61/rFTWlQKJpZAQ7Que53zm6mNdoupGY6Uhy93khxCBo08aqFX/o6o8We0KY86qHX/o6p8We0JJbM6Q6SLw2cD8WWXPIIvVXubZTemh5tXn/vmStm4/FjlzyCL1VFzY4nEC0/3ItFbYPWcTDcW9mNT3v+zUnm7yetegdSSBcp0BX97GebsIsiycsvLWRcbcbISbFO2XlkDsw1ZJITpakkJbjkzUMzj8MsteMf6zF12uQs4fBzRl8jQjlT/Ni62oiXUMBJuTG0/wAgshxH9RLzyR6hwP8AQ0+/xY+hCFXl2CEIQBzHt++PZ+Sz1AqxxGWOowylIjDJ6YGNzh+sYTdpPWLkeC3QrO7oAWzzfpYwj0AqvjdpwUiOxAnuxWHZux7C6I0dDi9ZTUxv96jlIaL8bdHmS8Kd7orGCXfcwuvIRq619fOmhQ0r3bzoh5iQspSNjgaGxMDG9SUY2Z2Wo901Mku4GB5uGN4NHMPMLJTXKDFIn2yJRhJ3+tJLr63TO/rxQXoEFOdoodcb4fUfIPaE+So1Wb0FSP3Z7Qkew+HSRfOzYX2Y5c8gi9VRc2MIrnn9qHT+Sm7NR+K/LnkEXqozbAeVgfbR7HM+tWWEllnExPGI3hUfU7/M0WMXKkBqaiFnEdCkht1fqRl5vUb3Ubid3bLwtS3OeYZLSvN1OkII0RccpDBCQQnnCxQIHu5rDr0SZrj0zRc5C2ZsA/5e1i61of0fT+Lb2BcnZ4j3Mz5eAdcnlRw62LrKhBFBTg80bewLKcQ/US88keqcBd8DTfb4sfQhCgF4CChBQBzZ3Rp/DCh8nb2uVRMdrxVp90Qfw3i8Uz1VU7HKRHYgz6TJjHaqVFKsex2qkNelOZlI5OtSGy3WMjkUhsl0CE8SaI5TmUQSar3lECEgv1TVQ69FUeLPaE2XpMjr0tR4s9oSPYdDpI6I2aD8V+W/4fF6qn5pp9/CRMBcwPDj4OdQtmQ/Fdlv+HxeqtlqadtVSyQPF2yNLSpUJZbMzWMo+tdSHXcqSePkat7ea90/HqE7idM+MXcPhxOMT/CExTvDtFoKVTNFMwM07a7od3V4W25lIjidK/dY3ed0BSH00VNpM7lJP2G83hTnOzsc4xbWZ7GObE+Q2Y0nwcyUaYM/OP8AM32qS+VzhYWa0cwTJC6KLe4mfqG7NafgNA6+dIcDfinbJJC6JpbC5jQ86C2b8s/Lk9Zi6zHBcmZ9Fs0Zc/5e1i6vp9aeP5I7FkuIa4iXnkj1v0fd+H0+/wDkxxCEKAXwIKEFAHMHdE/HiLxTPVVSNNlcPdJG2cqDyYdrlTQK7x2IUl7TJLXJ9r1Da6xTzXdCcMaJjH6J9sigNkTrXoG2JwkuliS6hB/Wlh/QgCUX6Xuvd68FQP3R7QowenGG8U/ij2hI9h0ekjpbZkPxWZb/AIfF6q2khavsx12WZa/h8XqrawF3jsiiqr8SXazUcyYcBXh9rRVo3L9EoGnzjTzLT46ScV4pmNJkc7dAVqYjQR4jQyU0lwHjRw4tPMR1grUK1k9NROq3U/8A5j7wufHqBbRzx0X4Dzp9PGfZW3Lov5MzePwCzuqtt3587+4jyzR0EXualIMnCSYdPQPb8yx5CaZJwToN1eYepCUbxdzLVqjnLXbkuoTqvLJa8sVIzHEbISbJ0hJIskuOTK/2gC2Z8uf8vaxdWwf2eP5I7Fyrnv435Y+XJ60a6uHBZfHfny88kev+jv8Aj6ff/JghCFCL8EFCCgDmTulDbOVB5M3tcqZBVyd0sfw0oPJW9rlTAOq7LYiy3Y8DdLa4phpsnAbhOGNEgOultdZRgbJxrko2xJbIl73WowclB5SCEoPKfgddk/ij2hQQ/RSaU3bUD9y76kPYWPSR1Dsx02WZa/h8XqralVWzuhrhkHApYMfq4A+jjIjc1r2N04DqW6xS4/Tj8/SV7esGNyzkPSShndNxeja01292hCqYRuTaZmqt746Z5j/OEbrPlHQfzKx9Xh9fA29NLHPFGNwUpYBvNHQ79riddEqlxF9XW09PUUc1NK1++Q7VpABOh+ZZZrg5twQR0hW8K1DHwvF3Xw82IroNJpldYnhbTH7toQTCSd5lrFh5wRzW6FimS9asbEMNc6R1VR7omI++Ru0bMOvod1/OtTr8Ijqi+WjaY5WG0kDxZzT1j/oKiU8ZW4VUy1Nab59RlOIcIzNzpLXq6+z6GLDwV7dRXcpC8se0tcOIKW2UdK2WGx1LERUoO5lJU5RdmPFJK8314XKZmGWZomfPjflf5cnrRrq0LlDPeubssfLk9aNdXjgs5jfzpeeSPYPR3/HU+/8AkwQhChl+CEIKAOYO6XNs60Hkre1ypcaq5u6YNs7UHkre1ypcFdVsRnuxwFLa6yaSgbpw0eBSgUyDZL3kDbDod1pYcmAUoOSiEgOspVE6/L+Jd2hY9rlNoDd0/iXfUh7CrdF/7PKm2z7Amk8KKMfyW2w1JYfgusq9yFNbI2Ci/Ckj7Ft0U+nFeIY2MoYmpKOntPxEzas2OKZtW9kT7gHeBsbXBaQm2Yc6lPKYZO6B3PE9xdG75+Cx9DU7lVESdN4Ke2rMcrmHSxsrOhjvwoOpum1fmue43Km2TaTEhPL7nqIzT1Q/Vng7raedeV+Hw1xEhLoZ2CzJmflN6usdRTUrIa2IMl5tWuGjmnpBRT1crJfclW4GW33uTmlHtW0wHFVUSo4rVPZ/0/rzIdfDpq6MHiVEWAjE6cbg4VcIJZ/uHFvYsHU4NLGzlaZzaiE6hzDdWCZFiqnA6OWR0sBkopnal9Od0Hwt4FTpcMnRl6zBzyvq5GdxWCp117Su/g/+9/xNCO8w2III5iEb5WzVmCYnY2FJXtHORyMn1hYCroa6mJL8KrGAfstEg+cFTqHEsZTeTEU32rVfUzmI4ZOnrDVee40DO53s3ZZ+XJ6zF1kOC5JzlJv5vy20xyxlr5LiRhb/AHmdK62HBSKtT1ss/Wei8Bi44Cmn7/FghCFzLwEIQgDl3umPjxQeSN7XKl1c/dM/Hmg8kb2uVLLonoR3uzJ4bhEuIs3mTwQl8nIxNlcQZX2vuiwNubU2GoUFZbA6jdiDWRMnqYJhUQRGQsJda2nM7gPg6HTRYfeN7lOG2HAV6kApW8lEF3SgU2D1r0FAg7fVTcON3z+Jd9Sx41U3Dj8OfxLvqQ9hUtUXHkeW2S8HHRSs7FtMU3BaXkyXdyfhI/0zOxbLHMvIMdTvXn2vxIzerM3HPa2uqyM9RvSh4OjwHLXY5+ZTmVG9TNN9WHd83EfWq5wbg4jkzNQVe6bX0U1+5WU3JudY8WuHFp6Qtbjn14qdT1e64a6LthcQ6TyT1ix17oy9NVumic2XSohO7IOnod50vlljqiYRSR1o1DfgSj9ph9idkfuPLd645j0jmK9N4PjniKbpTd5R+a5P+mU2Np5HnWzJfKhHKdBsoXK9aOVV3crsxWG2N29nLJ+t9ZvXiXSIXNG1t4dnDKNuYzetEulxwTGavh7vQj55sEIQmk8EIQgDlvumfj3ReSN7XKl1c3dM/H2i8kZ2uVLLokR3uzJUbxBSvkZNyLyd0yiEuc3T8kHm8PFQQU7STtp955LnOOnJ/wB1w/zdI6kxzJdgFgkJfgTd16NClEHAbJQSEIEHAbKbh35ybxLvqUAG5U7Dfzs3iXfUh7Atyz8ny/gnhY6KZnYtjZN1rUMqybuWMNt/7dnYtgZNpxXl+Mp/jT7X4kOT9pmWZOplLPvb8d/y26eEa+1YRsvWpEVSY3teOLTdQclmBlmVHWpkM9+dYd7w2UhvDiPBzJ6GbXiok6VhUzZIJmyxmJ/5LgWnwFEEzpMPjLjeSBxgf5uH1rGQy21TtJOfd1fBfR8bZx4RoVc8BxUqWLjF89Pj/wBscMZDPRkT+VKOW6SoXKle8qvTLmT9aV5tTkD84ZT6jN60a6fHBctbTHXzdlXqMvrRrqUcEjNrwt3w0X2+LBCEJCzBCEIA5Y7pn4/0XkbPWcqXV2d05TyMzxh05H3uWjAaekhzr9oVJrqtjg92C9vovEIEFr0FeICRAKSwbpCAbJwg4pmGn79L4p31KEDcKZhptUvHTE4fyQC3N/yw+2WsOH7hvYs2yTTVVxlTOFLR4eygxEui5HRkgFwR0G3QtmbnDAu+UXzO9iwuLwVZVZWi3qQ505qT0NobIfCn2yaLVW5ywEf4nF8zvYnW51wAf4pF6LvYoDwVf/R/BgoS6jcuU36eN/O27D2j+R/knI5dQtVp89ZcEcjH4tCA5tx8F3EcObwr1ue8tg/paH0XexcJ4Gu/2P4MXJLqN6p5dAlQz7uZ4Gc0tLI35v8A9WoQbQsrtFnYzCP9r/Yhu0LLH9ZaKo/piDkY4pGuduvsCeHMjBYHEQxMJODST6mFSEnTasbtyuq9Ei1QbRMpW/TlP6L/ALKbl2k5ThjL/wCmY325mRvcT5rL0sxX2TEf+b+DMXtHdvZsyv4ZfWjXVQ4LiiozO/PG0zDRSxPZTRObDTscPhG7xdxA5ybadQXa44INzw6lKjh4wnul/bYIQhIWAIQhAGlbTdm9FtFwBlLLL7mracl9NUAX3SeII5wVznX9z9n2iqHMiw+CsZfSSGdtj5iQQhCcnYY4pkX3itoNv0Gfpo/tI94naB3jP00f2kIS5huU994raD3jP00f2l77xW0DvGfpo/tIQkzBlPRsL2gd4z9NH9pHvF7QO8Z+mj+0hCXMGRChsMz+P8EP0zPtJcWxHaDFI2RuCkOabj78z2oQjMGRCJu58zrUB80eEOiPEsM0Z+b4Wqifc+5570zelH9tCE0cg+59zz3pm9KP7aPufc9d6ZvSj+2hCQUPufc9d6ZvTj+2j7n3PXemb04/toQlAPufc9d6ZvSj+2j7n3PXemb04/toQgD37nzPXemb04/tpUfc9Z6e8N/ouRtzxdJGB6yEIAt3ZJsEOUcWjx3Hpo5q2HWCnjO82N37TjzkcwGivFCEgqBCEIFP/9k=</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>téléphone Samsung Galaxy A05</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHQABAAEFAQEBAAAAAAAAAAAAAAgCAwQFBgEHCf/EAFIQAAEDAgMDBwQKDQoHAAAAAAEAAgMEEQUGIQcSMSIjQVFxgbITFGFzNTZVcpGUsbPB0RUWFyQlJjJCdJKTtNJTVmNkdYKhosLwCCc3Q0ZihP/EABsBAQACAwEBAAAAAAAAAAAAAAABAgMEBQYH/8QALhEAAgIBAgIJBAIDAAAAAAAAAAECAxEEIRIxBRMyM0FRYXGxIzSh8BQVIpHR/9oADAMBAAIRAxEAPwCSKIiAIiIAiIgCJcdaXCAIlwlx1oAiXCXHWgCJcdaXHWgCJcdaXHWgCJcdaXCAIlx1pcdaAIiIAiIgCIiAIiIAiIgBXxbNe0rFsRrZ4sFq/sfhsT3Rsmja0y1G6bF13Ahrbg2sLnjfWy+wYi90eGVL2mzmxPIPpDSooYxVy0uUKZ8Li1xgiBcOLQWi5HptdWiiGdLHm3GZK7yD80YkJCQNwVtnfAsnEMfx2mgL48xYxvAga1ZP0L4vW1UEtMTCyJoa6waByr9d+Peu3wWuqa3KMLqtznStO7vO4ubbQnuKssEMzqzPeaoCRHmPE++clYA2j5w8oG/bJiNr/wAsVqcSfzh1Wq3ue71OEQdedombgR+MeI6/05WLVbT820lOZpMyYjutGtpjdc+X6tVVBTx1uP4PTzDeifWx7wPSBc2/wVox4morxCOposy7XcSpmz01XXxwvF2Goqwxzh12JB/wWV9lNsnujL8fH1ruGuvqeJ1Vd16FdEVLm2WycGcU2y+6Mvx8fWsPFM0bXMHw2Wvq8TqBTwgF7mVgcWi9r2B9K+iudZY9QyKpgkgnjbLFI0tex4uHA8QQj6Irx/i3n99Cjk0fN8Hz1tTx2aeOgxWqkNOGmQuqt0De4ak68Ctr9l9sfulN8fH1rp8LwvD8Ep3QYdSR0sTnbzgy5uesk6lZwkB6Vih0TBR+o9/Q1p6hp7I4o4xti90pvj4+teHH9sdPzgrp5CNd0VrXE9xK7i4KEAp/W0+b/H/DF/Ll5FzZNtpxPGMxjK+a4THXOO5HK9gY8Pto1wFgb9BtxtxvdfdVFLGYhS7W8rVkXJlkfG1xHTuzNt8qlauFfV1Vjh5G/XLjipBERYS4REQBERAEREBiYp7EVnqX+EqKsjWVOA00Mgu11NGP8oUqMalZBgNfNISGR08jnEC+gaSVEbEql8OWad0Ti0+RjaXDiG2FyPTZXiQzV4bl7DafEfJ1ErKl1+TEZQy+vSBqewEL6PgWAR5grjh7q2Oi5BkDiwWcRpugXAA+QBfIK2qhlprQxRta3hZo016+JK6jC6uepy1Eaol0g0u7i5ttCe4qfYhmJjLfIV88IlZL5J7mb7DdrrG1x6DZacv5zvWXXPvI5a4v5ferEGUH8pqzcEP40YKf64zwlapr9Qtjgh/GTBj1VrPCVkq7yPugj7Kx+gVe+sNkmiub9+le9cSzRcfIrDnqpxv0q2VMVgrjIe7S6RyXVKpZcPIUShlGrbUZbXKoOVhpVYK0XHc0ZRwcrmE32l5S9aPn41KocFFDMszINoeVppDZkb95xAvYCaNSvHBeT1/fy/fBHU0/doIiLSM4REQBERAEREBqs0e1DGP0Kb5tyie4Nmwenjfq0wM8IUsc0e1HGP0Kb5sqJTX/AIOg9Sz5ArxKs1eHYDRU1SXTxmqseS1z91nHpAFz3ELd10nMOuRckE2AA4dAHAdFvQsNj+dPaPlVddJzB7foVsEGgrH84e1YJdyx2q/VPvIe1YZdqO1SC8x2oWzwR34wYR6KxnhK07DqFtMEP4cwo/1xnhKy0d7H3XyWXM+ttfoFcEiwWyXVxsi+jOBudUZgkS91Ya6/SroWNrBilDBVdUn8q6q6F4RqFDMUo7FbeCrCpHBVALTmtzmWRwcTnP25Ze7D86xS4CiPnP25Ze7D86xS4C8br/uJfvgjco7tBERaJmCIiAIiIAiIgMDHYRU5exGAuLRLTSMJHEXYQoeB9qGH0RN+QKYWPzGmy5iU4aHGKlleATa9mEqG2/8AecXqm/IFeJVlbX84e0fKqq2TmD/voWK1/LPaPlXtZJzB7vkVyDS1DrvPasVx5Q7Vendyz2rGJ5Q7UBcY7ULa4Kfwvhp6qtvhK0zDqFtsEN8Vw79Lb4Ss2n76HuvkyV7ySPprZNOKuskusZguFeY0r6dJI9CqcmVG+6ymHRYcYIWQwngtaZr3UmRdBxVpz7NVUR5F+vVYnyOVYsF9qqVu6qutOfM5tqOQzRAKnP8AliAuLRK7cJHEXmjClkFErNE5p8+ZanDQ4xO3wDpe0zCpaheN1/3EjPT2EERFomYIiIAiIgCIiA1uY2OkytisbGlz30kzWtHEncOihhv/AHtGP6NvyBTXxT2Jq/Uv8JUIS+0DPeD6FeJDK2v5Z7R8q8q380e0fIrIdyj2heVb+aKuVNZM7lntVlx1Haq5Dd57VbJ170JPWHgttgOuKYd+lt8JWmb0LcZfP4Uw8/1xvhKzafvoe6+S9XbXufU6eLeA0WwjpbgaKxh4DrLoael32iwX0K+3hZ6hzUeZqfNiOhUvj3BddO3CSW3IWnxiFlO0tvr0rUhqFOWEa1liktjSeUMkoYOF9VnN4LGp4bHeI4rLDdFnsl4I5Nqye3QuQhUOWs9znWRycfmpr5s7ZejY0ue7kho4kmVil0FEvFz/AMycq+tb89GpaBeN6R+5l++CMlaxFIIiLQLhERAEREAREQGLinsTV+pf4SoNudzLfeN+hTjxT2Iq/Uv8JUFy7mh70K8SGVB2p7Qqap3NlUB3KPaPlVNS7kHtVyphOPK71bdxHavXHXvVBPDtQk9aeC2uBu3a2icTa1W3wlagcAtlhTrS0x6qlvhKz6ZZvgvVfJkq7a9z69hFQHbut13mFCJsYfI5rR0lxXxqjxaenI8mPgC6ChnxjFnNY1z2tPVxX0TW6Jy3bwjvXcL3bPoWMZqoqCExU7hJKeFtfgC5Fr6zFarfex1r6NGv+ysz7HYRgUYkxerAmIuIWnekd3fWseTOkr3+b4HhQDuAc5u+/wCAaBc+qtQX0Y59Xsjk26yuvbJs6fB6l41ZYK5JRQU7eeqYoz1FwWjkp8y4kN6vrfN2HXdLtf1W6Kw7C8PpdarEXOd08oNU8Ge1P/Rhjb1m5t5KmgYT98NefRwWLJV09rNcT3LX+UwhukW/MfRdytvkjIPk6SUDo5sq6rh5kuMTUYpIyTaRlXcN7Stv+2YpbqH1Q6+0fLPNuZz7NCLf95imCF4rpJJameP3ZGIIiLngIiIAiIgCIiAxMV9iKz1L/CVBEu5se9H0Kd2KexFX6l/hKgY53N/3R9CvEhlYdr8C8qTyT2qkHXvCpqDoe1XIMY/ld6oJ1C9Ju7vVJ4hQAOjsWzwdpkqKVoFyapo/ylasLa4E/wAnW0clt7dq2m390rPpn9aGPNfJaDxJM7+joaekj84rZBDEzUuPT6B1rJGbq+rlbhuW6N8Rfp5RrbyvHX1NHp/xWup8Iq8eqwZZPJwt4vPBvoaOtdjRyUeAw+YYNS+VqZNHEC7nHrcelfRtbfGG8t3+DdulK/ltExKTK0OHsNbj9X5SV3KdG1+l/wD2dxPcs2mxasrX+Z5cwq7L2Dms3WD61vMMyV509tfmOoMh/KbTtOg7V03n9NQwCCihZBGOAYLXXm79dKbwt3+DBDT1Rey3OShyJilXaXHcZ83b/IwcexbCDLOWsOtuUpqXj8+Z17rIqKuWZ99dVj+Se8kuutV2TfbkbkKG+SMkvo4m8zTxRgcA1qxZ5t4cAAqvNSTqqX0ZsqxurT2Zm/jSSyfP8zm+0vKZ0HOt4evjUqworZqhMO0rKQPTK35+NSpC42radraOXasTaYREWsYwiIgCIiAIiIDExX2IrPUv8JUCC7kdwU98V9h6z1L/AAlQFJ5vuCvEhlwHXvC8qDx7VS0694XlR09quVLB496oPEKq+veqHKCQDp3LcZdYJcSomHg6rYD8BWlut7lSB1TjWHQtNnSVjGj9UrJS8WRfqvkmPNH1CiZPWTCloxuNGjngWAXcYNhtNhMQLG70p4vOpJVrCsJjoaVrGNF7am3FbeKmc8i4Nrr0Wq1HFlyZ1JPj2QfUyzabxHcqRTneu43WeylA4DoVzzb0LzWo6SUNoGzVVGO7Nd5Nt/yfhVQhFgbWt6Vn+b+hUmD0LlS1s5vmbysiuRjGEG+vBemGzdQsjyZaVbczVZ6pye+Srnk+Z57aG7S8nW6ZB8/GpOBRl2gC20vJo/pB+8RqTS2W88zz+p71hERQa4REQBERAEREBiYr7D1nqX+EqAZPI7gp+Yr7D1nqX+EqAH5ncFeJDLgOveEnPHtXgPK7wvJuJ7Vcqy2InOAdcW1R0DwRe3C6oBO9xNrqlziLan4VBJc82kHGy6XZ+w/bpgzDx+yDAf1XLlA5x1ufhXV7Odc7YJ/aEfhcpjtJBElYoLtAss+CCwVFO3QLMDLdFlsaqx8jbhbsUBmuvFVbgVYFl7ZeZujlm1GwtlgVJYFdsllgUTJxlh0asPjsswhY8pAC36W0XjM+VbQ/+pmTfWD94iUmAozbQzfaZk70SD94iUmQugczUPNjCIiGAIiIAiIgCIiAxMV9h6z1L/CV+f8A+Z3BfoHiEbpsMqY2C7nxPaO0tK/Pt7XRucxwsW2BCvEhlYOveEm4ntXgOveEl4ntVypZ/O71S9e/nKlygkpBXWbOD+O+Cf2hH4XLkhqtpguKyYJVU2KRN3n0VXHMG3tvW6O/Ud6J4eSCXtOdAs0AcFwuEbTcoYjRx1DcdpaUuFzFVP8AJPYeog/RcLcs2g5QDfbPhI/+pv1rZujGXJmvXZJPDR0YCWXPDaBk8f8AlOEfGmfWvfugZO/nThHxpn1rkWUG/C3zN+qSbLQnaBk7+dOEfG2/WqXZ/wAnke2jCPjTVrdQzZjajePfbisKols06rUyZ9ygRpmfCj2VTVqq3PWVQxzvtkw0gandnDj8AW/RSs7l+sicpnx+/tLyh1iVv7xGpQBQ5fmaLOe2DBG4aHPpaeoghic5u6XkzNLnW6B1dimMFmnji2NOyXFJtBERUMYREQBERAEREAIuFHPaT/w94nVY7U4rlPyE0FW8yvo5HiN0TibndJ0Lb3NiQRe2qkYicgQyOxDaG15acuym3SJoiPEvJNiW0I3P2uTftov4lM6wSw6lbiZGCFf3Edod/a3P+1j/AIlWNhW0SRocMvPHvp4gfEpo2HUlk4mMEKnbDNojHFv2uSm3SJoyPEqotiO0Nm8x+WpnRvFnDysf8SmnYJZRxDBCmXYJn1r9MAqbHXSSJ1vgeqW7A8/Oa4jApxbrfECf86mxYdSWHUoJITfcFz97g1P60X8aqZsCz+91hgU498+If61New6ksOpAQpfsAz+wXOBzH3skR/1qj7gufvcGp/Wi/jU2bBLDqQEKPuA5/wDcKf8AaRfxqqPYBn+SUN+wkzb9LpYgPh31NWwSyA+F7H9hFRlPGI8ezBJEaqDWnpo3b+461t97uFwCbAXFze/BfdALCyIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgP/9k=</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 50 45k UHD CRISTAL</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAMBAQEBAQAAAAAAAAAAAAUGBwQCAwEI/8QATxAAAQMDAgIGBgUGCwQLAAAAAQACAwQFEQYSITEHE0FRYXEUIjKBkdEIFSNC0iYzUqGjsRYXJDREVGJlhLPBQ0aU8HR1goWSlaKytOHx/8QAGwEBAAMBAQEBAAAAAAAAAAAAAAIDBAEGBQf/xAAuEQACAgEDAgQFBAMBAAAAAAAAAQIDEQQhMRJBBRNRcSIyYYGhM0KRwRXh8CP/2gAMAwEAAhEDEQA/AP6RREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQFP6T9QXHTOipbja5I46oTwxh0kYeAHPAPA+CxwdL2uC4tFxpMjH9Cb81qfTSM9HTx31lN/mBfz9URuhIlaPVOAcd//AD+5es8C0On1NcndHLz/AEC1TdMeuY34Fwoz50bfmvx3TLrdrQTcqMEj+pN+apVRJtBdGRx7cZXJE6Spl2kk47SV9+XhGi6sKtfkg3hl8j6aNcvl2fWFGOH9Sb81o+mb5qu+2g1s+oWwnY5+1lBGRwPiVh1NTMBJbGyR4wNzzw8gP9Vtdgjls+kIDOzqjPE5rGA5zyIP718HXaLTx2rjjc2UVqUW2SLbjqZ54alJ/wC74vmvoyt1I6UNOpiGluc/V8XPJHeq6b4A7bBTTSE/dDeSk6GrnfA30gBjskhgOdo7ie0rHLQ1rsccFFfEiZiOo5S38qHgHt+r4vmvr1eosH8qn8P7vh+a5qedpBBc4HnwOMrqFQAMArHLSxT4K2kR9bVappm7mal3Ac82+L5rmbc9VOAI1IMH+74vmpSZwlYQeKiWO6iZ0R9nm1aa9LU1hrc5hH1Fw1Uf95B/5fF819YavVEk0bHam2tc4An6vi4D4ry2Ud4X0bKO9JaSvG0Qkc31rqV1bPAzU2RE8sybfFnh710Cp1OWg/wn4f8AV8XzVZu9ZJadVtfNuZSXEdY13Y2QcHA+fP3lTxq2tja1rsggHOVJ6KtxTS5LrYKO6Wx9JK/U7Afyn4j+74vmo+fUGq4j6uo2nzt8XzXqaqyD3KLlldJJhoJyVoq0FX7omdYZ3M1Jq15x/CJo/wABH810NvWrXY/KNvH+74vmoynGJMHsUhFM2NuXEYClPRULiJd0ou+hLnXXfScVVcZmz1QnnidI2MMDgyZ7Ado4Dg0KxKpdGTxJoiN4OQ6sqzn/ABMitq8vNYk0UMIiKICIiAoXTIM6Ax31tN/mBYw2lbJEWPblp5hbR0wSGLQrZA0OLa6mOCMg/aBZZTXNj2NzSQPPaHRtx+5ew8BlKNE+ld/6LYRyU+uscjZS6IOkae7n7x8lzQUTqfewRv34yQWkfvWmOgtFVDvEbqWQ9kZJb8Cf9Qq/fLVJTx9dHiRrvVD2cj4eB8Cvu16rOevY5KhxXUVimpcTNExGSc7RyHzW2dbHNpq0RvkczbET6uPL/RYo15dWxxhrs7hkYPBaTXVbom0VK08YaRmR3F2XH94Xz7q/NlFL6stpf/lIlTAXcYZhJ/ZPA/JeGVBjcWvy1w7CMEKKhriwnJJHZhdLKxlcOqecSD2HHs8PJRlTKPO6KSbgqyRzXU2rzxyqxFWFri13Ag4I7l2R1eTz4LPKkE8akbSSeC46h3WDI5jiFHS1mC0Z8V9opw4g9hXFV07nVyeRXBhO4nDeeOalIa+jqXRCnaC4HLtp3cPFVqrBZeepGdrwHjHd/wDqmmUtcRuho5WkjjkBufHjhRsjF4ecEop7rBy6lEF1pH00/sk5a4c2kciFUI9Ry2FjYLs9z2MOGzAcHN8e5WKqp6x7nBsXWEcxG9ryPc0ldT6K1VdF6HIyKcR+q8jIcHd+eYK0RcIRSW/sTy3BxlwcNPeaK4QB9PO1+RngVHXC90dAzfU1UcTezc7n5BfK46GsNtkkrBWz0jAwyPMbg3aB7sZJwBw5lUsXy3WcvqLZRB1c/wDpVS7rpWjuaT7PuAXHqa4L4SuFEuW9i3C/3B8IlpKBtNARwqri4wMI72s9t3uCgrlqS2iTFzudZdnDnBBmlpx7gd7veQqqbxV3S4b6udzu9xJJJXyqrVNEzL4mPc47t2dxAPeqOqdu5J2Qhxv7n9R9DM0VR0V22aGJsMUktQ5kbeTAZ34AV7WfdBo29DtmbnOHTj9u9aCvJWbSZRyERFABERAUPphbv0I1vfXUw/aBZZSU+GAA8eS1npXbv0hA3vuFKP2gWcMoy3iBwXq/BJ4pkvr/AEaKTjqYHtcMP5dyi5rlLTmUBnXRlv2kR+8PmOYKm6yRtNEScZ8VQ7rVVtzrm0FtjkmqZnbWRwj1nH/nt7F95NOLTNcppbErb4Y7jWwSwk9U5wzk8h3rtfd46651FSHEMe/DB3tHAfqAXNb71YNI2VttqWNvleBiYQvIgYTnLA8cX4yckcPNT1qv2ibkGsnttsoZXD8z9pGfdIOA96pVvlfHKDa7cFbipQUINZ5ZyuqS4taxzeI44/1XumlcJQ4uPDhx7FMVejqGtjlm05W9ZMxu51HO8Ekdha8cD7/iqm2tnNVJTSRPZVMJa6N42kEc855K6m2u5Pp7c55MtkJVvE0SVRWhtwmw7huXTFX5I7jyUWy0vme6SS4wtkeckCNxA8M//S/aiCot2x8rWvhJwJYzubnuPaD5qpqPBUmSclbmcDPYpG3TGp2RxkZDsknkBjiT8FTZqwvqcNy4kcABkn3K0aeY6S0TTsO4mYMeR2YbkD44ULYqMPqXUpSlhnff7rWUDttopwHtbsdVEeu7txnm0eA+Kzy612qbmHx1F2qYoXcDFAerb78cT7ytCdUbKKGJ+MmQ5+C+ElrimyWYx4qNKrrXxR+4nKUuHhGTUGkKiOvFRTyPilB/OBxB4+KuVsvF5jvFJY7rIZJah22kuDuLosAksf8AptIHI8lbqK0sZ7XBvA4xxUNeJojf5K9jG9XaIHCPudO/1B8PWP8A2VHUWQkmorglRDDSz7kXqO6NnjltUk28ytzM7I3bcZ9n7vgD+vis5dTGOPid3dntUzQUL5bxUzu3PMjHbndpK/Z6BzXREtOJGkN8xx/cqKNP1/HNDUWqSxFYIplM4NBY3auqJj3SsExc8ezkc2hSNPQiRw7Grv8Aq6ETbDvxyBHavodEcYMWMm9dCrQ3ontbQcgSVA/byK+KjdDjNnRdb2fozVI/byK8r89t+eXuy1BERVgIiICmdJ7d2maRvfcaX/MCpdRVRU1OY+raThWnplrBbtBCsJwIK6mf+0C/n2TWtfdK3qbc3c5wLS77ob25K9F4THNcsvuaKZfsS3ZP3iqmudSaWj9aR3ZuwPjyAA4k9gGVUrjeBRQS2uzykMlG2rrgCH1Pe1va2Lw5u5nsAt1vsdUdK+lda2ae4bsyR8WthDsBrT/acCT5AKqVtmMUpaW5K9JUlNZb2XYX9VbwQUkhNOGwMaXA+/zXinM7JMOODniF3SU3UkYbgg80gAFRveMjOMnmuzTm9zGp9PBcdJajmtlU0xuD8Dbtd2Aq3ahbFdbQ6+RMYa6kLWVeznLEThrie9pIHkfBZc2YRV7nwj1WjtHBW22ahfBbbgx7WiGopHQnPa5wwAB354rJOHRPrjyv+wa46mVq8ue5+tlkdKGsBc53ssYMk+HirDbbFfJ2bX22TqZRtc2YhgcPIkFc9sv9ksUbfR5XdYWDfLtHXSOxxy7k0Z7G/Fea7V0dcCIL/UUJP6ELSD5nO79anbZdLaEdvVly08EszluSlBpG/wBmkPoNJM8SDL5A5gk8G5DuXb45X1udHcqGaO7y2ysc6BhFUza1pkB4bhx9YgAePDtWYya7lorhLA6KqqpY37TI+sIDvEYHJT1LrCpuUUTKhjxE1wJjNU94PdzCzOm9yy2v4/2EquFItEd50nc3xAXplK5rt3V1DTEQe7ip+Oko5YB6HW09Q3nlkgKqjdQ0zmFstvY9g5j1XD4OBC5pJ9JVBLprLTNd95zYeqd8Yy1Qn5nbP4OeSl3J68XJtnhAlk+0ecMaCCXHwCrGtKWr05YLPRVEZbV3KR9VOexp4NazzaDx8SV+y0mmhKyps8TKeojGT6xfI7BBA9c5+BX5eK2rvGqaR9xqevoCwTQBx4Z7R55yuYlPpS29SyFbUZSi90denNNu9AfNJHxPDivVy0/19I+FrQwsO5j+A2uHLnz8u5XShZG2nDR9m0jkeSga2rY3U0lPJMxrQ1r4+/BHH9YKthdJtpdjO69jP5pvq5z4qqB0JJ4P9qPPg4fu5+C9xSTVQaYBvA7WElW2tdS1Ze8QBwacF44Ejz7fIqGqLZb3xxyQwsY7cQ7YNh7MH1cd63Qk3yih1tGzdD4c3oyoA8EPE1TkHsPpEiu6pPRC3Z0a0Tck4nqRknJ/nEiuy/P7v1Je7OBERVAIiIDOunJlJJ0aSsr3StpHVlMJTEAX7etHLPDPmsKNZo2sp2UPoFwpaQDBMdZtc7+0RtwT4Hgtv6fml/RRUtGMmqphxOP9qF/LD52xnYzLzjiQvUeDQjKmfV6+pONrgsYN00LLDBHDpwSyS0MkBfQSzMa1zg1x3NyOZGQezh2LovOlnMdIY2DB4clnukb7Jc7SyzicU9xopvSbdK44G/HFhPiOC2PS2q7dqqj6qUej18Pq1EDhgsd2jjzHBabJSol1RW3/AG5bYlNKa4MsqtLva4kxrhm09JGB9mOPDK3l9qpmSkxhrnDtxkhcNxt1NLQzekvYGNaXdZIPYx97Pgpx8Rz2KfKRhVTZ3Qt2lrtxcGtAHtE8sJeLXd7Tb2PnttXT0wH5+SBzWZ8yMLUdImOokueq5I3VItlG+S3RPbkAcQZiD2nBwOxvmqGzpV1bDdqhz6761p6hj2Po6uMSQvBB+4OWOeB3cVqjqLZykq4p9POXj+P9nceX7lEfWPk4Ek+K+bppHN9VxWqtpNG6d6NNM3q56Xbda64tmD2tndC12HnLjjOSBgAeahnadotR9GNJdLHb44btRVwo62OLcetbKQInkEnkS0fFT/yMe8WlnGdsFbyyhspQ/dIXetnOT2qbtrnFrGsBJ8FpcOm9FQ63rNPNprfNXWi3RxxRVdS6KKvrCMvL3f2fV9Ud54cOHlkMOm+kLTgr9CR2qSrkbF9nVmSmfIXt2yxYzgtHYTxzy7Vll4jGW0YvjPb39SnDK3Eyej6ynqYzFUNcWvZINpbwzyUZWzdW85PA81pdyFju2vNU3G4WzqqLTjHvqY4ZSXVshPqk/o8jyUdb59J6t09qWZumYrfXW+2yzxdXM58eADh2OGHA48DlZFrcYk4vtn7k1Ka2yZpdaGuoHMbUU81K97RIwSNLS5p5EZ7D3qz6bqZbjRMsd6ilpJahvX0NRMwty7scCebTwBI7OPYvXTLUdXfrIMnjZac4/wDEvzpMqZYKLQNRE4tkbZoXA+9q1K53Qr2w5Z+2ApSrn1x7F6sMtdVUU9NVU80FZQkNnY9hBb3HyOMgqJ1PY6y40oqaISNqac7WyAHDs/cJ7M8MeK0uubborpqiqfWx0T/R6VtTJOcMYACWuz3YJHuXkUVPFpuXqK2GrZJVwP3Rch6zVgr8Qw+tLuvylk+q7I2R4MSY670dO5l1tVxo3NOD1lM8B57MHGF20NPVzyAhmTzdk4a3PeVqN0v10pNfvpGzuno5JmROpnjcwtcACMe9VLUlNHbr/XUVHhsEMpDGDsyM492cL7Gn1k7Wozik2srBQoPhmhdFDSzo8pWEgltTVAkcj/KJFc1S+iXP8XNJnn6RVZ/4iRXReFt/Ul7szMIiKo4EREBmnT4C7opqQOZqqb/NC/lINEEjDKSGk5xzyv7H6UtK1+stDT2e2PgZUvmikaZ3FrcNeHHiAe7uWIu+jrrFzsmotBHd6Q/H/sX2/D9XTRW42PfJxoyR9S6mqWyNIa4cQGn2VZm6sbBabbWRQvbcqeqcZqhkmx8kZHBmePLaeYPNW6T6NmsJOdVaR5VD/wAC5r10Caqsum6qtqai2GmoI31MgjncXuDW5IGWYzgcPNbpeJad93/BKEnHJZaDpzsMrA6opq6kkI9ZpjEo9zmuH7lGao6RqDVrY7fRy1Udqb9rcD1BYXRgj1dxcTgnAxjiSOKh7H0C6j1DZKW6264WqWkqmb2O694PPBBGzmCCPcrBR9A2tqK0VdBFNZttZJG6WT0iTcWsyQz2OW45PiAsy1Wli8pstV8n8yR+0nSK+2RQV1qMAfuc2SnkHqOby2Ed20DC4ZelSzWWWar03oqgtl4ka5vphlMrYs8yxhAA/UPNdDvo+60cMdfZ8f8ASH/gXh30edZu51Fo/wCIf+BaJ6zQz5z+d/f1+5VOcpvL5KveNZvvukbHZX0uyS1mZz5+sz1xkduzjHDHvVr6HbjUaedqO/PcHWqhoN87SOEku7MTR45z8V5j+j3rOMHE9n4jHGof+BdLOgrXzKJ9Gy4W1lLI4OfC2rkDHkciRswSPFRs1mklU6ovCf0frlkFkodg1ZSUl1udRqKwUmoI7puM4nOyVri4uLo38dvE/qHEKSvnSD6ZFZKWx2ttot1jm9IpoXTOncZd2cuceY8PEqfk+jvrKQfzi0N8qh/4F5H0dNZBu30q1H/EP/ArHrNA5dTz+cenHBV0yON3S2warlvVNp2kgbXwOgutI6Uvjrsn2uI9UgeB5nOV0fxnWagsl2tli0hDbqa6Uj6eR5q3SSBzgQDkj2Rk+r+tfV30ddYOGDUWkeVQ/wDAvbfo9azEIjNRaCAcgmofkf8AoWaV+h7Z/JNKRUNbal/hdc6OsNJ6G2gooqMt63fu2Z9bkOeeSlrX0nWr6itdBqTSdPfJrO3ZRVBnMRa0EENeMEOAwPgOCmXfR61k7P8AKLQAeY9If+BeB9HTWAcCai0nHYah/wCBXR1micVCTeFxydwzjs3St9Y3nUVPqKkbLFqcxxudG/a2la0FoDRjjgY7Rxb4q9aAv8lLba3S1azrKyhqGneHe2xpBa4d4IxxWfaj6ENQ6csM93uVfaqemo27y9kzy4nPqgDZxJJAHmrTZuj7X0jbNqS3i0vkNGxrc1T2uliI3N3+rjIBA4HsHcq3q9JiUF8r378rg16e1QXTPgvt/wBUQ2yrZW09np2XGcu+3keXlmG8wOWVSWvfL/KahzpZpiZHOdzJPapK66R6SbtNC+S0WOIw7sBla7ByPEL3F0f6/bBG00+nztbjjVS58vYVum12kogsc9+S52VL5S+dFWP4vqbHAek1X/yJFcVXNB2Wu0/o+mt9yMHpbJJpJOocXMBfK5+ASAfvKxrzU2pSbRifIREUDgREQBERAFU+kXS1w1lp2GzUNcKGKapYauTjkwgHIA7TnHA4CtiICOsFjodNWKltFtjMdJSs2MDnbieOSSe0kkk+akURAEREAREQBERAEREAREQEXqTT1BqmwVVouUbn01S3B2nDmkHIcD3ggEeSiejzTVx0jpc2a4Vra0U87/RpRn8ycFoIPI8+HEK1IgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgP//Z</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Guitare Ibanez electrique blanche</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TV Samsung 50" 4K UHD Crystal</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TV Xiaomi 43" 4K + Apple Watch Series 11</t>
+      <c r="B3" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>téléphone Samsung Galaxy A05</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHQABAAEFAQEBAAAAAAAAAAAAAAgCAwQFBgEHCf/EAFIQAAEDAgMDBwQKDQoHAAAAAAEAAgMEEQUGIQcSMSIjQVFxgbITFGFzNTZVcpGUsbPB0RUWFyQlJjJCdJKTtNJTVmNkdYKhosLwCCc3Q0ZihP/EABsBAQACAwEBAAAAAAAAAAAAAAABAgMEBQYH/8QALhEAAgIBAgIJBAIDAAAAAAAAAAECAxEEIRIxBRMyM0FRYXGxIzSh8BQVIpHR/9oADAMBAAIRAxEAPwCSKIiAIiIAiIgCJcdaXCAIlwlx1oAiXCXHWgCJcdaXHWgCJcdaXHWgCJcdaXCAIlx1pcdaAIiIAiIgCIiAIiIAiIgBXxbNe0rFsRrZ4sFq/sfhsT3Rsmja0y1G6bF13Ahrbg2sLnjfWy+wYi90eGVL2mzmxPIPpDSooYxVy0uUKZ8Li1xgiBcOLQWi5HptdWiiGdLHm3GZK7yD80YkJCQNwVtnfAsnEMfx2mgL48xYxvAga1ZP0L4vW1UEtMTCyJoa6waByr9d+Peu3wWuqa3KMLqtznStO7vO4ubbQnuKssEMzqzPeaoCRHmPE++clYA2j5w8oG/bJiNr/wAsVqcSfzh1Wq3ue71OEQdedombgR+MeI6/05WLVbT820lOZpMyYjutGtpjdc+X6tVVBTx1uP4PTzDeifWx7wPSBc2/wVox4morxCOposy7XcSpmz01XXxwvF2Goqwxzh12JB/wWV9lNsnujL8fH1ruGuvqeJ1Vd16FdEVLm2WycGcU2y+6Mvx8fWsPFM0bXMHw2Wvq8TqBTwgF7mVgcWi9r2B9K+iudZY9QyKpgkgnjbLFI0tex4uHA8QQj6Irx/i3n99Cjk0fN8Hz1tTx2aeOgxWqkNOGmQuqt0De4ak68Ctr9l9sfulN8fH1rp8LwvD8Ep3QYdSR0sTnbzgy5uesk6lZwkB6Vih0TBR+o9/Q1p6hp7I4o4xti90pvj4+teHH9sdPzgrp5CNd0VrXE9xK7i4KEAp/W0+b/H/DF/Ll5FzZNtpxPGMxjK+a4THXOO5HK9gY8Pto1wFgb9BtxtxvdfdVFLGYhS7W8rVkXJlkfG1xHTuzNt8qlauFfV1Vjh5G/XLjipBERYS4REQBERAEREBiYp7EVnqX+EqKsjWVOA00Mgu11NGP8oUqMalZBgNfNISGR08jnEC+gaSVEbEql8OWad0Ti0+RjaXDiG2FyPTZXiQzV4bl7DafEfJ1ErKl1+TEZQy+vSBqewEL6PgWAR5grjh7q2Oi5BkDiwWcRpugXAA+QBfIK2qhlprQxRta3hZo016+JK6jC6uepy1Eaol0g0u7i5ttCe4qfYhmJjLfIV88IlZL5J7mb7DdrrG1x6DZacv5zvWXXPvI5a4v5ferEGUH8pqzcEP40YKf64zwlapr9Qtjgh/GTBj1VrPCVkq7yPugj7Kx+gVe+sNkmiub9+le9cSzRcfIrDnqpxv0q2VMVgrjIe7S6RyXVKpZcPIUShlGrbUZbXKoOVhpVYK0XHc0ZRwcrmE32l5S9aPn41KocFFDMszINoeVppDZkb95xAvYCaNSvHBeT1/fy/fBHU0/doIiLSM4REQBERAEREBqs0e1DGP0Kb5tyie4Nmwenjfq0wM8IUsc0e1HGP0Kb5sqJTX/AIOg9Sz5ArxKs1eHYDRU1SXTxmqseS1z91nHpAFz3ELd10nMOuRckE2AA4dAHAdFvQsNj+dPaPlVddJzB7foVsEGgrH84e1YJdyx2q/VPvIe1YZdqO1SC8x2oWzwR34wYR6KxnhK07DqFtMEP4cwo/1xnhKy0d7H3XyWXM+ttfoFcEiwWyXVxsi+jOBudUZgkS91Ya6/SroWNrBilDBVdUn8q6q6F4RqFDMUo7FbeCrCpHBVALTmtzmWRwcTnP25Ze7D86xS4CiPnP25Ze7D86xS4C8br/uJfvgjco7tBERaJmCIiAIiIAiIgMDHYRU5exGAuLRLTSMJHEXYQoeB9qGH0RN+QKYWPzGmy5iU4aHGKlleATa9mEqG2/8AecXqm/IFeJVlbX84e0fKqq2TmD/voWK1/LPaPlXtZJzB7vkVyDS1DrvPasVx5Q7Vendyz2rGJ5Q7UBcY7ULa4Kfwvhp6qtvhK0zDqFtsEN8Vw79Lb4Ss2n76HuvkyV7ySPprZNOKuskusZguFeY0r6dJI9CqcmVG+6ymHRYcYIWQwngtaZr3UmRdBxVpz7NVUR5F+vVYnyOVYsF9qqVu6qutOfM5tqOQzRAKnP8AliAuLRK7cJHEXmjClkFErNE5p8+ZanDQ4xO3wDpe0zCpaheN1/3EjPT2EERFomYIiIAiIgCIiA1uY2OkytisbGlz30kzWtHEncOihhv/AHtGP6NvyBTXxT2Jq/Uv8JUIS+0DPeD6FeJDK2v5Z7R8q8q380e0fIrIdyj2heVb+aKuVNZM7lntVlx1Haq5Dd57VbJ170JPWHgttgOuKYd+lt8JWmb0LcZfP4Uw8/1xvhKzafvoe6+S9XbXufU6eLeA0WwjpbgaKxh4DrLoael32iwX0K+3hZ6hzUeZqfNiOhUvj3BddO3CSW3IWnxiFlO0tvr0rUhqFOWEa1liktjSeUMkoYOF9VnN4LGp4bHeI4rLDdFnsl4I5Nqye3QuQhUOWs9znWRycfmpr5s7ZejY0ue7kho4kmVil0FEvFz/AMycq+tb89GpaBeN6R+5l++CMlaxFIIiLQLhERAEREAREQGLinsTV+pf4SoNudzLfeN+hTjxT2Iq/Uv8JUFy7mh70K8SGVB2p7Qqap3NlUB3KPaPlVNS7kHtVyphOPK71bdxHavXHXvVBPDtQk9aeC2uBu3a2icTa1W3wlagcAtlhTrS0x6qlvhKz6ZZvgvVfJkq7a9z69hFQHbut13mFCJsYfI5rR0lxXxqjxaenI8mPgC6ChnxjFnNY1z2tPVxX0TW6Jy3bwjvXcL3bPoWMZqoqCExU7hJKeFtfgC5Fr6zFarfex1r6NGv+ysz7HYRgUYkxerAmIuIWnekd3fWseTOkr3+b4HhQDuAc5u+/wCAaBc+qtQX0Y59Xsjk26yuvbJs6fB6l41ZYK5JRQU7eeqYoz1FwWjkp8y4kN6vrfN2HXdLtf1W6Kw7C8PpdarEXOd08oNU8Ge1P/Rhjb1m5t5KmgYT98NefRwWLJV09rNcT3LX+UwhukW/MfRdytvkjIPk6SUDo5sq6rh5kuMTUYpIyTaRlXcN7Stv+2YpbqH1Q6+0fLPNuZz7NCLf95imCF4rpJJameP3ZGIIiLngIiIAiIgCIiAxMV9iKz1L/CVBEu5se9H0Kd2KexFX6l/hKgY53N/3R9CvEhlYdr8C8qTyT2qkHXvCpqDoe1XIMY/ld6oJ1C9Ju7vVJ4hQAOjsWzwdpkqKVoFyapo/ylasLa4E/wAnW0clt7dq2m390rPpn9aGPNfJaDxJM7+joaekj84rZBDEzUuPT6B1rJGbq+rlbhuW6N8Rfp5RrbyvHX1NHp/xWup8Iq8eqwZZPJwt4vPBvoaOtdjRyUeAw+YYNS+VqZNHEC7nHrcelfRtbfGG8t3+DdulK/ltExKTK0OHsNbj9X5SV3KdG1+l/wD2dxPcs2mxasrX+Z5cwq7L2Dms3WD61vMMyV509tfmOoMh/KbTtOg7V03n9NQwCCihZBGOAYLXXm79dKbwt3+DBDT1Rey3OShyJilXaXHcZ83b/IwcexbCDLOWsOtuUpqXj8+Z17rIqKuWZ99dVj+Se8kuutV2TfbkbkKG+SMkvo4m8zTxRgcA1qxZ5t4cAAqvNSTqqX0ZsqxurT2Zm/jSSyfP8zm+0vKZ0HOt4evjUqworZqhMO0rKQPTK35+NSpC42radraOXasTaYREWsYwiIgCIiAIiIDExX2IrPUv8JUCC7kdwU98V9h6z1L/AAlQFJ5vuCvEhlwHXvC8qDx7VS0694XlR09quVLB496oPEKq+veqHKCQDp3LcZdYJcSomHg6rYD8BWlut7lSB1TjWHQtNnSVjGj9UrJS8WRfqvkmPNH1CiZPWTCloxuNGjngWAXcYNhtNhMQLG70p4vOpJVrCsJjoaVrGNF7am3FbeKmc8i4Nrr0Wq1HFlyZ1JPj2QfUyzabxHcqRTneu43WeylA4DoVzzb0LzWo6SUNoGzVVGO7Nd5Nt/yfhVQhFgbWt6Vn+b+hUmD0LlS1s5vmbysiuRjGEG+vBemGzdQsjyZaVbczVZ6pye+Srnk+Z57aG7S8nW6ZB8/GpOBRl2gC20vJo/pB+8RqTS2W88zz+p71hERQa4REQBERAEREBiYr7D1nqX+EqAZPI7gp+Yr7D1nqX+EqAH5ncFeJDLgOveEnPHtXgPK7wvJuJ7Vcqy2InOAdcW1R0DwRe3C6oBO9xNrqlziLan4VBJc82kHGy6XZ+w/bpgzDx+yDAf1XLlA5x1ufhXV7Odc7YJ/aEfhcpjtJBElYoLtAss+CCwVFO3QLMDLdFlsaqx8jbhbsUBmuvFVbgVYFl7ZeZujlm1GwtlgVJYFdsllgUTJxlh0asPjsswhY8pAC36W0XjM+VbQ/+pmTfWD94iUmAozbQzfaZk70SD94iUmQugczUPNjCIiGAIiIAiIgCIiAxMV9h6z1L/CV+f8A+Z3BfoHiEbpsMqY2C7nxPaO0tK/Pt7XRucxwsW2BCvEhlYOveEm4ntXgOveEl4ntVypZ/O71S9e/nKlygkpBXWbOD+O+Cf2hH4XLkhqtpguKyYJVU2KRN3n0VXHMG3tvW6O/Ud6J4eSCXtOdAs0AcFwuEbTcoYjRx1DcdpaUuFzFVP8AJPYeog/RcLcs2g5QDfbPhI/+pv1rZujGXJmvXZJPDR0YCWXPDaBk8f8AlOEfGmfWvfugZO/nThHxpn1rkWUG/C3zN+qSbLQnaBk7+dOEfG2/WqXZ/wAnke2jCPjTVrdQzZjajePfbisKols06rUyZ9ygRpmfCj2VTVqq3PWVQxzvtkw0gandnDj8AW/RSs7l+sicpnx+/tLyh1iVv7xGpQBQ5fmaLOe2DBG4aHPpaeoghic5u6XkzNLnW6B1dimMFmnji2NOyXFJtBERUMYREQBERAEREAIuFHPaT/w94nVY7U4rlPyE0FW8yvo5HiN0TibndJ0Lb3NiQRe2qkYicgQyOxDaG15acuym3SJoiPEvJNiW0I3P2uTftov4lM6wSw6lbiZGCFf3Edod/a3P+1j/AIlWNhW0SRocMvPHvp4gfEpo2HUlk4mMEKnbDNojHFv2uSm3SJoyPEqotiO0Nm8x+WpnRvFnDysf8SmnYJZRxDBCmXYJn1r9MAqbHXSSJ1vgeqW7A8/Oa4jApxbrfECf86mxYdSWHUoJITfcFz97g1P60X8aqZsCz+91hgU498+If61New6ksOpAQpfsAz+wXOBzH3skR/1qj7gufvcGp/Wi/jU2bBLDqQEKPuA5/wDcKf8AaRfxqqPYBn+SUN+wkzb9LpYgPh31NWwSyA+F7H9hFRlPGI8ezBJEaqDWnpo3b+461t97uFwCbAXFze/BfdALCyIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgP/9k=</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 50 45k UHD CRISTAL</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAMBAQEBAQAAAAAAAAAAAAUGBwQCAwEI/8QATxAAAQMDAgIGBgUGCwQLAAAAAQACAwQFEQYSITEHE0FRYXEUIjKBkdEIFSNC0iYzUqGjsRYXJDREVGJlhLPBQ0aU8HR1goWSlaKytOHx/8QAGwEBAAMBAQEBAAAAAAAAAAAAAAIDBAEGBQf/xAAuEQACAgEDAgQFBAMBAAAAAAAAAQIDEQQhMRJBBRNRcSIyYYGhM0KRwRXh8CP/2gAMAwEAAhEDEQA/AP6RREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQFP6T9QXHTOipbja5I46oTwxh0kYeAHPAPA+CxwdL2uC4tFxpMjH9Cb81qfTSM9HTx31lN/mBfz9URuhIlaPVOAcd//AD+5es8C0On1NcndHLz/AEC1TdMeuY34Fwoz50bfmvx3TLrdrQTcqMEj+pN+apVRJtBdGRx7cZXJE6Spl2kk47SV9+XhGi6sKtfkg3hl8j6aNcvl2fWFGOH9Sb81o+mb5qu+2g1s+oWwnY5+1lBGRwPiVh1NTMBJbGyR4wNzzw8gP9Vtdgjls+kIDOzqjPE5rGA5zyIP718HXaLTx2rjjc2UVqUW2SLbjqZ54alJ/wC74vmvoyt1I6UNOpiGluc/V8XPJHeq6b4A7bBTTSE/dDeSk6GrnfA30gBjskhgOdo7ie0rHLQ1rsccFFfEiZiOo5S38qHgHt+r4vmvr1eosH8qn8P7vh+a5qedpBBc4HnwOMrqFQAMArHLSxT4K2kR9bVappm7mal3Ac82+L5rmbc9VOAI1IMH+74vmpSZwlYQeKiWO6iZ0R9nm1aa9LU1hrc5hH1Fw1Uf95B/5fF819YavVEk0bHam2tc4An6vi4D4ry2Ud4X0bKO9JaSvG0Qkc31rqV1bPAzU2RE8sybfFnh710Cp1OWg/wn4f8AV8XzVZu9ZJadVtfNuZSXEdY13Y2QcHA+fP3lTxq2tja1rsggHOVJ6KtxTS5LrYKO6Wx9JK/U7Afyn4j+74vmo+fUGq4j6uo2nzt8XzXqaqyD3KLlldJJhoJyVoq0FX7omdYZ3M1Jq15x/CJo/wABH810NvWrXY/KNvH+74vmoynGJMHsUhFM2NuXEYClPRULiJd0ou+hLnXXfScVVcZmz1QnnidI2MMDgyZ7Ado4Dg0KxKpdGTxJoiN4OQ6sqzn/ABMitq8vNYk0UMIiKICIiAoXTIM6Ax31tN/mBYw2lbJEWPblp5hbR0wSGLQrZA0OLa6mOCMg/aBZZTXNj2NzSQPPaHRtx+5ew8BlKNE+ld/6LYRyU+uscjZS6IOkae7n7x8lzQUTqfewRv34yQWkfvWmOgtFVDvEbqWQ9kZJb8Cf9Qq/fLVJTx9dHiRrvVD2cj4eB8Cvu16rOevY5KhxXUVimpcTNExGSc7RyHzW2dbHNpq0RvkczbET6uPL/RYo15dWxxhrs7hkYPBaTXVbom0VK08YaRmR3F2XH94Xz7q/NlFL6stpf/lIlTAXcYZhJ/ZPA/JeGVBjcWvy1w7CMEKKhriwnJJHZhdLKxlcOqecSD2HHs8PJRlTKPO6KSbgqyRzXU2rzxyqxFWFri13Ag4I7l2R1eTz4LPKkE8akbSSeC46h3WDI5jiFHS1mC0Z8V9opw4g9hXFV07nVyeRXBhO4nDeeOalIa+jqXRCnaC4HLtp3cPFVqrBZeepGdrwHjHd/wDqmmUtcRuho5WkjjkBufHjhRsjF4ecEop7rBy6lEF1pH00/sk5a4c2kciFUI9Ry2FjYLs9z2MOGzAcHN8e5WKqp6x7nBsXWEcxG9ryPc0ldT6K1VdF6HIyKcR+q8jIcHd+eYK0RcIRSW/sTy3BxlwcNPeaK4QB9PO1+RngVHXC90dAzfU1UcTezc7n5BfK46GsNtkkrBWz0jAwyPMbg3aB7sZJwBw5lUsXy3WcvqLZRB1c/wDpVS7rpWjuaT7PuAXHqa4L4SuFEuW9i3C/3B8IlpKBtNARwqri4wMI72s9t3uCgrlqS2iTFzudZdnDnBBmlpx7gd7veQqqbxV3S4b6udzu9xJJJXyqrVNEzL4mPc47t2dxAPeqOqdu5J2Qhxv7n9R9DM0VR0V22aGJsMUktQ5kbeTAZ34AV7WfdBo29DtmbnOHTj9u9aCvJWbSZRyERFABERAUPphbv0I1vfXUw/aBZZSU+GAA8eS1npXbv0hA3vuFKP2gWcMoy3iBwXq/BJ4pkvr/AEaKTjqYHtcMP5dyi5rlLTmUBnXRlv2kR+8PmOYKm6yRtNEScZ8VQ7rVVtzrm0FtjkmqZnbWRwj1nH/nt7F95NOLTNcppbErb4Y7jWwSwk9U5wzk8h3rtfd46651FSHEMe/DB3tHAfqAXNb71YNI2VttqWNvleBiYQvIgYTnLA8cX4yckcPNT1qv2ibkGsnttsoZXD8z9pGfdIOA96pVvlfHKDa7cFbipQUINZ5ZyuqS4taxzeI44/1XumlcJQ4uPDhx7FMVejqGtjlm05W9ZMxu51HO8Ekdha8cD7/iqm2tnNVJTSRPZVMJa6N42kEc855K6m2u5Pp7c55MtkJVvE0SVRWhtwmw7huXTFX5I7jyUWy0vme6SS4wtkeckCNxA8M//S/aiCot2x8rWvhJwJYzubnuPaD5qpqPBUmSclbmcDPYpG3TGp2RxkZDsknkBjiT8FTZqwvqcNy4kcABkn3K0aeY6S0TTsO4mYMeR2YbkD44ULYqMPqXUpSlhnff7rWUDttopwHtbsdVEeu7txnm0eA+Kzy612qbmHx1F2qYoXcDFAerb78cT7ytCdUbKKGJ+MmQ5+C+ElrimyWYx4qNKrrXxR+4nKUuHhGTUGkKiOvFRTyPilB/OBxB4+KuVsvF5jvFJY7rIZJah22kuDuLosAksf8AptIHI8lbqK0sZ7XBvA4xxUNeJojf5K9jG9XaIHCPudO/1B8PWP8A2VHUWQkmorglRDDSz7kXqO6NnjltUk28ytzM7I3bcZ9n7vgD+vis5dTGOPid3dntUzQUL5bxUzu3PMjHbndpK/Z6BzXREtOJGkN8xx/cqKNP1/HNDUWqSxFYIplM4NBY3auqJj3SsExc8ezkc2hSNPQiRw7Grv8Aq6ETbDvxyBHavodEcYMWMm9dCrQ3ontbQcgSVA/byK+KjdDjNnRdb2fozVI/byK8r89t+eXuy1BERVgIiICmdJ7d2maRvfcaX/MCpdRVRU1OY+raThWnplrBbtBCsJwIK6mf+0C/n2TWtfdK3qbc3c5wLS77ob25K9F4THNcsvuaKZfsS3ZP3iqmudSaWj9aR3ZuwPjyAA4k9gGVUrjeBRQS2uzykMlG2rrgCH1Pe1va2Lw5u5nsAt1vsdUdK+lda2ae4bsyR8WthDsBrT/acCT5AKqVtmMUpaW5K9JUlNZb2XYX9VbwQUkhNOGwMaXA+/zXinM7JMOODniF3SU3UkYbgg80gAFRveMjOMnmuzTm9zGp9PBcdJajmtlU0xuD8Dbtd2Aq3ahbFdbQ6+RMYa6kLWVeznLEThrie9pIHkfBZc2YRV7nwj1WjtHBW22ahfBbbgx7WiGopHQnPa5wwAB354rJOHRPrjyv+wa46mVq8ue5+tlkdKGsBc53ssYMk+HirDbbFfJ2bX22TqZRtc2YhgcPIkFc9sv9ksUbfR5XdYWDfLtHXSOxxy7k0Z7G/Fea7V0dcCIL/UUJP6ELSD5nO79anbZdLaEdvVly08EszluSlBpG/wBmkPoNJM8SDL5A5gk8G5DuXb45X1udHcqGaO7y2ysc6BhFUza1pkB4bhx9YgAePDtWYya7lorhLA6KqqpY37TI+sIDvEYHJT1LrCpuUUTKhjxE1wJjNU94PdzCzOm9yy2v4/2EquFItEd50nc3xAXplK5rt3V1DTEQe7ip+Oko5YB6HW09Q3nlkgKqjdQ0zmFstvY9g5j1XD4OBC5pJ9JVBLprLTNd95zYeqd8Yy1Qn5nbP4OeSl3J68XJtnhAlk+0ecMaCCXHwCrGtKWr05YLPRVEZbV3KR9VOexp4NazzaDx8SV+y0mmhKyps8TKeojGT6xfI7BBA9c5+BX5eK2rvGqaR9xqevoCwTQBx4Z7R55yuYlPpS29SyFbUZSi90denNNu9AfNJHxPDivVy0/19I+FrQwsO5j+A2uHLnz8u5XShZG2nDR9m0jkeSga2rY3U0lPJMxrQ1r4+/BHH9YKthdJtpdjO69jP5pvq5z4qqB0JJ4P9qPPg4fu5+C9xSTVQaYBvA7WElW2tdS1Ze8QBwacF44Ejz7fIqGqLZb3xxyQwsY7cQ7YNh7MH1cd63Qk3yih1tGzdD4c3oyoA8EPE1TkHsPpEiu6pPRC3Z0a0Tck4nqRknJ/nEiuy/P7v1Je7OBERVAIiIDOunJlJJ0aSsr3StpHVlMJTEAX7etHLPDPmsKNZo2sp2UPoFwpaQDBMdZtc7+0RtwT4Hgtv6fml/RRUtGMmqphxOP9qF/LD52xnYzLzjiQvUeDQjKmfV6+pONrgsYN00LLDBHDpwSyS0MkBfQSzMa1zg1x3NyOZGQezh2LovOlnMdIY2DB4clnukb7Jc7SyzicU9xopvSbdK44G/HFhPiOC2PS2q7dqqj6qUej18Pq1EDhgsd2jjzHBabJSol1RW3/AG5bYlNKa4MsqtLva4kxrhm09JGB9mOPDK3l9qpmSkxhrnDtxkhcNxt1NLQzekvYGNaXdZIPYx97Pgpx8Rz2KfKRhVTZ3Qt2lrtxcGtAHtE8sJeLXd7Tb2PnttXT0wH5+SBzWZ8yMLUdImOokueq5I3VItlG+S3RPbkAcQZiD2nBwOxvmqGzpV1bDdqhz6761p6hj2Po6uMSQvBB+4OWOeB3cVqjqLZykq4p9POXj+P9nceX7lEfWPk4Ek+K+bppHN9VxWqtpNG6d6NNM3q56Xbda64tmD2tndC12HnLjjOSBgAeahnadotR9GNJdLHb44btRVwo62OLcetbKQInkEnkS0fFT/yMe8WlnGdsFbyyhspQ/dIXetnOT2qbtrnFrGsBJ8FpcOm9FQ63rNPNprfNXWi3RxxRVdS6KKvrCMvL3f2fV9Ud54cOHlkMOm+kLTgr9CR2qSrkbF9nVmSmfIXt2yxYzgtHYTxzy7Vll4jGW0YvjPb39SnDK3Eyej6ynqYzFUNcWvZINpbwzyUZWzdW85PA81pdyFju2vNU3G4WzqqLTjHvqY4ZSXVshPqk/o8jyUdb59J6t09qWZumYrfXW+2yzxdXM58eADh2OGHA48DlZFrcYk4vtn7k1Ka2yZpdaGuoHMbUU81K97RIwSNLS5p5EZ7D3qz6bqZbjRMsd6ilpJahvX0NRMwty7scCebTwBI7OPYvXTLUdXfrIMnjZac4/wDEvzpMqZYKLQNRE4tkbZoXA+9q1K53Qr2w5Z+2ApSrn1x7F6sMtdVUU9NVU80FZQkNnY9hBb3HyOMgqJ1PY6y40oqaISNqac7WyAHDs/cJ7M8MeK0uubborpqiqfWx0T/R6VtTJOcMYACWuz3YJHuXkUVPFpuXqK2GrZJVwP3Rch6zVgr8Qw+tLuvylk+q7I2R4MSY670dO5l1tVxo3NOD1lM8B57MHGF20NPVzyAhmTzdk4a3PeVqN0v10pNfvpGzuno5JmROpnjcwtcACMe9VLUlNHbr/XUVHhsEMpDGDsyM492cL7Gn1k7Wozik2srBQoPhmhdFDSzo8pWEgltTVAkcj/KJFc1S+iXP8XNJnn6RVZ/4iRXReFt/Ul7szMIiKo4EREBmnT4C7opqQOZqqb/NC/lINEEjDKSGk5xzyv7H6UtK1+stDT2e2PgZUvmikaZ3FrcNeHHiAe7uWIu+jrrFzsmotBHd6Q/H/sX2/D9XTRW42PfJxoyR9S6mqWyNIa4cQGn2VZm6sbBabbWRQvbcqeqcZqhkmx8kZHBmePLaeYPNW6T6NmsJOdVaR5VD/wAC5r10Caqsum6qtqai2GmoI31MgjncXuDW5IGWYzgcPNbpeJad93/BKEnHJZaDpzsMrA6opq6kkI9ZpjEo9zmuH7lGao6RqDVrY7fRy1Udqb9rcD1BYXRgj1dxcTgnAxjiSOKh7H0C6j1DZKW6264WqWkqmb2O694PPBBGzmCCPcrBR9A2tqK0VdBFNZttZJG6WT0iTcWsyQz2OW45PiAsy1Wli8pstV8n8yR+0nSK+2RQV1qMAfuc2SnkHqOby2Ed20DC4ZelSzWWWar03oqgtl4ka5vphlMrYs8yxhAA/UPNdDvo+60cMdfZ8f8ASH/gXh30edZu51Fo/wCIf+BaJ6zQz5z+d/f1+5VOcpvL5KveNZvvukbHZX0uyS1mZz5+sz1xkduzjHDHvVr6HbjUaedqO/PcHWqhoN87SOEku7MTR45z8V5j+j3rOMHE9n4jHGof+BdLOgrXzKJ9Gy4W1lLI4OfC2rkDHkciRswSPFRs1mklU6ovCf0frlkFkodg1ZSUl1udRqKwUmoI7puM4nOyVri4uLo38dvE/qHEKSvnSD6ZFZKWx2ttot1jm9IpoXTOncZd2cuceY8PEqfk+jvrKQfzi0N8qh/4F5H0dNZBu30q1H/EP/ArHrNA5dTz+cenHBV0yON3S2warlvVNp2kgbXwOgutI6Uvjrsn2uI9UgeB5nOV0fxnWagsl2tli0hDbqa6Uj6eR5q3SSBzgQDkj2Rk+r+tfV30ddYOGDUWkeVQ/wDAvbfo9azEIjNRaCAcgmofkf8AoWaV+h7Z/JNKRUNbal/hdc6OsNJ6G2gooqMt63fu2Z9bkOeeSlrX0nWr6itdBqTSdPfJrO3ZRVBnMRa0EENeMEOAwPgOCmXfR61k7P8AKLQAeY9If+BeB9HTWAcCai0nHYah/wCBXR1micVCTeFxydwzjs3St9Y3nUVPqKkbLFqcxxudG/a2la0FoDRjjgY7Rxb4q9aAv8lLba3S1azrKyhqGneHe2xpBa4d4IxxWfaj6ENQ6csM93uVfaqemo27y9kzy4nPqgDZxJJAHmrTZuj7X0jbNqS3i0vkNGxrc1T2uliI3N3+rjIBA4HsHcq3q9JiUF8r378rg16e1QXTPgvt/wBUQ2yrZW09np2XGcu+3keXlmG8wOWVSWvfL/KahzpZpiZHOdzJPapK66R6SbtNC+S0WOIw7sBla7ByPEL3F0f6/bBG00+nztbjjVS58vYVum12kogsc9+S52VL5S+dFWP4vqbHAek1X/yJFcVXNB2Wu0/o+mt9yMHpbJJpJOocXMBfK5+ASAfvKxrzU2pSbRifIREUDgREQBERAFU+kXS1w1lp2GzUNcKGKapYauTjkwgHIA7TnHA4CtiICOsFjodNWKltFtjMdJSs2MDnbieOSSe0kkk+akURAEREAREQBERAEREAREQEXqTT1BqmwVVouUbn01S3B2nDmkHIcD3ggEeSiejzTVx0jpc2a4Vra0U87/RpRn8ycFoIPI8+HEK1IgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgP//Z</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 65 Crystal UHD 4K Smart TV One UI Tizen, HDR10+, design MetalStream + Support gratuit, 65U8075F</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAMAAwEBAAAAAAAAAAAAAAQFBgIDBwEI/8QAURAAAgEDAgMDBQ0DBwgLAQAAAQIDAAQRBSEGEjETQVEHImFxshQWFzI3QlZ1gZGU0dIjlaEVUlOSscHhM0NiZXSEosIkJTZFRlVyc4KD8IX/xAAbAQEAAwEBAQEAAAAAAAAAAAAAAwQFAgEGB//EADIRAAIBAwMBBgUDBAMAAAAAAAABAgMRIQQSMUEFEyJRcaEVYYGR8BQysQYjweFCYvH/2gAMAwEAAhEDEQA/AP0jSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgI2pahb6VpdzqF0xW3tYmmkIGSFUZO3fsKwg8uPBZAIuL8gjIxYy7/wAK0vHnye6//sE/sGvH9C069k4c0OGAFpbm1h7Ic2A3MABv3VxKTisIv6LSx1MnGUttlc3Y8uHBpO02oH/cJfyr78N/BucdrqOfq+X8qylodRt9Zt7GG4tp7iXnKtHOSg5M84YkAqRynqKupF1a9u70Fo19wYM0ay4L+bnIPeMdB6a8U2+hdn2ZTi1aqrWv/gsfhv4Nz/ltQ/AS/lT4b+DT0m1A/wC4S/lVbHaand21kqOvJdr7ot42nJJ80E8383CtmpK3NxHbS8s6FIIRM0sUvMChONvTnuODXLqNdCtLRQTtGd2Sfhw4NHWbUR//AD5f00+HDg3OO21DPh/J836akpb3kT3UQkHNb47Vmk6EjO3jtXF9NvFuJDM6w8pEfO8uAzEbAGuHWmv+JytJDrM6Phw4N/ptR/d836afDhwaR/ldS/d836akW9xLdWkkLycpV8uuTkHoeldkkzpHyczsO4gnp0qN6rrYPRWdnIhHy48GgZMuo4+r5v00+HHg3vl1L93zfprjLdyqxZWOB0GaW9w7oX7SQk483m+LvvUcda5cRJn2a7X3H0+XTgsf57Uv3fN+mnw58Gf02pfu+b9NfZLd1RXikZlPzebcV2QSNnBkZT6Sa8etlF2cfcPs5Wupex1fDlwYP87qX7um/TT4cuDf6TU/3dN+mpbTEIOaUk9SoJz6s19tuaYh+ZySQC/PhQPQPHpUfxBuW1Rz6kD0aWWyGfLlwaF5jJqYHidOmx7NfPh04LzjttSz4fydN+mu+4UTzyn3S8ihuQBm29XhXQ9xJbSANKw7wGJwajfaclJqUMepJHQKSxL2Pvw5cG/z9T/ds36a+Hy6cGDrLqf7um/TXeupmSTCI8yjv5yBXZfOstrzqHUjrvXT7TTT2K9vzyPV2flJsifDpwX/AEup/u6b9NPh04LH+d1L93TfpqGs5Uks7AD/AEjRp3kQmOVhjrvVX41bmHv/AKLPwj/t7Ev4deCv6bUv3dN+mvjeXfglFLNPqKqoySdOmAA/q1XJMQ2C7Z9ZqDxhzPwFrrc5x7gm6n/QNSUe1nVkkoe/+jmr2V3cXLf7Hrul6jb6xpNrqNozNb3cSzRllKkqwyNj02NKp/J98m/Dv1dB7ApW8YZy48+TziD6vn9g147wdq6wcO6ZbXL9tDHHFIsYbDrsOZQ3UAjf0EV7Fx78nnEH1fP7BrxLRrC3t+GtIuEjCvJaxOzeJKivHfob3YkI1Kk4S8jY3N9Dfah7tgt5DOtjPbm4kZFlZnGFZiOvKuRk7moEuvvaXt1cm2mMtylmjL2gKkwsOc+jmUYr5p09pcytp4lHaXCMF8OZQWA+3BH21U6wjrqbRRkskA5kUZJZcZH24I+6utt0bcdDTdV0prCXt/6Xja/bzTWTSWNwqWtzJMoilw6owCoqkd68q+g4rm/EMOoandxyJdRR3NmLRirIs7MCGMpHxcnGMeiqS0ukW2eQJmM4aPqWxnoSepG9diTrf30lw8fKGQrz42Q5BXf7MVzKLR3LQUkrxja3z+dzWyav213Pde5mHbXaTOpbqqqymM+sN/GrI8RLdKGlhlEYmSVEQqThdirZ2IP31jo7v3FyCaZcySDYtntB4n/HepMshVCyuFZ/OAyKrSukUPh9Ny4LaNgsZuMBDPM2FDdDnp/EVLhX3RISVcMcHcmqfSZFtoo2d1z8ZGcbHu2HjVy2ovBbtL5mANs7mq6hm7I5wk24o6p1/bHcAjYrjcV1xoouUaIKzqOZlyc49QquF3cXNyxI85jscbAeNTrSIwIwQqZj3npXMVFyJ3Bxha+SZI0jhXityhzjmzscDcYNdckmJcNLzbYLkYxneuMEc2cuVGOuMn+2g7Oa5A5clgSHz8Uerv6dDXlSDdkVrbDtm7MiJAe0c5J+aAB/GlspRti3ZRAks3Ude6vrzyTanGqQiQLHzKVA5Tt456/fUfUJo7V5hJcu+Y8KkYC7AnqSO89/oFUqtPZLe+Cvff4epBjvnuZ2LKCz9QFAyO7p3+uu1pHngKFhGnOASxyM+j0+qvkMKQac91zqWdSORuoGcb+muhr1IVhUsABk74ODnFZcaLbvUlyXopftS4NLbaUDAmWKMO8Dcj0113YMQMRftF9I3rtsdRjuIwkMvMcb9xqi1dp/dLHDgjxq/VjCFK8SlRlKVXZI43KuX80eb6RXTh41OVxmoyXxVgJXb11yvbgqN2OMeNYrin4jdimmos+xAmXJ6Vw4uhPwf68T0/k+c/8AAak6dEHQN41y4xTl8nnEG3/d0/sGtjQ0LWkyh2hWsnFG18n3yb8O/V0HsClPJ98m/Dv1dB7ApX1J8icuPfk74g+r5/YNfnjQb+4ubHTrJrt0RLaMKGACjzRt6a/Q/Hvyd8QfV8/sGvG9GiSDg3SbpYVEhsYiGA6nkG9LXPpf6eqKFaatlrBH0y1g0zWbfUZrtTCcqQcnlLbA7fb1qcLKe18puiwycxilBXlzkHCMCKm2dwNZtbl17O3uc83IB5pGOno3GQfTUAXKXV3HM92/uqEMsbN8aPIwTn76sxirYPqpSqVZTU+dri/qsFdpErctxZvIsio7FOY+nff+NV9/fRQPOkMmZoSADsEYYJIPi24A7uvgK6754dPtpLmG5zCjdmCo85z4j0Z2z6DVVpyapqk7xxQRKe0E7FlwTyjAA8Rv0/Ko5xu8FmVOL/Y8EzS5XnkM/K8RjGVYk9mMdN2zuScYq/h1yV4v+kSMEfBGQCWOdhj7z91cEs7r3HcSX93czHl/aKEADDIGD/hXy6hla3t5I41eJcqvIAQp+wdfX/fXT0/mQqipTsy/0otPEG7VhybKD3Z61YTv2aDLZJ8az2nzTRR5OVAFdMmuC4direZGR53ifCq9WhtVyKWkcW7GssGyc8xxncmre3ZZMuhznesxZXDMixk4JG9XmkefdsAcF/NHgBVCMfFYyq1PZdk3mKqxyN/Gq5JmQMyDklyT02GcjIqTqjxRXKQxvzcwycnp6667xWFv2RVHBXKcrdD3b+NQzbu79Cuoxkk31Oa3WUW458FOZckDMbY6kemq+SVyzSzL2rfE5juV8M/cKj9rGlhdRz+dcGDzkzgsCRh8Y37ht35rjLO0cDTQWiIihWKzE88gzjlUZ3/wqvWi5pFZU1Gd4oS3BSF15t2G4I6VEtYxqV4I1cCboo/nbE/3Vx1TVY7kRRw2kUCJ8dxgszHoM9dvD/CqAazaWeolJMy8jZZV3BPgfQP4n1b0u48W2WUXH4o5PQdIsp4eynDgo4DAjwNTuILlYLRJeXmLbVTWnEj3FmrR23JkbFj/AHVG1DXjcWht5VUkHII7qnlKlGm6cWV6VKdWSmlax0sGuMyJg+gd1crmQS2RwDzDvPjVI9wObIJBHgamw38MnD1zJz5khkBwOuOhrPhQ3E1WFWEk74NPoCPJYpI4Iz09NfOO2A8n2vKCMnT59v8A4GnCWsWup6YkULrzwDlZe+ovHNwjcE6+hwcWM+PH4hr6ClDbCNjDqznWrTVuDeeT75N+Hfq6D2BSnk++Tfh36ug9gUrUMo5ce/J3xB9Xz+wa8h4ft2k4Q0WViSiWUIONwPNHWvXuPTjyd8QH/V8/sGsFwho8c/AOhSKADJp8JO3XKCoqraNfsmsqNVv5EUW6ojtGkUcgAIDqVFVz2FxdQmY6fZxo4w4UHnB/nA92K1cukzBOUv5uMcvdUOaCS1jOJAK6jU8z6elX3XaeWYbVbRYtMkmCGKaMAAMmSx5iTjGw2J871VV2eqTXDL2EKxxxEKzEkDJz1I333rb3F46wOrRq0fQ+aN6rbGOzhupDHaRAzryuCPNYeBHQ/wD7FTxqRTwzZo1XCnLdG7OmxjvDdctvcdpFIObkY8wPipz3H7K4XOlvGzJh0fm+IX+Kvobrnp41zk0/UtOmM1phkG6gHm28K6ptRnnKNNGUf51WO9i1k7UHKW+m1b3+pQ6reXcZayN1NIR81gAT6yBk1ZadFFpdul7qKiOGDdIR1ZvE+k9w7hVqsOnTt7tMXLMBy8xOWOPDwqovm92se2gKLED2UZ6VHKSSuyZf3fDayXI0jWZZ76eSccnM2VA6Adw+yt5oWp28M8XaHoD9p8KwOkWcsshndMCPovdn0/lUu+1K90/Nq0caPJgelc9N+6qMkk9xT1GkjWbhHkmm+uNQvyXwoaQ8ztt17jWusX9zorJLEsi9CxDA/wD7fesGssumTTiSSJpEIRlJzysDvjxwV3NXss8UnC8t2JVF3HICyAAOEHVvWBj7M1Q7u0m+pnaunujGMf24X3OUgkSRsApHIrHkwWCdx5sdxBHWqK/1NJbjmRH5U+KS/Xff1ZrlaXmbSOLsLl4ZVyeVcNJuxPjnffB8PVUZLKTsIruMMwE3KFXPODgMOo8MEGq0tzOKVBRe2XJaais1poEOqNPGxdhHJCCUZSebHMO/YDr41VQad/KWn3lyqW0E9oOdlQACQbHbO4Y5+0jFQtZna5ugs1msMMYK7bOPSzYyxzvvUX+Ub82rCCHs4GRY2lLecwBO6n5uckbffmrFNwT4wcyoShGz5f4i10vVpo5bu3uWkmgVQkbxAN2cmR5pIwDtnvONqmXsnuWNGcXCiQ+bzRbH7ebH2VkbB7vTb5UPaFR5+EQkLkbH7VH8KsOKeL9Q1KyisIUUWsZByiYbI6b/AGmpHSozjlZOHCVGMe6XPJZLc2bOpuJJCh+OobkwPDO5J+6oNxqfO0yWS9hauOTlHeuc4/gKy8eozpGFZAPSTmtLw7o93xAoMYCx5xzbVFGi3iCONVOKtK5acEX8lvr0kscBeNYwJCO4M6rn17/21ZcVamJeHNegGTi1nXPqU12QSadwvBJbpLGiOcSXMq8zzMPmRIOoB+cds9M1mtauobnQ9dbmuraX3NKymWNeSQ43XAOVO/pq5TpuklEoUWo97KS5R+hPJ98m/Dv1fB7ApTyffJvw79XwewKVbPlj7x98nXEP1fP7BrN8CKT5OuHj/q6D2BWk4/8Ak54h+r5/YNUfAUYHk04bY9DpsHsCoK3BPQltkWDoIzmUAofGqPW7cSWTvDGRyHp31dX0sYTAJLnotQOxn5ZJBIxJxmF8ZHqI6/2+uqPfdEbdGrsancxsN274s5BHGwPzlyftrvvNFkS87S3hKxsA2CcgHvwfD11c3lnHeck4RRKvmk9Dip/YvJYFFBHKO/vpCtLhmxLWbGpRx5mYKtBbdqsjCSMgOhGxB71P91V+puyz+dCpDAHmA8RV+kAljkZyOVNjvvUENZRIyTzxGMA7SHBFSfqGy5RrWbla5nrazaabtd0j3xn51d9xppd4+Uc3Mcbd1fdU1WxkSGKGOdQozlWA5fRg1M0m/wC0fEM7xzKpKrgMcfd1qzDUQttL86tVQ721ivvbT+Tjcq180Qt2UKsKgs7YzjJ2zj7s1WTaFqV0num5mSSV+kRctJ44AA8PVU7VWlieY3HLHzyc/nL5xI7/AO7HfUVne+uI42uIYJHj5jIrELgjoSBsxxg+rFeNps6pSqJKcZL1tf8AMkK4gltLYG5DfshsCQcDr3VVXmvz296ksRWQ5LkSb7kdfR9lTJLm8nkblilkjt2Cc5UsOuMHP9lTLHTtLurmXQrpEVzcKiXag5diSoG/QA4++o9t3gtVJQhBqqk31t5dSpt+JWubu1gmt41hVWDL3OxBwSeuM8o9G9a2z1CKLhuOExob4Sg5lzzIpjI5mcfGwSMAeGa4XXAWraVC1tHYadfw/GjeQ4lHoByAe/FZa71UussU0Tw3CvhWZSMY6gJnAOwzXLhtVzMVKlq3/ZeF5P8APxF5PLyTKZI2UyfthJJIFMm+CVGN9877VFkik1HUIre4dIpX5Y2eRwE5QNjn1b5zjfPfXy51G29w21zbpy3drGoDvhw+CWHL/NIyR6RgHB6xJrvQ7qznue0aK9PSGVGCk4yCuDtv45qLb0RMoTa4t04/MfmCVqNlJNql21slxfQR8sclwsLIoKjGF2GwAwPEd1VXYgKQRirq71oafAsnYNFLIRzQvNzrLjAy5BB5ipG4xt17qhWssS31sJXjEkmWzOvMFBGVJHeemK5lHxYfIoUnUV2uF/H50KmTSLi+kAtYhj50jHlRfWx2rfcKy6XoWmmzXUI/2aFri5PmlieoQHu/jVZq+jyWWhtq2oat2hmyIkQBWb7ug9AxXnkt3M3xTyodthsfXU8Z907FevoI6qPgl9vM1Wp8YabYXs8+k2LSXDEKt1cEs4A7lz0FZq/1q9vNNu3kmZC8LoQp5fNIO3qNTNI02LUYLqSbA7NPM/8AVVdd2/8A1ZeLIcPFGxH3Gu3U3WKVTRSpUpRT6f4P1t5Pvk34d+roPYFKeT/5OOHfq6D2BSrh8AfeP/k54h+r5/YNUvAMhPk04aXGw02Af8Aq68oHyccQ/V8/sGqLyf8Ayb8OnvGmwY/qCq2odkjqJZXViZbguh3xsKW8W4VxuKkXUjKi8gIIHUbfZXVFc9FIwayJuEZ4L8G3HJ0z2RtJjJFEJI5DkrnofGuYCOhJUj0HuqdkSxY76j9mUbB769nN9OCSNVvkpLiytxM0nIQp6hap59Ks5ZeYQqxJ2yN60V0hDNH1GapriF4pAwO2aqOq4s29NNrKkVl5w/p0y5WExsNm87JJ8aqns59HkLWpKAdJBjOcdM1p5pFVhzgqWHSqPVradLoFxlWGUOOoqzGsnlGpp6s5WhN3XzMPrGoT2t6qkc4Zctz78wr7qk9klvbX+mzyKk+Ukt5cM0TqB/WU52JG1T9ajW5kjSJFNxCCo5lBBBG/2+FZSO3eW7S2wVkdwm46ZOKtQrJo+toU4VIRm8befmvT3LG3uWtkkD2q3LNEzcxyzwd3MBnA6jqMbirnhvUtNvJobS5kWFppo5LiWULGqxxsGVEx1ZmAyxxsKznbXF3qkkdpIyG8YW4AOOZSQAp9Gy1vLvQ+FNBujpVxoN9qogPZ3epJcFCj487lQbYHpqzTm5cdDN7Q7tJQqRblJX8PKt6tLnhLk0Orcf2tpLNGmnzXcEa5MwGUBPTevP8AVF03iO3nukvEgaBS7OwKozdy+k9QKt4tC0scMW+pNxK9ppjXE8EC3MTFnAPxeVT84df8cVGh4Ym91aVp+lzJNFxJF2vu14hiJBkuoTOxXvOfQMVPKd42kZml/S6ZPY2mm8tPpze6tdJN2RjLWa4tLlI3It1kQBjyBgyncNg7E4Oxqy1XSby1hCntZrbkDGRoBlQW2GfHcd/eBWlbhDTtN0iz1C71iJZJImlszPBK0EqBjy80i5CZG/Jk9avdW0uLiPQdBez1VZ9S1Zzstu0cc3Ky5OPmCMKR6etV+6W218k1XtWjvg4K8W2m7O2L/L19Dyi/hkjcwOOZRlgcZKjPj+XfXGYSTSG6lbmYEKzDcjCgDbw2r0mHg3SL2fVbmx4htbxLRXnlt47UoDyDopPUdxI239IqdqHD2kJ5S7XRILIvYyyIs8Ct5oVkB3IJbAPTOMcxwailSksofGKEXtim2k28W6Jvmx5b7qa8vrd9T7aSyiOREjblfAE+PjVjr11Hq9h7rTRobGGJgiiF2GMjzVORue8kVptI4Vs5LriSDUbMFrJoTApcjkV5+XuPevj/AG1dP5OZxxrfrd6Xctw/DHcPb88h7OPCeZg82eua8UKjXqe1e0dJCp4sOKvzh3SdlnLdzyC2me1bKsQD1Ar7qlyLrTbl+UCRYmBOMZHKa9PvNO4PttW0fh+50OaB9Us7dzqFvdNzJJKMZ5GyMZ6+uvP9W0KXRJ9ctLoCUWKXEBYDZ2AIDDwG4Ofs6mvIxlFpck0+0KOopTtFx8LavbK4xZvqfp3yf/Jzw79XwewKU8n/AMnPD31fB7ApWsfkx98oHyccRfV8/sGqHgLbyb8N/Vtv7Aq+8oHyccRfV8/sGvMuE/Kdwfp/AuiWN1r0ENzbWMMUqNHJlGCAEbLiqer3bVtVySmrs9UjYFTzAGuCRpzkcgANYSPyr8Dq2TxPbgf+3L+mu5/K/wADIv7PiS1ZvTHL+msxRqNXcX9iw2o4TNs0QQ+Yces1X3huBgoA3qrIt5YeDf8Az62bP81JB/y11HytcGDccRwD/wCuT9NRTjN42MmpbU7to0PuxUl/bnlb01zuOS4iyoBI3FYy88qvC0txmPiG35MY3ic/2pXCfyocJvEqJxFAG72McgA/4ardzUeNr+xoxnBNPcl9S7e3mMrSSjp3HrXTeXDTW4MiZ7PcHvx4VUJ5Q+E5NpeK7PlxtmOU/wDLUCTjzhR5ynvjtTGPnckmD9nLXq09eHEWXoaqi5XlNYIeoc66lJIEKsDnBFV19H24hvljxKT5rKOjA9PScYq1fj7hSF2Ya3DdcxI86FgcY7yV336VVXPlH0qydk026tXiJz56s2/j8UAfdVmFGcf3J/Zm5R7Vpytta+sklb6ldqFtNFdNcxqsbRsMNDuqsADtjoe/HrrdwcXWJtl4nvNGv/dFy3ZXHuO6QWtzIoG8iNuuRju+01g/fvps+irG15FFf20qmKUKwLpk7NhcMVO4J3wSM13e/PRH0uey90wQQXU8dxLGqsApxyuBt8X5wHgcd1Xae6PCf2Gq1em1UIqpJXi7Yl0xfr1w/oTOJuKLTV+H7PTYdMXT57a7muJY4WBhHP3Jvn+6rrQ9en0byQ3k8iKJmuXtNNlPx07RQZuX0AD7zXmNzrNk9w8jXscjM3VQd/4UfX4JLaO3a/doYiSkZLFVJ64HQZqDvK25y2v7GlKn2dOhCgq0dqlud5J/NpZ68eh6Zw1xxpOj6ZGFh1ZbqCFw9p7rDWd2xGMsrZI65wBUXTuN7TSNE0MGzlfVtGmleEKwELRStllbv3UnGOmBWETUtFGl8zX491OxUJyP5mCMHOMYI5s+obVDOr2hO9wPXyn8q7c66ivDn0IVp+x6sp3qLLz4vVefGWer6TxVwhbXGoR6XpF7aS6hZywlp51McRbflUZyQT35zgACqfV+Mba847Ti7TIpITE8TiC4IzKVUKQOXONv7fsrE2Wp6IZlF7dTohYZeFMlRg5OD1OcfxrmuqaRGkyJdx8ykKjdk2HGRk56jvOP410pVpRV4+xA6fZtGtKaq7rqzvK+Hz+dD0eXjnSbUX7aHpWoi61G4jmvJbiUShEDhiqY+4E+NSodfifj671qE3rR3kMwFnJKjSczryjCKSAoxuSaxnDXGGkabbXVtdTRuLvbn5D5pX4pbb4pyfTtXbPxtZR2ctrZ6lDYL2hKpp9qYY5AMgFnKlz44OfXUy34b/gya09KpSp0msq25yvdO38WwbjV9b0HTLvTdem0y6utas4UsoYZJFSBZI1xzkDJ25s9fD7PJ+J9Ru75tUku51nmlLvK6nzS252Hd1qx1bjLTr6K2HZh2jIYgBwpOwyRjOSF8fnE9ar9T1bRJbCdbd4jNPbSedyMMORspBz6ACD1ySN8VxNTlPCx6E+nrabS6duUk5OLX7k7eSWcL+T9TeT/AOTnh76vg9gUp5P/AJOeHvq+D2BStU/PC+uLeG7tpLe4iSaGVSjxuvMrKeoIPUVSe8PhLGPezpP4OP8AKr+lAUHvD4S+jOk/g4/yp7w+EvozpH4OP8qv6UB5B5X+FOH9M0DRJ7HQ9OtmOuWcchitkUujMQVOBuD3it/7w+Ej/wCGdI/Bx/lXnXlWvr3jTi2w8n+ixBnhlS7u52G0RG679wUHmJ7yVAr2OJSkSKzcxUAE+PpoCh94XCP0Y0j8HH+VPeDwj9GNI/Bx/lWgpQGf94XCP0Z0j8HH+VPeFwj9GNI/Bx/lWgpQGf8AeFwj9GdI/Bx/lT3hcI/RjSPwcf5VoKUBn/eFwj9GdI/Bx/lT3hcI/RjSPwcf5VoKUBn/AHhcI/RjSPwcf5U94XCX0Z0j8HH+VaClAZ/3h8JfRnSPwcf5V994fCX0Z0n8HH+VX9KAoPeHwl9GdJ/Bx/lXz3h8JDf3s6T+Dj/KtBXGRS0bKDykjAPhQHjvkv4K4a4h0LiE6podjdBdfu0j54hlEUgKoI3AG+3StkPJFwECD717Hb/RP51i/JbfX3BHGd/wBrUY5rqV7u0uFG0rEZY57wwXIPcQwPdXs1AY34I+As/9l7H+qfzqzHAnCYGBw1pOP9kj/Kr+lAddvbw2lvHb28SQwxKESNFCqqjoAB0FK7KUApSlAKUpQFfaaFptjq99qltaJHe35U3E25Z+UYA36ADuFWFKUApSlAKUpQClKUApSlAKUpQClKUApSlAV97oOmahqtjqd1aJJe6ezNbzbho+YYPTqCD0NWFKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAf/9k=</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>200000</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TV Xiaomi A Pro 43" 4K UHD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TV TCL 65" QLED 4K UHD Google</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TV TCL 55" QLED 4K + PlayStation 5 Slim 1To</t>
+      <c r="B4" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Sharp Machine à laver 7kg / 1200 tr/min</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAUDBAYHCAIB/8QAUBAAAQMCAgUGBwoKCAcAAAAAAQACAwQRBQYHEiExQRMiUWFx0TKBkaGxssEUI0JSYnJ0k6LhFRczU2RzgpKj0iQ0NjdDhMLwJjVUVoOz8f/EABUBAQEAAAAAAAAAAAAAAAAAAAAB/8QAFREBAQAAAAAAAAAAAAAAAAAAAAH/2gAMAwEAAhEDEQA/AOkUREBERAREQEREBERAREQEREBERAREQEREBERAREQEREBERAREQEREBFE1uY6ShrH0z4qmR8dtbk4i4C4uNqs5c64dCAZIK1t914CL+dBkSLFzpAwgf4VZ9V968HSJg43xVn1Q70GVosSOkjBQbclW/VDvXg6TcEG+Gu+qHegzBFhh0o4EN8Vd9SP5l5OlXABvjrvqPvQZqiwZ2lzLTDZ/uxp64fvXj8cWVuL6sf8Ag+9BniLAjplykN89WP8ALOXn8dOTB4VZUj/Kv7kGfosJw/S9k7E8TpsPpsSldU1UjYo2uppG3cTYC5Fgs2QEREBERAREQEREBERAREQYBmNpfmCrNzvaPshQ74S7ft7VkWMQNkxmscZ4Y+eNj3EHwW9Swg59ydb+01B0bBJ/IgvX0w6Fbvph0K0dn7Jv/ctF+5L/ACK7wvMOWsdq3UuG49TVEzWGQtEcg5otc7W9YQWrqca7r7Nypy07RED0E8AFL1UMUUxDJ45QQNrb7PKrSojY6AsLg5rrg26LIKkWTMVqcLZWsNNHHO0PZHIXB7hvF7Czb+NQDqTU5WOVmpIw6rhsu0i9wsjqs9Y3SYFHQU2FwVlVG0Rsnlm1IwALBzhv8Sg43zvjkkqZg+pkOvI9rbAu42CtGt85RhuLRWG+EekrGpnsijdI8hrW7SStn4nh1BXTulq2wukYNUa7iD2bFj9ZlzCaqJutSwSBu0jXcA3rKg1ViWKvq3GOIFkI8ru1X+UnkVlSCd8XtCyyoyvgzWOf7lp2t26p5R3O7FaMwuhw+8tK2JrnixDXOJA37boJfKkvJZ5wOTdq18B/iBdkhcV4BJq5rwl191bB/wCxq7UCAiIgIiICIiAiIgIiICIiDU2cqHHZs3VzqCemZTnUsJHOBvqNvuC1A7QXiBe5xxWm5xJ8ArfuP/2gq+1nqNUW4oNKnQdWgf8ANKb6sqTy/oxxTLWIvrKbEqV0jozHYtcBYkHo6ltJxVjUVTuUMMDBJKPCubNZ84+zf6UGMyYXmFms91fRgDeecLeZRswxlxLWYjBORwhZJJ5wLedZHiD6KjiFRilS19t3K7G3+Sz/AOnrWO1ueqVh1KWllmA4vOoPJtKC0fHmMMLBI8NO/mW9qjpoMWbcTVghB367HgeW1ldnOdRIf6nCB84lVWY/y3hwanWx10EJLh+IuZrCshkb0tcSFYTUda086Zh8ZWRVLYJiZY+Y/wCM3mnx9PjUXOXbQ6xPSEEJJDUAm8gPjVrIyTi7zqSmN1ZSoLzKdM6rztgkAdblK6Ebfng+xdqhcaZDF9I2Xx+nxesuy0BERAREQEREBERAREQEREGB5iNswVf7HqBRTipPMh/4hqv2PVCiJHhjS5xsALk9SC3qZHlwhiNpHC+ta+o3p7ej7ljeZcy02W6ZtLTtElZINZrCbht/huPG/nUnimJx4LgdTilQLuDdfVJ2uJ2MZ6B5Vo3EsXmqKievq5NeaVxc49fR2BBf4njL5ZXVVdUOlldxJ29gHALHKrMry4tp2Dt3qJqKmbEKm2sbK5igZC3mjbxKD2MaxK+sA9XlJm6rp5AJ2aw6xf71ZHevD2teLPGsEGc4VmOkxLVjHvUrtgaTcO7D09R2q4rnCJlPI4FrKkOMZvsNnEDy2WspOUopS5hu0i46D962xmGma7LGFau5tJFY/sAoIOYazS4bx4Q9qj5FWpaovZd218Zs6/EKnUNDJCATbeOw7kEvkAX0kZeH6fF6y7JXG+j0X0mZdH6dH6V2QgIiICIiAiIgIiICIiAiIg1/mY2zFVdjPVCgaogxtjtflHhp7N58wU3mh1syVXYz1QoGY/0iDtcfs/egwPSjWPk9w4c0803qJB0/Bb/qWn8wPMcjYQdlty27nGnNTmck7Q2KNo859q01md5bi1rWFt3jKDxh7AGF3Eq8Ko4dC+YujY5oswO5wvvJHsV67D6jhJF5CgtSvJVw6gqrX5SG3jUM/EnNcW6rTY2uOKC8qWh9G+/wCCPQVsvDq1uMaP8AD5Abvgj5B/Tdmz0WK1nTB9bhNbMTqiLUFgN9yprLGNNweWSknJ9x1RAdx1H8HewoK+2DEdXg/Yqs5vEw23Xbfz+1fcTi5OujcLEF4sRxXmU+8kdDh6Cgm9HW3Sdl0D/ro12OuOtGwvpQy79NZ7V2KNyAiIgIiICIiAiIgIiICIiDXOanWzNVdjPVCgKh1nwv6H2PjBHpspvNjrZoqx8mP1QoCovJE5rTYkbD18POgx3MFNrYw2W2x8Q8oJHctM5yw8RY4RIw2u5t93G48zgt64mz3TRsqQLGPnEdAPhDxexYDnjAvwhQ+6Y7NcwAONvBI8F3ZtseojoQa1oJxS1Ic7Y0c1x+Sdx8R9Knr7FjTg9kha5pZLGSHNI2g8QepVqTFPc0zYZD7z0XuWdnSOpESWJ1HIYfI8HaRYeNYiBc2CyWvFNiUcbW18UTGm51muv5LJRtwzCyJYA6uqh4L3t1Y2HptxRVR1N+DMBhoZNlTUvE8rfisHgg+NWkcD6isihjBLvCsOncB4yQF6lmfLK+aaQySPN3OO89X3LPtGOVHVuLjEquP3qmeHuvuMg8Bn7PhHrsEGSZiyPh2H5XFYHvglooWAtbYtkeLDcdxJ6FrqY+926XXWy9JuMNEFPhET7uJ5eYDgPgg+c+RaxmN3diDItGm3Sjl36Y30FdijcuO9GO3Snl76W30FdiDcgIiICIiAiIgIiICIiAiIg1jnB1s1VfzY/VUE5ymc5m2bav5kfqqAc7YgpPdyUx/NyHyO7j6e1Q9dB7l1ubrQO2bdw+SepS8hDmlpALTsI6VavdqNLJefGRbWIvYdB70Gp81Zfpg51RTu1bDYAec3q62+cLXs0ErZCXtLSenYt2ZkyjJXsMmHVAjcdvJSHmnsdwWusQwDF8Pc5tTQTtb8Zrddp8YuEGLiKW4IHnUgyUGzR4Vtw2qp7kZrWNOAejVUzhOGVLpGugon2363J6o8p2IJTKmTqrFKhlRU3p4Ab65HO/ZB4/KOwcLrbM2JYflLAmNjjaxrG6sEDTtef97SfasPpcX/BdIG2bNPbYAeaO08fF5VA4jXz11QZqiQySHZt3NHQBwHUgt8Srp6+tmqqh+vPM7We7/fDgo52xVn71QegyfRd/epl76UPVK7DG5ce6LNulbL/0n/S5dgtNwg+oiICIiAiIgIiICIiAiIg1TnZ1s31X6uL1Vj7nbFO56dbONV+qi9BWOOfdB9c5UHuX1zlQe9BSkbqk6hLOrePIrWSaRvwQetpsq8j+Cs5n70FrPUO+K8HtHeoupnc7eCfnFXtQ/eouodvQWM7yTvVm9XMrtqtJCgovO1W71VeVRcUGV6KdulfL/wBJPqOXX0RvGFyBop/vWwD9efUcuvKU3gF+lBWREQEREBERAREQEREBeJnBkdybL2rav/qp7Qg1Ln+o5POM+qwvDoIjsIFth6SsYdWH8xJ+83vV1pSrHUudA0HY+kiPncFhhxZ/SUGSPrT+Yl+z3qi+s2fkZfs96x12LP6VSdirzxQT8lZs/Iy+Qd6s5qvZ+Tk8g71CvxNx4q3fiDjxQSU9SNvMf5u9Rs04PwXebvVrJVuN9qtXzE8SgrSy34FWz3qm6QlUnElB6e+6pOIX1eCCgy/RINfSvgfVK8/w3Lruk/IDtK5E0U3ZpNwp4+CZD/DcutMKk5Sga49JQXqIiAiIgIiICIiAiIgK2xDZSHtCuV4mibNHqO3b0HPml9ls3Uz/AI1G3zPeFr15sV1ZjGUcLxyBsNbEJGtNwSNoO3cd/ErGWaF8sRRhjGTNaBYDWB9KDnJxKpm66ROhjLR4z+Udy8nQtlo8Z/KO5BzaQbLw5psukzoUy0fhT/Z7k/Enlr40/wBnuQc0ObsVJzV05+JLLXTP9nuQaEssD88f3e5By+Wrzqiy6kGhXK4+BKf3e5VG6Gcrt/wpD4m9yDlbUHSE5MLqz8T2V9nvD9nYqrdEeVQLOo9cb+dYoNAaK6Zx0g0jw08yOV17fII9q6nwQEYYwH4x9Ks8NyjhWEQcjRU7IGXLiGNAuSbknruVMQQtgj1G7ggqIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiD//Z</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Thomson Google TV 55" QLED Pro</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAIDAQEBAAAAAAAAAAAAAAYHAwQFAgEI/8QAURAAAQMDAgIFBggJCQUJAAAAAQIDBAAFEQYhEjEHEyJBURQyYXGS0QgVFyNDVIGRFhgkQlZik6HSUlNVcnOisbPBREZkdJQmMzQ2RYKE4fH/xAAbAQEAAgMBAQAAAAAAAAAAAAAAAQIDBAUGB//EADYRAAIBAgMGAwcCBgMAAAAAAAABAgMRBBIhBRMxQVGRFCJhUnGBobHR4SMyFUJTwfDxQ2Ki/9oADAMBAAIRAxEAPwD9I0pSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlcq+6nsumWWnbzcWIDbyihtTpwFEDOB9lAdWlRD5V9DfpPb/bPup8q2hv0nge2fdU2ZF0S+lRH5VdDfpNA9s+6ty26/0teH1s269RpbiE8aktEqIGcZ5eNLNhtIkVK5/x7bvrI9lXup8e276yPZV7qtkl0K7yHU6FK5/x5bj/ALQPZV7q+/Hdv+sD2Ve6oyS6DPHqb9K0Pju3/WB7KvdT47t/1geyr3UyS6DPHqb9K0Pju3/WB7KvdT47t/1geyr3UyS6DPHqb9K0Pju3/WB7KvdT47t/1geyr3UyS6DPHqb9K0Pjy3/WB7KvdT48t/1geyr3UyS6DPHqb9K0Pju3/WB7KvdT47t+ceUD2Ve6mSXQZ49TfpmqNldNeom7o/Fj263uhDy22wEOFSgFEDYK57Vi+W7U5SpQtVvIT5x6pzA3xv2tt9qwb2J3FsXFNXsu6L3zSqJR016qcSVIs8FSRzKWXSB/ero6b6X79eNV2+1SoEFluS+GXClCwtPPPNXOiqxZWWx8VCLk0tPUuWlKVlOQKr/pW0HN19AtsOFMjxFxnlvKU8lRBHDw4GPXVgVhX/4tv+qr/SpTtqQ1c/PX4uN//p22/s3K+/i5X/8Ap22/s3Kt67s3herGmY13uEeCuO4+91TLZS3w8ISlJKDuSVHBydq4zV21w3Y7RxREvPvqU8pW/WrSEKWEOJ4AlGcJTzz9tN7I3YbPzxUoyWvrbr1930K7/Fzv/wDTtu/ZuVKdBdDt10ld5MyVdIchDzHVBLaVgg8QOd/VXVeveokwkybbKuU58x1mW29A6ptlwpwgIBSDxBZG2VbAk1tSLjrSK9AYlDgRHW6l59hjrlSwhCiFlIHZSTwjhG5OcYAqY1pRd0Wlsq6s5Lnzaenpa/8AtciQDTz4+nb+419/B9/+eb+41D4N91WliU6FzZhS0jjeEcqbbKlgKUltTSFFSU8SgkEjxrZen6mekeTWS4T34slxptubMhhJbcypSyBwJyjhSASRzOAayeLqMxPYcU7OS7v7fklHxA8Ppm/uNaLrCmXltkglJxkVm0pc7zdZdweukV2ElotsJjrTgBxKSXFJP5ySSMHwFbMpsGW6f1jWejXlN6nKxmDWHlkXH335XOdwmmD4VuhoeFfeqHgK2c5o7s0QPQKFPorf6oeFfOqHgKbwbtmgUjwp1dbpaHgKdWPAUzkbs0igmvPVqHhW91Y8KFCfCpzjdnPUFV8DaioZON/Gt4tpPcK+BpIWnbvFW3hV0z86gy06rdTBb62UuU422jGeMqUU8OPTnFWBcdJa6tVkXOPxW6llHG7HYQCtKQrrOWAFYVk4z486gsdF0XrVwWVLqrimU6pjqgOLIUrcZ25ZqyOj57ysahimTJ/DSQy4mQJmS2OE8I2G2RkZ91ecjq2j6tjZSpwjONnZK+l38ei9epELXI1LeoqJrcqGxDaWtBddTwtshKQtROAdu2PWVYArDphmVG6XoDM0JEpFyKXuA5Tx5OcejNZdEyLQzDmxLw7GbHEFNtOSZDanXU+aMNbYSRniIJ8KwaUS4jpatyXlBTouPbUOLBOTk9rtffv41XoZZab6KVkovlbl1P02OVKDlStw8CKhvSFr6NoCPAmyYL0wSXFshLS0pKTwhWTn1VMqo34T764+mrCpBSCZixv/AGZqVx1IfDQ2PxkLZ+j079s3X38ZC1/o9O/bN1Q2mbBdtUR50mPLtcKLA6vr5E+R1DaSskJHEQdzg7Vmsem7tfnbp5NcLOxGtakpfmSZPVR8qUUp4Vkb5IOPEVfylPMXp+Mda/0enftm6kWjemCFrG5vwmLTJiqZZ64qccSQRxAY29dfnK16UuNziPyUXO2IZZkSI5cytaVhhkvOOJIG6MAAHvKhWfo11TOtN7lPx/JgpcbhPWZxjiB7u+pioX1KzlNR0P1yLy2foV/eK9C7I/mlffVJp6Sbvw54rdj/AN1Zk9JF3/lW371VmyUjW3tUuj40SfolffWk4vrHlrAxxHNVT8ot523tfPHNVZR0hXvIA+LCTt5yqmKhHgRKU5cSz6+1Wq9dagbGVtWvH9pn/WvC9e39BUFItiSOYKyDVsyKWZZ1M1WH4f39Q/8AS/bNYjr7UCgCHLWM/rGozInKy0zzrzmqoVr/AFEDnr7XgHGDmvJ6Q9QcWOttfLP51TniMrLYJryTVTnpFv6QMvWzf0KrwrpFv2/5RbBj9VVTniVyMtgmvIX20+sVUh6R77w58rte/wCoqtdfSVfQsAS7Z6+rVVt5EjJIiy7lItGrXrhDcDciNLccQrmMhZ5jvHd9tTSV0yS1xZCoVjt8G4yUcDsxs5UfTjGSfDJOPTUPY1prqZZJF4Rd4Iisqwr8kZ2J63HMZ26vf+sK60e/apXBYdev0NTjrYcHAwykKyM4AKMg92+3f6K5appcJfL8nsqm16dXLvKCbX/b8HN01quZpeYp+KzFe4yCrrUdrbwWMKT9hrc0dJTL6UrXJSkoD0/rAlS+MjJJwVHnz518uFy16HB5Bd7eoEZLb7LKVADOT5uMbD07+useiukDWMfpVtFhuU+E4iVKbbfS3HaOUkE7KAyOfdUbqKWkvl+TJLbanm/Rs5K1834P1IOVKDlSsh54VRXwokpVpmwhRIHlq+X9mavWqL+FEAdM2IlQSBMWcn+yNQ720BA+jiDc39EGLbdOWnUsGddE+XsSCS7HCUhKVKHEAlOCohe+DnNdayWdcZq+2zSljtGqrG/fOreZkLUtxltAwhR7QHBurhc35HNQROiYbNxYsLmofJ9SSkoQmN5MfJw4tIUhhb3FkLOQPNKQTgnmawWrRzsi/wCnLUqeWnr7F68lLRPU9p0cBSFDj/7o7ZHOqXlYhGtq2Fa7XrC7QrPMcctTMpxtjq3eIcB2ODntDuz3gCujoNzT8CbNkXtxwstRVL+aeDaiQoHAGDxHuwPXtvXTOi7cu3OD40Xb1mWzb2PLbYps9a43xjrEhRLQ7snPMHlULEVUOZPjS4yWp0VRaW2+vsqUlwBSCOR5Hl4Vk+IsnxRc8NnSF9tAlWlctoKIAU4/xekpxwDfevf4O2364v7z7q4cS33uezHt8a1Fu3rwWpCHWGODs5PCSkKIznY8x6qkVg0nf4QW1eW1rKl9gsPIdJ8BsfDcjurlVa2JlDeUGnrouf15CpRcJONkYZFns0RoLlXJLKFci45wjP2prfh6Tiz0KMR7rgEcfF1oCTtkb8PfUP6QLbNjzmpkltTdliEJWoDLuVYCsjOBjGB6edSaQxczplmFZZUxDjjSFm4BS1Op280NBfB4DPr2rZw3iZuKrWXXXtzf9zL4emqKqSerbVre71RxLpqHS9qlriOpZvfza0yo7Lqz1ahtgLSkZx3kGupZ7orUEGBapLKkyozSiJLE1vKY6U7BfFhS+HYd576jMW0a2bLi313lS1NqSlLCmo6eLuKllR7PiMb+ipZpDT78AMz7vqG2ybsWyhCXZaSpkqBHCnfHfueZ9Hf2KmIp0YZFHj6u4w2z1iJNxk0lx00+pq3dy02t2CmVPkqTLbLyQVhSy3jsrSM8idskH7Odb8Gx2ybFbfYkSFocGUpLiQR6CMc64sbQcWRqWVIuFnn3RLZ6lD8N75tpQBynq/OO+c74Ttipb8Y2RlcVtEtLbklsuNJdWGFLyQCAkHA5jbOedc2vOThB05K76t/HmXWCUK8qNS6tror8eBzjpmGlZy7JOfzesTmitKRi31v5YUcHHxBaccPj6vTUjbtbrScoipQlxHB84/gFPPh3XXmTPDSn237bayoISl4KCThA80K7RwB91Y4qol52u7+5meGw7dqWaXwIyvRHECvjuQQCPzUEAnl9/d41rr03AS6GlvXDrFu9QEgDJcAyUbfnY3xUpcvDctwIXGtQMpSXcloZcUnzVZG5I7j3VqhqH88tUq2oSh7rnHC4ohLveo7bK9POr5or+b/0yFgHzhLsRNNksDiE8Nyl8OSASQMkHcfZWRGk7O9uibLWOWQupU3GgsqKG5VsDiwVhBjqUVA8yAU5+0VoOzAppakJhqjhfAXEsICSfXgb1beUl+6XzZK2bUm/JB/HQhCwhC1JDTBCSQCWG9/7tbMZhMhIJehNYVjDjaBjbOfN5d3rrZt4kRLmpwxUKB4k4kMKUgeBwB44rrTZBlx1JVHhJ7aVhLLC0kAKJUAeDmrIHhgV5iLm7tyfzPo040oWhGmuWtl9iPymxGUjD8N/OTlpCDw+vs9+a62iCDryy/Nsg+VJ3DKAe/vAzXUlXQLfUpq329TZ80OMrUR6Nkjb3Dw3wacXJmdJttluMKTxS0ZKEK4cBOOZHorKs0akbSb1XU15budCeaml5Xrpx7H6HHKlBypXpz5oKo34T6QvTViB5GY5/lmryqjPhQEjTVhx9cX/AJZoCq4HSHCg3drUEjTrcy+JQhtx1yRiO6UcOHS3wEpc7CTlKgMjOOYPGtvSJAj3LTc42R9y4WVHUB0z8Ida4nVEFPBsr509rPdyrUk6YfEJpbjxabkFoBxxvhbPHjkrO+M5O3ca+J6OrgJP5M/EeBOEhx5KVnONijJIO/Lc/aQCTT1TuLO1zpR9eQIEaWwLG9PbTMZuMbyy4qd6t1DZQOsISC4nJzjs9w5V86P78+/rC4z5khpb0ppa3FyHQ2grU4FFXrzk4FcqdomZEnLgvT4CHVhBRwLBSolRTgkeaQRvmsWlrFLlz5MdpmNLRwZIcUpAUArYgggj1VhxFBV6UqT5mWjU3U1PodPUuq5t1vPXMzT1ENRU0tJIQTnzgD92c71Z2mtSNat0XLU+5wqaZKZCApRJIQRxJwD3cskVX8jQ11kJSE2y3JSk8QBluqH71EVsW7RWqIrjpjSGYCXUdW4iO+QlafA7jNKWHjSpqEY8OBFSo6k3NvibI1teHiWru4iVEfGzTjQ4UqTggb54tu899fbfqpEF9SYDUdoEE/lEtaU537PCN8VFtb3qDIuTaILZZU0PnkqRwFDnClKk+nBSd/1q+6YtV1lxPjJFtclxes5oRlSuHmkHOwPI7VtWSWVFIVJRea5bNonfhdaFtSJrNphr4BIeRxuLf4twhGVYABBBO+SO/lW+zo/QYuSISrtOU68EltR4Ak5HEBgHi5b71X0KVqjTDuWrH1sVQCyhXA8jhGcBWdwRk789693npKkXKQ0/8RKiLaAT2XkpTt/h9laboQk7yidz+J4qjG2HqpJ8bafVX+bN+86pafuLwftUpxmJLUol6QkOHqzw8YTjzsDJ57d53qQ3PW1qRakKgWCA9NGEtvONJc4E7nO4yTk8s43qENyWnNMPXlx1ZLqHA7ghSesCldhR9IUCPHeodbrg5MmRIPER1qksjB7zsPsrPKChTajoaFHEyrYmEsR5kml0VvgWQ30lXeKtKZLdskthfGQ7DbAznxSAc/bViWHVth1PHcD1qiMv8OXmkMp40frjAHGnx7x++qYuOnZkFLYbLU8rVwhMRXW789+HOPXitu1229NXFl1h2PAdbUFIcedW0pJ8c8O1cuO95K69T2tV4JXjOSjJcLJ/2/2T7VbrVijKuMdDS4gSQhB2UFdyQc9/d9tQGF0gSHllt2LCIySA1kpVjmk9+fT31Pkak0vc7dcLZq9ZieTgNyX4CA5HfJ3StOBlK84OU7ZHdyqnpWmrpCecTbm1zYrb56iQEdUXEAHCilWCM55HvzWzRpU1rJdzh7RxmMbUKbaS6c/e/wDPXUteFe2ZUBuWylkJVseLzknOCDvmvrl0cPZSwwlAP82Diq2tt9vumYamX7GmQFLLnWKd3GwBHZJHdVsxUOWvSErVki3fNNQRKZacUFNuOr4Q2kgcxxK5d+K4VfC4p18tP9renp77HKrY/HyV5za+FiovIXO2JNmvDr6lrJcal8CTlRxhJSfR31nLUBKUEadviiB2wq4YBPLw5Hn6/RVjXG4dJGmtVMNpU/qNDLbT0thi2DqUFYyWSUo2ITg5GMZG1S1ubdbgEvQFqWw4FKCH47SHWiCAptxJTstJIBHfsRsa71Xf0YpuzXon9zVwtB4mTjmSfqUIUQ2wSuyXsDlvcMfb5nOpT0ZWmVP6QLJJtllu4bhT0OSn1yOtbabIOAoADG45+urgiJuL8YF550OZIIRHYKR94519EjUNulBVudUG85VxIaQF4PIgAZHvqka81rJfL8m4tmzcnHPH5/YtccqVy7De2b5bw+2OB1CuB5rOS2scx6vA0rdTTV0c2cJQk4yWqOpVFfCjVw6asB/41f8AlGr1qjPhPjOm7Dv/ALav/LNSVPz3YrNKv812LBShT6GVvBGDxOYwOFOB5xJAGdqkczo7u9onxGZDjLapNyNuZcSFAFSQCtwHA7CSSM9+CRtXEsFkmXmY/HhSmI60R3HlqeeDKVITglPFy8Nj4V3ZGidQoupiG4sPOtvrCnPKlcCV7pKwo44s4xlOe4GhJyr9p2Xp5EZcpbDiJScpU24Fb8KVKGx3xxjfke6ux0cym2r5KKxkGPjmP5QqP3ePc4rrMS6POOFtHE0hT3WpQk+G5Azj91dzo7hIkXuSlSQQGM7g/wAoUuLFoIlR3MbfeBQpiupIU2nlvkVqJs7IXukjwHEQP8KzJtSCs4C8Y7lnlU5hY1nNOWSQouOQoqirclSAT99ZU6WsZbCFQIpSOQxgAejato2kkbKcxt5rtekWySCcOS9v101OYixoOaG027uq3tJ/qrUk/uNajnRrph4ZMZXF4dcsj/Gu98XzBuHH+HfmgK/wr35JMBHzjmfSwaZhYiEnomsTyAlt6VHRz4W17H7DmsUfoksjHKXKLmchXFuPuAqZKZmJISVEgn+aI/0opMhA3WkZPftS4V1qiKHoziBQKLtLA8OPNbcXRiIo7E8Lx/LjtL/xrvLMhI3UjI/WHvrEpcpKVAIQfUQf9aqlFcEZZVasneUm/ic9zTY/NkM5HJSYbGfs7NcF7o1s65q33vKVOKPETwpCSf6oGPsqTuOy0Ep8mGB6KxF+SFEeTknmSP8A8q10Ym2zDFs0SMgNcKlJSMAdQhO32JFdNTCLjYZNpgoK5bjseQ1GdWQiSGXOPqM/mle2PSAO+uYqW+kZ8neB35CsCp7wSVcDqfTjH+tWzFWiY2jpP0xJ6m63Jtdqurrxdmxm0vrypPZSMhaUhWEjOUnwxtWCxR3r3ZYMhUphh2e7Ju6zNd4OIOvYQCe/sIT9lROTeIkuWZU7T1nmS14UuRIg8TjhHeo8QCj4kjfvrdka7kyHeN23Wpa8AdqIeQGAPO2AGKxVo54ZYm3g6yoVd5Lle1iY+QKU4pKjac5IHDnG6wrnyx3f1a8Ks7s9zhRKtUUDiPF1hbByc8/RnA9FQn8O5DfaRbrShXoiEH/Gp30WPQtYKuouVrtyvJC1wdVH4PO4s5335CtN4Z/4zrR2pFO6b7L7kt6OoBhWeUtSkrU5JUnjQcpUE9nIPeM5pUsZYajsoZZbS22gYShIwAPQKVtU4ZIqJx8RWderKo+ZkqkPhNAHTliz9cX/AJZq76on4UefwasGDj8tX/lmrPRGAoWNMMdoNiPGcA3y6yFH766HUTnEeWot0Utlrz0MJwkDtZPgdvu9dR+AmKXVqlyHGuEAtgNdYlZyNlbggYzyz6q63lFuUVFYhKzvkCQnHqAGB6qw7wm57kXFyU0ULYjDshPEhkJIAxjf7KlnRVGS7qCcMoH5L+cnI89NQOcuOOFcSUtallRWjqihDe+wSSSSPWByqUdHN7nW28y1xi2VLjcOVtpWB2h41iq4hU4uUlwGax+srpd7bY2YglMZ68FKAhsHJABPqrCNSWtKnguItstZzxNo3wQDjffmK5XykaXdZbEhTrikpGQYxVg43r2rpF0stGVdcsDkPJCef2VHjaH9RdzJGVKyTWvvNjVgZuGiVSWG+BLiA8jYJOCkkcqqS02+S/Bae65lKVpynrHwknBwdjU61bru2TtOKhWgrDyiBwuRylPBgg48OdV1AK4oQcKStPIgV1Nn7SwkVOMqsVw4tep5/alKdScXCLa14HdbtMhZWA9GBRz+fT765eoYj34K3xrrDxtR0kltzbz09458+6tly4OuNcB7KFjtBDSU59eAKwPSAu2TIgTkS2w2Ty4cKBz+6tnEbVwbpP8AVi+HBrqjSoUakKieV8/oVjD07cpYStoyn0qOAll/Ks+B37PrNY0W4Sj1SHpTDx8zjfKkrP8AJJ2wT3cxnwqwIbkq3soixpQbSFFxB6sHhyADgnburfXMu7rBaXOTnrEuBfVoSpODnAwOWcH7K0Xj8Iv+SPdG+nUtwfYy/B9hK+OrgXip1PCnAc7Q5Hxq0U690wZT7Ko7iOo4uJZjgjCVhCjsc8z4VB+jiXA0xNmSrg+4kvEAcLZVk75Jx66nB1po9l1xxDQ6xY7akwjlWeeTjetGpj8M5+WpHudjCSgqT3kXflyt7zOjXeklyA0JbHaUEpV1XZVkDlt4nHrqsOnaE85qS2swkgOPgJShB4MnB79h99WR+HWkAUkNnPMYhnb91Vl0tSWdZSYci0PZS15/X/NAbYGM08dhv6i7klex9I6jkuJbbaPWLWG0pMgZKjnbYkbBKic4AAr27orVDURUlyG71KUdYSHc7cKlcgeeEkY7jtzry1pa8qT1aJcVA4Qnh8sCRgbgEeGTWYaNv6CViXETw7ki4Ac/t76zLFUJcJruiDmTpiodvtpK1DrWCvJVz7RFdqTpa+Qrdb5s0MxGriw7JYLzwGW0N9Zk4JxlPcftrXv+hr/doNqbtwgumBGUy/iUhOFcZVz79iN648iLrryOHDfvbS48NBRHaVcUlLSVJKCAPApJTjwNN/T9pEnu5OS7TI6iajqXSkq4eIE44inO3pSceI35Grz6BmFMovSlDHWBhQ2x3Lr88v6W1XdHutdWzLdCEtBapaVnhSkJSn1AAAeqv0l0LANt3NggB1luOhzA3yAr/wC6upxk/KyS1KUpVyBUE6UOjw9IMG3x/LGYyYbynT1rZWFZTw9xGKndYZEVuSnhczj0HFAUC58G1Jxw3yA1jniOs5+9dYj8G4DnqOB/0qv46vNzTsNw7lz2jWurSMBX57vtGosgUn+LmlIx+EsAD/llfx1nidAj1vcUuLq6EwtSeElEY7jw86rgVou3q+ke9qvB0NAP0r3tVVwjJWaBVaehq5tk8OuIyc88Rz/FXv5JLuMf9vWBj/hz/FVnHQcA/Sve1Xk6BgH6Z72qxvDUXxguyIsisD0Q3TOTryN/05/ir6eiO6KIzryOT3Zjn+KrMPR/BP07v31je6O4TrDjaZb7ZWkpC0ndORjIp4aj7C7IWR+dJ7t3g3KTFj6gVJbYcU2l5KOELwcZA8K1zcb7zN5X91XH+Lxav0guXsN+6h+DvaSMG/3H2G/dUeFoewuyJKHf1ldGbkYRur6lpWGwoJHCc9/L011hc78cYvSzj0Va6/gyWFcjr1X25cec54W/dW2Pg72kcr/cfYb91R4Sh7C7IFPx5d3clNNu31bLbi0pW5w8XACd1Y78c6sv5LLypAHygsFPMfMH+Kur+Lvaf6fuXsN+6pbD6NoUSCzHVNkPFpAR1izhSsDGTjap8LQ9hdkLFejonvGMDXzGP+XP8VPkku5/39jn/wCOf4qskdH8EfTu/fXoaBgD6Z72qeFoewuyBWfyPXU/78xv+mP8VPkauyj/AOeIxz/w5/iqzhoSAPpXvar2ND28fSve1U+Go+wuyBVvyKXUpUn8NY2Fcx5Md/71fFdBdzcKSrWEVRTsPyU7f3qtdOi7en8972qyo0nAQdlO+2ancUl/KuyIsVK30D3VK+JGro4PPIjH+Kp/0d6FnaOeuLk27puPlgbCcNlPBw8XiTnPF+6pI3p+I1yLntGugyylhHAjOPSasqUIu6iuxNjJSlKyAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKA//2Q==</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Infiniton Réfrigérateur Américain SBS-668 559L</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAIDAQEBAAAAAAAAAAAAAAMGBAUHAgEI/8QATRAAAQMDAQUDBQsGCwkAAAAAAQACAwQFEQYHEiExshNRYSZBc3SxFBYiMjZkcXKBkdEVUlVjkpQIFyMkN0NGgoOiwTVFhJOhs8Lh8P/EABkBAQEBAQEBAAAAAAAAAAAAAAABAgMFBP/EACQRAQACAwACAQMFAAAAAAAAAAABAgMRMRNBEhVRoRQhkbHS/9oADAMBAAIRAxEAPwD9BXO+WyzOphca2GlNVJ2MPaOx2j8E7o8cArU2zaLpC818FFQahoZ6io4QxiTBkPc3PM+AVd2tWq4XOo0oaGinqhT3XtZuyjLuzZ2TxvOxyGSOKq503eBsF0XR/kmr/Klvr6SYw9ie1g3ZnFziObcNPHwQdOqde6WpLy60zX2jFe2RsToA/ec154BpxnB8CvFVtC0lRWuG41F/oY6WokfDE8yZ7R7ThwaOZweeBwVO2VaW1BQWyerqrrX2wS3WpqJqGSkiHbAyn4Rc5u/8IY45+hVPZVpm9UO0KyTXS0VsFPSUNfh88DmtjkfVOI4kYBLTnxBQdYpdpejq2JslPqGika4yhuHHJMbA+QYxn4LSCfpXu37RtI3WuFHQ3+jnqDn4DXHIwC454cMAE8e5ci0lpq+0+2Slr5rRXRUbNQ3ed074XBgjfAwMfnucQQD51YX6Wvdxtu1ihgpZoJrtUH3E6VpY2cdkB8EngQcbueXFBf7btB0leKmSnt+obfVTRxulLI5gSWN+M4d4GDkjK82vaJpG818NFb9QUNRUz57KNsmDJ9XPxvsXMq6kuWphoykt+lrtbJLDTyuq5amkMLYgKcs7JhPx9535vgVJPpu8fxG6EpW2qrNzt1wo5XRCE9rAGyO3nEc2gA8UHbkQIgIiICIiAiIgIiICIiAq3rzVbtGaWku7KQVhZKyPsjJuZ3jjOcFWRc625DOzGo9Zg611w1i2Stbc2zbep0qbP4QlTJkjTcTWjm51YQB/kR/8ISpjwTpqIhw4EVhIP27i40wB8XZlwYQ7eBdwB83E/wD3nXx+GwtjB3zkuJA4DwC9v9Jg3rX9vn3kfrTQuqXax0tDeH0gozJI9nZB+/jddjngIq/sR/owpPTzdZReJlrFclqxyJfRXkbdDREXJoREQEREBEUNVV09FF2tVPFBGTjekeGjPdkoJkWtdqOyt53ehH/EM/FfPfLY/wBMUH7wz8UGzRav3zWL9M0H7wz8V7h1BZ6mZsMF0o5ZHnDWMnaST4DKDYosOovFtpXNbUXClhLhkCSZrcj7SoffFZf0vQfvLPxQbJFrffFZf0xQfvLPxXoX+0H/AHpRfvDPxQbBFgfl20nlc6M/47PxWVT1UFU0up5o5mg4JY4OAP2IJUREBVnaBbZbrpOWlgtzrhI6RhETS0HgfjfCIHBWZCAeaxekXrNZ9umLJOO8Xj04KNC3XcA95b844n+Q4nv+Ovr9DXQnLNEvHm5wn7vhrvGB3L7gdy876Zi+8/y9f61m+35t/pWtC2+W2aYgppbYbY9r3kwFwOMnnwJHHmisgAHmRejjpGOsUj08jJknJebz7fURFtzEREBERAVI2sDOjohz/nbPY5XdUrapg6SiHzpnsckDixjHcFG5gxyCyyxRli0yxizB5BYV1u1RYbVU3GkbGZ4WENEjct+ENw8seZxWzcxaHWDfJOu+oOoKo+aa3n6VoC8lxEeATx8wWc5g7gsbTLcaUoPRj2BRxX2gqbs+3RyONSwuBbuEDhz4rQncwZ5D7lE5g7h9yzHNUD2qohEhaN0NZgd7B+C7fsPAGlrhgAfzzzejauIlvFdv2IDyVr/XD/22rFlh0tERYbEREBERAREQEREBERAREQFStqfHS8HrTelyuqpe1HjpmD1pvS5ByJzVGW8FkuaoyxbRjubxWg1i3yTrvqt6grG5vFaDWLfJOu+q3qCD5pxvkpQeiHsCqtqMbtay7rAJGz1G87vBAwPswfvVv063yVt/oh7Aqva7bUx62lqH0krIy+f+UMZAweXHkcrTK2Y4BROasktULwqjHc3iu2bExjS1f64ehq4q5dr2KfJau9cPQ1YssddIREWGxERAREQEREBERAREQEREBUzacM6bg9Zb0uVzVO2mDOnIPWW9LkHKHN4rwQpyFG4ZWkY7gq/rQbukK8nzMb1BWN44qva5HkXcfqDqCok02M6Wt/om+wLOcwdyxNMt8lLd6FvsCz3DgqkcYr2HuKx3t4edeo9kfvgq6mujvksL5WGo7N0eWgk/F5qGLRzNKRHcuEtZ7qJz2jcbm7w4cTzypEkw8O4Fdq2K/JWu9cPQ1cWeF2vYsPJKsPzx3Q1LEOioiLDQo6ioipKaWonkbFDEwve9xwGtAySfsCkWJdaAXS0VdA6QxtqoXwl4GS0OaW5/6oPD7zb2TU8PupjpKhgkjY3Li5pOA7A5DjzPBYvvssfud04uMRhDxGHjJa9xzgMOPhn4J+LnkVpotL3SG4Ute19F28NJFRyguk3ZGRkkEAAFp+E7znn4LXR6bvdLbrTSwTsJscjTQP7ElzGiN0W68HAeNx+MjdPAHvQXyjrKa4UcVXSTx1FPM0PjkjcHNcD5wQi1ulLSLHpmjt43yYWu3i/m5xcXOPIcySceKINwiIgIiICIiAqdtL+TsHrLelyuKp20s+TsA+ct6XIOXEKMhSlRuW0Ruaq3rr5E3H6g6grK7kq1rv5E3H6jesIMnTQ8lLb6BvsCznDgsLTXyVtvoG+wLOdyVSOLFZa6GkpGOmqGRucd0AyBpwB9PJaLUdTHUVr2wuD445HBpacjjg8FhSLGeromWO9dq2LjGkav1x3Q1cVeu17GPkhVeuO6GqW4kOhoiLm2IiIGQF8yFT9W6lktlnFTT2+a61M0jm01viOHVDWHMjuYz8EOI5+bgfNW9Na4qb7qQ22jtdPRMAibHcKeR0lLLK6MSui8284MzkAZGCcjCDqqKCjqPdVKybd3S7m380jgR9hBRBOiIgIiICIiAqhtIbvafp+8VA6XK3qp7RP9gQ+sDpckDlhYQV4LCst2FGcYW0YrmFVrXbCNEXH6jetqtjsKta5AOjq8HlhnW1Ue9NsPvUtvoG+wLNewqPTwA0vbh+ob7Ast+AqzHGA9hWO9hWe/CxpMKowHsOV2rY03d0hVeuO6Wrjj8Ls+x/5I1B76t3S1ZtxY6vyIi5tiIiDlW0fSdReKOnlttoZX3u2b/uZs7iInsflrTwI3nN3845DBJ8wOg0XszNl1HTyXOxe5LZbXNqqSaaTfqZpnRhr4iGO3SO0y5vDPLjgYXcJaeKdm5LG17fHzKKG3UlO/fjhbv8t4kucPtPFAt8UkNE1soxI4ue4dxcS4j7yiyUQEREBERAREQFUdoxxp+D1gdLlblTtpbt3TtOfnLelyQS5qX8VGXKN0nFRuk4LaJXPVa1y/Gjq7+51tW9dLxVa1zJnR9d/c62qpLaaff5MW70DfYFlPetbYJMaXt3oG+wLJfLlVPT696x3vR8ix3yKoPdxXa9jxzoyb1t/S1cNdJxXcNjRzoqc/PH9LVm3FjroCIi5tiIvEz3Mhe9oyWtJA7+CCOSoLXFsUbpXDnjgB9JK8MrSHtZPC6AuOGkkFpPdkef6Vpbj2jaWL3FIZqjfG+wzmPIOCcebPLn3qO3TPuck7a2OSiy7djjMu8XN4OJOOHcpv99M/KN6WhFBQyPmoIJJPjvja4/ThFWk6IiAiIgIiICpO1J27pqnPzpvS5XZUTay7d0vTett6XKx0crdKvBlWMZD3rwZCtIyHSqt63kzpGtGfzOoLbukPeq7rSQnStYPq9QVSW3sUmNM24Z/qG+wLKfKtXZHkact4/UN9gWQ+QrTKR8qgfL4qN8hWO+RBK6Vd22KO3tDzn57J0sX5+Lzld+2HHOg5z8+k6WLNuLHXR0RFzbEREFN1hadQ1VE2nsvYmnOe0aHBkp8A48MfcVi6PsOo6OJ8F0bDFR4w1rnB8w8GkcgR3k+CviLn44+XzcPDHk8m53+HxrQxoaBgDkO5F9RdHcREQEREBERAVB2vnGlKX1tvQ5X5c92yu3dJUp+eN6HKx0lx0ycF4MigMijdJ4rppnaZ0ir2sn+S9UO/d6gtw6TxWg1e7OmqkeLeoJKNrZ3+T1B6FvsCnc9YFof5P0HoW+wKZ0niiPT3qB7uC8veoXP4Kj2Xcea/QWws50BP69L0sX53Ll+hthH9H8/r0vSxS3FjrpaIi5NiIiAiIgIiICIiAiIgIiIC5xtsdu6OpD89b0OXR1zPbs9sWhqaV7gxjK1m85xwBlrhxPm4qx1J44iZfFeDL4rCbWwP+LPG76Hgr12zD/WM/aC6ubIMnitHqt+dOzjxb1BbIyN/Pb961WpG9tYZmsIc4luADkniFJWGwtMmLBQj9UFK9/isK1yN/IlGzeG8yPdcM8Qe5SvkaDxe37wrED096ic9eHSs/PZ+0FGZo/PIz9oKiXeX6L2DHOzyX16XpYvzWamEc5ox9Lwv0psFBOzcyAZZLWSvY7zOGGjIPnGQePgs241DpiIi5NCIiAiIgIiICIiAiIgIiICx66hprlRyUtZAyeCQYdHI0OafsKyEQUODYpoGDOLC1xJyS6eTj/mWS3ZDoNvLTdKfrOefa5XNE2Kg3ZRoZvLTNCfpaT/qvQ2WaHH9mLd/ylbUTYqI2VaGbMZRpi3h5GCez/8Aa+nZZod3PTFuP+EraiCoHZRoUjHvXt32R4/1Xg7I9Bn+zFD9zvxVyRBR5djOz6bG/pik4ceDnj/yV0ggipoWxQxtjjYMNaxoaAPABSIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiD//Z</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>350000</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Lave-vaisselle LG 13 couverts inox</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Lave-linge LG 10.5kg TurboWash Steam</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TV Samsung 75" Crystal 4K + PlayStation 5</t>
+      <c r="B5" s="2" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 50 45k UHD CRISTAL</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAMBAQEBAQAAAAAAAAAAAAUGBwQCAwEI/8QATxAAAQMDAgIGBgUGCwQLAAAAAQACAwQFEQYSITEHE0FRYXEUIjKBkdEIFSNC0iYzUqGjsRYXJDREVGJlhLPBQ0aU8HR1goWSlaKytOHx/8QAGwEBAAMBAQEBAAAAAAAAAAAAAAIDBAEGBQf/xAAuEQACAgEDAgQFBAMBAAAAAAAAAQIDEQQhMRJBBRNRcSIyYYGhM0KRwRXh8CP/2gAMAwEAAhEDEQA/AP6RREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQFP6T9QXHTOipbja5I46oTwxh0kYeAHPAPA+CxwdL2uC4tFxpMjH9Cb81qfTSM9HTx31lN/mBfz9URuhIlaPVOAcd//AD+5es8C0On1NcndHLz/AEC1TdMeuY34Fwoz50bfmvx3TLrdrQTcqMEj+pN+apVRJtBdGRx7cZXJE6Spl2kk47SV9+XhGi6sKtfkg3hl8j6aNcvl2fWFGOH9Sb81o+mb5qu+2g1s+oWwnY5+1lBGRwPiVh1NTMBJbGyR4wNzzw8gP9Vtdgjls+kIDOzqjPE5rGA5zyIP718HXaLTx2rjjc2UVqUW2SLbjqZ54alJ/wC74vmvoyt1I6UNOpiGluc/V8XPJHeq6b4A7bBTTSE/dDeSk6GrnfA30gBjskhgOdo7ie0rHLQ1rsccFFfEiZiOo5S38qHgHt+r4vmvr1eosH8qn8P7vh+a5qedpBBc4HnwOMrqFQAMArHLSxT4K2kR9bVappm7mal3Ac82+L5rmbc9VOAI1IMH+74vmpSZwlYQeKiWO6iZ0R9nm1aa9LU1hrc5hH1Fw1Uf95B/5fF819YavVEk0bHam2tc4An6vi4D4ry2Ud4X0bKO9JaSvG0Qkc31rqV1bPAzU2RE8sybfFnh710Cp1OWg/wn4f8AV8XzVZu9ZJadVtfNuZSXEdY13Y2QcHA+fP3lTxq2tja1rsggHOVJ6KtxTS5LrYKO6Wx9JK/U7Afyn4j+74vmo+fUGq4j6uo2nzt8XzXqaqyD3KLlldJJhoJyVoq0FX7omdYZ3M1Jq15x/CJo/wABH810NvWrXY/KNvH+74vmoynGJMHsUhFM2NuXEYClPRULiJd0ou+hLnXXfScVVcZmz1QnnidI2MMDgyZ7Ado4Dg0KxKpdGTxJoiN4OQ6sqzn/ABMitq8vNYk0UMIiKICIiAoXTIM6Ax31tN/mBYw2lbJEWPblp5hbR0wSGLQrZA0OLa6mOCMg/aBZZTXNj2NzSQPPaHRtx+5ew8BlKNE+ld/6LYRyU+uscjZS6IOkae7n7x8lzQUTqfewRv34yQWkfvWmOgtFVDvEbqWQ9kZJb8Cf9Qq/fLVJTx9dHiRrvVD2cj4eB8Cvu16rOevY5KhxXUVimpcTNExGSc7RyHzW2dbHNpq0RvkczbET6uPL/RYo15dWxxhrs7hkYPBaTXVbom0VK08YaRmR3F2XH94Xz7q/NlFL6stpf/lIlTAXcYZhJ/ZPA/JeGVBjcWvy1w7CMEKKhriwnJJHZhdLKxlcOqecSD2HHs8PJRlTKPO6KSbgqyRzXU2rzxyqxFWFri13Ag4I7l2R1eTz4LPKkE8akbSSeC46h3WDI5jiFHS1mC0Z8V9opw4g9hXFV07nVyeRXBhO4nDeeOalIa+jqXRCnaC4HLtp3cPFVqrBZeepGdrwHjHd/wDqmmUtcRuho5WkjjkBufHjhRsjF4ecEop7rBy6lEF1pH00/sk5a4c2kciFUI9Ry2FjYLs9z2MOGzAcHN8e5WKqp6x7nBsXWEcxG9ryPc0ldT6K1VdF6HIyKcR+q8jIcHd+eYK0RcIRSW/sTy3BxlwcNPeaK4QB9PO1+RngVHXC90dAzfU1UcTezc7n5BfK46GsNtkkrBWz0jAwyPMbg3aB7sZJwBw5lUsXy3WcvqLZRB1c/wDpVS7rpWjuaT7PuAXHqa4L4SuFEuW9i3C/3B8IlpKBtNARwqri4wMI72s9t3uCgrlqS2iTFzudZdnDnBBmlpx7gd7veQqqbxV3S4b6udzu9xJJJXyqrVNEzL4mPc47t2dxAPeqOqdu5J2Qhxv7n9R9DM0VR0V22aGJsMUktQ5kbeTAZ34AV7WfdBo29DtmbnOHTj9u9aCvJWbSZRyERFABERAUPphbv0I1vfXUw/aBZZSU+GAA8eS1npXbv0hA3vuFKP2gWcMoy3iBwXq/BJ4pkvr/AEaKTjqYHtcMP5dyi5rlLTmUBnXRlv2kR+8PmOYKm6yRtNEScZ8VQ7rVVtzrm0FtjkmqZnbWRwj1nH/nt7F95NOLTNcppbErb4Y7jWwSwk9U5wzk8h3rtfd46651FSHEMe/DB3tHAfqAXNb71YNI2VttqWNvleBiYQvIgYTnLA8cX4yckcPNT1qv2ibkGsnttsoZXD8z9pGfdIOA96pVvlfHKDa7cFbipQUINZ5ZyuqS4taxzeI44/1XumlcJQ4uPDhx7FMVejqGtjlm05W9ZMxu51HO8Ekdha8cD7/iqm2tnNVJTSRPZVMJa6N42kEc855K6m2u5Pp7c55MtkJVvE0SVRWhtwmw7huXTFX5I7jyUWy0vme6SS4wtkeckCNxA8M//S/aiCot2x8rWvhJwJYzubnuPaD5qpqPBUmSclbmcDPYpG3TGp2RxkZDsknkBjiT8FTZqwvqcNy4kcABkn3K0aeY6S0TTsO4mYMeR2YbkD44ULYqMPqXUpSlhnff7rWUDttopwHtbsdVEeu7txnm0eA+Kzy612qbmHx1F2qYoXcDFAerb78cT7ytCdUbKKGJ+MmQ5+C+ElrimyWYx4qNKrrXxR+4nKUuHhGTUGkKiOvFRTyPilB/OBxB4+KuVsvF5jvFJY7rIZJah22kuDuLosAksf8AptIHI8lbqK0sZ7XBvA4xxUNeJojf5K9jG9XaIHCPudO/1B8PWP8A2VHUWQkmorglRDDSz7kXqO6NnjltUk28ytzM7I3bcZ9n7vgD+vis5dTGOPid3dntUzQUL5bxUzu3PMjHbndpK/Z6BzXREtOJGkN8xx/cqKNP1/HNDUWqSxFYIplM4NBY3auqJj3SsExc8ezkc2hSNPQiRw7Grv8Aq6ETbDvxyBHavodEcYMWMm9dCrQ3ontbQcgSVA/byK+KjdDjNnRdb2fozVI/byK8r89t+eXuy1BERVgIiICmdJ7d2maRvfcaX/MCpdRVRU1OY+raThWnplrBbtBCsJwIK6mf+0C/n2TWtfdK3qbc3c5wLS77ob25K9F4THNcsvuaKZfsS3ZP3iqmudSaWj9aR3ZuwPjyAA4k9gGVUrjeBRQS2uzykMlG2rrgCH1Pe1va2Lw5u5nsAt1vsdUdK+lda2ae4bsyR8WthDsBrT/acCT5AKqVtmMUpaW5K9JUlNZb2XYX9VbwQUkhNOGwMaXA+/zXinM7JMOODniF3SU3UkYbgg80gAFRveMjOMnmuzTm9zGp9PBcdJajmtlU0xuD8Dbtd2Aq3ahbFdbQ6+RMYa6kLWVeznLEThrie9pIHkfBZc2YRV7nwj1WjtHBW22ahfBbbgx7WiGopHQnPa5wwAB354rJOHRPrjyv+wa46mVq8ue5+tlkdKGsBc53ssYMk+HirDbbFfJ2bX22TqZRtc2YhgcPIkFc9sv9ksUbfR5XdYWDfLtHXSOxxy7k0Z7G/Fea7V0dcCIL/UUJP6ELSD5nO79anbZdLaEdvVly08EszluSlBpG/wBmkPoNJM8SDL5A5gk8G5DuXb45X1udHcqGaO7y2ysc6BhFUza1pkB4bhx9YgAePDtWYya7lorhLA6KqqpY37TI+sIDvEYHJT1LrCpuUUTKhjxE1wJjNU94PdzCzOm9yy2v4/2EquFItEd50nc3xAXplK5rt3V1DTEQe7ip+Oko5YB6HW09Q3nlkgKqjdQ0zmFstvY9g5j1XD4OBC5pJ9JVBLprLTNd95zYeqd8Yy1Qn5nbP4OeSl3J68XJtnhAlk+0ecMaCCXHwCrGtKWr05YLPRVEZbV3KR9VOexp4NazzaDx8SV+y0mmhKyps8TKeojGT6xfI7BBA9c5+BX5eK2rvGqaR9xqevoCwTQBx4Z7R55yuYlPpS29SyFbUZSi90denNNu9AfNJHxPDivVy0/19I+FrQwsO5j+A2uHLnz8u5XShZG2nDR9m0jkeSga2rY3U0lPJMxrQ1r4+/BHH9YKthdJtpdjO69jP5pvq5z4qqB0JJ4P9qPPg4fu5+C9xSTVQaYBvA7WElW2tdS1Ze8QBwacF44Ejz7fIqGqLZb3xxyQwsY7cQ7YNh7MH1cd63Qk3yih1tGzdD4c3oyoA8EPE1TkHsPpEiu6pPRC3Z0a0Tck4nqRknJ/nEiuy/P7v1Je7OBERVAIiIDOunJlJJ0aSsr3StpHVlMJTEAX7etHLPDPmsKNZo2sp2UPoFwpaQDBMdZtc7+0RtwT4Hgtv6fml/RRUtGMmqphxOP9qF/LD52xnYzLzjiQvUeDQjKmfV6+pONrgsYN00LLDBHDpwSyS0MkBfQSzMa1zg1x3NyOZGQezh2LovOlnMdIY2DB4clnukb7Jc7SyzicU9xopvSbdK44G/HFhPiOC2PS2q7dqqj6qUej18Pq1EDhgsd2jjzHBabJSol1RW3/AG5bYlNKa4MsqtLva4kxrhm09JGB9mOPDK3l9qpmSkxhrnDtxkhcNxt1NLQzekvYGNaXdZIPYx97Pgpx8Rz2KfKRhVTZ3Qt2lrtxcGtAHtE8sJeLXd7Tb2PnttXT0wH5+SBzWZ8yMLUdImOokueq5I3VItlG+S3RPbkAcQZiD2nBwOxvmqGzpV1bDdqhz6761p6hj2Po6uMSQvBB+4OWOeB3cVqjqLZykq4p9POXj+P9nceX7lEfWPk4Ek+K+bppHN9VxWqtpNG6d6NNM3q56Xbda64tmD2tndC12HnLjjOSBgAeahnadotR9GNJdLHb44btRVwo62OLcetbKQInkEnkS0fFT/yMe8WlnGdsFbyyhspQ/dIXetnOT2qbtrnFrGsBJ8FpcOm9FQ63rNPNprfNXWi3RxxRVdS6KKvrCMvL3f2fV9Ud54cOHlkMOm+kLTgr9CR2qSrkbF9nVmSmfIXt2yxYzgtHYTxzy7Vll4jGW0YvjPb39SnDK3Eyej6ynqYzFUNcWvZINpbwzyUZWzdW85PA81pdyFju2vNU3G4WzqqLTjHvqY4ZSXVshPqk/o8jyUdb59J6t09qWZumYrfXW+2yzxdXM58eADh2OGHA48DlZFrcYk4vtn7k1Ka2yZpdaGuoHMbUU81K97RIwSNLS5p5EZ7D3qz6bqZbjRMsd6ilpJahvX0NRMwty7scCebTwBI7OPYvXTLUdXfrIMnjZac4/wDEvzpMqZYKLQNRE4tkbZoXA+9q1K53Qr2w5Z+2ApSrn1x7F6sMtdVUU9NVU80FZQkNnY9hBb3HyOMgqJ1PY6y40oqaISNqac7WyAHDs/cJ7M8MeK0uubborpqiqfWx0T/R6VtTJOcMYACWuz3YJHuXkUVPFpuXqK2GrZJVwP3Rch6zVgr8Qw+tLuvylk+q7I2R4MSY670dO5l1tVxo3NOD1lM8B57MHGF20NPVzyAhmTzdk4a3PeVqN0v10pNfvpGzuno5JmROpnjcwtcACMe9VLUlNHbr/XUVHhsEMpDGDsyM492cL7Gn1k7Wozik2srBQoPhmhdFDSzo8pWEgltTVAkcj/KJFc1S+iXP8XNJnn6RVZ/4iRXReFt/Ul7szMIiKo4EREBmnT4C7opqQOZqqb/NC/lINEEjDKSGk5xzyv7H6UtK1+stDT2e2PgZUvmikaZ3FrcNeHHiAe7uWIu+jrrFzsmotBHd6Q/H/sX2/D9XTRW42PfJxoyR9S6mqWyNIa4cQGn2VZm6sbBabbWRQvbcqeqcZqhkmx8kZHBmePLaeYPNW6T6NmsJOdVaR5VD/wAC5r10Caqsum6qtqai2GmoI31MgjncXuDW5IGWYzgcPNbpeJad93/BKEnHJZaDpzsMrA6opq6kkI9ZpjEo9zmuH7lGao6RqDVrY7fRy1Udqb9rcD1BYXRgj1dxcTgnAxjiSOKh7H0C6j1DZKW6264WqWkqmb2O694PPBBGzmCCPcrBR9A2tqK0VdBFNZttZJG6WT0iTcWsyQz2OW45PiAsy1Wli8pstV8n8yR+0nSK+2RQV1qMAfuc2SnkHqOby2Ed20DC4ZelSzWWWar03oqgtl4ka5vphlMrYs8yxhAA/UPNdDvo+60cMdfZ8f8ASH/gXh30edZu51Fo/wCIf+BaJ6zQz5z+d/f1+5VOcpvL5KveNZvvukbHZX0uyS1mZz5+sz1xkduzjHDHvVr6HbjUaedqO/PcHWqhoN87SOEku7MTR45z8V5j+j3rOMHE9n4jHGof+BdLOgrXzKJ9Gy4W1lLI4OfC2rkDHkciRswSPFRs1mklU6ovCf0frlkFkodg1ZSUl1udRqKwUmoI7puM4nOyVri4uLo38dvE/qHEKSvnSD6ZFZKWx2ttot1jm9IpoXTOncZd2cuceY8PEqfk+jvrKQfzi0N8qh/4F5H0dNZBu30q1H/EP/ArHrNA5dTz+cenHBV0yON3S2warlvVNp2kgbXwOgutI6Uvjrsn2uI9UgeB5nOV0fxnWagsl2tli0hDbqa6Uj6eR5q3SSBzgQDkj2Rk+r+tfV30ddYOGDUWkeVQ/wDAvbfo9azEIjNRaCAcgmofkf8AoWaV+h7Z/JNKRUNbal/hdc6OsNJ6G2gooqMt63fu2Z9bkOeeSlrX0nWr6itdBqTSdPfJrO3ZRVBnMRa0EENeMEOAwPgOCmXfR61k7P8AKLQAeY9If+BeB9HTWAcCai0nHYah/wCBXR1micVCTeFxydwzjs3St9Y3nUVPqKkbLFqcxxudG/a2la0FoDRjjgY7Rxb4q9aAv8lLba3S1azrKyhqGneHe2xpBa4d4IxxWfaj6ENQ6csM93uVfaqemo27y9kzy4nPqgDZxJJAHmrTZuj7X0jbNqS3i0vkNGxrc1T2uliI3N3+rjIBA4HsHcq3q9JiUF8r378rg16e1QXTPgvt/wBUQ2yrZW09np2XGcu+3keXlmG8wOWVSWvfL/KahzpZpiZHOdzJPapK66R6SbtNC+S0WOIw7sBla7ByPEL3F0f6/bBG00+nztbjjVS58vYVum12kogsc9+S52VL5S+dFWP4vqbHAek1X/yJFcVXNB2Wu0/o+mt9yMHpbJJpJOocXMBfK5+ASAfvKxrzU2pSbRifIREUDgREQBERAFU+kXS1w1lp2GzUNcKGKapYauTjkwgHIA7TnHA4CtiICOsFjodNWKltFtjMdJSs2MDnbieOSSe0kkk+akURAEREAREQBERAEREAREQEXqTT1BqmwVVouUbn01S3B2nDmkHIcD3ggEeSiejzTVx0jpc2a4Vra0U87/RpRn8ycFoIPI8+HEK1IgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgP//Z</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 65 Crystal UHD 4K Smart TV One UI Tizen, HDR10+, design MetalStream + Support gratuit, 65U8075F</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAMAAwEBAAAAAAAAAAAAAAQFBgIDBwEI/8QAURAAAgEDAgMDBQ0DBwgLAQAAAQIDAAQRBSEGEjETQVEHImFxshQWFzI3QlZ1gZGU0dIjlaEVUlOSscHhM0NiZXSEosIkJTZFRlVyc4KD8IX/xAAbAQEAAwEBAQEAAAAAAAAAAAAAAwQFAgEGB//EADIRAAIBAwMBBgUDBAMAAAAAAAABAgMRIQQSMUEFEyJRcaEVYYGR8BQysQYjweFCYvH/2gAMAwEAAhEDEQA/AP0jSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgI2pahb6VpdzqF0xW3tYmmkIGSFUZO3fsKwg8uPBZAIuL8gjIxYy7/wAK0vHnye6//sE/sGvH9C069k4c0OGAFpbm1h7Ic2A3MABv3VxKTisIv6LSx1MnGUttlc3Y8uHBpO02oH/cJfyr78N/BucdrqOfq+X8qylodRt9Zt7GG4tp7iXnKtHOSg5M84YkAqRynqKupF1a9u70Fo19wYM0ay4L+bnIPeMdB6a8U2+hdn2ZTi1aqrWv/gsfhv4Nz/ltQ/AS/lT4b+DT0m1A/wC4S/lVbHaand21kqOvJdr7ot42nJJ80E8383CtmpK3NxHbS8s6FIIRM0sUvMChONvTnuODXLqNdCtLRQTtGd2Sfhw4NHWbUR//AD5f00+HDg3OO21DPh/J836akpb3kT3UQkHNb47Vmk6EjO3jtXF9NvFuJDM6w8pEfO8uAzEbAGuHWmv+JytJDrM6Phw4N/ptR/d836afDhwaR/ldS/d836akW9xLdWkkLycpV8uuTkHoeldkkzpHyczsO4gnp0qN6rrYPRWdnIhHy48GgZMuo4+r5v00+HHg3vl1L93zfprjLdyqxZWOB0GaW9w7oX7SQk483m+LvvUcda5cRJn2a7X3H0+XTgsf57Uv3fN+mnw58Gf02pfu+b9NfZLd1RXikZlPzebcV2QSNnBkZT6Sa8etlF2cfcPs5Wupex1fDlwYP87qX7um/TT4cuDf6TU/3dN+mpbTEIOaUk9SoJz6s19tuaYh+ZySQC/PhQPQPHpUfxBuW1Rz6kD0aWWyGfLlwaF5jJqYHidOmx7NfPh04LzjttSz4fydN+mu+4UTzyn3S8ihuQBm29XhXQ9xJbSANKw7wGJwajfaclJqUMepJHQKSxL2Pvw5cG/z9T/ds36a+Hy6cGDrLqf7um/TXeupmSTCI8yjv5yBXZfOstrzqHUjrvXT7TTT2K9vzyPV2flJsifDpwX/AEup/u6b9NPh04LH+d1L93TfpqGs5Uks7AD/AEjRp3kQmOVhjrvVX41bmHv/AKLPwj/t7Ev4deCv6bUv3dN+mvjeXfglFLNPqKqoySdOmAA/q1XJMQ2C7Z9ZqDxhzPwFrrc5x7gm6n/QNSUe1nVkkoe/+jmr2V3cXLf7Hrul6jb6xpNrqNozNb3cSzRllKkqwyNj02NKp/J98m/Dv1dB7ApW8YZy48+TziD6vn9g147wdq6wcO6ZbXL9tDHHFIsYbDrsOZQ3UAjf0EV7Fx78nnEH1fP7BrxLRrC3t+GtIuEjCvJaxOzeJKivHfob3YkI1Kk4S8jY3N9Dfah7tgt5DOtjPbm4kZFlZnGFZiOvKuRk7moEuvvaXt1cm2mMtylmjL2gKkwsOc+jmUYr5p09pcytp4lHaXCMF8OZQWA+3BH21U6wjrqbRRkskA5kUZJZcZH24I+6utt0bcdDTdV0prCXt/6Xja/bzTWTSWNwqWtzJMoilw6owCoqkd68q+g4rm/EMOoandxyJdRR3NmLRirIs7MCGMpHxcnGMeiqS0ukW2eQJmM4aPqWxnoSepG9diTrf30lw8fKGQrz42Q5BXf7MVzKLR3LQUkrxja3z+dzWyav213Pde5mHbXaTOpbqqqymM+sN/GrI8RLdKGlhlEYmSVEQqThdirZ2IP31jo7v3FyCaZcySDYtntB4n/HepMshVCyuFZ/OAyKrSukUPh9Ny4LaNgsZuMBDPM2FDdDnp/EVLhX3RISVcMcHcmqfSZFtoo2d1z8ZGcbHu2HjVy2ovBbtL5mANs7mq6hm7I5wk24o6p1/bHcAjYrjcV1xoouUaIKzqOZlyc49QquF3cXNyxI85jscbAeNTrSIwIwQqZj3npXMVFyJ3Bxha+SZI0jhXityhzjmzscDcYNdckmJcNLzbYLkYxneuMEc2cuVGOuMn+2g7Oa5A5clgSHz8Uerv6dDXlSDdkVrbDtm7MiJAe0c5J+aAB/GlspRti3ZRAks3Ude6vrzyTanGqQiQLHzKVA5Tt456/fUfUJo7V5hJcu+Y8KkYC7AnqSO89/oFUqtPZLe+Cvff4epBjvnuZ2LKCz9QFAyO7p3+uu1pHngKFhGnOASxyM+j0+qvkMKQac91zqWdSORuoGcb+muhr1IVhUsABk74ODnFZcaLbvUlyXopftS4NLbaUDAmWKMO8Dcj0113YMQMRftF9I3rtsdRjuIwkMvMcb9xqi1dp/dLHDgjxq/VjCFK8SlRlKVXZI43KuX80eb6RXTh41OVxmoyXxVgJXb11yvbgqN2OMeNYrin4jdimmos+xAmXJ6Vw4uhPwf68T0/k+c/8AAak6dEHQN41y4xTl8nnEG3/d0/sGtjQ0LWkyh2hWsnFG18n3yb8O/V0HsClPJ98m/Dv1dB7ApX1J8icuPfk74g+r5/YNfnjQb+4ubHTrJrt0RLaMKGACjzRt6a/Q/Hvyd8QfV8/sGvG9GiSDg3SbpYVEhsYiGA6nkG9LXPpf6eqKFaatlrBH0y1g0zWbfUZrtTCcqQcnlLbA7fb1qcLKe18puiwycxilBXlzkHCMCKm2dwNZtbl17O3uc83IB5pGOno3GQfTUAXKXV3HM92/uqEMsbN8aPIwTn76sxirYPqpSqVZTU+dri/qsFdpErctxZvIsio7FOY+nff+NV9/fRQPOkMmZoSADsEYYJIPi24A7uvgK6754dPtpLmG5zCjdmCo85z4j0Z2z6DVVpyapqk7xxQRKe0E7FlwTyjAA8Rv0/Ko5xu8FmVOL/Y8EzS5XnkM/K8RjGVYk9mMdN2zuScYq/h1yV4v+kSMEfBGQCWOdhj7z91cEs7r3HcSX93czHl/aKEADDIGD/hXy6hla3t5I41eJcqvIAQp+wdfX/fXT0/mQqipTsy/0otPEG7VhybKD3Z61YTv2aDLZJ8az2nzTRR5OVAFdMmuC4direZGR53ifCq9WhtVyKWkcW7GssGyc8xxncmre3ZZMuhznesxZXDMixk4JG9XmkefdsAcF/NHgBVCMfFYyq1PZdk3mKqxyN/Gq5JmQMyDklyT02GcjIqTqjxRXKQxvzcwycnp6667xWFv2RVHBXKcrdD3b+NQzbu79Cuoxkk31Oa3WUW458FOZckDMbY6kemq+SVyzSzL2rfE5juV8M/cKj9rGlhdRz+dcGDzkzgsCRh8Y37ht35rjLO0cDTQWiIihWKzE88gzjlUZ3/wqvWi5pFZU1Gd4oS3BSF15t2G4I6VEtYxqV4I1cCboo/nbE/3Vx1TVY7kRRw2kUCJ8dxgszHoM9dvD/CqAazaWeolJMy8jZZV3BPgfQP4n1b0u48W2WUXH4o5PQdIsp4eynDgo4DAjwNTuILlYLRJeXmLbVTWnEj3FmrR23JkbFj/AHVG1DXjcWht5VUkHII7qnlKlGm6cWV6VKdWSmlax0sGuMyJg+gd1crmQS2RwDzDvPjVI9wObIJBHgamw38MnD1zJz5khkBwOuOhrPhQ3E1WFWEk74NPoCPJYpI4Iz09NfOO2A8n2vKCMnT59v8A4GnCWsWup6YkULrzwDlZe+ovHNwjcE6+hwcWM+PH4hr6ClDbCNjDqznWrTVuDeeT75N+Hfq6D2BSnk++Tfh36ug9gUrUMo5ce/J3xB9Xz+wa8h4ft2k4Q0WViSiWUIONwPNHWvXuPTjyd8QH/V8/sGsFwho8c/AOhSKADJp8JO3XKCoqraNfsmsqNVv5EUW6ojtGkUcgAIDqVFVz2FxdQmY6fZxo4w4UHnB/nA92K1cukzBOUv5uMcvdUOaCS1jOJAK6jU8z6elX3XaeWYbVbRYtMkmCGKaMAAMmSx5iTjGw2J871VV2eqTXDL2EKxxxEKzEkDJz1I333rb3F46wOrRq0fQ+aN6rbGOzhupDHaRAzryuCPNYeBHQ/wD7FTxqRTwzZo1XCnLdG7OmxjvDdctvcdpFIObkY8wPipz3H7K4XOlvGzJh0fm+IX+Kvobrnp41zk0/UtOmM1phkG6gHm28K6ptRnnKNNGUf51WO9i1k7UHKW+m1b3+pQ6reXcZayN1NIR81gAT6yBk1ZadFFpdul7qKiOGDdIR1ZvE+k9w7hVqsOnTt7tMXLMBy8xOWOPDwqovm92se2gKLED2UZ6VHKSSuyZf3fDayXI0jWZZ76eSccnM2VA6Adw+yt5oWp28M8XaHoD9p8KwOkWcsshndMCPovdn0/lUu+1K90/Nq0caPJgelc9N+6qMkk9xT1GkjWbhHkmm+uNQvyXwoaQ8ztt17jWusX9zorJLEsi9CxDA/wD7fesGssumTTiSSJpEIRlJzysDvjxwV3NXss8UnC8t2JVF3HICyAAOEHVvWBj7M1Q7u0m+pnaunujGMf24X3OUgkSRsApHIrHkwWCdx5sdxBHWqK/1NJbjmRH5U+KS/Xff1ZrlaXmbSOLsLl4ZVyeVcNJuxPjnffB8PVUZLKTsIruMMwE3KFXPODgMOo8MEGq0tzOKVBRe2XJaais1poEOqNPGxdhHJCCUZSebHMO/YDr41VQad/KWn3lyqW0E9oOdlQACQbHbO4Y5+0jFQtZna5ugs1msMMYK7bOPSzYyxzvvUX+Ub82rCCHs4GRY2lLecwBO6n5uckbffmrFNwT4wcyoShGz5f4i10vVpo5bu3uWkmgVQkbxAN2cmR5pIwDtnvONqmXsnuWNGcXCiQ+bzRbH7ebH2VkbB7vTb5UPaFR5+EQkLkbH7VH8KsOKeL9Q1KyisIUUWsZByiYbI6b/AGmpHSozjlZOHCVGMe6XPJZLc2bOpuJJCh+OobkwPDO5J+6oNxqfO0yWS9hauOTlHeuc4/gKy8eozpGFZAPSTmtLw7o93xAoMYCx5xzbVFGi3iCONVOKtK5acEX8lvr0kscBeNYwJCO4M6rn17/21ZcVamJeHNegGTi1nXPqU12QSadwvBJbpLGiOcSXMq8zzMPmRIOoB+cds9M1mtauobnQ9dbmuraX3NKymWNeSQ43XAOVO/pq5TpuklEoUWo97KS5R+hPJ98m/Dv1fB7ApTyffJvw79XwewKVbPlj7x98nXEP1fP7BrN8CKT5OuHj/q6D2BWk4/8Ak54h+r5/YNUfAUYHk04bY9DpsHsCoK3BPQltkWDoIzmUAofGqPW7cSWTvDGRyHp31dX0sYTAJLnotQOxn5ZJBIxJxmF8ZHqI6/2+uqPfdEbdGrsancxsN274s5BHGwPzlyftrvvNFkS87S3hKxsA2CcgHvwfD11c3lnHeck4RRKvmk9Dip/YvJYFFBHKO/vpCtLhmxLWbGpRx5mYKtBbdqsjCSMgOhGxB71P91V+puyz+dCpDAHmA8RV+kAljkZyOVNjvvUENZRIyTzxGMA7SHBFSfqGy5RrWbla5nrazaabtd0j3xn51d9xppd4+Uc3Mcbd1fdU1WxkSGKGOdQozlWA5fRg1M0m/wC0fEM7xzKpKrgMcfd1qzDUQttL86tVQ721ivvbT+Tjcq180Qt2UKsKgs7YzjJ2zj7s1WTaFqV0num5mSSV+kRctJ44AA8PVU7VWlieY3HLHzyc/nL5xI7/AO7HfUVne+uI42uIYJHj5jIrELgjoSBsxxg+rFeNps6pSqJKcZL1tf8AMkK4gltLYG5DfshsCQcDr3VVXmvz296ksRWQ5LkSb7kdfR9lTJLm8nkblilkjt2Cc5UsOuMHP9lTLHTtLurmXQrpEVzcKiXag5diSoG/QA4++o9t3gtVJQhBqqk31t5dSpt+JWubu1gmt41hVWDL3OxBwSeuM8o9G9a2z1CKLhuOExob4Sg5lzzIpjI5mcfGwSMAeGa4XXAWraVC1tHYadfw/GjeQ4lHoByAe/FZa71UussU0Tw3CvhWZSMY6gJnAOwzXLhtVzMVKlq3/ZeF5P8APxF5PLyTKZI2UyfthJJIFMm+CVGN9877VFkik1HUIre4dIpX5Y2eRwE5QNjn1b5zjfPfXy51G29w21zbpy3drGoDvhw+CWHL/NIyR6RgHB6xJrvQ7qznue0aK9PSGVGCk4yCuDtv45qLb0RMoTa4t04/MfmCVqNlJNql21slxfQR8sclwsLIoKjGF2GwAwPEd1VXYgKQRirq71oafAsnYNFLIRzQvNzrLjAy5BB5ipG4xt17qhWssS31sJXjEkmWzOvMFBGVJHeemK5lHxYfIoUnUV2uF/H50KmTSLi+kAtYhj50jHlRfWx2rfcKy6XoWmmzXUI/2aFri5PmlieoQHu/jVZq+jyWWhtq2oat2hmyIkQBWb7ug9AxXnkt3M3xTyodthsfXU8Z907FevoI6qPgl9vM1Wp8YabYXs8+k2LSXDEKt1cEs4A7lz0FZq/1q9vNNu3kmZC8LoQp5fNIO3qNTNI02LUYLqSbA7NPM/8AVVdd2/8A1ZeLIcPFGxH3Gu3U3WKVTRSpUpRT6f4P1t5Pvk34d+roPYFKeT/5OOHfq6D2BSrh8AfeP/k54h+r5/YNUvAMhPk04aXGw02Af8Aq68oHyccQ/V8/sGqLyf8Ayb8OnvGmwY/qCq2odkjqJZXViZbguh3xsKW8W4VxuKkXUjKi8gIIHUbfZXVFc9FIwayJuEZ4L8G3HJ0z2RtJjJFEJI5DkrnofGuYCOhJUj0HuqdkSxY76j9mUbB769nN9OCSNVvkpLiytxM0nIQp6hap59Ks5ZeYQqxJ2yN60V0hDNH1GapriF4pAwO2aqOq4s29NNrKkVl5w/p0y5WExsNm87JJ8aqns59HkLWpKAdJBjOcdM1p5pFVhzgqWHSqPVradLoFxlWGUOOoqzGsnlGpp6s5WhN3XzMPrGoT2t6qkc4Zctz78wr7qk9klvbX+mzyKk+Ukt5cM0TqB/WU52JG1T9ajW5kjSJFNxCCo5lBBBG/2+FZSO3eW7S2wVkdwm46ZOKtQrJo+toU4VIRm8befmvT3LG3uWtkkD2q3LNEzcxyzwd3MBnA6jqMbirnhvUtNvJobS5kWFppo5LiWULGqxxsGVEx1ZmAyxxsKznbXF3qkkdpIyG8YW4AOOZSQAp9Gy1vLvQ+FNBujpVxoN9qogPZ3epJcFCj487lQbYHpqzTm5cdDN7Q7tJQqRblJX8PKt6tLnhLk0Orcf2tpLNGmnzXcEa5MwGUBPTevP8AVF03iO3nukvEgaBS7OwKozdy+k9QKt4tC0scMW+pNxK9ppjXE8EC3MTFnAPxeVT84df8cVGh4Ym91aVp+lzJNFxJF2vu14hiJBkuoTOxXvOfQMVPKd42kZml/S6ZPY2mm8tPpze6tdJN2RjLWa4tLlI3It1kQBjyBgyncNg7E4Oxqy1XSby1hCntZrbkDGRoBlQW2GfHcd/eBWlbhDTtN0iz1C71iJZJImlszPBK0EqBjy80i5CZG/Jk9avdW0uLiPQdBez1VZ9S1Zzstu0cc3Ky5OPmCMKR6etV+6W218k1XtWjvg4K8W2m7O2L/L19Dyi/hkjcwOOZRlgcZKjPj+XfXGYSTSG6lbmYEKzDcjCgDbw2r0mHg3SL2fVbmx4htbxLRXnlt47UoDyDopPUdxI239IqdqHD2kJ5S7XRILIvYyyIs8Ct5oVkB3IJbAPTOMcxwailSksofGKEXtim2k28W6Jvmx5b7qa8vrd9T7aSyiOREjblfAE+PjVjr11Hq9h7rTRobGGJgiiF2GMjzVORue8kVptI4Vs5LriSDUbMFrJoTApcjkV5+XuPevj/AG1dP5OZxxrfrd6Xctw/DHcPb88h7OPCeZg82eua8UKjXqe1e0dJCp4sOKvzh3SdlnLdzyC2me1bKsQD1Ar7qlyLrTbl+UCRYmBOMZHKa9PvNO4PttW0fh+50OaB9Us7dzqFvdNzJJKMZ5GyMZ6+uvP9W0KXRJ9ctLoCUWKXEBYDZ2AIDDwG4Ofs6mvIxlFpck0+0KOopTtFx8LavbK4xZvqfp3yf/Jzw79XwewKU8n/AMnPD31fB7ApWsfkx98oHyccRfV8/sGqHgLbyb8N/Vtv7Aq+8oHyccRfV8/sGvMuE/Kdwfp/AuiWN1r0ENzbWMMUqNHJlGCAEbLiqer3bVtVySmrs9UjYFTzAGuCRpzkcgANYSPyr8Dq2TxPbgf+3L+mu5/K/wADIv7PiS1ZvTHL+msxRqNXcX9iw2o4TNs0QQ+Yces1X3huBgoA3qrIt5YeDf8Az62bP81JB/y11HytcGDccRwD/wCuT9NRTjN42MmpbU7to0PuxUl/bnlb01zuOS4iyoBI3FYy88qvC0txmPiG35MY3ic/2pXCfyocJvEqJxFAG72McgA/4ardzUeNr+xoxnBNPcl9S7e3mMrSSjp3HrXTeXDTW4MiZ7PcHvx4VUJ5Q+E5NpeK7PlxtmOU/wDLUCTjzhR5ynvjtTGPnckmD9nLXq09eHEWXoaqi5XlNYIeoc66lJIEKsDnBFV19H24hvljxKT5rKOjA9PScYq1fj7hSF2Ya3DdcxI86FgcY7yV336VVXPlH0qydk026tXiJz56s2/j8UAfdVmFGcf3J/Zm5R7Vpytta+sklb6ldqFtNFdNcxqsbRsMNDuqsADtjoe/HrrdwcXWJtl4nvNGv/dFy3ZXHuO6QWtzIoG8iNuuRju+01g/fvps+irG15FFf20qmKUKwLpk7NhcMVO4J3wSM13e/PRH0uey90wQQXU8dxLGqsApxyuBt8X5wHgcd1Xae6PCf2Gq1em1UIqpJXi7Yl0xfr1w/oTOJuKLTV+H7PTYdMXT57a7muJY4WBhHP3Jvn+6rrQ9en0byQ3k8iKJmuXtNNlPx07RQZuX0AD7zXmNzrNk9w8jXscjM3VQd/4UfX4JLaO3a/doYiSkZLFVJ64HQZqDvK25y2v7GlKn2dOhCgq0dqlud5J/NpZ68eh6Zw1xxpOj6ZGFh1ZbqCFw9p7rDWd2xGMsrZI65wBUXTuN7TSNE0MGzlfVtGmleEKwELRStllbv3UnGOmBWETUtFGl8zX491OxUJyP5mCMHOMYI5s+obVDOr2hO9wPXyn8q7c66ivDn0IVp+x6sp3qLLz4vVefGWer6TxVwhbXGoR6XpF7aS6hZywlp51McRbflUZyQT35zgACqfV+Mba847Ti7TIpITE8TiC4IzKVUKQOXONv7fsrE2Wp6IZlF7dTohYZeFMlRg5OD1OcfxrmuqaRGkyJdx8ykKjdk2HGRk56jvOP410pVpRV4+xA6fZtGtKaq7rqzvK+Hz+dD0eXjnSbUX7aHpWoi61G4jmvJbiUShEDhiqY+4E+NSodfifj671qE3rR3kMwFnJKjSczryjCKSAoxuSaxnDXGGkabbXVtdTRuLvbn5D5pX4pbb4pyfTtXbPxtZR2ctrZ6lDYL2hKpp9qYY5AMgFnKlz44OfXUy34b/gya09KpSp0msq25yvdO38WwbjV9b0HTLvTdem0y6utas4UsoYZJFSBZI1xzkDJ25s9fD7PJ+J9Ru75tUku51nmlLvK6nzS252Hd1qx1bjLTr6K2HZh2jIYgBwpOwyRjOSF8fnE9ar9T1bRJbCdbd4jNPbSedyMMORspBz6ACD1ySN8VxNTlPCx6E+nrabS6duUk5OLX7k7eSWcL+T9TeT/AOTnh76vg9gUp5P/AJOeHvq+D2BStU/PC+uLeG7tpLe4iSaGVSjxuvMrKeoIPUVSe8PhLGPezpP4OP8AKr+lAUHvD4S+jOk/g4/yp7w+EvozpH4OP8qv6UB5B5X+FOH9M0DRJ7HQ9OtmOuWcchitkUujMQVOBuD3it/7w+Ej/wCGdI/Bx/lXnXlWvr3jTi2w8n+ixBnhlS7u52G0RG679wUHmJ7yVAr2OJSkSKzcxUAE+PpoCh94XCP0Y0j8HH+VPeDwj9GNI/Bx/lWgpQGf94XCP0Z0j8HH+VPeFwj9GNI/Bx/lWgpQGf8AeFwj9GdI/Bx/lT3hcI/RjSPwcf5VoKUBn/eFwj9GdI/Bx/lT3hcI/RjSPwcf5VoKUBn/AHhcI/RjSPwcf5U94XCX0Z0j8HH+VaClAZ/3h8JfRnSPwcf5V994fCX0Z0n8HH+VX9KAoPeHwl9GdJ/Bx/lXz3h8JDf3s6T+Dj/KtBXGRS0bKDykjAPhQHjvkv4K4a4h0LiE6podjdBdfu0j54hlEUgKoI3AG+3StkPJFwECD717Hb/RP51i/JbfX3BHGd/wBrUY5rqV7u0uFG0rEZY57wwXIPcQwPdXs1AY34I+As/9l7H+qfzqzHAnCYGBw1pOP9kj/Kr+lAddvbw2lvHb28SQwxKESNFCqqjoAB0FK7KUApSlAKUpQFfaaFptjq99qltaJHe35U3E25Z+UYA36ADuFWFKUApSlAKUpQClKUApSlAKUpQClKUApSlAV97oOmahqtjqd1aJJe6ezNbzbho+YYPTqCD0NWFKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAf/9k=</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 85" Crystal UHD 4K Smart TV 85U8075</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAAAAgIDAQEAAAAAAAAAAAAAAAYFBwIDBAEI/8QATRAAAgEDAwIEAwUFAwUNCQAAAQIDBAURAAYhEjEHE0FRFCJhFSMycYEIJJGh0UKxwRYzUnKiFxg0U2J0goOSo7LS8DZDVISTlLTh8f/EABwBAAEFAQEBAAAAAAAAAAAAAAABAgMEBQYHCP/EADERAAEEAAQEBAQHAQEAAAAAAAEAAgMRBBIhMQUTQVEiYXGBMpGh8AYUscHR4fFCwv/aAAwDAQACEQMRAD8A+kdGjRoQjRo0aEI0aNGhCNGvGYKMnWCu5lx0/L/doQtmjRo0IRo0aNCEaNGsXfp4HLYzjQhZaNYRMzL8wxzrPQhGjRo0IRo0aNCEaNGjQhGjWLv08AZOM68jZmX5hj/HQhZ6NGjQhGjRo0IRo0aNCEaxZwg7E59BrGRz+FMZ1j5YLdTZOewPfQheANLhnwF+mtqrgYxge2vQvqf4e2tc9TBTKGnmjiUnGXYKM/roQtujXgYFerIxjOdCsrfhIP5HQhe6NYiRScBgSPrrUZPMcqrAr2+U5IP10IWckpXhRk/y1isfOX+Yn01hG8KTCHzIzPjPT1DI/TvreGUN09Q6u+M86EL0D1PfXusRIhXqDDHvnR1rgHqGD650IWWjWuaeKnUNNKkYPGXYAfz1sBBAIOQdCEaNGg8DQhcd1utDZLZNcLlUx0tJCAZJZDhVycDP6nSb/uz7Pe6vSRXJHiRQxqhzFkgnAPfPYdu5GpLxHkkXYN0lTp+5VHGVDcrIp5BGO2kHcO3NuWPfNV5Qgp4JaMT1QBMjZJdWxGOx6Sp9AMZOkJA3T2RukOVgsp3Hibs3oMjX2Bx3yFcj+7WFh8VNt3tKbNQ1JPVuscMUynqctjGCOO5xqnLzZJq26VFRSpRwU8Y6Y4EmyURRgA8ctxk+5J1hRXKe32qmoJkkhenvNBVjJK/J5gBUj25Rhqs3EW/KQuhxPA+XhPzEb7IALh2/xfTmjQNGrS5tGvC6rjJ5PbSzvKG8u1oNnq66APXRw1QpVRsQtnrc9SnGMDn6+ulaK5bqN7taVSX2FJK+o86WKkWSHyFqGESsAuQWXB6sgBRnk6EKzutc4zzrS1SDM0SOnWuMrn5hn1x7aqez3PxBqbbEsiXFbm1fCrirpcQiH7wtk9AwpwgJUtgEHOnPYS11bZvta9W6aivU7ypMs6YkWMSt5anHBwvTyO/fSpDfRM6R9OM8t7e2toGPz0cDXudIlRqhPGvblc2/KTctbaG3Nt2nojDUW+KbEtMT1ZmVPXuDnB7c44Or7zqud6eF0l93hT7qsm4Kqw3lIPhHligWZXjOR+E9jgkZ/L20ISJc7zZbT+ydWHbt3rrhSS/ukT1mFmiLyDqjIHbAz29DxxrZ4LU52t4s3zbRdglTaaOsRWJPzCNC2M/WRv4aZ5PA60P4b0ezVulelLT1nx00wRS08mCMEHgDB7D2Gp9tg0o8S4N8Q1dRFVU9J8G1MFHlyIARknvnkf8AZGhC+f8AY91awbqn3QWYRT1d3pJGLEjKwCaMfxB00eAtFJavEuqoWZ1km27T1TliSQ8nluTz6/Pp1qPAKz1WzZ7A13r1jmubXMThEDqzJ0FBxjpI00Wjw5t9n39V7ngqpmepoI7eaZlHlqiKigg984Qfx0IXz9BYaTam54KXfUdfRVct1+JpN12+bzVmP+g5OcLnk/2h6jHOrEvUh/31kS9R6Tt9zjPH4ZNdafs80aILZ/lPcTtsV3x4tXlJjzO3+c74xx27fXnTHvHwsXcm6qbclsv1ZYbtDTGkaaCNZFeI546W7HDEZ/L20IVNWWR/95pfX626hX98nP8AnYtcFzZ7Rtuh2u00rG3bioqynLMcmnqYesDPrhgw/M6vKHwes9P4SzbDirataSdxJLU4UyM/Wrk4xgfhAx7a5dx+CVn3FeLNcZLlXU01rggp8RBemcRHKlwR379tCEmb/oKLcf7Qk9tvtJVXW2UNgepiooCS3XzyigjLc+/OB7aevA2pt03hlTparhca+jgnlijevjVJFAIPThWYdIzxz6627z8ME3DumHcltvlwsV3FOaOSalVXEkRzwQex5PIPt7am9k7PoNibWhsVsad4YSztLNy8jtyScce3b20ITJ1ggkc49NasvKcArjg8c6wJbyzIAepD7d9dAAxwMA84xoQlvf0HmeHF/RRkihlbP1Ck/wCGqk8UYIjuG33akqEmNXRxu4Rg3QU6Rk49CGXvq97jRrcbXVUTsyLUxNEWUcr1AjI+vOqrrvBJZ9xUtY1+uVWZUK1c08nzsqlelQVHbHVwfXHtqKWPmNpaHDsc7AziYC+hHcJBm3dcphIMQRCQksEUjOVZT65/tE/njXLFRpLs691fWGqqY0zxpkZ6VmVmPP0XjV10/g/tOAANT1U+P+MqX/wxr20eE22LXcqyoNvSaOV+qKKX5ljGB2zz36u/vqvHh3NdmebpbmP49DLhzh8LFkDqs+nRPCMHQMOxGRo16oCqFUYAGANGrq5NUR+07VVFLQbbaCqmp+qacHy5CnV8qd8HXzx9sXMvj4+sJPb94f8Arq/v2qc/Ze2cDJ8+f/wrqkNlwmTfViMnQR8fT5U8gjzF9NNNDW1Xk+JcAutxR8vcqtOk4YGpfP8AfrVJfLmaktHdKsJnOPiXx/fr7X3heNu7MsE92udHTdCt0RxLCnXNIeyLkdz/ACAJ1AbD35Y993y4WyDbgopKGNZHaZImBy3TgADTr0pLlo1a+UKa9XSeTykr6pnY4B+Jf+utdTdrvRytG9zrOoHn96f+uvqjafiNbdxeIV421JtyjoEtYnLVZdCGEThSSOgdIOc9+Nc9m8S6bd++J7JtvaNPcKGBvvbnKyxxqnYvjoPc56RnLfT0ZfmkDB0K+YIr1cynUbnWn/5l/wCutbXi7A9bXSuVc8D4l/66e/Fhqen8VdyU60sYAnTpKjGPuk9O2ovxJ8PqnZKWhqiugq/tOBp0EUZToA6eDk8/i/lqGzmICNQoGnuFxqiBFdrhz3/eX5/nrNLrdI2Ia41eFcKeqd/66fpfDKo2nVbcWevp6r7dUNH0xFfKz0d8nn8fp7amLz4L00N7e1z70sdNdallaOllVkZs/hGM+uNQ5nlxb0TAXFxBVd1dfXSzwwRV1UhK5JFQ46v56hq+tu1JUFDda5c/hzUP/XT8nhndp/E2j2fVyw0VaI2lWfBkjZQpYMMYJBwRqbuPg3FfrpLaqDedjqLrThh8H8yv1L+IHvjH5aIuYKJSAuzabKp6S5XWZQpuld1E/wDxL/111XSW90iwTNW18cE6t5T/ABD4k6Thsc+h41qmtlTYbvU0FfF5VTSytFIhOelgcHnU7uh0bam2mIADJVc/9dp7Hu5nkgyfNKTXa7qOr7UriP8AnD/11it7uxcD7Trf/uH/AK63VkAhhU5DBhkY0z+DMdvm8XbKtwETJ1uYVl/AZwh8oH/pYx9catnROjkLwuWq254gUVq+1aqg3BBb+nrMz+aFVfc85A+p1APebpHhhdKxh65qH/rq0tl3LxLm8ZKeCuku0lRJV9NxhqOswCHPzhlPyBAucY+mNd+4rtZdobDhudisFkrzLfq+Gmnq6VZgsCuSAB6jAABOcDtpmp6qSrVSfb9dK3SK+tRMc4qHyf567Ke8V7HyzW1ZJHyk1D/11dsW0do0+5b7uN6Cio/JtNFXxUrUb1VPTvP1dcnkIQWUdI47DJOlTxJj23VbNtV8oDC1yepaL4mjtMtBT1MYHPytletTjkHkE+2mPBqrRRGtpHq4r9RWyluVRUXCKjrGZIJWnfplKnDAc+ms7lad426Oslq4rrTpQGP4lnmcCLzOU6vm46vTTLuOCpufgZsdqanlqCtdWRN5aFsOX+VTj1Ppp58TCBZPEhOOpJLQrD2PQuRqZjtACoy2tbVCfa90Hevrcf8AOH/rolut1iCk3Ktwe37w/wDXWC4I5GddflRTwCMoMg/w0t66FRh7rX1/4JzSVHg1t6WaR5JGhfLOxYn71/U6NHgmnl+DW30/0YpB/wB6+jQro2SB+1FIIrdttioYebOMH/VTVG7QjjO+tvMpwWuVPkY4H3i6+hf2hLO17Tb9GrqjE1DAsCfSMcAevOqQpbTQbV3XaJ6yWuK01XFOzCnwnSrgkjnJ4Gq754WuDCfF2UEg8Vqwtz3TcV+8Xlud+2Xf7hY7PO60FDTUzdDsrcSMSMMGI6vqAo7Zzq8FL1PSeJNzlW01lSbrL5UpjXPwgMpbqk9gO356slv2g/DtXIN3qQQe3wUv9NQm2N8+EO16+suNnrqqCauBeVpI5mDDq6jgMOOT6akIF2h48QNqrKHbV43d4tbvs9nrFpZJpawzFmIEkYmz5fHu3T/jqyfALdNDRQ1mx62kjt94pJpH/D0tU4PzBvd17f6oGOx1IWLcfhNZb/X7mtVRUivqvMNRJ0yvnrbqb5D25HtqLum6vBW97pTcc9VWx3aNkcVFPHPCepfwt8owT6Z9RpjXMvQobQNgqq/GhgfF7ca9j5y8/wDVJq2PFys2jRWza7bnsdbdX+BPktTVXk9A6U6gRnnPGqS8T71Tbg8SLzdrYXmoauVWjdkKlh5ag8Hkcg613beV53p8HT7gq1kFFEYoD5SoEQ4/0QM9h30wuygkJrn5QSrt8VZYTdvDV6ZGihdkMaM2SqlocAn1OONQPjDSVVV+0BbFp4JZjiiwEQtn7057aTrved4X77Lq6lnngsvStI/kqvlEdOM4HP4V76YKDxS8RrqJo1v6wumesikiBUf9nUJnjALnHTRNjka9xpWPdJEb9q60KrgstqbIB7fLJjW2xRbYn3Vuq8besbS7stM0/wBzNVtidjkFlHIXqOR24yPfXz+L/uSwbwbc63KR7p081UoEjN1jp5Dcfh7ccak9rbludu3FW7mS4vDcahpZGlES9MvVywx25PpjjGRqXmNyc3oldJTvdQdXLXbm3BXXKvQJWVVQ80ihekBieQB6Y7fppku+1ay6bQsQp1VvISp6gfrNrru247ZUVjVa0sr3CrPnNKI1CO55Iwvqc541LXO8xf5K25nnSnneKby4gMeYfOAIOe2Bz+ms3nvLnOaq5zkmh92qbrrVWUUjxzL+DjAOQNcKK8bq69SsDkEcEHTjTXS3qAlW8cjs56jn8I/P11pjrGse5oK+11EYqaWXrikwrgH3wcg99W24lxdThSnYHZfFus6rxM31dLR9jT7juE1LIPKMfUOuQHjpLAdTZ7YzzqJutXfKK1xbYuonpoLfK0qUc8XQ0TuMknIzyD66t/xB3xuE7O2dCayIJfaMGuaOnjVpG81RkMBlDj/RxqZqfDuy3nxIv1PcrNcb3KKtAKyS6MnlReUmesnkgHPPsQNWnOAFkqX3VHrvrc8N8prxDeaiG4UtOlLHNHhSIl7IQBhh+YOte4N4X3d9Sk99uk9fJEOmPzCAqD16VAAH8NXRcPB3as12rrrb4pWsVBBGkdObgsPxk7MckzSfgQDA9ye3146Pwm2pW7w24AogprjLPBWWtLqlU8ZWF3R0lTnpPTyD6499OokJaJG6qnb2+90bSp5aew3uooYZj1PGnSyE9s4YEA/Ua523Nep6C50Utxllhu0qT1gkIZp3U5VixGcg+x07nbuytwbI3BXWCiuVvrNvGNy9TUiYVcTOUJK4ARuCcD+eq9qKXyZlER6wy9Q/LQd6UTiW6L2miPUuex1IPA0XVUkoqd8Z1HxVYEPbscEa2wqa+sjh6mKk5xnjTo2h4pyqEvabugvsLwUbr8GtvMP7UTn/AL19Gs/BhQnhBYVHAEcg/wC9fRqT0Wq02LSh+0PXT2+isslMxSaXz4EYcEdZiHH6Z1Xa3CzrcUkr/LZammaMIV+XKA/MBjgknGn39pCemgpduvUqGzLMsf0cmMA/oM6om4JJFuWBm/zbKVX6HHbWPjImvk100Puqk41UStnqbdVIt1p2ipnBMcgAZTwSMMOCDjsDqUtFspa9akhS8YSRwWB+XgdPTj1J45412bfn+BoY7hWUbsJWdYQU6l444BznBOum5VJFL5lvpaimiZRH0EZUNnLHn39B6atOlo0dFSfO51tArVLsArKS7zZpTSPKvlFSchVPBOTqWqLJb7bRRS1EZq1Z2hkXJRkYYwR9MHIz/jop7NcbvE1O1PKXYGQSrw57evqNOO3fDepeoigrJXVGKymKZTyB/wCvpqnLjImdfFomPkNA37BVi1C8kxFO5WM9gx5xqVtm2WrGQ1VRFErgkO3JGPQ+ursuHhZQ1kMFdTBKOP5hKBHzkHvkeuuCt8OaH7NeRKmsE0JBzIFKkegxk41AzFGZuhy33TH4l8Z1bYSBa5JttCpjJMsrwnyS/wA5hJPDYB6c8HHc86zttRdaae4+S8EjHy5pnQ/P2YggEc98kfTViVOzjWUtKHiSkq41VA2AepOPlK9v7tRV02Pb4SUqWjLsch426GU+xBByB7ZGq8uLw7LZKMydhXyynO3T1VfXl5p7dUTzRxSrMVUcghFC8D3BAA98+ms6yW6y7LQRWyBKEoR5iwFS2MfMGPcHq5+un/8AyK22tKkU1dIHY9JBY4zj1PONQtDt+lpnkpNx3Gq8tpWQxJH1oqIMrKGB4QDjt/dqzgsczEsdGwfCL1G48ldfHRAvUnuqyjRly5R4pwVZHjJATA123W93i82+kpqyoWeKjDqjgAMetuo9R9edWZuHZ1if92tlunpTjBInLEkZHzAk+oPtpVqNm1UVPF5Ik4yOYyV/v0ox8TjrofMJzjy/iCR1pldenyyje/cHUpBRTTUyxUtBLUsoyfLAYDJxyRyOe356bbfRRwfJd5lqGIwihT5ignAPPZc8ZzqTtFDaIXVqWCKFZo2EjlywV+cdY6gCvBPI99PONZ/0DQ7K1Dg5ZBmaRR7pZv8AU7irotv2+42c0cdgjFMvBJb5usFxnj8J+nfVnWnxaq6W+3BK+y0brcneaqcdXTGyxgCLPqB0HP1YjUXHAGRqGWf93ibzahEk85GjQluocljgdXykYHOSO2u24bAoqy3SzW6As2DI0MvySqgAIYtySvHYZPPB9NaLaxMdxGvle2irzsmgcL1S5W+LtTcoSILNavJnPw9TaJIWkp6pTyr4zkODxkfTRRb5q7VfrfWwWC1W/wCxkkalo6WEpCnWpWQu/LsxyPXGdbDYLbU00F8tFNUxVSOj/Dwr5kfckkSH5vTgMM+mu/b1oFTdkguMMiGrkeTy5FLLErH5V7A4yxP6D31aijc12psLOfjhlyg66LLYe3Uqdq3+kol6heKaOOZJAQ4GSyuPTHUTxzwB76r6+bGv1tgmmlppHEUzQtg9RXp9ePwjjudfTO1tr0tgeOnoaqXqbLSF0z5nsM4wAPYagN07qtxiraOOgeImXy/OVxGSQMZIIOR9D31JIGk2NEj8RyIw6V399V80wwASGINnpXqb0JP6+mtXnlKyMxgjpGeOM6cp7HDPXmWImUoCclQv/wDdQNbaZIWM8DhGQ9yMgjvjVHDuLpSwnYWkjxcUovqV9Y+CuT4ObfJ7mJ8//VfRr3wWLHwdsBbHV5Umcdv86+jVtbrdgq//AGnaaWppdrxwgmQTzkYGf7KaR6DakKRC43GRjMYVpumMdaw5BHWzehxj8uT7au3xLt1JdNwbfp61OqIRVT4xkEgxdx6jXDDQU9JTeTSCHCNn5skA4x6643j3EzBKIW71+vmkI11SjdtlCqpaby5E6ooRHCUHQgz64HbsMY751EV+0II6DzZ6+oFUnDiTGVA9Ao1ZcNBCY0CvPGI2JC056EUn1xyfU+2oSphtlJUyQ1Esjv6Ozxuf1zrCilxDWC3rOmDHOsBLdmrKOmpSXhkmV3VSF9FHrxz3xpxguNMOirE8UZhAAQhgxUenUe/fOky/QWioUtHVU8cyZYYPLfTjUc17itE/k1QkqIFA6cTjDcDJ9++nNjfL4o7s9FCGOvLStNdwU1PMwrYWhppMOJjyjD8vy+mvXvNVVI72SmSvhZT0/Jhz+edVBdd7VktPELNTSU0bP0SZUM7HJwAScc4x27n6axtqXS7GskFW8SdRRkSocMuSCelWPzYyR0kcAE57a1oIJmNHOofr7q8zATSCs1Dy3Vg2++x7nmuVDdauj8sRBwIeWgcNgq7YGGB9Oex51HXS61EV1qbDfj1QOyinqo1ChGPbJHAHfg+2ue0WaOhnjVpIo43UY65AQw+Yr1Zw3Yrgkc5x31IdbUs37rLLWRCTqNNURhucYOfUDnHPOtjLDM4RublJqux/tUOI4OXDs50JzNA17jv6j9FD0tsuk9zU09TC8BfyTOZAFK56QGQ8+vf6607ltlzoKlGph8bHSiRYAyK7p3yMD8YPBz+WmCn2kt4pKla8Q2+CT5ovh5AGBzkKQeWGfr6a22VLjt40lFW1sUtskZ+oz/O1Pg4BDjlQeDzkDWsyHkOIDbvra5iGV2VrmmiPqq2ppqi30yER1FWQoqnYzYMWcgjOc9zznsfT11puviI8jiOmQJIpKqpQ5UemB7euT76tfdFooZaY1NZDHPAEPXUZ6Co45z2YfnqjbnT0dTV/C00vkhQQGVO45Iz7n041DJgY5GmSUA1r9jVdJwvikk83Je36fuoNa2aSpqJvPmZ5GyzE9JIJ/tZPr7dtdlHXVnxEipIzoMNL1Bj8oP8AaPr37/l9NRtVC0F2KoiBV4ch+svg46jj00x7PkqqS9LVUQART1SOwDqq8Z+U8EEhfpqOQMbq7ZdGC6/Dume3VsMVMvmqhiUZjSEv2YgFcf2lK5PPYnPrjUlLvWSikoaiGSSnovNmZaeI5M8i4PlZUZC4KlmPbOADqMgtS1dyqZ3EHVMDIIwuFXnLgpkAgjkL8pOGxwOYetlpblcTR0Qmq56tZIaWnqCvkzMoCxlEVR0kYyDwc8EnkmrARGLabtWpTnNEUmC0b0q7FQzV81Y1ZUMFEEMC5E3Vl3kkIXHSFz2Jyc+oI04UlzMKW+u+FmJkBdGqW6mjYn7vkkZU88+2NK6bdq3lWOqqxQS1K9Cxr1RpTwxDqcxdK/J83oSGz1ZzjJmrPTyNC1NV01ZFUVgMhFQRJJkgIWZiCo6yCwdSAc/L66nwuOMcgEl5SsbifDg+IyQ6Obr69/dMts3k9/t6pWfd1MTvBOtNMwHy54HSckntjt650n11oEkcyTgl6g/dK0mZI2B5J9D9c6mI7FQU7wRxy+WI386V0BiMoJHCkjJPsSMAd++uv4eghhZY5paicZJkKdxn1P8ADXQvjaDdLzjHY2RxBsWPmlSPaNHAiSSGokaPsxbCuw5/T+Ou6DYPxtMtdK0VPTsw6gGBC541LxL1S9MrdKk4HsOeeNSkJpoB5HXG0Up5Lhvfg8aTSiCa/hUI8XI4guP16/wnDwqplovDS10qHKwNPGD2yBM40a6PDuMRbJpYwwYJPUqCPXFRJo1WO69bhvltvegl7xRSV75YRFNLC3kVZLRnBx91qIt61lFxHXyzdI6ilQoZST/ZPr/PTVvBUfeW30k4RqesBJHA5hwf46TblcGpJpI3byWjYq2Bkk+2uf4jgopZRI8H/FgcUxUmHkzNOi4r7uK3vD0XSCvtsoyvmUo6x9PqRquZ66Fa9jTyvJCc9MkydJP6E6ZLtVJU0jiUM7N29NQNdb1pLQJh5sFS8hCLlgTj8Rb04yMfrpIeHRnwx0AqGA4tK52d4Up/lJQUlgmm+DRxChMiyDB6hjpAz+Idj6+vtqv59zXGdJUnpoZ5ZhjzGiAKkuGAU+wwMAeg1jX1VxSAwVMzujEH5/mBIJ9f+kdcUMMtSHVWLscN1H8II7dI7cZOc99W2wNjJzj+gu1grEOBwzbJ7DUrCmDyu7PLJgnzS8fdAOQfoRkYH9dPluvVPZrZRUtYvmV8jeXLUKgLNGoLZHsQAB9ODpXoqGKWSYKqCOOQpOuM9SlRgjngfQc6abPQ1Swq3VTzyRfIQqjrf5QFwRnpxnvkH+Omvh/NPDen3X36KpNj/wAlYO+1LKyXqCuuFPV1STRKYCJXjdRIrZ6RhiCQpA4wODnuDqy7HVUFoWquitTzWWs6UlcoqmIYGHbo475Bbj340s7S8PvtYTpUSp0NgvUO/U5K8HjAyB276smz7HWy1IjpKpvJUAKijjGOT+vf9dLLgXONNNEH5ehU2FxwkYXObbTp6+y7LBb7Jc6D4yg/faZ2PlyuQ4cepGfTOR+ml7clBUUtwM1LbnpkVgPMjfKt+a9tWNTUa0ESRxRKsYzgIoULk5wAPTJ1rriZEwYSR65H+OtiOx8Wq5nH8MhfGRHTK7D7K+f76twNbHTCIVVLMSzwqTHyc5GFIB9+2uO67Qpa5qd4bDXxMoBYxzdUnfuAy4PpxkauGvoaWjpq2o+zoqpvxrD+HBHYg/qdV1WXSGsMkEhmpOB8jSMPXvkg/wAtTh0TrZta5502IwuUNIJG+hSRR7Dt7ysgnqKCWOURxmpiaIjuVyfwgnJAwx9fbXTRXG12K4VNFPAizI7RztH8xcrkkgdunOP586mKpJxQSyJVsKZM4jdzPFLjkZU/rrju9ksu4LFRQ2mupxXVM3mSoqhHVcEdJA9CSBg9saxOJSQ5GxkGid6K7L8PTTzve8vuhtYOv6rVJOlyi8kQxmldTlmnXrXPyF35xjLjH+iAASARrHw68Oqu47npbo9Z8PTUZaMuZQkqSjP3YQ89eQTjsR68jSvNSXGmgqrO69Ev4ZYp4+3zZAGMdPOCMdyR3400225VNvjW4W63/D1DxGGVWw5ZlBRpC+RlypGc5AIBxkZFaGB9kM2W3iMdFEBzDqFPXLfgt9a8VjtBlZ5y6rTq0b1DJEVZwqkEqe+W6s5IOTjUzsy23k2GnfcRNTXqkCwxy9P7vTr1dKthhk+YqFgAzDCryeBWeUp4JZLaks1Q1OoPlzfMVDYVF6iele59c6sXae6xBVWG1xrDTPPPE87S1Z8wuMjoCeWwZQTwFKjPtkk3m4TSn6rLw3E+dJW3bv8AJME1NWV0XxM9XTNDIoZSqiNivcZ4BHf89ZUcFGkEpMnXk4KxksTxzzgca1Vm4II7Yoq/MqJkZkneoK9asGXIYKcHDOO3AJ6e66krTRQRVwg+aRpOpH8v5lQg85Ycev56utxAMfLcdQuO4jwqWPFF7GWx3Xer6JflqmeviWnowVzlUIzkfX9dddJVxrOaGpjZZZGwSvyleeMY+umRrTR2+tl6pA80hypm5Cr6AD6ajqCyRRblZEY1TxHzCT+FD/yj7+w0pkzNo6hZP5CRjwBV3R2+/kmvw4jMOxqSIsWKTVKkn1xUSaNbdh/+yUf/ADqq/wDyJNGkXqkYysA8kueJdbLQ7hsEsX4jDVqeM8fdarfcm4aqvjnioKB6mSlAaeoRC6wLjsccH8z2wdOXjhcXtk1lljRWklhq4lYjPQT5XzfngHGlTwqvkFgtG6KycRTFIIiIJGA87lsqM9yQf56p4hwc4R7ea0uH/h5uIdJxPFNzsblDWHYmxZPkL9zvskgW+81rQn4OunNSpeHpiY+Yo7lcDkD6aylsF9hGZbRcYwFL/NA4wo7nt2HGdXhSVVjpNy7RFsrYxboqGs6DJIB5YboIVs9j3GDzxqJirvgt6Wlq6amjt9bHU0srJeXrVwyg9R6+EGQP46rGADd33ou4i4qGt5ccDQ2iaqti7SvQeap02O5VTQIbZVymoQyRDyWPmIO7LxyOe41yoixr0qoUD0AxjX0BVbnsotV6enliWo29DJRW8Bx1SI8SKCo/tfMvp7a+fjnAAyT21DO0trxWtbhOIZKHvMQjDa2AHn+lfVdllsNFV3EzvMhd85jbJGc9u2Afz41a1ls9ssFE81XJD1yxkMsWPX2I59Ow41VsNVFBJ5ymeBygj4IKtjjnVkbTrrMLb8RLUs9ZGMBZQuD9Broo6iYGEr5r4pinTYySdvwkuIvYak+6i13vNSXKuNLDBDTuFgpopc4LK2TgD04P6kasbbW8Pj7etS/SWQDzc9hn6+3bn+moyo2ZYd0xLWIFppVQ/exoMr9fqQdclBTfYtppbSzvFKisxwyqs/SxOQVwSSOPmPA9DzqDFPjayxutfhEksjg3/mr7q0euOspVlGRkZwDjGo2R50D9ErkZ/CfmwNcViukU9tipI5BLUKhLKrDIwcHnt31quNvrJsNTyyRtgjB+vvjSxlsjA4FN4m58TjTSvJ74sUZLDz8AnCpjt30ubgvUD2tpoozFI3YFQT+eu2p2zURK0izHIX5Ys9Sg+xJ9NLl7d6eJWkjpx1csWbsffv8Ay0tG7C4/FTYg+CUUD5fuq+ut4qJ3ZOpmYegGANK1HXUq18kdRMaRvMDF40/Ge3zY5/XTRd7nFO8kQaJgWz1JGFH9TpHucCfFSrGGfrPUBKAUcngA+wHfOopRmbb22V0XBmgOoeH0VhUdVUXOrSdJg8agN1zOzDA4GAerPpkYyPqOdO9q2lRT07yyMIJ6hcztN8gP1Cgdvrnn6arc2i6WzblruXl4qJpjIsKAB1Qj5CU79JKuASB2wdOlLct11Nqd4LEekt0iYxt1Y7lee/541cwrGkZh1+ibxUyGTK/b1IXclnp6RhGtDSSooC4Eo6cZ+mf/AEdRM3hvWJUVdbagkNRVksTG/wAyITn5Cex14LPvScgpO0QJ7GVIz+o00Wyg3pbggraammjBHXKzHqx7gqdWJXtGgH6LEwkMzXFzDvvVn52q+r4brTV3XKJ6BJ5REss3EcRRmdWUjguXIP55J76Zto7sg+zo1qKhaeoSQ9CquPMbAQBF7IuQSQMZJydPEm4tr3hRFXSQ1fScpDKgZBgnDKDgnkdxzrjvOz9ubis8KfBUtJHFL1CSnQqVbPIU+ufrkaoThk8XKIrzC6eDFugl5mYO7j7/AJWV4qaippoOqKNJxKAvXHkH259Of012Wmsu6GaoudOkUKsMfd9OTnuR6j66il2terFURra62nutKpDLRXGNS2FzjokxxjJxn3Omuy19bVQuLlb4aCUMWKJL5gOeTzjtnWVFFNE2i7M3v1CnxEOFlkE0dsf1HQ/4u7YTiXaMUikMHqqpgR2OaiTRo2CQdpR9OOn4qqxjt/wiTRrTW8z4Qq5/aAY+ZYUxxic/+DVa7Y3K+2q2omFKlWk0YHlucBZFIaN/zVhnVveNO27xf3sZtdsqa9IWmE3kdJZAenHDMB6HSKuyrpTKPI2He3cf+8mlgcn/AKPVgazpIJHSlzV2UPH8JguFtgfGZHa21vrdk2PpqsqbxUemekmFrMs0FKlOxefKuVKEtgLnJ6D6+utD+JSmgjp1s6uY45Yw00oYYfHBAUAjjnP8tScdgu8lK0VX4Z1Mzf2XXyY2/wBlxqGm2NuSSRmi2NXxDPC+ZHgD8/M00sxOw1+SpRfiDhpovwbx6EH/ANDupGPxZ8muEwsqzKWViKifzHOJGkwG6eACwC/6IX1zpCSLqmLyAoGJYDPudM8NiujV8thbadfHckgFQY4/J6ugsQGJL9sgjuda5PD3d6v1Jta549MtD/g+rDYCaMhs+i5/ivHMRiYn4fAYcxMfoSTbnDtvQHfe/RQIMaMFT+7U5almEwmVEIBxho8r/A66afY+8UYPJtG4tj2kh/8APpmtFqvlCc1ew7xUA91EsGP5vqwwlmy8/l4djHkNaz3Kldr3uSipmieniR5CFDquFPBz2zn0/v1qq46xr8tXAstVBMzCeB5AnlcHhCRhkOcEEZ7410SSXZSPI8ObwgHb76D/AM+spqzcEzArsjcEB6SPu3puCfXl9OkYyU+MLQwWHx+FFAbbV/q7LF9oUkFPm3JSp8zSvLOJlGUIDRDuOfQ9wx9tTFNd6ZpAtNWu7/8AFSHHHt20tUdZuSk8wts7ctQXGAZZ4Dj9OvWxK299ZeXYV8d/9an4/L59RtibG45BorE44hiA0ubqPT9j/KmNxVdTS201dKslW2cdCg5Q49cemqqnqa24VGapfMfPUBIOB9Me2rDnvu4wq+TsC9sw9ZJIMfwD86gKmn3LPM0y7DuaSse48jj/AG86tYd4ZeZZOO4dinuzRsv79UpUmy7ldapwjCCHuT+FANTQ2jabPMEgqklq25MoXPldPJ6eM55zx2A/hPwTbthjVG2nfWCDC/8ABSP5sf79cc9Jfp5Cz+HVzLMCHdaiNC3V+IYD4wdQY3PPGY4zVq/wyGfCyCWeMuroK3/f3WzbNZ5cySQNHTCuHUs6hB5bEljwSR9Ce56fUjixeiNoH82r81ioUylgBx/q++kKOnuNMiCDw8vxCLhY5qmF0XnIwC/v6nOpilvN9hpykmwL27dOMeZT9I/2841Sw8EkEeVzr9ls4vmYqXMIq06n9v33XHX3pLLcIYaplZ5Y2dehcgAE45Pf+GuyTe89Ld6CiTEsdQ/QSU5H8NcjVt6mT77w5uhk7Flen/xY61/v81ZT1U/hvejNTHKOs8AOfcjr0CGXntdYyC9K1RFEyPDBkcREnU3YOvbpouaus0F4vNVI0dNRKsQby6d1ZycjJP55Pb6d9M+2G8+wJIySkfKsfxDh2C8DGQBjvpTh3Td6+ethsWzbkrUUvw0/T5JaNxhuknrweCDxrrpN07ngbFVsvcs+CPlEEQUEfUHWkXAjTosaDByMlBdGet1VG9uo29E81ccTRNKwYyRoGwDk4HPGPp661TmCal6YiRJ5XmAEZMiAgE/zH8dKJ3Tf5R5EWwdyKGymHWPpwRjGSeBjWJrtwxq4h2DdkZxjIaHHByBjzMYz7Y1FqVoyQW01Gc3t/qdPDrnZNMcAfvFVwO3/AAiTRrZ4f0tbR7Ko4rjTSUlWzzSPDJjqTrldgDgkdiNGnLYjFMAKZdGB7aNeEgDk40J69wPbRge2vOoZxnnWt5SCQq55xzoQqX2va77vbxhl3rVR/B2y1yPT0wxzOF6k6V9wOokn3OB9LmEfU3UzZX0xr2OPoxkDI7Aa2gc5PfQhYhRjkAAdh7az41BbxukVn2zUVktyltoQqBNFEsj5LABQrcEntzpeod9R1/h5VXKruMdurIfNQmJo5ZV6HKghSelicD6c8calbE5zcw2ulE6VrXZT6p+wPbRge2ombctno6USz3OlIyq/LKrEkkAAAH3Otdn3VbL9VVEFBI8nkRpL19OFdWZlBU+vKEabkdV0nZ23Vqa41pZyWwuAO2e/OlLbN/u103fuW1V0lO8VskiSLyYynDAtk5JJ9B+muaDdr0/iRU2ypnqPgJCaeF8RmETLGHcEj5wQM98jvp/JdZHYWm81tA9zSdkiC4JGW7/lraFA5OM6XqPeVqqL3W241EMQpo45UmadOidHB5U59CCCDzrni3xaLzbLn9n1wpqimVlQ1AERJKEpIob8SnuD66byn9kvNb3TTxr3jUJtmvmn2Zaq641SyzT0sUkkxUIGZgPT8zjUZe9yVVJZSXkgorjTz0zVMCyiTy4HqAnUSQOGUHn00gjJdlCC8AWU3YHtrzjS/X74sVuudHQy1iu9UwUSRfPHETwvW44XJBAz31ybj3lbKemkoaG6ZubhDClIEldst2HUejspySRgc+2lETzWm6DK0XqmzA9taaj5o2QcZHJHcD31F7e3Cm5LDDcaeCSASsyNHIQWRlYqw44PIPOpRE6Tzy3p9NMILTRTwQ4WFTXhnab34f8AiFWbSuMQqLdcVeqp6tQQJCo7/njgqfYaukL6n9PpoCDIJGSPXWWkSo0YHto0aEI0aNGhCCcDOuZH6j5jdz+Eew1y7iurWayTVqxpIVKJ94/Qi9TBep2wcKM5J9gdJp8QhJtua4RQQvPTymIkl1p2Cv0l1dgM/wCpnqJBAzxkQn0sWkK557gjWUWJB1EDrUlSdI8viJDC8kkNrqKhoVJlAcIq/dtMMFsZ6o06h/rAHBzjnqfFBLcldC1qZaqlGXjapjJLsGKhQOWHALED5QfpoQrGAxo0h1fihBQvNFU2mdZ6YlJo1mjJ6+cBOfnXjlhwuRnUpbN5i4XiK1vbaiCqdpAcsrIBGWWRuodwGCj3+8X66EKculpob1QSUVxpYqqmk/FHIuQfr+f10j1/gvs6WsaqFJURF2GIYpisY4xwMZA/XTC+4a1d0TW1aSNoYmjBbr6X6X/tAH8QB749NKc3i0ILxW0tZblSChln6mjk6neOJpFJUHAz93nAznPSOdWA6WDY1fmqrTFiL0ujWo7LJfA/Zyn8Ncccn94//WmLa+y7Rs742W0pMoqWUusknWFC9gD3xye+dQFP4rW6OWU19DNBTeZjz0mjkCJ5aSF3VT1ABZBk4I+up287pWzbboK6SjmzXugMTkK8XUpI6sZ9gD+emyYmRzae40rEOFa54bE3Vd9o2nR2e9V91p6qsknuJDVAlkDK5H4TjAxgcDXIfDrbp3VUbgNNIa2oVg/3h6MsvSzAehIJ/jrkj3vVPS0s0dsRlqB8iiclgfOWIDHR/wAoHjW874UvQqlIrGreKP8Az4HQzu6Y7c48sk/nqIYg2SHb6KyeHyVWXb03UL/uF7O8voEdcOc5+I5/LtrWPAva79XxNRcqg5whacZRfRe3YaY98bvOz7PBWrSCraecQBGk6AMgnJOD7aXLd4tmf401dowKOaOF2pakTL83Vg5xyPlPI1P+dmBy5ykbwdzsOcUIxkHXTuBtvuUz7h2/WSbQitu350pKqjML0pl5T7sghW+hxqFt2zbteKe5z73npaiStplpRDRDoWONW6/xYyW6sH6Y+usm8WbIalPLSVqXoYyykdLIw7L045zzznjGpXbm97buhJYqeKeOohgEs8brwhP9nq7E9v0P54Y2VzRlHz6/NVHRNJs/0lYeCO2PkC1FxjjY5kiE46ZPbPHoedeR+Bu1PPlBeuZCAVXzgOn35xzzrbN4kz0FtNxrLdHKrCKSOOJ2XCuzDBJB5AXP9O+tqeLdkWnSSOmrJamaMP5KKpCfNg5fOO+fzx9dWZZ8TE7I5xtQRRYeVuZrRScduWShsFhprdb0ZIIAVXrPU3ckkn1OSdSwGNV43izaIKdVpKKsqpAT1KeiPHBPcsfp/wBr6HEzft6fZVitVdS0Iq57vKsVLDJULApLI0g6nIIX5VPvzx9dUiSTZVsAAUE1aNVva/FWqr5Zo59vimaJmTMdUZ1PSEJJYIAB86j6nOme47yt1mitL3ESQi6yGOEqOsKegv8ANjnsPQHn+OkSph0aQ18XbFLQ1VZT01ZPT0kbzTMpiDIiu6FuhnDEEo2MDnXj+L1lQu32fczAnmMZhHH09EcqxO2OvOA7qO2ee2hCfdGozb9+ptyWiO5Uccq08jOqmQAElXZDwCfVTo0IUkyhlKsMg8EHXP8AAU/ltG0atEf7BUdP8NGjQhYQ2ylp5JmhgUPPJ5sjN82W6QuefoANepa6NK2SsFOhqJUWN5CMkqM4H+0f46NGhC3mCJm6jGhPIyVHr3/jrWtBTLXmtEQ+I8vyuv8A5OerGO3fn68e2jRoQtpjQyByoLgYDY5H665TZ7cWdxQ0yyPJ5rOIVyX/ANLOO/176NGhC5qjbFnqqSankoYQk6hJDGgjZ16g3SSoBwSOR667J6Gnq8CenjkQHqw6hucYzz+ejRoSg1svYqClgULDTRRgHqwiAc5znj686wNqoD3oqfv1f5pe+c57e+jRpKRmO9rOst9JcYPJraWGqiz1dEyB1z74OtFPYrVSxvHT2yjhjkwWRIFAbHbIxz3OjRpUudwbkvTsvfsO1dJX7No+kkHHkJjIxj09MD+A1uprbRUZJpqSCAlekmONV4yTjgdskn9dGjQmrjp9s2enWRUt1P0ysGZTGCCQSRwfYkn9dbfsW2g/Jb6UHnLeSueeD6e2jRpS4uNk2kDQ0UAs1s9tQYWgpR27Qr6EkenuT/E6wuthtV8tf2ddLdTVtHkEQzRhkBHYgemNGjSJVxUGy9vWqlNLb7VDR05JYxQZRCT3JUHB1LtR07GEmCMmnOYiUH3fGPl9uDjj00aNCFxS7bsk79c1nt8jAk9TUyE8kk9x7kn9dbzZ7aylTb6UhgwIMK8hmDH09WAJ+ozo0aELop6eGlhENPEkMYJISNQoGTk8D6nOjRo0IX//2Q==</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="2" t="n">
         <v>500000</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Lave-linge LG 8kg DirectDrive Wi-Fi</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Frigo Sharp 560L Inverter 4 portes</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TV TCL 75" QLED + Lave-linge LG 10.5kg AI DD</t>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Hisense Smart TV QLED 4K 55"</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHQABAAICAwEBAAAAAAAAAAAAAAcIBQYBAwQCCf/EAFQQAAEDAwICBgQHCggMBwAAAAECAwQABREGIRIxBxNBUWFxFCKR0QgyN3WBocEVFhgjUlVik7GyQnKSlKKz4fAXJDM0Q0RFc4OEo9I1NlZ0gsPx/8QAGgEBAAMBAQEAAAAAAAAAAAAAAAIDBAEFBv/EACoRAAICAQQCAQIGAwAAAAAAAAABAhEDBBIhMRNBBSIyFFFhcbHwUoGR/9oADAMBAAIRAxEAPwCyNKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAZpmo/6c5UiF0NX2RFfdjvIS1wuNLKFD8agbEb1Tf769RD/b90/njn/dQH6EZrjPn7K/Pkar1H/6guv88c/7q2nSt3viWHr3cL1c3Isf1WW3JbhS654jO4HP2Vxui3FillltRd7NM1Q6Rqq/yZaii9XIcR2SmU4PqzW4WaVd2oqQ/dp7jit1FUlZx4c6tjByLIadzdJlwc0zVWEzJ5T/AJ/L/Xr99dzT09Z/z6V+vX761x0Upeyx6SS9loc0zVbGUzlneZKP/GX7697caYRvJkfrVe+p/gH/AJFTwNeywmaZ8/ZVS9e6sesLP3OiTH/ug8nKlB5X4lJ7efxj2e3urQIl+vrixm9XI/8ANue+smXFsltTsh4uasvnnz9lM1TO3T7w6Bm5z1eclZ+2s2h25BGVT5mf9+v31ox6Gc1dl34Z12WxzTPn7KqWubcR/r8z9ev314Jd5uLSDi5TB/zC/fXoQ+EyTW5zSIeB/mXDzTPn7KpKm73aQtTjl5nMRm91r9KWNu4b1gr1ru8TH0twrpPjRmtk8MlYUvxJzXlajT+F1usjPFsVtl980zX56ffbqLP/AI/dP54576ffdqMf7fun88c/7qylJ+hefP2Uz5+yqBWW7az1BeY1qtl5usibKX1bTYnLTxHzKgBy7a2i+6P6XNNWSRd7s5d4sGMAXHTc+LhyoJGyVk8yKAurnz9lM+fsqmzXRx00yI7b7aLuptxAWk/dUbgjI/0ndWrtffu/ZjdEXqeYoYdkEm4qzwNrQhe3FnPE4nbtzQF8aVqvRi+7J6LNNPPurddct7KlrWoqUo8I3JPOlAYPp8+RHUH8Vn+uRVJ+2rsdPnyI3/8Ais/1yKpSlJUoJSCSTgAczQ6jJ6escrUV6Yt0UYU4crWeTaB8ZR8AK2jU8phT7NmtaT6HEHVthI3We/zJrYPucjo20KGXgE3+7oC3x2sNHdKPAnmaxnRjbYV71O4uXIW3KjqQ+ykEAOYJ4hv2g8JH01GVpb366PSivHj2LuXZgzY71ZHhMkWSSI6PWKnBw7Huz21u9qCZMZp5o8TbiQpJ7xXu1nIlCU3BcuDkiPhXECEgqVnYE43GNtvHnXdo+2FGn4aC2U8KNge7JwfZVulm5vkswQcZOPo1rVd1uNvdZhWxB65bfWOLCclIzgAZ+mvjROprm5f2rZeApaJCuBDikYUhZ+KMjsJ2rbLrbHHb2eqZAdZRxJ4zwhYSM8+3mfZWK08wJXSIlxxothCwrqyCCpWRhX10eqn5qT4IZE73WSbEtYIHq1jLvcp8NCzbrZ17aQR1yzgA7747s+2tjul4gaftKpctxKQpQabTnBccUcJSPM9vYMnsrWpEa4WvSctxElLjDbCmwhw8R6zHPJHmc537qt1Gql1Ep2uTIFvcCQLmqU/KVLVJWpanVDCirO4I76yFrtwSyX3QQ2gZOBknwFZyRYW5UyKhgl3jWsheScjY7+IzUh27RqI9nStwBCgtCkqUNgoKBGfDNSx0sbyy9EscdqtkeuTbvZGm5TunnkwlDiC3EqBKe/PZ7K2iHKi3e0Mz4nF1TgOyhgpI2IPka79czLmqPFtk1+AZK0Oq4GzgcKQOHc+BJzjsrD6JKEaJSnKitD7oWT2nOdvoIrV8Zqcmae2b4ONtPsTiGga1ea6lfEtxYQ0nck1lb5PbaClOLASKjm73ddwcKEEpZB2HfXtfIa9YYeOHYclBWzm8Xlc8hhnKIqDsn8o95rEk0Jrivk5ScnbMUpOTtilKVEibz0NvSI3SraJMW2PXV9guOIiMuIbW4Q2rkVkDbnz7K3u+2Ky620pqq/W7747VPtEgOTIlxkBbDxU56yE42BBzt2bd+ahW2XOZZrnHuFvkuRZcZYcadbOFJUO0Vtuqul7WOsbMLVdbmkwlEKcaZZQ0HSORXwjfffHKgJovMW2dIPSMjTV1tmqtMXtUIJYU3KQthtCEkpUUoyCDyznnttVdZc+5W1cm0ic4WGVOx1JQo8CgVgqA8CUJP0Ctsa6cNeM6eFnRe1BpLfUh7qkF8IxjHWYzy7efjUfE5JPfQF9uir5JNL/NrP7gpXHRT8kml/m1n90UoDD9PnyI3/8Ais/1yKrv0Wabhw47+uL82Db7erhhsr/1mQOXmlPM+NWZ6XLWm9dGdxtq3gwiQtlK3DyQnrUkn2A1V/XuqWZQj2a1J6i1W9HUsNjuHNR8TzNacOJNPJLpF+GK+5mA1VqGXqS+vzZDinHHVk4+ytg6Prc4nU9vDSCtaHQ44UjOAOZPh2fTXxoHo+makzcnj1MJOcLPNW++Pr+upVhqZ02GI1oiN9WSQ6VD/K9wJ5/3FWrBLMm+iqeuhjnSVv8Ag1bXce5w5MdTjLZh8fGHE54lYOwI7Mb+dbZaFoUhKgRgjINd95lxpjLa3GFOuEbMr5A9x7hXlbgSeMhTvVPqSSlSU8TZI7CP/wAO1V4tLPFGpNWW6f5fFue2La9/oY/XD6UoZLYWtQQeLq91JGe7yzWuaGvlsh3mbLlLMdCW1LU68MAY7N9+QO1b5PsTmooh9AZSm4xGQHGXFgB7sylWACDz3wQQQeYNa/Zeim4zGZVxnxERXeHMaNIIClLG+VDfAJATv2EnurE4SjkaaLXqYZF5IsivXWtpWsb4HcragxyUxmSccI/KP6R+rYVKkF2e/wBF9ulz40q4ByMpxxxCsuJVxHdSTzBHbWTc6MrBpi7Ju8e0onN5C/RnVY6s/o/wT5EDNb1FhMXGztmGtLjTw+Kv1CEHsPiOR8u+pZIOlRTDNzZHXRVDavEZ6S6wlr0Vzq0t8ykEZ/v5VJk9DK7e7FCdloI27NudYODoW32BLkgSeF9wgF0LLaQSew578AeA86zsCTGjv+iTW1OLeTw9dzU3vjixy54ztVslKUaQ86XDIF15JkoWhp5LpWEn1+aVZ7j2Dwrsfvtst+k4SYhbSjqhlCdiXMDiz4551OU7ophXG6KckScwsghsD1iM7o8vGsk50f6SkQDAkWuI821sv1Akjzxt9gqej1EsCfFMnkypS3LkpTery7c5CvWPV59v9lYonFTP04dGVj0pHj3fTqXWWHHOqejrVxJSSMhSc7jy8QahY1XOTbuXZQ57nbFKUqBEUpSgFK9cJlt2PNUtOS0xxpOeR40D9hNdtktDt7u7UBlQSpzJKsZwACTt2nA5VxulbOpNukY+lSY/0XtmP1TS3GnUcWHysLDmCAMoA9UHfkTjxqN5DK48lxlYAW2ooVg53BwahDJGf2ssyYp463Ivj0U/JJpf5tZ/dFKdFHyR6X+bmf3aVYVGO6b31Ruh+9PIOFIDWD/xUiqaMtOXCYlsHdagM+JOKuL09Z/wK33Hcz/XIqqGl4yX9R22KVcPWym0lQGcesOyroP6a9F+PlUWMtkZFpsDFtjhLaUp6sJIwRjbBHYcD215n4M2TcWfRsFsLCFcCM8Rxkp+gb7eB8K+ZrbhgrTMkMvOOvhSVtkpKlE55bYOe6vmwyJbNwbbddwzxKd9VI4s8OMjtHYK9bFPdj3QpnzzwN5J77PWuyP9YhxTKx1S9wE5NYzUUp2yMGQrDR4hwpXkEHu/t5+2tpl3hFvtj0xTjxRxHiB34RnYjaoe13Mm3i5ux3pReiJWFs59U8BTn3j6Kq2PNJSl6LcElgjtXskqwTFJuTCgdnGjn2A+6txcLrsVfVKw4pBCVHcA42NRnJlojx4URt0tyD6wcaVlXCEgYwP771w2+/6IlAvE5CElRC0jG6TtgcXIAEDzrPnacuC3TRahybetUhuxeiz1J9I4ilJCirI78n6duysPo3U1tbjvR13BopafUApRwnCvWGCeYxnflnaubobfCKIF6vTcdiWzISh+Q7g4IAABPMgKrU7ZCh9dDj2ydbr440oIKowWhDaU5wfWIycY233zWXrg2Lnkk++y7HPjJjSLq0w42esThwDB3G+duw7HxryW91uRe/xalL6pj1lk5wnYZPng/XWPasDiZjZkwGfRzxlboUeIEpUMfGPMrIPmfCsZp7UtqtGpryidMaiNNtMtthQJJKckgAAk7GpKlyRdt0SFpnXlruek4d0deUyHUDKVJJUN8DkOZGD9NdDN3t702S5bZvpKAQFpJ9VKjk9o7edaZY2oUixyHbE2Hoan1utiQlORlScgBW4TtsDy2rJFAtYS4800082uMXSjkELQUkD9EKJxikYqTs7dGhayVP1XpplMlpTj0iS+Eo48JKxnJJ8EoSkfT41Xx5pbD7jTgKVoUUqB7CNqs1abzpRzRUZF1elKciy3lLTFQoqQUuq2yO8Abdx8arzqiRbZepZz9pacZhOOlTaHB6yR7TXMm1rgnFNdktw+hCwSdQ3O3Jvkh1cMwWzHGUuNLeSFLDii3w4xxlPDnGBmsA30IzJLEaSxdm1RXo65KnCwoBIQkEtgKIUpwcQ2KUjGTnAqMhLkhSlCQ6FKIJPGcnHLNc+ny+sbc9Ke42v8mrrDlHkeyqSRJSuhN5Lf/mKGpamnZSCiO6pCmUPpZKsgZzlYPDwk7Gu5/oKnMOyC5e4zUZvq0tvuNEJd4wopWAkkhvCfjc8nHDsai8zpal8ZlPFXeXDnnn9u9cpuExLy3Uy3w44OFaw4cqHcTnegO+AnhYuQznEfs/3iK2zo60u1dFyrtIjOy2oRSG47fNxznv3AbeG+TsDnUrcf8VuP/tv/ALEVIvQvqa3W27OWq5yG4jUxWz7g2AI4VJ+nCSPEVVmvZ9JOFXyS7BTpzW1oVbbRZ4br3DwPONOFSxk8KiU7HhJ2zywciq6a400nTOpXYbZUWFjrGgo5KRkgpJ8CCPLFTvqWwydKriX3TL8ZCoj56tceQhpASs8S1qSo7oxkFJwBnuxUIdIuo2dR6rcfiq447SerSsclnJKlDwydvAZqvHiUGpY26d8OvXXX5k5ytNP+/wDS4/RP8kel/m5n92lOib5I9L/NzP7tK0lJiunk46Fr6fBn+uRVUNFSG29cWdTikhAkp3JwM74+vFW26a4rU3oku8Z+R6M251KS7w8XB+NTvjtqmF3s86ySEpkBKm17tPtK4m3B3pV9nMVKm4stg3FWWEupmPXywsspKmDOaU7jnwhWSPq9mazlrQUKdcxuSSDzIHZWg9Dur3dSXNm13MKclwGy+2/z6xCRw4V+kOIb9vnz3h+UmFFS1kF1xZ9Xwz+zatXxsHDFKD/MxfIZPJmW32uf0PrUclKLA4wgglacAfbUR3OQt22JdKiXGmFpJG5OEn7QfbUhznlusrKySVDO30VqgsbklTjaFgktubJGTugn316zhtxtHmPJWTaz2WCZ90dRW1SSCEQ+JXmcCpegoAjpJA28Ki3RNtZjqSWkEZSElSjkkDlmpbiNgRgPCvAxw2Ro9rNPyysizputanbVa5qE5RFfU2ojmAsDH1itZ6MFlq88PFsBv51IHS4sDo8uBx6yFNFJ7j1gGfrqNOjp0NXJG/ZXHzKzq+2iwa3AuArIHxcioLuCmm9fXfKQsEggHvKRUwtzQYRHFzFRemz+l3qVLIPrvKHsOPsqU47o0RhLbKzbdIr9GtAjpxg5O3IZrv1e+tduiOBRCZcRbKiPyk+sn6wayFjtyGIrZxua6NSQjK0w60kZcjL40Y7s1OP0rgg3btkNaQWpVrv7r6uJluSsISfyjufs9tRdJIMp0jkVn9tSjb3xC0hfV54EenOK8/VHvqKlHiWT3nNZ17Zpl0kcV7Lda5V0eLUVsLXsACoJyScADPaTXjrsZkPR1FTLq2iRglCinI7tq6VmXVpO6JTxFpopJCch5OMkkAc+ZKTjyrr+9m6JlsxlRuB19BcQFqAykJ4ic9mAaxzc2Uznq5LyMjB4VkbVyqbKWjgXJeUkEnBWSMnn7aAzSNJXxoqa6lLJdPVELeQni5EDc9+PZXmkaXukSO4+8wG0tth1YK08QSTgEj6DWN9MknH+MO7fpnvz9p9tHJkp1IS5IdWkDAClk4HdQBcuQ4yGlvOKbTyQVkgfRXTSlAXz6Jvki0v83Nfu0p0TfJFpj5va/dpQHPSjBZufR/OhSFrQ08tpKlN44k/jE7jO1VL1LZrnpvjZdKZdueOywCW1d2R/BV/cE1bLpWkeidHM9/OOBbJ/6qar+u+R5cZbT4Q42scKkqGQR4iteLb43fZdjb6Mb0GNxmL7eZ+6erjIaQDzHEvJ38k1JEyXDS+tbpClE7HtAqLrY4zpxcxdtJLUlSVKazkpxnke0b8q5c1EzJUpwr3OM5zt9Gat0+WMFR52oxTU9xIMtqIRht1SRjAzvXktgQzcg4XUrT1ZSR25xj7a0d7Uqnt0uBIHec10tahDLnGHAVEVpepTjR5z085T3Ek6UcYbwniHqnFSFHnsJbA4xVcbfqwxXl4Vj1idvOs2nXysD8Z9deU2ewkSL0oqYl9HN5QheVpaS4AP0VpP2VDOjZYYnpJVgVm52sRPgSIq1gpfbU2RnvGK0K0TFMvDCsEVF9k0T01eEeh7Kyccqwka9tomPtKyhQcOx8d60pm+OdVgvEDwwKx0u6OJuZcQpKgrBOSc1KzlE8xbqDHbCHOyky5pDDwQtJWtBABI7R3VDrGtno6eAIScD8v+yvuRrGT6ISkNoWrbmVHeu7qRzbbMTrGQmLZFRmlcKZLy5Ck8vjEY+ofXUe1mtQ3X7pSioKykHArDZqlW1yXTq6RximKZpmukBTFM0zQDFMUzTNAMUxTNc5oC+XRN8kWmPm9r92lOiX5ItMfN7X7KUBi+nh0sdC98cHNPUn/rIqo1plybpPTGaURkFSlfkgczVtfhAfIhfvJn+uRVRNG3aJZtSMyJ6FKiKBbdKRkpB7cduCB9FThVpPonCSi030brp9vSt4mvWiTPkxppSUsvJJKVLHZvsfLbPYa1KZbpytSPWfCRMaUpJXxcKeFIKiok/wAHhGa2m0p0vY7wu5ofhTYzclLzHWLw83vtjB9cA8wQDivBd7jbbl0pzLtMuCI0V1PWMPQnlI4SEhKRxJSopOx7Ofgc1mksmPUOEuqNmTLDUYPLFJc1S4r90/5MWnSWrA+7HFpkKcZVwqxjGcZwN99jny3r4XpXU6VtJNsdJdBKcLSQAOeTnbv37N+VZhVwsqHY4Tq+9SescV1pcecbASpClAKwCRlwJ4iM4BOOLnXw2rTYhFo6yuzfWI9ZCUuFIAB9XGBxdmM4zjmOL1b7Z59I1K5xLjZ5pjT2Fx3iOLhURyPl5H2V8xuvkSozCVhKpCkpSTyGVcNezUTVrbTGMK7v3V9SVdatxJCUb7BPEATzJPZWMTI6l2K6lSkqaAPEnmkhROR41w6SZeehjVVgj3+TLlwfR7I224pxK1HrwvlwDGRjt4sfTWuStF3OO+79zX2bm21IciurbJa4XkEAt4XjKjkFIGSrfG4Nd72p5Ux+5rkaxuDxuuG5hWDiQlOOHIwcAb422HLto/qh+RPVIXqyWouM4XiOEesVAqAAGAfjK48ZzjfnQHZctEajgShHjttXD1UKJjOAlPGrhSFJJ4hv2kYwCeQNamqW4XHQSMtg5wcjY451uQ1bltDjmpn5DqmFs/jWSkscaeBRBTjiUErcAJyAFEjetDyhtyQlK+JOClKsYzuMUBJFms+kX+jNd0m3BlGoD1hbjuXDquPDqUo9Th5EFW+ewnsrr1LpyBb7HLfafhvqbSVIMOUt3GFoGVAkjhUFnHb6p5YwfDZGNM3XR7ca4SI7V2SlbTDr8pTSWSVqKSoYwU5Xknwr2TGNFwOi11uLKir1MpHUull1xXWYfGcD4pHCnPLuoDQrfa5l6uCIdvjrkPrBIQnuAJJyeQAFZFWi76h+Syq3rDkRLan08ScthfxM77ZG/lWWs8LTTVubnHUcq2zUISVpaB4wonCgMAZ79jyO5HI+9p7T6XHlOa4uq0qQAShDgLnxhvtvgHkezzwAI8HOpItHRvbJ1ihzX7hJS7IaDhShKcDO+N606/xbLDloas096e1glTrjXVgHJwAOfLf6a3uz6mgNaegsqmsoW0ylCkqXgggYrXpcUMkmpl2Hbf1HS90b2hvlcJf0hHur1TehiVDsxuq25giBAdKiW+JKDyWUfGCfEiut/UcBYI9PY322WK297pX0w+zPluQli8XGCqE++h9JQgdWEBSAew4BKTy7DXoZMWDHW1J/39yc1BdIj9zowkIny4XVykyIbXXvoWUJ6pGAeJRJwB6ye3trq/wZXFUZEhmPIeacStbZbW2suJQcLKQCSoDtIBrcnukyxOX+83VKZTbt1hGGpAdaUGvVQOIZG/xOR766InSRZYL1jlttPvzLH6QqOXHm0IcW4sqClhIyAM8k8/CqZeN9RX9/2VuiOhp2Of8ATOY+iviVYGWIbryXnCUJ4sEDBrKi4xFKKlSmck5PrAV13CdDVbJCUSWlKUggAKySajOGKnVE1GNFwuiX5IdMfN7X7KU6JPkh0x83tfspXmGc9mv9KK1to+TYfSBHblKQXFEE5SlQVjbxAqIl/BbgKVlNzCB3YWftqwVKAr6PgtQO26j+Sr319D4Ldu7bp9SvfVgKUBWXUPQHYtNvwBMnKLMta0l3iKQ1woK9+JQznGOdZiP8GK0SYzT7dyJQ6gLScL5EZHbWyOWzUXSXqtqRMCYWnYTighKkbqWCUnAPNW3xjsOzepajMIjRWmG88DSAhOd9gMCgIF/BbtX5yPsX764PwWrV+cj7Fe+p/pQFfz8Fm2dl0P8AJV764PwWLd+dj/JV76sDSgK9n4K8Hsu/9BXvr5/BWh/nkfq1e+rDUoCug+Cy2ZKkG6pDIGznrEk93D/bXZ+CrF/Pn/SV76sPSgK7/gqxfz4P1SvfT8FWN+ex+rV76sRSgK7/AIKsb89D9Wr31z+CvG/PKf5CvfVh6UBXj8FiL23dJ/8Air3157h8Gi2Wq3PzpV3SlhhBWs8KtgPpqx9eW529q621+E8VBt9PCop5jyoCt+nfg9WzUUWVIYmhtpiU5GCioqDnDj1gQcYOe81mB8FuB23JPsX762vTcTUvR/qwWl9KJdguEkJjrbQQEKUd9h8Q9pHI4yKlccqAr9+C3b/zin+n765HwXLd+cE/0/fVgKUBhdIWJWmNJ2+yl0PCC31KVgEZSCeHn4YFKzVKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKA//2Q==</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 75" Crystal UHD 4K Smart TV 75U8075</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAAAAQUBAQEAAAAAAAAAAAAAAAMEBQYHAgEI/8QAShAAAgEDAwIEAwUEBAoJBQAAAQIDBAURABIhBjEHE0FRFCJhIzJxgZEIFUKhM1KiwRYXJGJykrGz0eEYJTZDU6O00vA0N3OClP/EABsBAAIDAQEBAAAAAAAAAAAAAAAEAgMFAQYH/8QAMxEAAQQBAgQDBgYCAwAAAAAAAQACAxEEEiETMUFRBWGhFCJxgZGxIzLB0eHwQvEkM2L/2gAMAwEAAhEDEQA/APpHRo0aEI0aNGhCNGjRoQjRrxmCjJ1wruZcbfl/2aEJTRo0aEI0aNGhCNGjXLvt4HLYzjQhdaNcRMzL8wxzrvQhGjRo0IRo0aNCEaNGjQhGjXLvt4AycZ15GzMvzDH9+hC70aNGhCNGjRoQjRo0aEI1yzhB2Jz6DXMjn7qYzrnywW3Nk57A99CF4A0uGfAX6aVVcDGMD216F9T+ntpOepgplDTzRxKTjLsFGfz0ISujXgYFd2RjGc6FZW+6QfwOhC90a5Eik4DAkfXSRk8xyqsCvb5Tkg/XQhdySleFGT/LXKx85f5ifTXEbwpMIfMjM+M7dwyPy76XDKG27hu74zzoQvQPU99e65EiFdwYY986N64B3DB9c6ELrRpOaeKnUNNKkYPGXYAfz0oCCAQcg6EI0aNB4GhCZ3W60Nktk1wuVTHS0kIBklkOFXJwM/mdU3/HP0e91ekiuSPEihjVDmLJBOAe+ew7dyNSXiPJIvQN0lTb9iqOMqG5WRTyCMdtUHqHpzpyx9c1XlCCngloxPVAEyNkl1bEY7HaVPoBjJ1wkDmpsjdIdLBZV3Hib0bsMjX2Bx3yFcj/AGa4sPip03e0ps1DUk9W6xwxTKdzlsYwRx3ONY5ebJNW3SoqKVKOCnjG2OBJslEUYAPHLcZPuSdcUVynt9qpqCZJIXp7zQVYySvyeYAVI9uUYaWbkW/SQvQ5PgfDxPaI32QAXDt/pfTmjQNGml5tGvC6rjJ5PbVZ6yhvMjWg2erroA9dHDVCmVGxC2d7ncpxjA5+vrqrxXLqr992tKpL7CklfUedLFSLJD5C1DCJWAXILLg7sgBRnk6ELTd65xnnSLVIMzRI6b1xlc/MM+uPbWT2e5+INTbYlkS4rc2r4VcVdLiFYvtC2TsGFOEBKlsAg51c+glra2zfva9W6aivU7ypMJ0xIsYlby1OODhdvI799dXDfRWdI9uM8t7e2lQMfjoGPY6M/Q64ur3WCeNfTlc3XlJ1LW2hupunaeiMNRb4psS0xO7Myp69wc4PbnHB1vedZz1p4XSX3rCn6qsnUFVYbykHwjyxQLMrxnI+6exwSM/h7aEKiXO82W0/snVh6du9dcKSX/JInrMLNEXkG6MgdsDPb0PHGlPBanPS3izfOmi7BKm00dYisSfmEaFsZ+sjfpqzyeB1ok8N6Po1bpXpS09Z8dNMEUtPJgjBB4Awew9hqffoGlXxLg63hq6iKqp6T4NqZVHlyIARknvnkf6o0IXz/wBD3VrB1VP1QWYRT1d3pJGLEjKwCaMfqDq0eAtFJavEuqoWZ1km6dp6pyxJIeTy3J59fn1dajwCs9V0bPYGu9esc1za5+eEQOrMmwoOMbSNWi0eHNBZ+vqvqiGqmZ6mgjt5pio8tURUUEHvnCD9dCF8/QWGk6U6ngpeuo6+iq5br8TSdV2+bzVmP9Ryc4XPJ/iHqMc60S9SH/pWRLuO09PucZ4+7Jp2n7PVGiC2f4T3I9Niu+PFq8pMeZ2/pO+Mcdu3151Y+sfCxepOqqbqS2X6ssN2hpjSNNBGsivEc8bW7HDEZ/D20IWNWWR/+hpfX3tuFf3yc/0sWmFzZ7R03Q9LtNKxt3UVFWU5Zjk09TDvAz64YMPxOtyh8HrRT+Es3QcVbVrSTuJJanCmRn3q5OMYH3QMe2mvUfglZ+orxZrjJcq6mmtcEFPiILtnERypYEd+/bQhUzr+gouo/wBoSe232kqrrbKGwPUxUUBJbfzyigjLc+/OB7avXgbU26bwyp0tVwuNfRwTyxRvXxqkigEHbhWYbRnjn10r1n4YJ1F1TF1Jbb5cLFdxTmjkmpVVxJEc8EHseTyD7e2pvono+g6E6WhsVsad4YSztLLy8jscknHHt29tCFZN4IJHOPTSWXlOAVxweOdcEuEMgB3KfbvpwAMcDAPOMaEKt9fQeZ4cX9FGSKGVs/UKT/drJPFGCI9Q2+7UlQkxq6ON3CMG2FNoycehDL31u9xo1uNrqqJ2ZFqYmiLKOV3DGR9edZXXeCSz9RUtY1+udWZEK1c08nzsqldqgqO2N3B9ce2qpY+I2loeHZzsGcTAX0I7hUGbq65TCQYgiEhJYIpGcqyn1z/ET+ONNYqNJejr3V7w1VTGmeNM87VmVmPP0XjW10/hB0nCAGp6ufH/AIlS/wDdjRaPCbpi13GsqDb0mjlk3RRS/MsYwO2ee+7v76Xjx3B2p5tbmf49DLjnHxYtAdVn4dFekYOgYdiMjRoUBVCqMAcAe2jTq8msj8caM19d0xTCaqQPJP8AJTyFC5wnBI/E6zXqXw+IMdFbOqYaS+fL/wBXTXY+a3HYKWyG+mtt64gefq3p0wlFqI4a1oS/YSbECH/WI1k1BU9DweGDW+7pbhdvh5EuFNURg3N6455XI3li5GCOMfnpFzCZteo7UKHL5pppAj06RZvc/osqlsHW9NUyQyQXnzIsg4eTkj89SnTFV1LPTSqtsnrZIDsJk80kH3bB51qtitl+vUvUdJfeob3R1lmtNBIIqasaLy6g0pZmYDucryOxJJOdQEHVF9vRElfVGhEVrpaqLyb2lpDM8W56kgofOJfI9hjGOdMSxcVuklUh5bu1V+g6V6u6onWriqfg42kEccXxBh819pJRFJ+Y8dudWWk6Nv8AarfIsj0VbXoQi001cQ4cru2Ebs7to3AdyNW2srDT2Lw1vV6noo5Dc0lrquJgIcvDIEkJwAobg+gyTqHnqqa5eKc1xopo6min6phSOeJgyOUt7BgrDg4PHGqnYzXtDXE0OxQyR7TqHNYdW3q8zXCd5q6phbzMMkUroi84IAB4Gpay1Fwmu9OklZVOhOCHqH255+uo6vpXF2rCFztmclf6w3H+enlCzmeJadnEwOFKHDAe34D66vlb+GWt22Q1pcVMXeaot1bWTR1FT5YbbFE074YkcY54GefyOq5JfakXvzIquu+EDjMXxDt8vAPc985xp31BWJIYZ6acyy0koklkJz5j/wATfgOAPwOk6iGFamYLAHEknmb1O0YIyOD2/wCWk2udE1oed6/ZRc4OOlvRTfUjT2+o8mGvmlgnRJo6mOZgdrDg7Q3r6j0I41FW03SNqaWsrqww1I3q3nO3AYgjGfodJ4aipYopqVhMUWT7QZDKT8p+g/46e08tRDPSbQdis52Mw2hwdxCj29Pz1W6R7hWq+5/vyXWUHe6OuwT6nWvjqYp2uO+N51SD7VyrFvuhlzjbz/LUDW11c7uVq6qFg23atVJtPAGRz9M/nq4W/pqKvpklqmngoaJWnIVAQ5J9M+vpjVbrHoYrk1tiogpEzOHaQsdpHCf7P00vj5TZHuAJNeiZyonwlod1UDJX3VHUNXXBCVBG6ocZHv30/Nfcf3c83xdSwwMOtS4Kn1G3OT+Ol5IXMcMNUCxpfuK/BZc8pkcjHPB0peLP+7qSn8zZJBMpkEUTbTGSMgfjgj9R66c44JDTzSul25U9Y5jVqk0j1MwYAbfNfGcj698Z1zeI5KS9xOtTUmmZFby453GBzyefpr3plEiILAgnA3EZzx3/AB15caAJ1FcWmgaWKp2sqM5wwKnbj25zrDEzhO4ajVL0xiBjYdItRnUN6jFRTfu+5uEVcyLCWYk59STt7emmtHcJam6wo1dWPD/3pSR1IGfQBypP4EaUnorjQTQyk0VLLJysUUStsB7A5H951ovhp0Xauqqa9fvKdqeSnjjaOdCEVXcsMsMYIyBxrVjsNaxhuxsb/j9UnjYftJkyMj3Y2EXQ33rYb+e+2wVKmeWUqEqKlAmV3CocFx7kZ4PY8HSdKs9NMzSVdTURnsslRJle3rnnt6612h8LbdFdunbddY6mOorKaperVJsDfGV27Tjgc/7NNoeienK3qCG0x0ksMtTT1DQsl0jqcyIAVyEHHr37/lo0TadN+q9M1vgoNiImhd+QsXz8uyyutaomlU09TPEg3Egzv3OMDg9gB+p05SomWHyxLJycljIxb9c8DWuN4T2Wmp6apnknkioqSVroFmwUmWNHAHHA5PH4ax4EYyBjOqpuK2tZ9VoeFYnhcznPxmXXffv3+H2X034S7j4XWbfI0jbZPmYkk/av6nRrnwicSeFdmcDusn+9caNbMd6Ra+bZekTyaOVmvhajPFCqFJeen2IPzrUJkdxzEf7tZB134n3KjvmLW9GJ0QBatqZDOo7YDkbhrXvFKGKe9dPJOcR7akk5we0fbXzX4iWyS39aTKWLxThXib/NPp+usPY+KFoNHTfkU9X/AAAa6qVk8X+racqxnp97ACWXyF3T4GAHOPmABI513SeK12ro41rqC01sdN/9PHLRRsKcDttBHyj8NUStjKwxPhiz8YJxnjv+mm1MqxsCCSRznHfWsGue00sqYFpoK9VviR1BF1PV1Bqkq4qqNVqKapiEkRA527WGDjjT2HxX6i8uOkijtsFNGxECRUiKsDEEbkwPlJB7j66oUvlLM3lbljydoYjP54408pKd3CY+YsQMehHpz6HTLWhjACuMBOyl2o3rKHzXx8b5hBTcMsc/eH9XGOfTTrpyli+JZ5goZU3AnnI9P56ZUNvnrrg0FM7sNpBY8hYxySPb/nqctQhpJZIPI2M8eFLc5x2Gs3On/Dc1h96vRPQUyVgcNiVxaOj6SqqVWesSNfIMbRBfmkLEnI/UaZX+m21VPWxuheNlhaJj6DgHHsCO2u7601N1BEsaDyqhe5GNhAJ3A+mMdtRDQzVlRNN5jTsTsEjP97J5+XOQCOPz0rDC8lszn6gR9FPIYwkta3TR381I3K4vcK6erdWenCIzRgZDEDjkfw+un8dvo46meOBaiSeNIhTrGAy7T8zs2Ox7Y1HUNqnjq3RZhHtmA3CTHylScg/TIP0zqwxxT222KsUe0SyYqdrDcpA3cNns2O/P8xrha1g4bDQKIsanB/ZTdgjNVYbi8tXFDTRU7ggksQeCDt/Eemspq6Gvp6eOveB/LqJGAnYfKWGCQPc8jWhdO1HnXOoAZl+J3qTGcE7hyAccd9UW4u7y/CeYRHFIScc8k9gNJYNMke0dd1f4pZLHHspajmirPJq5BmRyqMpYgjA7/wAtIVVFU1Na1W8UkkQchpQRIPxIH5c49NOoJI7XNDFHB5rRP8xHDZyPx9NOKRPPmeaJnhmbMiyx9x/pAcEe+rXucwlwWYeXmpbpnyqpvhz80Zbkj19se2ka64CXqKWJ/mhT5FYDO4L/AMzp1Y5jDdxUSU8cUqoAQowCc/expzWpSQdWtHRFDFIoYrkFVY/eA+g1kOcBK6x0Xqscl0LLUJeqEpcErZpfNkmRdi9hGoHYasfQM6SU97tE1fFQw19MvmySKOY1b7QKT2baxI+o1D9XQTUd4jeclY5oA8StxtUHB1AxVEU9Q0XmxRbVJLykhO2cZAPJ1q4krjG1x329F6GB2JH4eY5HhlknzsOu668gt6pbkZbjYa6ovyYprefLqJxHz5nlAq3uwz/LnHOo+Z6dJbZeI62122roxPNmKmhiy4G3DKpJZcE55zn21ktmtb3qmSaF4oy4ztYE45xzga6qLLWQPUiGFaxKUZlkpiHVfp+I9QO2mjns1Fh5jzSbMHDoPbOAD/56G/3Ww+XHPLerfN1NHTR3uRTUCUxs3LtHlWU4UPGgK5zjgH31mfSXTNVfr9sghWWClYu5kOFbbyFyO+ccgemoe0UH70nPlo0sKIruYlzjP8J9iNaRQVVJbK7p6jEJDLUGTy6bBkTjGQO/J5PuM86Sys0F7YgN/t1UXZLMHHkONJr1ULqgOm3f+FpvhVLJP4a2yaU5kkad3+XbyZ5CePT8NGnfQGP8EIsdviqvH/8ATJo16hvIL56eapHjjcI7VNYKyaOSSOIVJYIccYj7/TXzP1X1VN1Jemr5EEK4CQxA58tRyB+PqdfQX7TDYsdq78rUdjj/AMP/AOY9dfMMMW58tqhmOwzmcj3qpWmd5j4N7JyZJqpwzk4C7Fz6DTmnhyxIPyqAT/frxIyYztGQOSPXUlSfCtGI3JjOPmyfp3H1+mn9mhVAFxTSooSiZV1dcjB9/wDhpWjMtRXJTxl95yu0d8kHnP66USFqmoWCnVnlPAQdvx+g1O2W2PbpdvlEzOfmkPcj2HtpGfIawGzurhTXNB6lWyw9PPF0vcpqVh8SkXLHsR6j9NRNxqIpaG2SRoFnjIDemdXnpaLZ0zWmXGwgrljkapFwiS8XN2oW2UsQBZwOMgc415TCe2V8k87uTvrtyWl4nFTo2Rj5KOv1css6wBIWaIltzuFxkDIB7ng9hpq9KKOmNfKuJEkHmdg4Xd2BHdhkY59Dz6a8tYeS60xjlZJJAziQqGAGcEgNxn8vT66l7nSx109LAzDM4IGWLEkcAnk5Pqedeiig4MQb0HNUvl4slnmnFj+GqbR8Q4YyKojBJIUMw2ZOM4UA5OpowtB0vWGWGKNXXYgyAwAZewwPTk57/kRph0pYKulqaqnqKNVFIpFQxqMqV7grx82729PXGrZcZKeot8VHtYrVxIGwxKORkjOD94DcxIHAwOdUT43BLgRfVMxSiQAg+SqNrRbfXQPHIJXBDeWqk4zjPAHbDcn01HP0tLUo9RTT0rbsyhGyhALsD+Q2/wDznXaSO8i0GyVirLFIqhcAbhg4BAIJ3Ej/AIjHlNVRRQo0ckssowIt+I9rADcH5wxIbcP4R69zpcMZ+do3KlMwSgNk6KOahuNPcVkmhMMgfCuo4UgD1/LH56sXSURfqeneSMeWxJkXHyZPr+frqHr706KwhaL5VViyAncw9s84yCQRgDHb00ra+oHoagOgQOoAkMgzk5AIyMYPfHoSD78U5cUkjSQOaWZjMa4aTy7rTur+jrdR9G1FfTqHqoDlW3YwhbsR64BxqidJWlay4qgdIg3B3DJPvjUrN1NFdenp6ZZiksoVjCW3dj3BHGleiaRZ7gm+Mkbvlx37+/56xp5HNiLdOk/VbmM3az0TfquOsuPVTUk0NCfIQRUyNSmrqGTvkIDhQTk5bGq/fbJU9LWNw+6EXBW3T+cVjOD/AEbRpwDg5ySRjtrRL9bI6fqiChhp0HxMvm/CQk/b85aWofuVHog4OnPX9kir7bSsQwjSXCRQRgySNghURCMFs55PCjJ9NaEBc3TH0FWsWaPUHv6rJ+macwVAgjrKmlh2gB/LVWkzn5gDkqPx5P01frVaEsVHLNS5ejgiaZgMFyACT+J47nVOpunYLRcBUb2ll81kqI4ZD5UbhciPzTzI4zknt6D11eLNUJWUc1FKWcTRmJyRtbaw9x+YzpHxYkOtpsHmtLw1ruBy3F1Z/tKG6cqlmvZqaSIU0dXB8Q0aLxwxP64Opnp68Wm5dSyRUdtjaKSYzJUSAJIG4J4IyeR6HIz2Gobp21SxeT8JXeStM00McnDSPGSQCM8enGfb66fQ2ZbDfKOc1kc1PWyqhEylftFwQQMnDY7EH6YxqLOFx3AO94igPh/HJVvfKQxxbTevLr/K2Pw5/wCw9Kc5+3qf/USaNc+G3/YSj/8AzVP/AKiTRr3rPyhedf8AmKyz9qVJJLb02kZIBlqN+D6bU76+enHlqVQDAXGRr6J/aeyaLptFGS8lQuPf5U188oocHaAUB2k/lxq9g2UFxBUgPubJXPO3UjHSifkygQj+Nh9wf/PbUVHTMlQQp4PdSM6mRiWmFNFHkgZ4GMn/AIarc0ncq5jgAlaO/wBPZ43hpqQSv6zF8GQfpx+GlR1rUvIW+Ei79ix1BvEZpxHGgSRuAp9BqRFvoYocVE8gkIB+QDjjtjS7sbH3LxZPxQGPe7V2U/TeJddTWaagFBTiOfILFmB59tNaXrdaam+HNt2rtIPly9/ryNQ9ZBFJHBFT1KvTx54lwrLn14769gt0DbfMrUyQPlA9Me50uPD8Pf3Kvfr+6bM2RrD7s/Jex3aneJY5jLEEwVf7zK+Mbxj1AwCOxA9CNWGnq0rlgkSKap+EcTNJHIqZI/q4JPze3HfUStnpniXbNGcttBLjJ59vb8ddzWVKcK8TATDuYsg/rnWlraRQSvBeDZVwgu1uZKoRW65SVlfGYpFeqwMnna2DwcA98bRk/TXtHcJqqORjjyo4ncMBtMsX/fSKTwikKsaFiMjJ1UIqitpUkAqDNHICkkNQuUYE889v1/np1TX8VtYI+YqsSrL5LktE7A4BIGd+xQMKSF+mpyRe0NOp26ra845FN2U1dKdbiiVIMSTSRBlwCRt25DlQCRkZAzycaSaQtf4oZKimWlqX86EzBF84SBuQuM7iGAycfdAJ00iuMlbUbxvDsZZABKrBFH3uGyR3zwfxxpHqSGkoK+nus8U9VI5jjhiRsKoVf4iMncBjg/Q8g6zMGOPXwn/L+/ZO5j3hnEZ81F1MpenZkSncwO0cixAOqjae+D8xLZxz+euoBvE8cExnaN9m1NzE4HzZUDOAxHGT349dC9L1kawrbqtdsHzzFsjBbnn8FA0hUvVOXpqSijnhkqfMiEQPyjb8x3A8EnjJ9tP5OKWVQSePk6rNqahq3wJVqEDMCxUMGCqDgcLyM4AAyMEY9daT0DIUmjqFkVI4uCc5BHHzZI5/56zKlrw9YjbqORY0MoZaksqqvcHB3AkdyPXnBHOtDt0yWvpKtllzKgpBPFKHB8zkYTgkZ4257683m4Ylpo9Fv48+kG+SvEl8pZ7m0saqCeGb+JlHYZ0rcq1LhbSkEphJ4eZPvxxn75X2baCPz1TLRVw3CBKiBkIcA4U5AOM4zqeo5dhZHAGeCPcag5mxLVZQcKKqNzoJD0va5/hRFQmoaZ4kJHls4ygIB5ATav4g++lLBJh5Ujh3qpY5xnjGc51dWeFKfCqNsQLD3HByR7HvqoWCnlgWSRJ23SgvGxPzKjDgn+R41k5jS4e8pQyez6WAJgqvbIXkpyJYUm2Ism6J/qACM9j37asK01H1NReXOjskQMkTRnD5Azx6c4xqtVtHWWq3Sy1gDR+Yq7lcHPc59+3vqx9PTQTWGVXhWOEx4J5HJ9Pfk+2kslpaQ9oo2ntOqMtduKWmeFTB/DW1sN5BM5+0Xa39PJ3HodGu/C9/M8PKB/60lQf/AD5NGvozeQXininFZh+1IQKLpnIyPOqM/wCqmvn+mlEW8hchgV5OvoP9p8M1L0wqjcTLUce/ypr55hDN8uDkH5gRyD7++rQ6ha4BZSsRLVDpGoJ25yTwPrqWo3lemNJBSCsmB3bx8ojz3BbS/TnT0t5ukVKszR00j8uBnCn0+pOO3p66tF5p6S1X392UcBhhpsJg93PcsfcnSJyRLN7O38wBKcMRhj4vc0oy3eH891tVTcKy5LEtOu4xQx5/mdMF6XoEpmL+c7N9078fyGtN6eiQdL3aRlypQjAPbjVXaBZIkXAGBrH8NfPnPk1PoNP6K3xMCAsazqFX4ej7cxVvMqBk8qHH/DU5H4bW2bpyouArqyKSLIVSVKk+meNcRU7NVKm7Cr/t1eadDB0BUFcOxbBz+OlvFsySOdscDiNwFbgAGCR8gugsJ+BrVO2OQyMBkKUIP5Htp3aaO+3aZ4aKjlmeFd7bTwBn3Pr9DzqSVRR3KSDaXHneXIjBtrqxAwfc+o9BgnV/8PLVUQXGpnkqZZKV0KxRyEj+IYZG7SJ8p78qQNb+TM2LDfkDm3p9ktBb5ms/xcs0mrrhQVUkFwgnglU4cTIQQf79N6VFlrZq5fK+yUtEW3CMMeSW2/dAXP541rFPDJW9WTpUxhlNSwZCMqR+Gqn1W9HB1RVxW74WmQkrtgAjZjkKxDH5RzxjHOMc6QxPEXzPMRbR039Uw+IFgf5kfRN7VAvxW7/JytOBh2UghW5UiTuGKl9rY2nA7cjUdfr3HcqhYYQUp6UYiDoFZ8gZY44znOPpqQ2VVwsNXHSrtn3LiGaZDIEcknkY2r8u0KffjGoF56y3p8PcqOVYWGAJFGOPY4xrRx3Nj3PNUyESO0g8kvSV8lKi7YxLE7EuyjdIo98HIOMA/hplcK2BahaqGnMn2gchU2D7uOR2ODz766pKtIqpfhYCV253PyQfdMc8acVNfHV7lmjjaTOzzF/i+p1p8UOSvBA8kwoDEbZJHTVD2+KN1lmnnbIc4wqAKM5HJx66txrDP0zW21XgFHDslEoiML1EmBlUU5DBlXd6cjn2NGlX4ST7SOOopnYO0ZPysRxnjkHVotUhaamnkZpWbBEki/0QJGAgOVXG0YAViPfSc1NbrHRWxXq0FSXSHUUMdxaISqiyAB1RGCIeMEsc5PuTtBJ49NaYlWGRfc6yO5tBauumh/eFZSq7h44YQV3OygkyevzN9O3pjV6oLkKmjjlKtGzL8yN3U+o0lPGC4OHI7puKUhtHpsrbHKgX7wweDqFg20ox8u4sVyq7eBnAx+ekVq2fCq+3TOarjLRgOd6qd3PY54/lrKkgc6ZpHn9lfxLIK9v9U89MEXayB8OCR68A/XUnbIJJelaujkY+ase5fLwG3KQQwH0xnH46rdbUoQkQi37m3O5XOCM4APp76tVAorLHVS26eOOseLKjGRsA+YD2JAOsfxD3JABtRH9+C1o6dE4nfZad4Tu0nhna3bbuZpydvbPnv20a48IefCuzn387/fPo170LxzuZWc/tPgNS9MAlQTLUYB9flTjWDwrHHUlJCN4ODx835H+/W/ftJx+bN0hHhW3VMwwxwDxHxn01Xbp4Cva1NVX9Y2i3RTSfZmoUxr2yFySMnHtoduKU2ENGpVvoioVbpTkNtCSDsMZJPOl+sdo67qGUnG9M/oNW21eDk1qvdNQ/4W2tq2ZPPigEbb5EH8QGeRx31D9bdIilo6+/wdR2+5ilqEinipgSUZjgAnOAfprLxsV0fiL5/wDEtI9Qr8jKD8RjDzBtSvTkyxdL3jceBGWx9MaqkMweHk8413R1NwSwmnSknP7zwlP9mftucfJ/W54402t1ovlWsoprRX1HkyGOTy6d22MO6nA4I9tV+DYxgMxd1d9go+LTCYs0dAnrCOKeIdy2Tq119Stu6HghHLVTcc9vUnVIhobvcbgY6O2VtTJTnbKkUDM0Z/zgBkdj31J3ypq4xTUVZDLTSQJjypEKMM+4Ost+IXZcTnctRJ+VkKuHL4cEre+wVV6odI50qtxRZlKAqgbZJjG7v3wf5HVx8M7871QtdXPK0MeBTR/eWMqpDBm/rHOfbVK6uwtjjcKC6zLtPqM57aQ6WhqluUE8MsqfDq0gCrkLhCcZHHbPf6+ut/KxBlQviPUf69VzByS1rXdj/fRaZFXJSXapqBGHJlY4zg5ydUG60LxXKZMkp8z7g2Mg9h9fT8OffU9TTF1ySd55J99EsUEjAyoshU5wfXvwfpzqUUMULiSNyB6JZuTIHV0sn6pv0vTPSxV3nn7ARhk24UNIWGMrgc4z29tWMRwVVmnLBWKg/KRnP5agkqWCQwlyYqddka54UZzxpRasbtik7W4IHrpXOxjkNqPat/oroXuM4c7lyTmPoqxXbpKsr5KLyaiBSweFinb6dv5ao9d0e8ZWWknEiE7hHL8uR7ZGtUoZvhvDq7M7HG0px7njVTgmFTbjkgtGONY3hc05LnOcS0Or4WFr+KO0OGjbZUG4WuuNQI6mnEJZQM4wgAHfI4OpSjpJRNDAs4XAKAE7CCQBnPcc/n2+urDXUs90sPlwwSTiGZWdI1zleckgd8aY2i3RmL4+sZ6eFXPydpmbHAUe3ue2Cfpr0sdzNcHEbEg9/okOLVOrf0UZ1NV0dL1ZevjYZMoEp1ZHxJlVCnaT2BwTn2P11xS3yno7VRyWZp4VXMc8M0olCnuCDgEDBPHPY40tfqWGsrKq9V0wLyzmd0kb5AWJ9e5A9vXURTw1dzpZIKf4OppNwZDHEIzC/oCcZGRnuSDjTbP+gE17qXEoMpIvdWeg61SWE/ExOGU4MkQ3A/XHfT2O5U9W6yQVCSKe+08/mNZ/Pbaygcs0MkRxg7gf5EaeWKlqamvSc7o44znzFPc+2dUnhkWNim7cOav6zu0c0cSjeync3GQvqBn1Ofz1NWKcp0VcpaaVWnjixhGwUXOG5x3APbVdhhWtZ4VnVMqCVPd+QQB9fX8tKzypS9Mz09HM0SJIPiN3JmJPAyPbGcev5a81nRNlnDB3b/f0WlFkhsenyK+gfB87vCmzH3Ex/wDOfRrjwZO7wisZ91l/3z6NeqWC7mVTf2gyBcuj2K7gs85IDbTjCdj76iPFqxdTXWlvN1udpE1DDHHDbmjqQ/w6bwWfygMl3GAT6DjVm8c+mL91DJ09LZLXLcDSPOZVjK/KGVQPvEex1VI6/wAc4ymaKvKhj8uynxtxwPy1E87U9i3Sn3UVt6gv/X3T1PSZs1fPYXRnBMix/fyu8AAFhjn0zpj1Fc6T/EDVWlbabVcLVWQQ1dMUIy+/mQE/e3Y7+4x2xpE1fj0QNsFwGPeOn51GX60eNXU9qa23egraqkdlcxkQLkqcg5GD31ZpAOpJHVpqipmx3ayw2nwujroJaiq8xhHJHWCNac+cOXXByOx7jtruoW4XXpHqWmsdSvxv+FUso2VaQnywOW3FhxkjWeWfoPqii6sW3zdOVE1dDCKh6YPGCYySobJOO4P6aXuHhJ1vUV8s8XSlVHE7blXfESP7WoNd+IW1tV359lJuoj3gtPuXUdmF06/q5Kr4ukWC3o5o6oRvIw4fY47kHvjvjGqt4mXJZuobckDxzW2KgjWhqFlMrzRd8ux53A5BB/v1VV8IevdmB0zU4HbLx8f2tKR+FXX8aYHS9Tu998fP9rSuRG47RqDw87Uou+rFWW9qd5AucOpPOCNP7JUQ2+1z0VPI7zVcaRMyMfLRMhmGCBliVH0AzzzwtL4WeIMrAt01VcDH34//AHakLd4d9bUcbCTpGudm7FZIuP7WuOfLGwhrbUIBIz3SNvsmTSGkZXk+4fXTS4XBRKGiPfg6n5Og+uJqQwSdJV7AnIPmRcf2tM6jwy60dx5PSlwCnlg8kX8sNqePLKRUzd0wG72oSOuYgtgkepGu6e4BJVkUjIII1M1Xh11y1MkNP0nWx/1mZ4yT+jabU/hd13Efn6YrSD7PH/7tMMdxWnWK/ZWscQbUve6ySDpGKFHQRVj7pM9yRzxqnQVxp3aPPB1cLj0R15X26hpP8EaxfhQQXMseWz/+2mR8MOrmpSp6QuC1GeHWWPH6btIeGwezQGN43JJ9dvRXZMplfzvZcWyXFoqpVfaNuM5xye2mAiMgKBMn3HpqXi8PuvoaX4ZOmK0xFtxBeMZP+tp0vQXWUQjaHpS5rIPv5liKn+1rgxngPLXUXGx+lqh4DgAOiod+Eo8qhUqJJsupbBxt/H8dMrPHc7ZHVRS08sPmbc7RiOUAkg+xII7j3I1frj4X9U3kbK7pK6LtO6OWGWEOh9eC2CDpWm6D6/p6NaVuma+ohhBSHzpYyyqTk/xe+nGSSCAMePe69lRbw3VW/ZVlKovGuSRxrlZBuA4AHoNP6Xozqq6T1sdB0/VSvRTeRUKjJ9nIADt7+xHb3163QXW4LqelLoM/KCIuBqEQdw6dzV7Ca3TO3Tq94gK7cbskOSAQByP01KdWtT09uelJCyJKrxrHkjawySx/kNIUnQHW6zxqekrk+GHePaP1zx+Opat6B66q6V4n6YuJaWQO7F4jnA4H3tITYz35LJANh+6bZMAKW4eCv/2esX+hL/vX0ae+FtprbH4a2m3XCmelqoVk3xPjK5kYgHHHYjRrXSxVu0YHto14SAOTjQuL3A9tGvNwzjPOk3lIJCrnnHOhCxfpe133rbxhl61qo/g7Za5Hp6YY5nC7k2r7gbiSfc4H02YR7m3M2V9Ma9jj2YyBkdgNKgc5PfQhchRjkAAdhrvjUF1jdIrP0zUVktyltoQqBNFEsj5LABQrcEntzqvUPXUdf4eVVyq7jHbqyHzUJiaOWVdjlQQpO1icD6c8catbE5zdQ5XSqdK1rtJ+Kv2BowNRM3Utno6USz3OlIyq/LKrEkkAAAH3Ok7P1VbL9VVEFBI8nkRpLv24V1ZmUFT68oRqOh1XSlrbdWprjSLOS2FwAeM9+dVLpm/3a6dX9S2qukp3itkkSReTGU4YFsnJJPoPy02g6ten8SKm2VM9R8BITTwviMwiZYw7gkfOCBnvkd9T4LrI7C1HitoHuaV2SILgkZbv+GlQoHJxnVeo+srVUXuttxqIYhTRxypM06bJ0cHlTn0IIIPOm8XXFovNsuf7vrhTVFMrKhqAIiSUJSRQ33lPcH11HhP7LvEb3Vp417xqE6Zr5p+jLVXXGqWWaelikkmKhAzMB6ficajL31JVUllJeSCiuNPPTNUwLKJPLgeoCbiSBwyg8+muCMl2kILwBZVuwNecar9f1xYrdc6OhlrFd6pgoki+eOInhd7jhckEDPfTTqPrK2U9NJQ0N0zc3CGFKQJK7ZbsNx2dlOSSMDn210RPNbc0GRovdWzjSNR80bIvGRyR3A99RfT3UKdSWGG408EkAlZkaOQgsjKxVhxweQedSiJtPPLen01AtLTRUwQ4WFjXhnab34f+IVZ0lcYhUW64q9VT1aggSFR3/HHBU+w1tIX1P5fTQEGQSMkeuutcXUaMD20aNCEaNGjQhBOBnTZH3HzG7n7o9hpr1FdWs1kmrVjSQqUT7R9iLuYLudsHCjOSfYHVNPiEJOm5rhFBC89PKYiSXWnYK+0ursBn/QzuJBAzxkQr6WLSFc89wRrqLEg3EDepKk6o8viJDC8kkNrqKhoVJlAcIq/ZtMMFsZ3RpuH+kAcHOG9T4oJbkroWtTLVUoy8bVMZJdgxUKByw4BYgfKD9NCFowGNGqHV+KEFC80VTaZ1npiUmjWaMnfzgJz868csOFyM6lLZ1mLheIrW9tqIKp2kByysgEZZZG3DuAwUe/2i/XQhTl0tNDeqCSiuNLFVU0n3o5FyD9fx+uqPX+C/R0tY1UKSoiLsMQxTFYxxjgYyB+erC/UNavVE1tWkjaGJowW37X2v/EAfvAHvj01U5vFoQXitpay3KkFDLPuaOTc7xxNIpKg4Gfs84Gc52jnTAdLByNX5pVpiyL2ujW47LpfA/o5T92uOOT/lH/LVi6X6LtHR3xstpSZRUspdZJN4UL2APfHJ751AU/itbo5ZTX0M0FN5mPPSaOQInlpIXdVO4ALIMnBH11O3nqlbN03QV0lHNmvdAYnIV4tykjdjPsAfx1GTJkc2nuNJiHFa54bE3dP7R0nR2e9V91p6qsknuJDVAlkDK5H3TjAxgcDTQ+HXTp6qqOoDTSGtqFYP9odmWXazAehIJ/XTSPreqelpZo7YjLUD5FE5LA+csQGNn+cDxpc9cKXoVSkVjVvFH/TgbGd3THbnHlkn8dVDINkh3PZMnw+Sq08vhzUL/iL6O8vYI64c5z8Rz+HbSY8C+l33fE1FyqDnCFpxlF9F7dhqx9cdXno+zwVq0gq2nnEARpNgGQTknB9tVy3eLZn+NNXaMCjmjhdqWpEy/Nuwc45Hynkav9tmB06yuN8Hc7HOUIxoHXbuBy58yrP1D0/WSdIRW3p+dKSqozC9KZeU+zIIVvocahbd0bdrxT3OfreelqJK2mWlENENixxq2/72Mlt2D9MfXXTeLNkNSnlpK1LsYyykbWRh2XbjnPPOeMalenOt7b1QksVPFPHUQwCWeN14Qn+Hd2J7fkfxxBsrmjSPr1+qUdE0mz/Cqw8EemPkC1FxjjY5kiE42ye2ePQ868j8DelPPlBeuZCAVXzgNvvzjnnSs3iTPQW03Gst0cqsIpI44nZcK7MMEkHkBc/8O+lU8W7ItOkkdNWS1M0YfyUVSE+bBy+cd8/jj66ZlnyYnaHONqiKLHlbqa0Urj05ZKGwWGmt1vRkggBVd53N3JJJ9TknUsBjWeN4s2iCnVaSirKqQE7lOyPHBPcsfp/rfQ4mb91p+6rFaq6loRVz3eVYqWGSoWBSWRpBucghflU+/PH10kSSbKbAAFBWrRrN7X4q1VfLNHP0+KZomZMx1RnU7QhJLBAAPnUfU51Z7j1lbrNFaXuIkhF1kMcJUbwp2F/mxz2HoDz+uuLqsOjVDXxdsUtDVVlPTVk9PSRvNMymIMiK7oW2M4YglGxgc68fxesqF2/d9zMCeYxmEce3ZHKsTtjfnAd1HbPPbQhX3RqM6fv1N1JaI7lRxyrTyM6qZAASVdkPAJ9VOjQhSTKGUqwyDwQdN/gKfy2jaNWiP8BUbf00aNCFxDbKWnkmaGBQ88nmyM3zZbaFzz9ABr1LXRpWyVgp0NRKixvIRklRnA/tH9dGjQhLmCJm3GNCeRkqPXv+uk1oKZa81oiHxHl+Vv8A83O7GO3fn68e2jRoQlTGhkDlQXAwGxyPz01NntxZ3FDTLI8nms4hXJf+tnHf699GjQhNqjpiz1VJNTyUMISdQkhjQRs67g20lQDgkcj108noaerwJ6eORAd2HUNzjGefx0aNC6DXJexUFLAoWGmijAO7CIBznOePrzrg2qgPeip++7+iXvnOe3vo0a5SNR52u6y30lxg8mtpYaqLO7ZMgdc++DpCnsVqpY3jp7ZRwxyYLIkCgNjtkY57nRo11d1uDdF7dl7+47VtK/u2j2kg48hMZGMenpgfoNLU1toqMk01JBASu0mONV4yTjgdskn89GjQopnT9M2enWRUt1PtlYMymMEEgkjg+xJP56V/cttB+S30oPOW8lc88H09tGjXS4uNk2uBoaKAXa2e2oMLQUo7doV9CSPT3J/U64uthtV8tf7uulupq2jyCIZowyAjsQPTGjRri6mVB0X09aqU0tvtUNHTkljFBlEJPclQcHUu1HTsYSYIyac5iJQfZ8Y+X24OOPTRo0ITKXpuyTvvms9vkYEnc1MhPJJPce5J/PS5s9tZSpt9KQwYEGFeQzBj6erAE/UZ0aNCE4p6eGlhENPEkMYJISNQoGTk8D6nOjRo0IX/2Q==</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>750000</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TV LG QNED70 55" 4K AI</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Frigo Infiniton SBS 588BVA 483L</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Lave-linge LG 15kg + Seche 8kg + Frigo Sharp 560L</t>
+      <c r="B7" s="2" t="n">
+        <v>600000</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Thomson Google TV 55" QLED Pro</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAIDAQEBAAAAAAAAAAAAAAYHAwQFAgEI/8QAURAAAQMDAgIFBggJCQUJAAAAAQIDBAAFEQYhEjEHEyJBURQyYXGS0QgVFyNDVIGRFhgkQlZik6HSUlNVcnOisbPBREZkdJQmMzQ2RYKE4fH/xAAbAQEAAgMBAQAAAAAAAAAAAAAAAQIDBAUGB//EADYRAAIBAgMGAwcCBgMAAAAAAAABAgMRBBIhBRMxQVGRFCJhUnGBobHR4SMyFUJTwfDxQ2Ki/9oADAMBAAIRAxEAPwD9I0pSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlcq+6nsumWWnbzcWIDbyihtTpwFEDOB9lAdWlRD5V9DfpPb/bPup8q2hv0nge2fdU2ZF0S+lRH5VdDfpNA9s+6ty26/0teH1s269RpbiE8aktEqIGcZ5eNLNhtIkVK5/x7bvrI9lXup8e276yPZV7qtkl0K7yHU6FK5/x5bj/ALQPZV7q+/Hdv+sD2Ve6oyS6DPHqb9K0Pju3/WB7KvdT47t/1geyr3UyS6DPHqb9K0Pju3/WB7KvdT47t/1geyr3UyS6DPHqb9K0Pju3/WB7KvdT47t/1geyr3UyS6DPHqb9K0Pjy3/WB7KvdT48t/1geyr3UyS6DPHqb9K0Pju3/WB7KvdT47t+ceUD2Ve6mSXQZ49TfpmqNldNeom7o/Fj263uhDy22wEOFSgFEDYK57Vi+W7U5SpQtVvIT5x6pzA3xv2tt9qwb2J3FsXFNXsu6L3zSqJR016qcSVIs8FSRzKWXSB/ero6b6X79eNV2+1SoEFluS+GXClCwtPPPNXOiqxZWWx8VCLk0tPUuWlKVlOQKr/pW0HN19AtsOFMjxFxnlvKU8lRBHDw4GPXVgVhX/4tv+qr/SpTtqQ1c/PX4uN//p22/s3K+/i5X/8Ap22/s3Kt67s3herGmY13uEeCuO4+91TLZS3w8ISlJKDuSVHBydq4zV21w3Y7RxREvPvqU8pW/WrSEKWEOJ4AlGcJTzz9tN7I3YbPzxUoyWvrbr1930K7/Fzv/wDTtu/ZuVKdBdDt10ld5MyVdIchDzHVBLaVgg8QOd/VXVeveokwkybbKuU58x1mW29A6ptlwpwgIBSDxBZG2VbAk1tSLjrSK9AYlDgRHW6l59hjrlSwhCiFlIHZSTwjhG5OcYAqY1pRd0Wlsq6s5Lnzaenpa/8AtciQDTz4+nb+419/B9/+eb+41D4N91WliU6FzZhS0jjeEcqbbKlgKUltTSFFSU8SgkEjxrZen6mekeTWS4T34slxptubMhhJbcypSyBwJyjhSASRzOAayeLqMxPYcU7OS7v7fklHxA8Ppm/uNaLrCmXltkglJxkVm0pc7zdZdweukV2ElotsJjrTgBxKSXFJP5ySSMHwFbMpsGW6f1jWejXlN6nKxmDWHlkXH335XOdwmmD4VuhoeFfeqHgK2c5o7s0QPQKFPorf6oeFfOqHgKbwbtmgUjwp1dbpaHgKdWPAUzkbs0igmvPVqHhW91Y8KFCfCpzjdnPUFV8DaioZON/Gt4tpPcK+BpIWnbvFW3hV0z86gy06rdTBb62UuU422jGeMqUU8OPTnFWBcdJa6tVkXOPxW6llHG7HYQCtKQrrOWAFYVk4z486gsdF0XrVwWVLqrimU6pjqgOLIUrcZ25ZqyOj57ysahimTJ/DSQy4mQJmS2OE8I2G2RkZ91ecjq2j6tjZSpwjONnZK+l38ei9epELXI1LeoqJrcqGxDaWtBddTwtshKQtROAdu2PWVYArDphmVG6XoDM0JEpFyKXuA5Tx5OcejNZdEyLQzDmxLw7GbHEFNtOSZDanXU+aMNbYSRniIJ8KwaUS4jpatyXlBTouPbUOLBOTk9rtffv41XoZZab6KVkovlbl1P02OVKDlStw8CKhvSFr6NoCPAmyYL0wSXFshLS0pKTwhWTn1VMqo34T764+mrCpBSCZixv/AGZqVx1IfDQ2PxkLZ+j079s3X38ZC1/o9O/bN1Q2mbBdtUR50mPLtcKLA6vr5E+R1DaSskJHEQdzg7Vmsem7tfnbp5NcLOxGtakpfmSZPVR8qUUp4Vkb5IOPEVfylPMXp+Mda/0enftm6kWjemCFrG5vwmLTJiqZZ64qccSQRxAY29dfnK16UuNziPyUXO2IZZkSI5cytaVhhkvOOJIG6MAAHvKhWfo11TOtN7lPx/JgpcbhPWZxjiB7u+pioX1KzlNR0P1yLy2foV/eK9C7I/mlffVJp6Sbvw54rdj/AN1Zk9JF3/lW371VmyUjW3tUuj40SfolffWk4vrHlrAxxHNVT8ot523tfPHNVZR0hXvIA+LCTt5yqmKhHgRKU5cSz6+1Wq9dagbGVtWvH9pn/WvC9e39BUFItiSOYKyDVsyKWZZ1M1WH4f39Q/8AS/bNYjr7UCgCHLWM/rGozInKy0zzrzmqoVr/AFEDnr7XgHGDmvJ6Q9QcWOttfLP51TniMrLYJryTVTnpFv6QMvWzf0KrwrpFv2/5RbBj9VVTniVyMtgmvIX20+sVUh6R77w58rte/wCoqtdfSVfQsAS7Z6+rVVt5EjJIiy7lItGrXrhDcDciNLccQrmMhZ5jvHd9tTSV0yS1xZCoVjt8G4yUcDsxs5UfTjGSfDJOPTUPY1prqZZJF4Rd4Iisqwr8kZ2J63HMZ26vf+sK60e/apXBYdev0NTjrYcHAwykKyM4AKMg92+3f6K5appcJfL8nsqm16dXLvKCbX/b8HN01quZpeYp+KzFe4yCrrUdrbwWMKT9hrc0dJTL6UrXJSkoD0/rAlS+MjJJwVHnz518uFy16HB5Bd7eoEZLb7LKVADOT5uMbD07+useiukDWMfpVtFhuU+E4iVKbbfS3HaOUkE7KAyOfdUbqKWkvl+TJLbanm/Rs5K1834P1IOVKDlSsh54VRXwokpVpmwhRIHlq+X9mavWqL+FEAdM2IlQSBMWcn+yNQ720BA+jiDc39EGLbdOWnUsGddE+XsSCS7HCUhKVKHEAlOCohe+DnNdayWdcZq+2zSljtGqrG/fOreZkLUtxltAwhR7QHBurhc35HNQROiYbNxYsLmofJ9SSkoQmN5MfJw4tIUhhb3FkLOQPNKQTgnmawWrRzsi/wCnLUqeWnr7F68lLRPU9p0cBSFDj/7o7ZHOqXlYhGtq2Fa7XrC7QrPMcctTMpxtjq3eIcB2ODntDuz3gCujoNzT8CbNkXtxwstRVL+aeDaiQoHAGDxHuwPXtvXTOi7cu3OD40Xb1mWzb2PLbYps9a43xjrEhRLQ7snPMHlULEVUOZPjS4yWp0VRaW2+vsqUlwBSCOR5Hl4Vk+IsnxRc8NnSF9tAlWlctoKIAU4/xekpxwDfevf4O2364v7z7q4cS33uezHt8a1Fu3rwWpCHWGODs5PCSkKIznY8x6qkVg0nf4QW1eW1rKl9gsPIdJ8BsfDcjurlVa2JlDeUGnrouf15CpRcJONkYZFns0RoLlXJLKFci45wjP2prfh6Tiz0KMR7rgEcfF1oCTtkb8PfUP6QLbNjzmpkltTdliEJWoDLuVYCsjOBjGB6edSaQxczplmFZZUxDjjSFm4BS1Op280NBfB4DPr2rZw3iZuKrWXXXtzf9zL4emqKqSerbVre71RxLpqHS9qlriOpZvfza0yo7Lqz1ahtgLSkZx3kGupZ7orUEGBapLKkyozSiJLE1vKY6U7BfFhS+HYd576jMW0a2bLi313lS1NqSlLCmo6eLuKllR7PiMb+ipZpDT78AMz7vqG2ybsWyhCXZaSpkqBHCnfHfueZ9Hf2KmIp0YZFHj6u4w2z1iJNxk0lx00+pq3dy02t2CmVPkqTLbLyQVhSy3jsrSM8idskH7Odb8Gx2ybFbfYkSFocGUpLiQR6CMc64sbQcWRqWVIuFnn3RLZ6lD8N75tpQBynq/OO+c74Ttipb8Y2RlcVtEtLbklsuNJdWGFLyQCAkHA5jbOedc2vOThB05K76t/HmXWCUK8qNS6tror8eBzjpmGlZy7JOfzesTmitKRi31v5YUcHHxBaccPj6vTUjbtbrScoipQlxHB84/gFPPh3XXmTPDSn237bayoISl4KCThA80K7RwB91Y4qol52u7+5meGw7dqWaXwIyvRHECvjuQQCPzUEAnl9/d41rr03AS6GlvXDrFu9QEgDJcAyUbfnY3xUpcvDctwIXGtQMpSXcloZcUnzVZG5I7j3VqhqH88tUq2oSh7rnHC4ohLveo7bK9POr5or+b/0yFgHzhLsRNNksDiE8Nyl8OSASQMkHcfZWRGk7O9uibLWOWQupU3GgsqKG5VsDiwVhBjqUVA8yAU5+0VoOzAppakJhqjhfAXEsICSfXgb1beUl+6XzZK2bUm/JB/HQhCwhC1JDTBCSQCWG9/7tbMZhMhIJehNYVjDjaBjbOfN5d3rrZt4kRLmpwxUKB4k4kMKUgeBwB44rrTZBlx1JVHhJ7aVhLLC0kAKJUAeDmrIHhgV5iLm7tyfzPo040oWhGmuWtl9iPymxGUjD8N/OTlpCDw+vs9+a62iCDryy/Nsg+VJ3DKAe/vAzXUlXQLfUpq329TZ80OMrUR6Nkjb3Dw3wacXJmdJttluMKTxS0ZKEK4cBOOZHorKs0akbSb1XU15budCeaml5Xrpx7H6HHKlBypXpz5oKo34T6QvTViB5GY5/lmryqjPhQEjTVhx9cX/AJZoCq4HSHCg3drUEjTrcy+JQhtx1yRiO6UcOHS3wEpc7CTlKgMjOOYPGtvSJAj3LTc42R9y4WVHUB0z8Ida4nVEFPBsr509rPdyrUk6YfEJpbjxabkFoBxxvhbPHjkrO+M5O3ca+J6OrgJP5M/EeBOEhx5KVnONijJIO/Lc/aQCTT1TuLO1zpR9eQIEaWwLG9PbTMZuMbyy4qd6t1DZQOsISC4nJzjs9w5V86P78+/rC4z5khpb0ppa3FyHQ2grU4FFXrzk4FcqdomZEnLgvT4CHVhBRwLBSolRTgkeaQRvmsWlrFLlz5MdpmNLRwZIcUpAUArYgggj1VhxFBV6UqT5mWjU3U1PodPUuq5t1vPXMzT1ENRU0tJIQTnzgD92c71Z2mtSNat0XLU+5wqaZKZCApRJIQRxJwD3cskVX8jQ11kJSE2y3JSk8QBluqH71EVsW7RWqIrjpjSGYCXUdW4iO+QlafA7jNKWHjSpqEY8OBFSo6k3NvibI1teHiWru4iVEfGzTjQ4UqTggb54tu899fbfqpEF9SYDUdoEE/lEtaU537PCN8VFtb3qDIuTaILZZU0PnkqRwFDnClKk+nBSd/1q+6YtV1lxPjJFtclxes5oRlSuHmkHOwPI7VtWSWVFIVJRea5bNonfhdaFtSJrNphr4BIeRxuLf4twhGVYABBBO+SO/lW+zo/QYuSISrtOU68EltR4Ak5HEBgHi5b71X0KVqjTDuWrH1sVQCyhXA8jhGcBWdwRk789693npKkXKQ0/8RKiLaAT2XkpTt/h9laboQk7yidz+J4qjG2HqpJ8bafVX+bN+86pafuLwftUpxmJLUol6QkOHqzw8YTjzsDJ57d53qQ3PW1qRakKgWCA9NGEtvONJc4E7nO4yTk8s43qENyWnNMPXlx1ZLqHA7ghSesCldhR9IUCPHeodbrg5MmRIPER1qksjB7zsPsrPKChTajoaFHEyrYmEsR5kml0VvgWQ30lXeKtKZLdskthfGQ7DbAznxSAc/bViWHVth1PHcD1qiMv8OXmkMp40frjAHGnx7x++qYuOnZkFLYbLU8rVwhMRXW789+HOPXitu1229NXFl1h2PAdbUFIcedW0pJ8c8O1cuO95K69T2tV4JXjOSjJcLJ/2/2T7VbrVijKuMdDS4gSQhB2UFdyQc9/d9tQGF0gSHllt2LCIySA1kpVjmk9+fT31Pkak0vc7dcLZq9ZieTgNyX4CA5HfJ3StOBlK84OU7ZHdyqnpWmrpCecTbm1zYrb56iQEdUXEAHCilWCM55HvzWzRpU1rJdzh7RxmMbUKbaS6c/e/wDPXUteFe2ZUBuWylkJVseLzknOCDvmvrl0cPZSwwlAP82Diq2tt9vumYamX7GmQFLLnWKd3GwBHZJHdVsxUOWvSErVki3fNNQRKZacUFNuOr4Q2kgcxxK5d+K4VfC4p18tP9renp77HKrY/HyV5za+FiovIXO2JNmvDr6lrJcal8CTlRxhJSfR31nLUBKUEadviiB2wq4YBPLw5Hn6/RVjXG4dJGmtVMNpU/qNDLbT0thi2DqUFYyWSUo2ITg5GMZG1S1ubdbgEvQFqWw4FKCH47SHWiCAptxJTstJIBHfsRsa71Xf0YpuzXon9zVwtB4mTjmSfqUIUQ2wSuyXsDlvcMfb5nOpT0ZWmVP6QLJJtllu4bhT0OSn1yOtbabIOAoADG45+urgiJuL8YF550OZIIRHYKR94519EjUNulBVudUG85VxIaQF4PIgAZHvqka81rJfL8m4tmzcnHPH5/YtccqVy7De2b5bw+2OB1CuB5rOS2scx6vA0rdTTV0c2cJQk4yWqOpVFfCjVw6asB/41f8AlGr1qjPhPjOm7Dv/ALav/LNSVPz3YrNKv812LBShT6GVvBGDxOYwOFOB5xJAGdqkczo7u9onxGZDjLapNyNuZcSFAFSQCtwHA7CSSM9+CRtXEsFkmXmY/HhSmI60R3HlqeeDKVITglPFy8Nj4V3ZGidQoupiG4sPOtvrCnPKlcCV7pKwo44s4xlOe4GhJyr9p2Xp5EZcpbDiJScpU24Fb8KVKGx3xxjfke6ux0cym2r5KKxkGPjmP5QqP3ePc4rrMS6POOFtHE0hT3WpQk+G5Azj91dzo7hIkXuSlSQQGM7g/wAoUuLFoIlR3MbfeBQpiupIU2nlvkVqJs7IXukjwHEQP8KzJtSCs4C8Y7lnlU5hY1nNOWSQouOQoqirclSAT99ZU6WsZbCFQIpSOQxgAejato2kkbKcxt5rtekWySCcOS9v101OYixoOaG027uq3tJ/qrUk/uNajnRrph4ZMZXF4dcsj/Gu98XzBuHH+HfmgK/wr35JMBHzjmfSwaZhYiEnomsTyAlt6VHRz4W17H7DmsUfoksjHKXKLmchXFuPuAqZKZmJISVEgn+aI/0opMhA3WkZPftS4V1qiKHoziBQKLtLA8OPNbcXRiIo7E8Lx/LjtL/xrvLMhI3UjI/WHvrEpcpKVAIQfUQf9aqlFcEZZVasneUm/ic9zTY/NkM5HJSYbGfs7NcF7o1s65q33vKVOKPETwpCSf6oGPsqTuOy0Ep8mGB6KxF+SFEeTknmSP8A8q10Ym2zDFs0SMgNcKlJSMAdQhO32JFdNTCLjYZNpgoK5bjseQ1GdWQiSGXOPqM/mle2PSAO+uYqW+kZ8neB35CsCp7wSVcDqfTjH+tWzFWiY2jpP0xJ6m63Jtdqurrxdmxm0vrypPZSMhaUhWEjOUnwxtWCxR3r3ZYMhUphh2e7Ju6zNd4OIOvYQCe/sIT9lROTeIkuWZU7T1nmS14UuRIg8TjhHeo8QCj4kjfvrdka7kyHeN23Wpa8AdqIeQGAPO2AGKxVo54ZYm3g6yoVd5Lle1iY+QKU4pKjac5IHDnG6wrnyx3f1a8Ks7s9zhRKtUUDiPF1hbByc8/RnA9FQn8O5DfaRbrShXoiEH/Gp30WPQtYKuouVrtyvJC1wdVH4PO4s5335CtN4Z/4zrR2pFO6b7L7kt6OoBhWeUtSkrU5JUnjQcpUE9nIPeM5pUsZYajsoZZbS22gYShIwAPQKVtU4ZIqJx8RWderKo+ZkqkPhNAHTliz9cX/AJZq76on4UefwasGDj8tX/lmrPRGAoWNMMdoNiPGcA3y6yFH766HUTnEeWot0Utlrz0MJwkDtZPgdvu9dR+AmKXVqlyHGuEAtgNdYlZyNlbggYzyz6q63lFuUVFYhKzvkCQnHqAGB6qw7wm57kXFyU0ULYjDshPEhkJIAxjf7KlnRVGS7qCcMoH5L+cnI89NQOcuOOFcSUtallRWjqihDe+wSSSSPWByqUdHN7nW28y1xi2VLjcOVtpWB2h41iq4hU4uUlwGax+srpd7bY2YglMZ68FKAhsHJABPqrCNSWtKnguItstZzxNo3wQDjffmK5XykaXdZbEhTrikpGQYxVg43r2rpF0stGVdcsDkPJCef2VHjaH9RdzJGVKyTWvvNjVgZuGiVSWG+BLiA8jYJOCkkcqqS02+S/Bae65lKVpynrHwknBwdjU61bru2TtOKhWgrDyiBwuRylPBgg48OdV1AK4oQcKStPIgV1Nn7SwkVOMqsVw4tep5/alKdScXCLa14HdbtMhZWA9GBRz+fT765eoYj34K3xrrDxtR0kltzbz09458+6tly4OuNcB7KFjtBDSU59eAKwPSAu2TIgTkS2w2Ty4cKBz+6tnEbVwbpP8AVi+HBrqjSoUakKieV8/oVjD07cpYStoyn0qOAll/Ks+B37PrNY0W4Sj1SHpTDx8zjfKkrP8AJJ2wT3cxnwqwIbkq3soixpQbSFFxB6sHhyADgnburfXMu7rBaXOTnrEuBfVoSpODnAwOWcH7K0Xj8Iv+SPdG+nUtwfYy/B9hK+OrgXip1PCnAc7Q5Hxq0U690wZT7Ko7iOo4uJZjgjCVhCjsc8z4VB+jiXA0xNmSrg+4kvEAcLZVk75Jx66nB1po9l1xxDQ6xY7akwjlWeeTjetGpj8M5+WpHudjCSgqT3kXflyt7zOjXeklyA0JbHaUEpV1XZVkDlt4nHrqsOnaE85qS2swkgOPgJShB4MnB79h99WR+HWkAUkNnPMYhnb91Vl0tSWdZSYci0PZS15/X/NAbYGM08dhv6i7klex9I6jkuJbbaPWLWG0pMgZKjnbYkbBKic4AAr27orVDURUlyG71KUdYSHc7cKlcgeeEkY7jtzry1pa8qT1aJcVA4Qnh8sCRgbgEeGTWYaNv6CViXETw7ki4Ac/t76zLFUJcJruiDmTpiodvtpK1DrWCvJVz7RFdqTpa+Qrdb5s0MxGriw7JYLzwGW0N9Zk4JxlPcftrXv+hr/doNqbtwgumBGUy/iUhOFcZVz79iN648iLrryOHDfvbS48NBRHaVcUlLSVJKCAPApJTjwNN/T9pEnu5OS7TI6iajqXSkq4eIE44inO3pSceI35Grz6BmFMovSlDHWBhQ2x3Lr88v6W1XdHutdWzLdCEtBapaVnhSkJSn1AAAeqv0l0LANt3NggB1luOhzA3yAr/wC6upxk/KyS1KUpVyBUE6UOjw9IMG3x/LGYyYbynT1rZWFZTw9xGKndYZEVuSnhczj0HFAUC58G1Jxw3yA1jniOs5+9dYj8G4DnqOB/0qv46vNzTsNw7lz2jWurSMBX57vtGosgUn+LmlIx+EsAD/llfx1nidAj1vcUuLq6EwtSeElEY7jw86rgVou3q+ke9qvB0NAP0r3tVVwjJWaBVaehq5tk8OuIyc88Rz/FXv5JLuMf9vWBj/hz/FVnHQcA/Sve1Xk6BgH6Z72qxvDUXxguyIsisD0Q3TOTryN/05/ir6eiO6KIzryOT3Zjn+KrMPR/BP07v31je6O4TrDjaZb7ZWkpC0ndORjIp4aj7C7IWR+dJ7t3g3KTFj6gVJbYcU2l5KOELwcZA8K1zcb7zN5X91XH+Lxav0guXsN+6h+DvaSMG/3H2G/dUeFoewuyJKHf1ldGbkYRur6lpWGwoJHCc9/L011hc78cYvSzj0Va6/gyWFcjr1X25cec54W/dW2Pg72kcr/cfYb91R4Sh7C7IFPx5d3clNNu31bLbi0pW5w8XACd1Y78c6sv5LLypAHygsFPMfMH+Kur+Lvaf6fuXsN+6pbD6NoUSCzHVNkPFpAR1izhSsDGTjap8LQ9hdkLFejonvGMDXzGP+XP8VPkku5/39jn/wCOf4qskdH8EfTu/fXoaBgD6Z72qeFoewuyBWfyPXU/78xv+mP8VPkauyj/AOeIxz/w5/iqzhoSAPpXvar2ND28fSve1U+Go+wuyBVvyKXUpUn8NY2Fcx5Md/71fFdBdzcKSrWEVRTsPyU7f3qtdOi7en8972qyo0nAQdlO+2ancUl/KuyIsVK30D3VK+JGro4PPIjH+Kp/0d6FnaOeuLk27puPlgbCcNlPBw8XiTnPF+6pI3p+I1yLntGugyylhHAjOPSasqUIu6iuxNjJSlKyAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKA//2Q==</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Infiniton Réfrigérateur Américain SBS-668 559L</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAIDAQEBAAAAAAAAAAAAAAMGBAUHAgEI/8QATRAAAQMDAQUDBQsGCwkAAAAAAQACAwQFEQYHEiExshNRYSZBc3SxFBYiMjZkcXKBkdEVUlVjkpQIFyMkN0NGgoOiwTVFhJOhs8Lh8P/EABkBAQEBAQEBAAAAAAAAAAAAAAABAgMFBP/EACQRAQACAwACAQMFAAAAAAAAAAABAgMRMRNBEhVRoRQhkbHS/9oADAMBAAIRAxEAPwD9BXO+WyzOphca2GlNVJ2MPaOx2j8E7o8cArU2zaLpC818FFQahoZ6io4QxiTBkPc3PM+AVd2tWq4XOo0oaGinqhT3XtZuyjLuzZ2TxvOxyGSOKq503eBsF0XR/kmr/Klvr6SYw9ie1g3ZnFziObcNPHwQdOqde6WpLy60zX2jFe2RsToA/ec154BpxnB8CvFVtC0lRWuG41F/oY6WokfDE8yZ7R7ThwaOZweeBwVO2VaW1BQWyerqrrX2wS3WpqJqGSkiHbAyn4Rc5u/8IY45+hVPZVpm9UO0KyTXS0VsFPSUNfh88DmtjkfVOI4kYBLTnxBQdYpdpejq2JslPqGika4yhuHHJMbA+QYxn4LSCfpXu37RtI3WuFHQ3+jnqDn4DXHIwC454cMAE8e5ci0lpq+0+2Slr5rRXRUbNQ3ed074XBgjfAwMfnucQQD51YX6Wvdxtu1ihgpZoJrtUH3E6VpY2cdkB8EngQcbueXFBf7btB0leKmSnt+obfVTRxulLI5gSWN+M4d4GDkjK82vaJpG818NFb9QUNRUz57KNsmDJ9XPxvsXMq6kuWphoykt+lrtbJLDTyuq5amkMLYgKcs7JhPx9535vgVJPpu8fxG6EpW2qrNzt1wo5XRCE9rAGyO3nEc2gA8UHbkQIgIiICIiAiIgIiICIiAq3rzVbtGaWku7KQVhZKyPsjJuZ3jjOcFWRc625DOzGo9Zg611w1i2Stbc2zbep0qbP4QlTJkjTcTWjm51YQB/kR/8ISpjwTpqIhw4EVhIP27i40wB8XZlwYQ7eBdwB83E/wD3nXx+GwtjB3zkuJA4DwC9v9Jg3rX9vn3kfrTQuqXax0tDeH0gozJI9nZB+/jddjngIq/sR/owpPTzdZReJlrFclqxyJfRXkbdDREXJoREQEREBEUNVV09FF2tVPFBGTjekeGjPdkoJkWtdqOyt53ehH/EM/FfPfLY/wBMUH7wz8UGzRav3zWL9M0H7wz8V7h1BZ6mZsMF0o5ZHnDWMnaST4DKDYosOovFtpXNbUXClhLhkCSZrcj7SoffFZf0vQfvLPxQbJFrffFZf0xQfvLPxXoX+0H/AHpRfvDPxQbBFgfl20nlc6M/47PxWVT1UFU0up5o5mg4JY4OAP2IJUREBVnaBbZbrpOWlgtzrhI6RhETS0HgfjfCIHBWZCAeaxekXrNZ9umLJOO8Xj04KNC3XcA95b844n+Q4nv+Ovr9DXQnLNEvHm5wn7vhrvGB3L7gdy876Zi+8/y9f61m+35t/pWtC2+W2aYgppbYbY9r3kwFwOMnnwJHHmisgAHmRejjpGOsUj08jJknJebz7fURFtzEREBERAVI2sDOjohz/nbPY5XdUrapg6SiHzpnsckDixjHcFG5gxyCyyxRli0yxizB5BYV1u1RYbVU3GkbGZ4WENEjct+ENw8seZxWzcxaHWDfJOu+oOoKo+aa3n6VoC8lxEeATx8wWc5g7gsbTLcaUoPRj2BRxX2gqbs+3RyONSwuBbuEDhz4rQncwZ5D7lE5g7h9yzHNUD2qohEhaN0NZgd7B+C7fsPAGlrhgAfzzzejauIlvFdv2IDyVr/XD/22rFlh0tERYbEREBERAREQEREBERAREQFStqfHS8HrTelyuqpe1HjpmD1pvS5ByJzVGW8FkuaoyxbRjubxWg1i3yTrvqt6grG5vFaDWLfJOu+q3qCD5pxvkpQeiHsCqtqMbtay7rAJGz1G87vBAwPswfvVv063yVt/oh7Aqva7bUx62lqH0krIy+f+UMZAweXHkcrTK2Y4BROasktULwqjHc3iu2bExjS1f64ehq4q5dr2KfJau9cPQ1YssddIREWGxERAREQEREBERAREQEREBUzacM6bg9Zb0uVzVO2mDOnIPWW9LkHKHN4rwQpyFG4ZWkY7gq/rQbukK8nzMb1BWN44qva5HkXcfqDqCok02M6Wt/om+wLOcwdyxNMt8lLd6FvsCz3DgqkcYr2HuKx3t4edeo9kfvgq6mujvksL5WGo7N0eWgk/F5qGLRzNKRHcuEtZ7qJz2jcbm7w4cTzypEkw8O4Fdq2K/JWu9cPQ1cWeF2vYsPJKsPzx3Q1LEOioiLDQo6ioipKaWonkbFDEwve9xwGtAySfsCkWJdaAXS0VdA6QxtqoXwl4GS0OaW5/6oPD7zb2TU8PupjpKhgkjY3Li5pOA7A5DjzPBYvvssfud04uMRhDxGHjJa9xzgMOPhn4J+LnkVpotL3SG4Ute19F28NJFRyguk3ZGRkkEAAFp+E7znn4LXR6bvdLbrTSwTsJscjTQP7ElzGiN0W68HAeNx+MjdPAHvQXyjrKa4UcVXSTx1FPM0PjkjcHNcD5wQi1ulLSLHpmjt43yYWu3i/m5xcXOPIcySceKINwiIgIiICIiAqdtL+TsHrLelyuKp20s+TsA+ct6XIOXEKMhSlRuW0Ruaq3rr5E3H6g6grK7kq1rv5E3H6jesIMnTQ8lLb6BvsCznDgsLTXyVtvoG+wLOdyVSOLFZa6GkpGOmqGRucd0AyBpwB9PJaLUdTHUVr2wuD445HBpacjjg8FhSLGeromWO9dq2LjGkav1x3Q1cVeu17GPkhVeuO6GqW4kOhoiLm2IiIGQF8yFT9W6lktlnFTT2+a61M0jm01viOHVDWHMjuYz8EOI5+bgfNW9Na4qb7qQ22jtdPRMAibHcKeR0lLLK6MSui8284MzkAZGCcjCDqqKCjqPdVKybd3S7m380jgR9hBRBOiIgIiICIiAqhtIbvafp+8VA6XK3qp7RP9gQ+sDpckDlhYQV4LCst2FGcYW0YrmFVrXbCNEXH6jetqtjsKta5AOjq8HlhnW1Ue9NsPvUtvoG+wLNewqPTwA0vbh+ob7Ast+AqzHGA9hWO9hWe/CxpMKowHsOV2rY03d0hVeuO6Wrjj8Ls+x/5I1B76t3S1ZtxY6vyIi5tiIiDlW0fSdReKOnlttoZX3u2b/uZs7iInsflrTwI3nN3845DBJ8wOg0XszNl1HTyXOxe5LZbXNqqSaaTfqZpnRhr4iGO3SO0y5vDPLjgYXcJaeKdm5LG17fHzKKG3UlO/fjhbv8t4kucPtPFAt8UkNE1soxI4ue4dxcS4j7yiyUQEREBERAREQFUdoxxp+D1gdLlblTtpbt3TtOfnLelyQS5qX8VGXKN0nFRuk4LaJXPVa1y/Gjq7+51tW9dLxVa1zJnR9d/c62qpLaaff5MW70DfYFlPetbYJMaXt3oG+wLJfLlVPT696x3vR8ix3yKoPdxXa9jxzoyb1t/S1cNdJxXcNjRzoqc/PH9LVm3FjroCIi5tiIvEz3Mhe9oyWtJA7+CCOSoLXFsUbpXDnjgB9JK8MrSHtZPC6AuOGkkFpPdkef6Vpbj2jaWL3FIZqjfG+wzmPIOCcebPLn3qO3TPuck7a2OSiy7djjMu8XN4OJOOHcpv99M/KN6WhFBQyPmoIJJPjvja4/ThFWk6IiAiIgIiICpO1J27pqnPzpvS5XZUTay7d0vTett6XKx0crdKvBlWMZD3rwZCtIyHSqt63kzpGtGfzOoLbukPeq7rSQnStYPq9QVSW3sUmNM24Z/qG+wLKfKtXZHkact4/UN9gWQ+QrTKR8qgfL4qN8hWO+RBK6Vd22KO3tDzn57J0sX5+Lzld+2HHOg5z8+k6WLNuLHXR0RFzbEREFN1hadQ1VE2nsvYmnOe0aHBkp8A48MfcVi6PsOo6OJ8F0bDFR4w1rnB8w8GkcgR3k+CviLn44+XzcPDHk8m53+HxrQxoaBgDkO5F9RdHcREQEREBERAVB2vnGlKX1tvQ5X5c92yu3dJUp+eN6HKx0lx0ycF4MigMijdJ4rppnaZ0ir2sn+S9UO/d6gtw6TxWg1e7OmqkeLeoJKNrZ3+T1B6FvsCnc9YFof5P0HoW+wKZ0niiPT3qB7uC8veoXP4Kj2Xcea/QWws50BP69L0sX53Ll+hthH9H8/r0vSxS3FjrpaIi5NiIiAiIgIiICIiAiIgIiIC5xtsdu6OpD89b0OXR1zPbs9sWhqaV7gxjK1m85xwBlrhxPm4qx1J44iZfFeDL4rCbWwP+LPG76Hgr12zD/WM/aC6ubIMnitHqt+dOzjxb1BbIyN/Pb961WpG9tYZmsIc4luADkniFJWGwtMmLBQj9UFK9/isK1yN/IlGzeG8yPdcM8Qe5SvkaDxe37wrED096ic9eHSs/PZ+0FGZo/PIz9oKiXeX6L2DHOzyX16XpYvzWamEc5ox9Lwv0psFBOzcyAZZLWSvY7zOGGjIPnGQePgs241DpiIi5NCIiAiIgIiICIiAiIgIiICx66hprlRyUtZAyeCQYdHI0OafsKyEQUODYpoGDOLC1xJyS6eTj/mWS3ZDoNvLTdKfrOefa5XNE2Kg3ZRoZvLTNCfpaT/qvQ2WaHH9mLd/ylbUTYqI2VaGbMZRpi3h5GCez/8Aa+nZZod3PTFuP+EraiCoHZRoUjHvXt32R4/1Xg7I9Bn+zFD9zvxVyRBR5djOz6bG/pik4ceDnj/yV0ggipoWxQxtjjYMNaxoaAPABSIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiD//Z</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Samsung 50 45k UHD CRISTAL</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="2" t="n">
+        <v>700000</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 65 Crystal UHD 4K Smart TV One UI Tizen, HDR10+, design MetalStream + Support gratuit, 65U8075F</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAMAAwEBAAAAAAAAAAAAAAQFBgIDBwEI/8QAURAAAgEDAgMDBQ0DBwgLAQAAAQIDAAQRBSEGEjETQVEHImFxshQWFzI3QlZ1gZGU0dIjlaEVUlOSscHhM0NiZXSEosIkJTZFRlVyc4KD8IX/xAAbAQEAAwEBAQEAAAAAAAAAAAAAAwQFAgEGB//EADIRAAIBAwMBBgUDBAMAAAAAAAABAgMRIQQSMUEFEyJRcaEVYYGR8BQysQYjweFCYvH/2gAMAwEAAhEDEQA/AP0jSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgFKUoBSlKAUpSgI2pahb6VpdzqF0xW3tYmmkIGSFUZO3fsKwg8uPBZAIuL8gjIxYy7/wAK0vHnye6//sE/sGvH9C069k4c0OGAFpbm1h7Ic2A3MABv3VxKTisIv6LSx1MnGUttlc3Y8uHBpO02oH/cJfyr78N/BucdrqOfq+X8qylodRt9Zt7GG4tp7iXnKtHOSg5M84YkAqRynqKupF1a9u70Fo19wYM0ay4L+bnIPeMdB6a8U2+hdn2ZTi1aqrWv/gsfhv4Nz/ltQ/AS/lT4b+DT0m1A/wC4S/lVbHaand21kqOvJdr7ot42nJJ80E8383CtmpK3NxHbS8s6FIIRM0sUvMChONvTnuODXLqNdCtLRQTtGd2Sfhw4NHWbUR//AD5f00+HDg3OO21DPh/J836akpb3kT3UQkHNb47Vmk6EjO3jtXF9NvFuJDM6w8pEfO8uAzEbAGuHWmv+JytJDrM6Phw4N/ptR/d836afDhwaR/ldS/d836akW9xLdWkkLycpV8uuTkHoeldkkzpHyczsO4gnp0qN6rrYPRWdnIhHy48GgZMuo4+r5v00+HHg3vl1L93zfprjLdyqxZWOB0GaW9w7oX7SQk483m+LvvUcda5cRJn2a7X3H0+XTgsf57Uv3fN+mnw58Gf02pfu+b9NfZLd1RXikZlPzebcV2QSNnBkZT6Sa8etlF2cfcPs5Wupex1fDlwYP87qX7um/TT4cuDf6TU/3dN+mpbTEIOaUk9SoJz6s19tuaYh+ZySQC/PhQPQPHpUfxBuW1Rz6kD0aWWyGfLlwaF5jJqYHidOmx7NfPh04LzjttSz4fydN+mu+4UTzyn3S8ihuQBm29XhXQ9xJbSANKw7wGJwajfaclJqUMepJHQKSxL2Pvw5cG/z9T/ds36a+Hy6cGDrLqf7um/TXeupmSTCI8yjv5yBXZfOstrzqHUjrvXT7TTT2K9vzyPV2flJsifDpwX/AEup/u6b9NPh04LH+d1L93TfpqGs5Uks7AD/AEjRp3kQmOVhjrvVX41bmHv/AKLPwj/t7Ev4deCv6bUv3dN+mvjeXfglFLNPqKqoySdOmAA/q1XJMQ2C7Z9ZqDxhzPwFrrc5x7gm6n/QNSUe1nVkkoe/+jmr2V3cXLf7Hrul6jb6xpNrqNozNb3cSzRllKkqwyNj02NKp/J98m/Dv1dB7ApW8YZy48+TziD6vn9g147wdq6wcO6ZbXL9tDHHFIsYbDrsOZQ3UAjf0EV7Fx78nnEH1fP7BrxLRrC3t+GtIuEjCvJaxOzeJKivHfob3YkI1Kk4S8jY3N9Dfah7tgt5DOtjPbm4kZFlZnGFZiOvKuRk7moEuvvaXt1cm2mMtylmjL2gKkwsOc+jmUYr5p09pcytp4lHaXCMF8OZQWA+3BH21U6wjrqbRRkskA5kUZJZcZH24I+6utt0bcdDTdV0prCXt/6Xja/bzTWTSWNwqWtzJMoilw6owCoqkd68q+g4rm/EMOoandxyJdRR3NmLRirIs7MCGMpHxcnGMeiqS0ukW2eQJmM4aPqWxnoSepG9diTrf30lw8fKGQrz42Q5BXf7MVzKLR3LQUkrxja3z+dzWyav213Pde5mHbXaTOpbqqqymM+sN/GrI8RLdKGlhlEYmSVEQqThdirZ2IP31jo7v3FyCaZcySDYtntB4n/HepMshVCyuFZ/OAyKrSukUPh9Ny4LaNgsZuMBDPM2FDdDnp/EVLhX3RISVcMcHcmqfSZFtoo2d1z8ZGcbHu2HjVy2ovBbtL5mANs7mq6hm7I5wk24o6p1/bHcAjYrjcV1xoouUaIKzqOZlyc49QquF3cXNyxI85jscbAeNTrSIwIwQqZj3npXMVFyJ3Bxha+SZI0jhXityhzjmzscDcYNdckmJcNLzbYLkYxneuMEc2cuVGOuMn+2g7Oa5A5clgSHz8Uerv6dDXlSDdkVrbDtm7MiJAe0c5J+aAB/GlspRti3ZRAks3Ude6vrzyTanGqQiQLHzKVA5Tt456/fUfUJo7V5hJcu+Y8KkYC7AnqSO89/oFUqtPZLe+Cvff4epBjvnuZ2LKCz9QFAyO7p3+uu1pHngKFhGnOASxyM+j0+qvkMKQac91zqWdSORuoGcb+muhr1IVhUsABk74ODnFZcaLbvUlyXopftS4NLbaUDAmWKMO8Dcj0113YMQMRftF9I3rtsdRjuIwkMvMcb9xqi1dp/dLHDgjxq/VjCFK8SlRlKVXZI43KuX80eb6RXTh41OVxmoyXxVgJXb11yvbgqN2OMeNYrin4jdimmos+xAmXJ6Vw4uhPwf68T0/k+c/8AAak6dEHQN41y4xTl8nnEG3/d0/sGtjQ0LWkyh2hWsnFG18n3yb8O/V0HsClPJ98m/Dv1dB7ApX1J8icuPfk74g+r5/YNfnjQb+4ubHTrJrt0RLaMKGACjzRt6a/Q/Hvyd8QfV8/sGvG9GiSDg3SbpYVEhsYiGA6nkG9LXPpf6eqKFaatlrBH0y1g0zWbfUZrtTCcqQcnlLbA7fb1qcLKe18puiwycxilBXlzkHCMCKm2dwNZtbl17O3uc83IB5pGOno3GQfTUAXKXV3HM92/uqEMsbN8aPIwTn76sxirYPqpSqVZTU+dri/qsFdpErctxZvIsio7FOY+nff+NV9/fRQPOkMmZoSADsEYYJIPi24A7uvgK6754dPtpLmG5zCjdmCo85z4j0Z2z6DVVpyapqk7xxQRKe0E7FlwTyjAA8Rv0/Ko5xu8FmVOL/Y8EzS5XnkM/K8RjGVYk9mMdN2zuScYq/h1yV4v+kSMEfBGQCWOdhj7z91cEs7r3HcSX93czHl/aKEADDIGD/hXy6hla3t5I41eJcqvIAQp+wdfX/fXT0/mQqipTsy/0otPEG7VhybKD3Z61YTv2aDLZJ8az2nzTRR5OVAFdMmuC4direZGR53ifCq9WhtVyKWkcW7GssGyc8xxncmre3ZZMuhznesxZXDMixk4JG9XmkefdsAcF/NHgBVCMfFYyq1PZdk3mKqxyN/Gq5JmQMyDklyT02GcjIqTqjxRXKQxvzcwycnp6667xWFv2RVHBXKcrdD3b+NQzbu79Cuoxkk31Oa3WUW458FOZckDMbY6kemq+SVyzSzL2rfE5juV8M/cKj9rGlhdRz+dcGDzkzgsCRh8Y37ht35rjLO0cDTQWiIihWKzE88gzjlUZ3/wqvWi5pFZU1Gd4oS3BSF15t2G4I6VEtYxqV4I1cCboo/nbE/3Vx1TVY7kRRw2kUCJ8dxgszHoM9dvD/CqAazaWeolJMy8jZZV3BPgfQP4n1b0u48W2WUXH4o5PQdIsp4eynDgo4DAjwNTuILlYLRJeXmLbVTWnEj3FmrR23JkbFj/AHVG1DXjcWht5VUkHII7qnlKlGm6cWV6VKdWSmlax0sGuMyJg+gd1crmQS2RwDzDvPjVI9wObIJBHgamw38MnD1zJz5khkBwOuOhrPhQ3E1WFWEk74NPoCPJYpI4Iz09NfOO2A8n2vKCMnT59v8A4GnCWsWup6YkULrzwDlZe+ovHNwjcE6+hwcWM+PH4hr6ClDbCNjDqznWrTVuDeeT75N+Hfq6D2BSnk++Tfh36ug9gUrUMo5ce/J3xB9Xz+wa8h4ft2k4Q0WViSiWUIONwPNHWvXuPTjyd8QH/V8/sGsFwho8c/AOhSKADJp8JO3XKCoqraNfsmsqNVv5EUW6ojtGkUcgAIDqVFVz2FxdQmY6fZxo4w4UHnB/nA92K1cukzBOUv5uMcvdUOaCS1jOJAK6jU8z6elX3XaeWYbVbRYtMkmCGKaMAAMmSx5iTjGw2J871VV2eqTXDL2EKxxxEKzEkDJz1I333rb3F46wOrRq0fQ+aN6rbGOzhupDHaRAzryuCPNYeBHQ/wD7FTxqRTwzZo1XCnLdG7OmxjvDdctvcdpFIObkY8wPipz3H7K4XOlvGzJh0fm+IX+Kvobrnp41zk0/UtOmM1phkG6gHm28K6ptRnnKNNGUf51WO9i1k7UHKW+m1b3+pQ6reXcZayN1NIR81gAT6yBk1ZadFFpdul7qKiOGDdIR1ZvE+k9w7hVqsOnTt7tMXLMBy8xOWOPDwqovm92se2gKLED2UZ6VHKSSuyZf3fDayXI0jWZZ76eSccnM2VA6Adw+yt5oWp28M8XaHoD9p8KwOkWcsshndMCPovdn0/lUu+1K90/Nq0caPJgelc9N+6qMkk9xT1GkjWbhHkmm+uNQvyXwoaQ8ztt17jWusX9zorJLEsi9CxDA/wD7fesGssumTTiSSJpEIRlJzysDvjxwV3NXss8UnC8t2JVF3HICyAAOEHVvWBj7M1Q7u0m+pnaunujGMf24X3OUgkSRsApHIrHkwWCdx5sdxBHWqK/1NJbjmRH5U+KS/Xff1ZrlaXmbSOLsLl4ZVyeVcNJuxPjnffB8PVUZLKTsIruMMwE3KFXPODgMOo8MEGq0tzOKVBRe2XJaais1poEOqNPGxdhHJCCUZSebHMO/YDr41VQad/KWn3lyqW0E9oOdlQACQbHbO4Y5+0jFQtZna5ugs1msMMYK7bOPSzYyxzvvUX+Ub82rCCHs4GRY2lLecwBO6n5uckbffmrFNwT4wcyoShGz5f4i10vVpo5bu3uWkmgVQkbxAN2cmR5pIwDtnvONqmXsnuWNGcXCiQ+bzRbH7ebH2VkbB7vTb5UPaFR5+EQkLkbH7VH8KsOKeL9Q1KyisIUUWsZByiYbI6b/AGmpHSozjlZOHCVGMe6XPJZLc2bOpuJJCh+OobkwPDO5J+6oNxqfO0yWS9hauOTlHeuc4/gKy8eozpGFZAPSTmtLw7o93xAoMYCx5xzbVFGi3iCONVOKtK5acEX8lvr0kscBeNYwJCO4M6rn17/21ZcVamJeHNegGTi1nXPqU12QSadwvBJbpLGiOcSXMq8zzMPmRIOoB+cds9M1mtauobnQ9dbmuraX3NKymWNeSQ43XAOVO/pq5TpuklEoUWo97KS5R+hPJ98m/Dv1fB7ApTyffJvw79XwewKVbPlj7x98nXEP1fP7BrN8CKT5OuHj/q6D2BWk4/8Ak54h+r5/YNUfAUYHk04bY9DpsHsCoK3BPQltkWDoIzmUAofGqPW7cSWTvDGRyHp31dX0sYTAJLnotQOxn5ZJBIxJxmF8ZHqI6/2+uqPfdEbdGrsancxsN274s5BHGwPzlyftrvvNFkS87S3hKxsA2CcgHvwfD11c3lnHeck4RRKvmk9Dip/YvJYFFBHKO/vpCtLhmxLWbGpRx5mYKtBbdqsjCSMgOhGxB71P91V+puyz+dCpDAHmA8RV+kAljkZyOVNjvvUENZRIyTzxGMA7SHBFSfqGy5RrWbla5nrazaabtd0j3xn51d9xppd4+Uc3Mcbd1fdU1WxkSGKGOdQozlWA5fRg1M0m/wC0fEM7xzKpKrgMcfd1qzDUQttL86tVQ721ivvbT+Tjcq180Qt2UKsKgs7YzjJ2zj7s1WTaFqV0num5mSSV+kRctJ44AA8PVU7VWlieY3HLHzyc/nL5xI7/AO7HfUVne+uI42uIYJHj5jIrELgjoSBsxxg+rFeNps6pSqJKcZL1tf8AMkK4gltLYG5DfshsCQcDr3VVXmvz296ksRWQ5LkSb7kdfR9lTJLm8nkblilkjt2Cc5UsOuMHP9lTLHTtLurmXQrpEVzcKiXag5diSoG/QA4++o9t3gtVJQhBqqk31t5dSpt+JWubu1gmt41hVWDL3OxBwSeuM8o9G9a2z1CKLhuOExob4Sg5lzzIpjI5mcfGwSMAeGa4XXAWraVC1tHYadfw/GjeQ4lHoByAe/FZa71UussU0Tw3CvhWZSMY6gJnAOwzXLhtVzMVKlq3/ZeF5P8APxF5PLyTKZI2UyfthJJIFMm+CVGN9877VFkik1HUIre4dIpX5Y2eRwE5QNjn1b5zjfPfXy51G29w21zbpy3drGoDvhw+CWHL/NIyR6RgHB6xJrvQ7qznue0aK9PSGVGCk4yCuDtv45qLb0RMoTa4t04/MfmCVqNlJNql21slxfQR8sclwsLIoKjGF2GwAwPEd1VXYgKQRirq71oafAsnYNFLIRzQvNzrLjAy5BB5ipG4xt17qhWssS31sJXjEkmWzOvMFBGVJHeemK5lHxYfIoUnUV2uF/H50KmTSLi+kAtYhj50jHlRfWx2rfcKy6XoWmmzXUI/2aFri5PmlieoQHu/jVZq+jyWWhtq2oat2hmyIkQBWb7ug9AxXnkt3M3xTyodthsfXU8Z907FevoI6qPgl9vM1Wp8YabYXs8+k2LSXDEKt1cEs4A7lz0FZq/1q9vNNu3kmZC8LoQp5fNIO3qNTNI02LUYLqSbA7NPM/8AVVdd2/8A1ZeLIcPFGxH3Gu3U3WKVTRSpUpRT6f4P1t5Pvk34d+roPYFKeT/5OOHfq6D2BSrh8AfeP/k54h+r5/YNUvAMhPk04aXGw02Af8Aq68oHyccQ/V8/sGqLyf8Ayb8OnvGmwY/qCq2odkjqJZXViZbguh3xsKW8W4VxuKkXUjKi8gIIHUbfZXVFc9FIwayJuEZ4L8G3HJ0z2RtJjJFEJI5DkrnofGuYCOhJUj0HuqdkSxY76j9mUbB769nN9OCSNVvkpLiytxM0nIQp6hap59Ks5ZeYQqxJ2yN60V0hDNH1GapriF4pAwO2aqOq4s29NNrKkVl5w/p0y5WExsNm87JJ8aqns59HkLWpKAdJBjOcdM1p5pFVhzgqWHSqPVradLoFxlWGUOOoqzGsnlGpp6s5WhN3XzMPrGoT2t6qkc4Zctz78wr7qk9klvbX+mzyKk+Ukt5cM0TqB/WU52JG1T9ajW5kjSJFNxCCo5lBBBG/2+FZSO3eW7S2wVkdwm46ZOKtQrJo+toU4VIRm8befmvT3LG3uWtkkD2q3LNEzcxyzwd3MBnA6jqMbirnhvUtNvJobS5kWFppo5LiWULGqxxsGVEx1ZmAyxxsKznbXF3qkkdpIyG8YW4AOOZSQAp9Gy1vLvQ+FNBujpVxoN9qogPZ3epJcFCj487lQbYHpqzTm5cdDN7Q7tJQqRblJX8PKt6tLnhLk0Orcf2tpLNGmnzXcEa5MwGUBPTevP8AVF03iO3nukvEgaBS7OwKozdy+k9QKt4tC0scMW+pNxK9ppjXE8EC3MTFnAPxeVT84df8cVGh4Ym91aVp+lzJNFxJF2vu14hiJBkuoTOxXvOfQMVPKd42kZml/S6ZPY2mm8tPpze6tdJN2RjLWa4tLlI3It1kQBjyBgyncNg7E4Oxqy1XSby1hCntZrbkDGRoBlQW2GfHcd/eBWlbhDTtN0iz1C71iJZJImlszPBK0EqBjy80i5CZG/Jk9avdW0uLiPQdBez1VZ9S1Zzstu0cc3Ky5OPmCMKR6etV+6W218k1XtWjvg4K8W2m7O2L/L19Dyi/hkjcwOOZRlgcZKjPj+XfXGYSTSG6lbmYEKzDcjCgDbw2r0mHg3SL2fVbmx4htbxLRXnlt47UoDyDopPUdxI239IqdqHD2kJ5S7XRILIvYyyIs8Ct5oVkB3IJbAPTOMcxwailSksofGKEXtim2k28W6Jvmx5b7qa8vrd9T7aSyiOREjblfAE+PjVjr11Hq9h7rTRobGGJgiiF2GMjzVORue8kVptI4Vs5LriSDUbMFrJoTApcjkV5+XuPevj/AG1dP5OZxxrfrd6Xctw/DHcPb88h7OPCeZg82eua8UKjXqe1e0dJCp4sOKvzh3SdlnLdzyC2me1bKsQD1Ar7qlyLrTbl+UCRYmBOMZHKa9PvNO4PttW0fh+50OaB9Us7dzqFvdNzJJKMZ5GyMZ6+uvP9W0KXRJ9ctLoCUWKXEBYDZ2AIDDwG4Ofs6mvIxlFpck0+0KOopTtFx8LavbK4xZvqfp3yf/Jzw79XwewKU8n/AMnPD31fB7ApWsfkx98oHyccRfV8/sGqHgLbyb8N/Vtv7Aq+8oHyccRfV8/sGvMuE/Kdwfp/AuiWN1r0ENzbWMMUqNHJlGCAEbLiqer3bVtVySmrs9UjYFTzAGuCRpzkcgANYSPyr8Dq2TxPbgf+3L+mu5/K/wADIv7PiS1ZvTHL+msxRqNXcX9iw2o4TNs0QQ+Yces1X3huBgoA3qrIt5YeDf8Az62bP81JB/y11HytcGDccRwD/wCuT9NRTjN42MmpbU7to0PuxUl/bnlb01zuOS4iyoBI3FYy88qvC0txmPiG35MY3ic/2pXCfyocJvEqJxFAG72McgA/4ardzUeNr+xoxnBNPcl9S7e3mMrSSjp3HrXTeXDTW4MiZ7PcHvx4VUJ5Q+E5NpeK7PlxtmOU/wDLUCTjzhR5ynvjtTGPnckmD9nLXq09eHEWXoaqi5XlNYIeoc66lJIEKsDnBFV19H24hvljxKT5rKOjA9PScYq1fj7hSF2Ya3DdcxI86FgcY7yV336VVXPlH0qydk026tXiJz56s2/j8UAfdVmFGcf3J/Zm5R7Vpytta+sklb6ldqFtNFdNcxqsbRsMNDuqsADtjoe/HrrdwcXWJtl4nvNGv/dFy3ZXHuO6QWtzIoG8iNuuRju+01g/fvps+irG15FFf20qmKUKwLpk7NhcMVO4J3wSM13e/PRH0uey90wQQXU8dxLGqsApxyuBt8X5wHgcd1Xae6PCf2Gq1em1UIqpJXi7Yl0xfr1w/oTOJuKLTV+H7PTYdMXT57a7muJY4WBhHP3Jvn+6rrQ9en0byQ3k8iKJmuXtNNlPx07RQZuX0AD7zXmNzrNk9w8jXscjM3VQd/4UfX4JLaO3a/doYiSkZLFVJ64HQZqDvK25y2v7GlKn2dOhCgq0dqlud5J/NpZ68eh6Zw1xxpOj6ZGFh1ZbqCFw9p7rDWd2xGMsrZI65wBUXTuN7TSNE0MGzlfVtGmleEKwELRStllbv3UnGOmBWETUtFGl8zX491OxUJyP5mCMHOMYI5s+obVDOr2hO9wPXyn8q7c66ivDn0IVp+x6sp3qLLz4vVefGWer6TxVwhbXGoR6XpF7aS6hZywlp51McRbflUZyQT35zgACqfV+Mba847Ti7TIpITE8TiC4IzKVUKQOXONv7fsrE2Wp6IZlF7dTohYZeFMlRg5OD1OcfxrmuqaRGkyJdx8ykKjdk2HGRk56jvOP410pVpRV4+xA6fZtGtKaq7rqzvK+Hz+dD0eXjnSbUX7aHpWoi61G4jmvJbiUShEDhiqY+4E+NSodfifj671qE3rR3kMwFnJKjSczryjCKSAoxuSaxnDXGGkabbXVtdTRuLvbn5D5pX4pbb4pyfTtXbPxtZR2ctrZ6lDYL2hKpp9qYY5AMgFnKlz44OfXUy34b/gya09KpSp0msq25yvdO38WwbjV9b0HTLvTdem0y6utas4UsoYZJFSBZI1xzkDJ25s9fD7PJ+J9Ru75tUku51nmlLvK6nzS252Hd1qx1bjLTr6K2HZh2jIYgBwpOwyRjOSF8fnE9ar9T1bRJbCdbd4jNPbSedyMMORspBz6ACD1ySN8VxNTlPCx6E+nrabS6duUk5OLX7k7eSWcL+T9TeT/AOTnh76vg9gUp5P/AJOeHvq+D2BStU/PC+uLeG7tpLe4iSaGVSjxuvMrKeoIPUVSe8PhLGPezpP4OP8AKr+lAUHvD4S+jOk/g4/yp7w+EvozpH4OP8qv6UB5B5X+FOH9M0DRJ7HQ9OtmOuWcchitkUujMQVOBuD3it/7w+Ej/wCGdI/Bx/lXnXlWvr3jTi2w8n+ixBnhlS7u52G0RG679wUHmJ7yVAr2OJSkSKzcxUAE+PpoCh94XCP0Y0j8HH+VPeDwj9GNI/Bx/lWgpQGf94XCP0Z0j8HH+VPeFwj9GNI/Bx/lWgpQGf8AeFwj9GdI/Bx/lT3hcI/RjSPwcf5VoKUBn/eFwj9GdI/Bx/lT3hcI/RjSPwcf5VoKUBn/AHhcI/RjSPwcf5U94XCX0Z0j8HH+VaClAZ/3h8JfRnSPwcf5V994fCX0Z0n8HH+VX9KAoPeHwl9GdJ/Bx/lXz3h8JDf3s6T+Dj/KtBXGRS0bKDykjAPhQHjvkv4K4a4h0LiE6podjdBdfu0j54hlEUgKoI3AG+3StkPJFwECD717Hb/RP51i/JbfX3BHGd/wBrUY5rqV7u0uFG0rEZY57wwXIPcQwPdXs1AY34I+As/9l7H+qfzqzHAnCYGBw1pOP9kj/Kr+lAddvbw2lvHb28SQwxKESNFCqqjoAB0FK7KUApSlAKUpQFfaaFptjq99qltaJHe35U3E25Z+UYA36ADuFWFKUApSlAKUpQClKUApSlAKUpQClKUApSlAV97oOmahqtjqd1aJJe6ezNbzbho+YYPTqCD0NWFKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAKUpQClKUApSlAf/9k=</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Tab S10 Ultra 14.6" 12GB+512GB</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAQCAwUGBwgB/8QAURAAAQMCAgQIBwsIBwkAAAAAAQACAwQFBhEHITHREhdBVmGSk7ITIjJRVHF0FBY2RlOBgpGxweEVJCZDRXJ1gyczN0RSVaElNEJiZZTC0vD/xAAZAQEAAwEBAAAAAAAAAAAAAAAAAgMEAQX/xAAlEQEBAAMAAQQCAgMBAAAAAAAAAQIDERIEEzFRIUEUMiJCoWH/2gAMAwEAAhEDEQA/APSKIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICxl1xFbLK9rK2qEb3DMMALnZefIciya47jwl+NqprvGAa3IH9xu8rsnXK34Y+w+QCKqTI6/6l25Pf7YPSpOxduXKoaWaoYXRNBa05HWByZq4bdVNdwfBjPPLyh/9yqXjDrqPv8ArB6VJ2Ltye/7D/pUnYu3Lk0sb4X8GQcE5Z+dWi5PGHXXff8A4f8ASpOxduXzjAw96VJ2Lty5CXBUlyeMOuwcYOHvS5OxfuTjCw76XJ2Lty4+wOkkaxoBc8hoHSVnveZc/lKYfSO5d8I510HjCw76XJ2L9ycYmHPS5OxfuXPTgy5/KU3WO5UnBVz+Upuu7cngddD4xMOemSdi/cvnGNhv0yTsH7lzv3k3T5Wm653L4cEXT5Wm6x3J4HXReMbDXpsnYv3L5xkYa9Nk7B+5c5OBrr8rTdd25UnAt1P62l6ztyeB10V+kzDTTkKqZ3SIHblSNJ2Gi4A1U46TA5c6OBLqf1tL13blScB3X5Wl67tyeB10d+k7DLTqq5neqB25VcZ2F8v9+k7B+5ccFkr5LxPbI4myVUIc5zQ8AZNGZOZy5FgKu9W+hu1FbJ3z+6q0NLSxgLI+G4tZwjnmcyOQalzxjvXoLjOwt6dJ2D9yn2bGthv9V7moK9r5yOEI3scxzh0ZjWvNlwvVutdZRUdW+cT1mtvg2BzYwX8AF2vM5uB1DPVr6FsWEeFBjy0NHiuFWxpy/eyP3p4w69HoiKDomaHYvMWNbriDF+lbEFt98FdbqG0vEMUNK8tHmzyBGZJzJJUscbleQenVxvHZPv5q9vkt7jVzU4Xu/PK99u7/ANlYkwdcpHcJ+K7s93ndISfrzWnH0uz6QuUbnwj0r4XHpWkOwfcB8aLp1zvVt2E7iPjPdOud6tnpN1/SPni3kn1qknoK0N2F7iPjNdD/ADDvVt2G7kPjJc+ud67/AAt31/1z3MW/Fx8ypLlz52H7kPjHc+0O9WnWS5j4x3LtDvXf4W/6/wCnuYuicLlV83SuA1VlT2rt65dJaLqGng4iuPCy1ZyHLP61j/yfifhDhXmYDzipkKhl6Tdj/qTZj9uvm6V/ptT2rt6pN1r/AE2p7V29cqdbrqNmILh2h3qxJR3lgJF7uDh0Su3pfS7p+j3cft1o3a4em1Pau3qg3a4D+/VXau3rjrn3Uavy5cO1dvVp091H7brz/NdvUfY2fSXlHZTd7h6dVdq7eqDd7gP79Vds7euNGquo/bVf2rt6turbqP2zXds7euezs+jyjs5vFx9Pqu2dvVBvFy9Pqu2dvXGDXXbPVeK4/wA129Z62YYxhdGh4r62miOsPnmc3P1Dak07L8Q8o318r3vc9znOe45lxOZPzqglplimMcTpoM/BSujaXx57eC4jMfMsRT6ObsW/nOK63M7RHwvvcodNDXWHGctjqLjLcIH0oqGPm8ppz2fb/oo56s8J3KEyl+GwkML4ZHRRPfAS6J742udETytJGbfmWXwgf06svtUfeCwvCWXwef07svtUfeCqSj0siIqkg7F5gDeFppxz7SPtXp87F5jhGemrHftI7ynrvMpUsJ28ZrgL4WKRwVSWr1New2a0Z0asvjU0tVpzF6GGXWDOcY98SjviWRexR3s2rVjVXWOfEo741kZGKM9isGPfGrDos1Pe1WnRpxyoJhzOxfRTZ8inNiz5FIip8+Rc4jWCq7IysYS3xJeR2W31rVaunlpKh8MzCx7doP2rqkFFwstSg4mwsblanzQR51VO0uZlte3aW7ulZ9uEs7Pl3DZy8rlz1XR0FRcqyOkpYjLNIcg0fafMFQ7X8663gfDDbRbhPMz88qAHPJ2sHI3f0+pYpO1pt5FGGsD0dmYyaZramtyzMjhqZ+6OT17VtsdJnyKZBTZ5alkIaPUNSZbJj8I8tYttJq2LmOJmeC0vgZfswfaV21tFq2LjeOY/BaaQ0DL/AGU37SsXqNnljxbrnKqzWXwef06snL+dx94LC5rM4N+Hdk9rj7wWOro9NIiKlIOxeZKXXprx57SO8V6bOxeZKQf01489pHeK7Fmr+8bIQqS1XSFQQteutOyLTgrbgr7grTl6mqvM3RHkao727VKfyqw8bVvxYkN4UaQKZIFGkVsERwVIbrV1w1r40a10VRx5rI01PmRqUaFuZCzFFGCQoZZcRqVSUeeWpZunoNQICooYRq1LPU0A4I1Lz9m2xyYdcJrMJNpdLUtD4MCkaRWtbycA6wOtq+ZdNpYc8lexLbGR4np7gAOG+k8CT6pCfvV+jjzyVXl/j1qxnU2lp9mpZWGnyAVqkj1BZFjcgsGefavmPFLYWgLhWklobpwaB/lDO8V3kLg2kv8Atxb/AAhneKz5VKIeazWDfh3ZPa4+8FgwVm8G/Duye1x94JXY9OIiKlIOxeZaIZ6a8e+0jvFemjsXme2t4WmzH3RUjvFFur+8bNkqSFILFQ5i16o07EZwVp21SXjJWXjWvU0x5e6oz9hVh+0qRJsKjSL0MYxI8m1RZFJkOsqLIVbBYdtRu1UuK+NdrXXU+ny1LN0WWpYCB+RWZo5NYVOwk62mg2BbBS7AtYoJdQ1rYKWXxQvJ3NGGvrCYqq4zfqWjz8dtMZSOgv4P3L7Q8i51eMVsqtNc7WyA0zGC3tOeoubrJ6+YW/0Uo1JZfCJ4zmTZabyVMGxY2klBAWQa4ELzr8tFn4VhcG0mf24N/hDO8V3jNcG0l69N7f4QzvFRyVxBCzeDPh3ZPbI+8FhAs3g0gY7sntkfeCV2PTqIipSDsXmuzDhabdIHtI7xXpQ7F5ssZ/pu0g+0jvFTwnleJ4Xxy628sVpzVIcrL16WvUbN0RnhR5FIkOSiSv1r0teHHmZ5+VWJDrUSQq9K/pUSR+papEFqQqJI5X3lR3AlS6nIsOKpBOauFhK+tiJOxRuUiXFcLjmFlqNxzCx0UJWTpmZELPs2Rbhh1n6KQgBWsW4sZhjDktQxw92Sgx0zDyvI8r1N2/UOVYu43+isFF4erk8YjxIm+XIegffsXI8QX2rxBc3VlW7LVwY4wfFjb5h955SsNx8r1oyswn/rEmWRs3hg93hA7hcPPXnnnn6812/B+I475aI5+EBUR+JMzzO8/qO1cOcptjvtXYLk2rpTnySRk+K9vmO/kUqol49L0lUNWZWWhqAQNa53hzFNFfKUTUsvjtHjxOPjsPSPv2LZ6eu2a1i2ar8teGUrZRKCuF6SDnptb/CWd4rrsdaMtq45j6Twumdrv+lM+0rLlLEs5OdWQs3gz4d2T2uPvBYQLN4N+Hdk9rj7wSqI9OoiKlIOxeZLXUsptNuPy/PxqoZZDP8A4ivTZ2LzDb4vC6bcfdFUO8VdovNkqOX5jbn3OEDU159TVBqL9BFqcyZvSWHJS/curYrUlHm3It1L2MdvPhmuEvyxkmIKZ3+PqqLJeoHbOF9SuV1ka7N0I8G/zchWAlifC8skaWuG0FX47cnZqwZJ91iP+L6laNxiO0u+pY4qunppqudsMEZkkdsAV02WueEnwmGvgz1l3VV+n4VX/UQTSDzhmr69iztqwnBTNElUBUTbcj5DfUOX51nfc2TcgMgORUZ+oxn4i7HTlWoC11JGZj4PrIX33DIzymj61s8lP0KDPCQqfemSd1ZRhXZwtzETnnzAgfasZXXG+FhZQ0kFP/zvlD3fMNn2rPTMUCZuWatkxqu5ZT8NDrLHeKqd01Q5s0rtr3y5lQZMPXAbWR9cLfpWqDM3MJlEPloz7HWt2tZ11Hfaapu1rOstymYsfPH0LPlbE5I1uCG4UFQ2emlMEzNj2PyIW5WnSTdaRojuVJHVtH6yN3Af842H/RYKaNQpWKq5VKfj4dRpdJ9lc0eGNTAfM6PPL6iVp92vdJiDSgKyikdJELeIyS0t1gnPb61qcjVNwfSVFZjQQUsElRM6mflHG0ucdhOQCz7v6p+Vs43MBZvBvw6sntcfeCs+9m/f5Jcf+2fuWxYEwffJsY2+qnttTSU1JK2aSSeMsGTdeQz2knLYs1+HI9AIiKpI5F5qsLOHpv0hdFSO8V6VOxeYIb1bsM6dMdMvVWy3+6pw+J02Ya4Z8Lb0hwKnheXrl/LofgR5lS6BpCwvGBhHnFb+0O5fDpAwjzit/aHctM2IXBkZ6TMbFr13tYnjJaAJG+SfuU44+wifjFQdp+Cg1eNcJvaeDiCgPqk/Bate6fuq+WVq3Ac54YGkvJyDRtz8y6Hh6wNttIC8A1DxnI7/AMR0BafbsQYTGI/dc1+oGRMbwhnJtfs83zrbm6QsHNAAxHb+0/Bc9T6jk8ca16Ncv+WTPiENC+OYMlgjpEwfzkt/aHcqHaQsIEfCO39odywTJt7iy8rAoE8e1QZNIGETsxFQdodyiS47wo4asQUJ/mfgrcc0MvG/tdqI9qx0zNRVubGuGHeTfaI/T/BY+XF2HDnleqM/T/Bbde2fbLsxn6XZW5KHK1WpcVYfdsu9Kfp/gokmJrEdl1pT9Jafcws+WOyyq5WbVBmj1KqTENlOy50x+kosl9tB2XGnP0lTnlj9pzqxNHtUGaNSpbxa3bK+A/SUOS6W52ythPzrNcp9poksa3PQQMtOlv8AZZ+4VpslfQnZVRH51u2gUe6tOFLNTgyRQ0cxe5o1NHBy+0gKjdlLj+K7HrlERZEhERAWv3/AmF8U1Lai92Kir52N4Illj8fLzcIa8lsCINJ4m9HvNO3dQ7184m9HvNO39Q71u6INI4m9HvNO39Q704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHvNO39U704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHnNO39U71ncP4Pw9hVkrbHaKS3eF8swxgF3rO0rNIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiIP/9k=</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Samsung 65 Crystal UHD 4K Smart TV One UI Tizen, HDR10+, design MetalStream + Support gratuit, 65U8075F</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>900000</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 75" 4K UHD Crystal Smart TV 75U8000F</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAAAAQUBAQEAAAAAAAAAAAAAAAMEBQYHAgEI/8QASBAAAgECBQEGAwUEBwUHBQAAAQIDBBEABQYSITEHEyJBUWEUMnEIFYGRoSNSscEWF0LR0uHwM0ZTYpIkQ2SDlKLxNFSywsP/xAAbAQACAwEBAQAAAAAAAAAAAAAABAIDBQEGB//EADARAAEEAQMCAwYHAQEAAAAAAAEAAgMRBBIhMRNBBVFhFCIycYGRBiMzobHB0eHw/9oADAMBAAIRAxEAPwCo59m+e5H2hZrk+b57mGXpFJI8Z+KaMMpYFdpNxbaSfwtglzushooalteV4iqQxhYVBtxxyC1/4eQ5OPqLUOitO6rVBnmT0teY/kaVPEv0I5xBDsW7PB/urQn8G/vxMus3agG0KXzcNTTMEZ9fVtmF9pkcEdetmNv439rHCbagqBNEG1zUGJi4dhMxZbW2kANyDc+fFsfS/wDU12e2t/RPL/8Apb+/Hh7F+zw/7qUA+gb+/HA4juukA9l87ZZ2mZrozNaKtotTPnFPIxNRTOxYbQR1BJsSCenQjH13RVKVtDBVR/JPGsi39CL4pR7E+zw/7r0Y+hb+/F3pqaOkpYqeFdsUKBEX0AFgMdJsKLRR2CVwY8ZgouemE1dzLbb4f4YgrErgwYMCEYMGDAhGDBjl328DlrXwIXWDHETMy3YWx3gQjBgwYEIwYMGBCMGDBgQjBjl328AXa18eRMzL4hb+eBC7wYMGBCMGDBgQjBgwYEIxy7hAOCSfIY5kdvlS27/X644EQLF2ub9AeuBC8AaXxPYLhZVsLWsPTAF9fwHpjrAhGDBgwIRgwXthFi7NYXCm4uOoOBC9kl2+FRdv0xysfm/iY+WPY4ggHF29bdMKgWwIQB5nrj3BfBgQjBgvgwIRgwYCbDAheO4RGc9FFzjM6rtz06mZU1JRwVtSZbmRjTuhRbgAhSLte56envjRnvKSh+Q3U2/njEquXKKXTWkKmscR1571ZKnu90hVCy23t0s1jzx7Y4SALKtiifM4MjFkq4L2w6TI3mSuYG9iaVlv+eO8h7WsszdEkmy+tpkmqFp45O6Lpdn2rubotzbr64zjNMmOoq5KmPfRwrEgigEQ2xIeQC24XYlrk8cnpiDpaySjyiam3xvHFW0FaHQ32lZ1BF/o/I9RhYTnXpI2K9DL4KxuGZ2Pt7Rbh2+ny+q+pMGAYMNLzKMeM6ra55PT3xWNYzZ1BU5L90109MlRWpT1Ijp0lAjYMS5LA7bbQL9PF9MVSHVOfvneUxVNRX0hqK2oWYnLt8PcJUMiKSEJDMu2xuAF8RPqIWo713WvzhJ5z3hRSoYW4vz9bemMhyrV+ta7K0JMz5m9fDEYJ6MpGkRZ91z3S7QQFBIZrXvfFy0HVS5xl8ueZpSSUWaSzTQMk67JEiWVu7UjobKByOvXHVw32VtSPb7t6emFQLc+eORLGP7a/mMHfR/vr/1DHF1d4zHtxynUmaaXoTkMVTV09NViWvoaWYxS1UIHKqRyfPgc8g2NsaV38X/EX/qGKZ2jaJg1xQ5eYs3lyrMMtqRUUlTFZ9j8fMpIuOAfwwIVJ7M8+yXLez/V+Z5PnmYzQUaSVH3XmAPeZYwRiEBLEsCQBf8A5fW+Kp2O12a5Tr/Sor81raqPUeTTyFKiod17wSuQQGNgdsY/PGg0HZJBFp/VFLmGpZqzM9TbTW16wpHYA3ssYNhe5v8AXD3+rHLIqvSFdT5rLDLpOLuYrBD8Qthfd6X56fvHAhZnR55W0fbpmObz5nV/d9LqJqCSJp2MQSSGXaNpNuDH6Yc9iVbmx7UoRX5hVz/eeQtmBjlmZ1Bea6kAmw8NsXnM+xnKc0pNSxPndRE2f5hHmJdFS9O6liAvr85HOJjI+zjLMh1lS5/BmTsaXKY8pSnYKFKIFAa/W/h/XAhYzRU1ZkGvYKbW+bZ3kmeS5p39NnaTNPR1kRItCV3BVBPnbgGxAxcc9zKtj7d9X0q1lQsEelpZI4hKwRH2L4gL2B98O07B6RXjoG1dVvpuPMPvFcsaKMnvOlu9vutbjp+vOJvWHZcuo9Vz6hyvVE2R1tXRGgq+7ijmWaE8EWYjabcX9h0wIWZ1mY5hP9l7SMzZnWxz1ObLFLUJO4kKmSUHxXv0t+Qw4yDO81/rA7Pclq8yqpKnK6zMMrrlMrWlMROxmF/F4GXk40mt7KclquzjJ9HR5pNBS5XUJUpMCjPI6lib345Lk8dOMeS9lOUP2rx65jzaaKdJe/NINpiL933Zb1BIAJwIWVageHOdRdomaZ5nmd0b5NmENNQ1NEZJFolJbkxqwG3wAXuOT6nH0RpqsWt0tlVT8W9YZqSKQzumxpboDvK/2SetvK+M41J2OUubZvnM9Hquty2h1DIkmZUUSxuszKb3DNyvNz59fTjGj5bBRZVldNl1JIkdPSQrDGC4JCqABz58DAhSW8FSRzbywjueVgAVtweOcIfExiMyCWPch/eHOHIngtxLGAebbhgQukXaLD8SfPHz7rHMcnj0lluTVFRHFmtNmFWIwXBVYjK5O4gnb/ZsDbH0F8RD/wAVP+oYrWa6H0tmrGSTLaBJnnE8kqIqu5ub3Ycm9ziLmhw0lX42Q/GlbNGdwvnhc3rHRYxmErrGAqgS3A29APph3loirdPZ7l0FPUzZhPFF3ISB2sUkR9vA4vaxJ46Y+lqaky2jRUp4aWIKLDaqjBBSZfT5hUVsawrUVNu8kBFzYADn6AflhePGDHartbud+IJcuEwNYGA813TyJi8SsQVLAEg+XGDHqSI/yMrfQ3wYaXm1hf2k4Kysk0rR0KyyVFRPNFHHGSC7HYAPzOMmq9DZvBTT/BZzQ5xU0jrHV0tBVO8sBZgguCAGG4hSVJAJxsH2hs0qMkzXR2aUoU1FFUyzxhhcErsNj7HpjMqPWGm9O5jJXZLk+YxT18kZqRUVKSJDD3qyPHCAASW2gAt0GNPHa7pgtCSlLdVEqvS6U1XS1VLTVGVZmk1YzRwIytd2X5l4PBA5IPlz0x3BpjPZM7fKqmKWjq46aSq2VDst40QuSCL3uFNrcXxZ8g7RqXKI80jmoZpkzPMZ6l2IRykUsbKbBrguCRcHgi4OOJNd0Z1JQVS0lRLldDRTULKIoaeTZKrK7IsY2Ly9wOenXnDlyDYtCWJZzartRpPNYdKJqB6lPg5I45FAlbfZ5HjW4+sbX56WxBrMxTmWQOvTxGx/XF1zvV+WS6PfTWX0lcsEMVNFBLVFN7BJZZHZwvAuZeAL9MU1RTPTSFnYTAjaD0I6dcWMFi3Duq3uA4K9UyyE3kkDHmxY84dK5SUtGXGwX2sbn8cIQvLGFkUr4L+LgkDCjlXVmV1uegXjF4Y2+Eu5zkstQCoBQNYHzP59ecSNJ3c12jijd0I8DEr3imwsBfqOvHPJ9MQ8cZJAI6+vFsSECoirI0gUqbgDr+nTFcsTS3bZLvdXdOYKQsJt37MxXJV3ANh5cnk+2O0SIMHXa4vcBjww97dMImaVvCTcAWvYG/44eU8cttwJYAc34Hvikh9G0rJIRva5EKFAO7juwBBMliLXvx5XxwYkZSdgSwuPFe+Fo6FJqju0s5vcm97D1OJSPL6VIzHI0j+jDw2/Dz/HF+PiSyglg2S78jTy5Vyem2PuUgkdOeL4Q+GIXeTyDawOLjSZVSlmaWdnXyQDbx7m5wt90Uc7BIVMUg6bjuU/zGLXeHz6S7SLU25nA1Kpx0bimaRrC1idx+bngAfgTccYViijjH7RR4xxx+uHtblkuW1RjqAylelh5eRB9DhkQxXvAD0sbcWOFIIyCQ9TdK53dNZgpuAoA9hh/lmjM3z1FejiiSNxcPLMEFufLr5HEdM5+RlIceeJHJtUVmSSKsUcMqgcCQHjr5g++Gs0ZAhvDa0u9Vq+HnH1H2pzgK2rz9fRR2eaRzTKg47xaruiqyCnZnKk3txbp4TzhCbRuaUlBR12YV1Fl0NbH3kPxVSyM48+LGxFxcH1GHeZ6qr6qSc04ajaZ1d3gkZX43cAgjjxdPYY8rtaz5tllBQZrldLmK5fGY4pJZZhIQQASxVxc8DFOmfQ0yNF96Tcb21uuZ9B5xRiJqytoqUTr3kJepYiVOLOpVTdTce/tiLqsmzSjzaoy14J3q6Z2SRI7vYgXPI9hf6YsFR2n6gmSngBiiooYxD8HGXWJ1Hy38W4MAAAwIb3xHZdrTN8qrIKmjcLJTmTu9zMwG8EEnnxEX4LXxUOoOWhWEsI5Wu/ZeYsNSksWF6e1zf9/BhX7M4l73U5n5lZoGdr/MT3hJ4wYx8kVK5OxG2BH2nFLRabCi7bqg/omMGQCSML0I6emN3+0+bQabHq8/8ABMYMhLgLx6Y1cEnprPyvjXdivhsRbqD5YUWR4JN0QDBbEgi48uvrjtJ+62wVEIKqPLhufMHHgljjjZgGJYWNugGGy69nBJfResGn3SM136sW9MJSKI5RZlO5bgA+uFYahoplkjdokseV63AwgimVi8hJPUnzvibRq2CBtyuFDSPzx52w4WM9CLe2FI4LkPtJI8vbDlYCbe/TzxPTSrfIFzGoRxzvHX8cPo4gzXiYlTjlISzEmwv1t0xN5TlU9bUx09NH3ksnCqDa9hz1xwkD4khNL5Lily41FSkSkBn5JPIUepxLrT0lKV7uPe6/94/J/AdBiegyI5VQMGG+okH7Rgbgf8o9v44gZ0ZWPBFsauHjsI1uFlZuQXsoeaXiT4piONx5vbCv3SxHzjjDWkmEU6kk2GLjSUkVVAJI3SQHrz0w9LJ0vkq4IhLYPKqTUU0R+X8cOMvid6tBtPXnErmtdluWkLV1CRva4jHLEfTFQzPVK1RWCGJ4KeT5bGzSN6MfIdOB1xX19Q2V3sZDrvhNc0zWSXNKiVy0y7ytvRQbAD8sJNTGOzqAUkB2n09sQ843V8atN3ZDcuD5+f44lsvqgGNFP4YmayXNyp/1/rnGfPFe9cJuVhaNTfqmlUhcqFW5Vbm+IyVWU38x0GJ+sS6NsjCbSAfI4ip4gVsAbgevXEIyXDcKyF+yjJ1ZyHPiB8v5YZuPF6e2H80drny9MMmsshDX/DEZRYWnGdkkwB8rY8AuAOAMErgNY49Ck228nCRG6Y7LffsxAL/SUBg1jT8j/wAzBj37MaFP6R3Ftxpz9f8AaYMeeyv1nLVh/TC8+1AB8Ppo8331FvyTGCJIRYra+N9+06QI9Mll3DfPx08kxgAXaQb40cK+mksn41I0c22TvJ4xLGFIIbz46Xx3U0sQhEqo0aOAUubgj/LHFNKqgI6mx8/LC8tK6xWdiiC4Unp6j8/441iLassmnJm0I2s0bXA4sfPHcanba3n6Y9WFgQeAwNrnDtGubAWNuffHWDzQ9+y9jjJsAPLElBA3dkXJHmoF8IUqbuuLPQ5RJJSxyRBVuPFu5virIkDG7lZWRkCPlQ6U5B2RKT9RbC9W75YsDJK0c7Hcu02IA9/rixU+VpHMGayhRckngYomZVrZlnc9TchA22O3ko6Y7hStkfTe3KWxpPaHmuAtByjPzXUnd1FUsdUvhO7gSD1+vrhtmFfRRPaappwSbeJrYpazCILZ34N79LH/AF54fDPVMTlowXC8PLaQ7vQccY2hII+EzJCZOdwrAYoRTrUtPEkD/K+64P0t1wyrM6lpAEy+coCLmUCxb6A+X4YrAkqZU3PUQoOuy3I+gAwmKiREsRex6AXIxB+W0j3l1mGGGwbKcZlmUld3lRUTPLNwr7jzbyt/dhDLJBMViqkYxx+Ndp5HoccySRzQCSNAsyG7Nfg+Y4w6WgipVSthkk3y3VibDki5sMVNOpwI4TZLWs0nlN6iNRUqxBtuBN/rhxmMIjkijWTcysLi1gt/fD6GmWopvBT97Ot3JdrKFHn74bukLcyq/eDkBRxe3A9rYvfQB9VS2WyPRSMc3xMLM5VnB2NbzPv/AB+uI2rj8AdCXI8JI8zhvBUmjqdr3WGTiQeZ9/ww+qiY/mA4NyR15xnsAEh8lXoMbvQqEmFmNxb1wyMbyNujVmKnk+mJSWJWNt4X0v0wwkV1dgASQLn3tib1pROTCRWWe5INjzbnCnjSEsxIEpv16j6Y9aUsy+G49PXHU4kg2s8alyfCzHqB5Wwk4hOWdgt3+zHY/wBJLW60/wD/AEwY8+zFa+pehN6e5BuCf2mDHm8neVy14fgC5+1EbQaav+9UfwTGDJ44wQQbeWN6+1BJ3a6YJjWRS9QCp+iYwLazOGcDaehXi2NDDdUaSyR7yfQOI2s/T09cSNPVEwvFMokiI4U9R7/hiKiCqxBu6jzHliRpqTdGxQLI1723C5X1HvjR6paLWVK1vJSH7RZfEenHIuPrhxTqd4FxcHoeMJ1MTR7S3F7blv09MOKHazqrdGYbiOTbzxwPVbz7tqWoKfcYxbazNwMaI1J8DlkTyLayg3/19cVSKBYk71QGUWCW5vx/njTc9gRdCK8MX/1Lw7Te58Vv88eC/E/iz4pI4IjzysX2N3iDXvBoMF/8WcalqaiDJ1DblSqLAOONwFrgfiRik08W5jbjxXvi26vqZKirr4UOyny4JDFGSOLHxH6k8nFVphtiYg34OPYfh4OZhsc/k7n68ftSdihbjtMbex3+ab1NVvktCh2cjnzOEYY3cqlibHpjpIGNRtYkgcWvizaeyCfM8wihpqczuQW2jg2HU4bycjpsdLIaATjnBgDWCyUjl2nMzq4yYadX2oX2kncABe5w3hzCDKqnbmkEksI6pENrdPXFz0tqX7r1CaTOKCB6abdEG2EPH5Wv74p2qkWfNKgi7qrG1+OP9Wx53HnnysiTHlFNqwQTx81SzSQwvIJN2PKqpMI5FrZZmjjsLC1ha4tcG2JaogCUKLfkKD+NsJ6fy/4jOoIX/wBkwFyOLAC/+vriYmpLVyxTXEYfaSPTHrcd4gj6Z7BJ5M7RKGj5qJO6OnXbcBl5APUYayOgsvz3HJ98WHUn3a9YRlSOlMqqBvNzewv+t8VaQsst7kW9MSbOZY2yEEX2PKsiFkhI1cZIO0Gx4588SUbd9l0UrNZ1UcDrfp/LEdWXIJYEEG5v5D6YkYopfhIonV3Yp/3Q5A/+PXFRcbsK+T4RaYyxsXPoOBc/zwwqVUmPaxLsDuHW2H1Z3itZkAB6ADp7YiJDvcq7Ri3N2NuMTc/ZNQtvdKU0/wANGJFETJvFi63sf5YTcyBpJFLNfg7P3SOAB5Y5VGUyrTkSwFeWcEAkc8X8+uH9Dl01XTGp3dyXkDKu3ggdOPzGEfzpXFjeQm3FkY1uW1fZkLkaj3rGCPhxdLWPz+mDC32bKaWlbUSTKqk/D2CkdP2np54MYmSCJXBy2ICDGCEy+1MxWHTJAvZqg/omMBhqQyjdcY+i/tJUUdcdOpIWAX4gjabfuYw4afjM4bvP2QUDYR+uNPCx5XxhzOEhlTxNeWv5TGOdFWMpYuwO4N5H/wCMX/SGY5BDklXSZlSMZp/9jUDbeMep8zz6YrFNksMMj3UukgtYngfTDuCioY+8iDIS1rgsLjFmb4Q7Nh6T3afkfJZwzWxu1MF/Sxum2bPCJ2eMkobG4HNx/wDGE6KQwsF+Vj1v+mJSoyuGaikijVVZuVb3xH0uT1QbfO1nSxHmCMXDDliIZyK5SrZo3RkE0tP7Ostos3zqFKqbu4oUNQFPysQOn52P4YvTtHPmmXZZDY0yFqhgwttNgFt6DliBjEMtqK7K6yOpgl2GJgyj+P6YsFHq+aHUHxuYyGVJ1ZO6U2I4twR0t/fj5x+JPAs10xnaLBB+d1x/YTeHlxQwCDuXAk+l2ojOaZIo61pHLzO0lm3dVBIu3qff3OK9ArbbWuRwbc4sesa6EZlXTQKUp6mIVEaXv86gt0974qMdUiDcqgL5Le/H1x7jwebViscRWw/hKCJwLxd7qTlkieeIxxqoSMA2N9xA5P44nFz2fTtKYaOYxzVMSszrwQvoD+eKqJgpQnq2JTUUAizCigCEymFEXni9rkn6XxT4mYnMbjv3B8/Tf/FXThK0g1zwvKOtlzNcyhqZHm7p+8TcfFzfz+tvzw3+KbMGYSi8iLYkf2v88SMuXSZPlbVU4AkrVHdkdWC8X/P+GIuFHoNjTRvG8gYjcCCLedjjnhpjIa5nHb6IrUXOA8q+2/3Vq07QOMvp5zuU3tf6G1rfpi0a2ofgZxHIgLNHG4cC1+LH9Rit6Y1MtCtM1kkMYuA4uDc9T74fa21iudJQpJYyQwBWtxc3JPP+uuFp5sw+LxgN/LAIv/flSQEDZGyGQ+/qFD07/wA/sqpJKBDICR81rYjqnd3HxG1URW2GxN7/AE+mPKqp7+cJFEVdiPAp3bj7YnMvylKKGRqlg7TAAoebfyOPVsaZDpCZLhA0Odz5Kt/t2lVY1bcTbgfridEkNNGUeV3soG2K/wAvvbCzxU2XkfCo3xEoKIhYnd6kj2xXajMZFYhAqW8JUC4t9D1wH8k+9uVY0+0/CKCdz0Yq1vTLx5Sbrgj0I/niImyPMDN4YlserF+MOcqemlmMs0yQ7TcICTb3A6DErWb6yjPwFSodh8w5Nv5YmBHMzV39Ff1HwP0DjzIKjqPI1pHFRJMXkW5EaNZfpz1xI9820AqsVh8o8sQscOZ/FbZCFWK5Mko8Kj8Ov0w/NWkUe+OGaUfvlbbvcDEoZGtBoUiZjnmydS237Pu41Wflj/Zp7fnJgwh9nOo+Jm1CxRkIFOLH/wAzBjyuc4OyHkL0uGC2BoKT+0lWR0Q09JIGIPfjgX/4eMFm1GVT/s0JBPm7dPwxu32k8qq88zTRuV0MZlqquaeONAQCxITi5sPzxlEvYX2jmSyadcr+8amEf/ti6HMfFFpaaVU2KySTU4Wqi2Zz1BvK28XuVubH9cCSKW6AX5HPT6YucXYb2iLwdPH/ANVD/ixXc70/mGmc2kyzN6f4ariCl49ytbcLjkEjoRiQnL+Sqns0cClxT5pUUbM28ur8MpPDD+WFosz3K215FYfKd97j6eR98MHC7QLjHUCo3RgfcHDDZ3ja0m5jDuQpejz6RlK1Q710HBU2LfXywrQZpTrVztIu7d403DkEW49v8sMqGLfMVWzfTD9IV3Snp7YTk8WLHaSb0pSVsYvblSlZmeUZhRSLUbQ5j2I5JDRXN7ixsRfyPripyqUiZjNG6C4urjy9uuHdUvgN+g4w1LMwA3G2HGyiQlwAFqcDdDaBsJfL5Yqkqe9RjEwO122hva+JjNczmfU0E8cfhjkSRQ62FrAW6e2IWP8A20ak3uwxYc/JXO4grHYAvhvxa2MfxBodK3Vzpd/ShI8NmbQ7H+lb67Pvu3ROVVkiwzyQMBG+zlFYEE39eAOR1wjk2dUes5/hczovioY42tMeWUm3Ab39sVrUObSZTl2XUMVPTtIEL1BYFgdxG0Gx4IHp64aZTn2YZpWLl94qGKT9nupwdwv53J6fTHimYZDNbdqJo3wL8h917vGkj6DQWcgbV3pJV1ClPnNdSUVWopaZysbSOCxA8uOpGG0kUbMpkrI5SWF1SQFwb8+H/PE1V6VlynMVpnnjnEiblkQEBhex4PQjHupNOPlmU5XWFIjHVozAqljcNbn8MfQ2ZsDRFHr1OdwfOhz+y8Q83M4AVXPok5aqmyRQsVTFI7rxtjW6n35vhWGo75i0tRHFIihihfc4HuBYfgMQ9TQUVUF/YRo23qBbCT6epJVJXdGxXgo3TGs102s0AR2FpEMhI94m/OgnFXmsmYSmOBXinK2EgAuR6X/sj/RwwXLpShM9TFAQQrI5uQT62xGHKaiKQIZWjH4gH64eZDpzMc8z+nymmqljNVMsbTMSQL8liBybAHjrxbCrpnE3I0rVjhjA0xuA+ifmjzCmkcwmGKJTv3I3X+f8sJ1OYQzSLULD+2pyC7qCBf046/jiQi07lucV7U+nc8rYHhilmqTm1OI4+5jXd3gaMsebfKRf64aUui84qYlejzihfLqiF5hWMzRw3Ewg7tiyghizJ1HRgfXETmNbsAR81c3Dc7ckH5bJpmmbRVkAkhd12Er3bH/3C388R3x7M5LzO24WJ3EW4t/DFsfs6qMtGdJJnccNdl1LE8MPw06mdnmEQXxoOCTYEXBLKbgXt7Q9mkdRPNBLneXTijmemrFoi7SwTCGWTb41ClbwkFhcdbdMVOzdZsndXswwwaQNlp/2YGLDUqkkhGp1Ave3z9MGEPspuklNqUpu+anuD5cPgxmSO1PJWgwaWgK2drDGPtO7OJVjaVo6ydxGltzkIpCi/memKVR5jqj+uzS+aagyrOKevr56gNRblEKQhdsaxgPZggJZ2YAkk2BxoXaxpXVGeZxpvM9LJCavKZJZd8rIAjELt4Y89Diumj7dS6uZMsLr8rGKnuPocAArlBvyVDyqSsWnmnz3vZdDRalqFrxTyEP3hI2NL59yDbgdbn2xZ6qKjqPtP2VYpKRqK67FDJt+DNio6Wta2JP4Dt0EbIHyvY5uyiGmsT7jzxSNYdnfaHO9bqbPqen3RRBppYZI1sigKLKh9PTFjS29yqXtcQKHdWDSVFkppuz/AO7e/qaZ86qgz1kCI7fsjwQpII9OcOsppq6aTS8up6JY82Oo3ih7+nSKV6Xuz1AAum7zIxn+SdlGsdR5RBmWUwwy0kl9jioVLEcHgtwcSA7Ee0GF1kaihZh0Jq0J/wDyxIuZexVemSvh/dX7NKKmzjRgrIpZMxZayY/FTQRxSU20lTBZByPME+2MxpKAbsw3KpEaNbdjRcm0v2h5Tpz7qh0xl8ikktK1ct2Pra9sRR7N+0ImqK5BRj4kEH/tqeG/448fNj5ks0jtNA1W44CrzcUyMj6e57rJ65gICPcYZREeeNGqOw/tAnFjldMv0qo/8WEh2Ea/Ug/dlObH/wC6j/xY9nDKyNlE7pVmHKG0QqVHTyz5qtNBG0srOAqKLknG0ab09k1HmK5jmlZRPmMVrJLMm2Egfuk3Le54HliKyzsx7Qcohnaj05QLWzdapqxGZR6KL2GK/Vdg/aHVVUlQ9DFvkO5iauM3Pr82MPPGRmP0tOho79z/AIFqYmHDFUsu7x9h/pVX1VKXLM3iDIGv73/yGFdHRCbOEkUnZfvSLdDY8fwxZpuxLX7UsNM+Wwt3SspY1UZLXN/3vLDzLexzX+WqSmTUzuSCG+LjFv8A3YpOK4R9MJhz3CIgbmqU/RZVR55llSzz93UU7L3LsQCbrcra/S9sNddpE2hcmVbF6dnhcWIKsAOLH6Yhs27Fe0LNswerbLooi4F1FZGegt+9ieXQHaVJkf3VW5NSVkItsZ6tA6ge+7CbPDposmKdrrDHXXobv+fRVGCKXHIcNMhaAT22o/8AisqkcxFWv1GHFLWBxa/QYuE3YpryVVUZTAtv/FRn+eE4uw7X0TEjLYOf/Ex/4se7jzmNNrBPh8jm0QqjVPHKp55w009FXS6toKTL6s0lTNUIsM4uTG97huOeMXhuw7X5N/u6D/1Mf+LHVP2JdodJWxVdNQxw1ETBkkSqjup9R4sRmzI37gq+DCkj2I2XeZvq7xB67JqaklglaS0UdGSrookklj2gqwEiqb8gtYdcNafJtQ0WnE01BDTx1ElecxkhmqEYgIllcxkHweBmJ53eHjpfiu7PdfaJy5c1qnNHS0e8Aioje3eEbhtub7iBwfQYfUOlu07Mslo6+ijq6mlqAaiJxNGSb3vuDNfnc3BuOTxzihszKokfYpt0L7sA/dMqjLNdSyiOWTK4Y5YXoFpoxEsKJu74kKAQp3jepHivawwkazXk9POzSZLSm5rKt9kMTgmKRRNPYXu6NJYnrcGwJF5ZNF9qqgxpS1wBkMp5jszc9bnnqeDwMdt2X9qlfQmKf4hopA4ZJauK7Br7g3iuep6ni5tbFTnR9iPsrWiTuFN/ZWiWGLU6r030/nfyfBi19h+gc80MM6Gc0ywfGGEx2kV77d1/lJt1GDCr61Gky263WtYMGAkDqbYipIxQ+1TINRalynLssyBxGs1Vardn2ose08t5kXtwOpti97gTa/OE3lIJCr0Nrn1wIUHpHTcejdLUuTU871Rh3O8rgAsxN2IHkLngYmgm5yzMSvlbAiEWLcnqB/PGO1naJT5P2xx5ZQ5zW1ME+YfCZj94VSfD0pKs2yCPhhyLFzcDp1OBC2cAAC/AHQY6xStX6tyCGkyy+oWhaTMqeNfgKyNSxL2tITf9la+72GLB/SfIVW5zvLgB1Jqo/wC/AhSuDFHXtZ01UVuX09FLNVitmp4t8aWWIT7+6Z78gHZ6f2lva+Irtr1Fn2mdNZfmOSZr8GJa6KllQQq5YOSbhj8vy26eeBC03CLOzNZeAbgN15xW+0HN5Mp0Fm9WjyRSrBtiMM3dO0jMFQK9jtJYgDjzxBdnutqaXScsGbTT0eaZfUtRVCZnWxyO820yBRNwreHp6Ae2BC0FIttifE3X6YVAt164o+Q9qWRZhok59mE8GXSxd4Kij79ZJUdGKlFA5ckgWsObi2H+m+0XT2o8nFctWuXSLI8UtLXusM8LqbMrKTwcCFauDgxRey+sqq2l1HJUZvNmcceeVUUJdg6xxhgVVWHUWYH26DEzXajOXVzVlXPl8WntixCrMzGT4ky93s22ttvxe/W+BCsODFF0fqinSs1PTZxnMCTU2dzxRrUzqrLFtQoACR4QDYYXg7VNMz6xfT4qmRgjFK17LSyuti8aSk2ZlDC9uPK98CFc8JySFTZRe3Lew+mIHNNcaeyvLp6yfOaIQwi7FKhHY+VgoNyecUnLO0qj/rCijo0zHMMqzypWjgrJKqP4eOVEP+xh+fY1jdzwSLi/mIV11hpWPV+mKrKZ6qSn74qySoLlWU3U28x6jEN2V5BqHTeU5hlmfsJFhqrUjLJvRo9o5XzAJvwehxewPPzx7gQiwwYMGBCMGDBgQgmwvhqj7j3r9T8o9BhLOM1hyiiEskUs7yyLDFFEBukdjYKLkAeZuSAADiuya2y1cqjzJVlkj7zunhVk3xHcVJc7tqqCD4r7TxY8jAhWgkvIVJ56gjHcNpBuIG9TtJxWZtc6fpJTK1XK9lYsEp3fu7Eht1gdttpvfy58xhM9oWRUVLO7vVvJE1pEFK4KuSf2ZuAA/hPhJvx9LiFcLYz/AFX2J6J1bLWVNVlnwtfWMHkq6Vtkm69ybG63Pmbc4m319kEYJeonXa3dtemk8MlyO6Ph4k4Ph68YeUGq8pzOpSmpZ3aobd+yaJlZdou1wRxY8c+fHXAhZZF9lnRSFt9fnEgKkC80YsfI8J5YQl+yzo2NLjNM6JJsP2kf+DGsR6np5M7ky34eoDRyiEy7boGIuASOl/LEDD2qacqppkaSWmjpmcSzTgBU2kLc7SbAk9Ta3F7XGJOY5nxBVRyslssN1sq5kP2fdJac1Dleb0FVmJqMtk70rNIrrMw+UsNotY2PHpi0a40PTa7y2npq3Mq2kp6WYT93Td2N7r8rEspPFzwOOecdUWvtPTTPFPWyU0hlkiUVEDxhigu1iRbp5XuLgEAm2JDMdQZfllBRtNM+3MGHdEIbtcAjjqOMQJrcphjHPOlosrvPtIZfqnR82ns4eWqpqhFEkoISRmBBD8Cwa4vwLe1sU1/s/wCkG0NHpcSZglOlX8aahZV71pNu3nw2tt4tbFrTW+XmOnKwVm2dY2jbu1swdiq87vVT+WHQ1Xl7VFJCoqC9Z3fdWiNjvUst/Twqx/A44HA91YceVvLSsvl+y1o07WgzLOYHRQAyzIfEP7XKYST7Lempk73Mc+zmsrHu00+9F7xieTYqx/MnGqak1bl+lYaaSvWokNVJ3USQR72ZvS1/piLoO07TtYrmSSpo9k3cMKmEpte17HrbgHr6H0x2xdKQxZul19J0efby/lPdEaJy3QOmEyTKnneBZHlMkxBdmY8k2AHkB08sZNTaY7W67KxobNqXKo9ORMI5czO15ZYVbcCo3X3ccEqDfqfPGuTa50/DVNCcwjcLCZzIhDR2B+Xd03f8vXDqk1Hk+aUM09HXQ1CRQiaQIwLIpBIuOo6H8sdSxNblZ3qzsD0trLUtTn1dV5lTVlaQ0qQSJsuABexUkcAYgx9mHTsk5gfUGcvQRruipyyeByfE17W5AHFh9Ti+t2i5TTU61lfFU0qO8aou0SMRIGZTZT6KeOvS174fHXemadEm++acvUKvdx3JcbiByB05YX9OfTE3sdG7S7lRY9rxqbwszf7LOlZqZGps3zZH3ruLtGw2hvEAAo5te3p74sWk/s96V0hqmjz6jrMzqKmjYvGk8iFLlSLkBQeL+uLW3aDpeigiVs2ilLWJMSs+0HzNhwBfzw9zvV+XZDRUlRPHV1D1ptBBSwNNLJYbiQq+QHJOIKSnsGKblnahkWa7hFFXQsrFNs8HdsSLXspNzbcOnrbFjfO8viqKKCWqSKavDGnRzYyhRdrfQEH8cCE/wYrp19pgRJN97w9zIAVls2yxO35rWHPHXCa9ouk2qRAM8pe8LBAPFa+/Z1tb5vDfpfjAhWbBhrluZ0eb0MVZQTrUU0qhkkS+1gfMHBgQvcwy6kzSjelrYFnhexKt6g3BBHIIPII5GIr+hWnvu0Zf91wClF7RqCtgSSRcckG54vbk4MGBCIdIZRF8WGpI5jVyySyF1AA3qqlQBbjaij8MJDQuRNm1ZXzUazyVTB2V77Q3N2A9SSTf3NrYMGBCdPpLIpKxqp8shaZnMhY35ctu3WvbdcnnrzbphSj09QUOcy5lBEEmkh7kAAWVTI0jW8/Ezkn6YMGBCcrldGle9asCrUSW3uL+K3QkdCR64gm7N9KuZC+Vh+93Bw80jBlLbihBa2zdzt6X8sGDHSSeVwADhI1nZpp6ppJIBTyftnVpGlmeYkd4juBuYhS3dqCw5NsTWaZBQZ13IrYO8WB+8QBiPFxY8fQYMGIkA7FTa5zDqaaKKbTmWUqQLHTX+HCiMu7MVCklRcny3H88Ix6SymGWmkjhlV6VleI9852lbgdT0AJH0JGDBg0hT60nOo7+q61BpbK9T08EWZwPIKd+8jKSMjK1rXBBxH0nZzpujoZqSOikMc0glctO5YuFZQd17ggM354MGChdqXtM3S6Os6fK9vsvD2baW7sp93NtJvbv3/Lr09sSGVaSyfJUqkoaQxrVqEm3Oz7xYjm56m/ODBjqo5UevZ5kUlH8LWRT1sQZSvfSm6hQwVbrbizN163wR9nOmIXJiywKSNpbvpOlwbDxe36n1wYMSc9zzqcbKgxjWDS0UEpH2eaYiFly488m80hufMnxefU+pscLah0Xluo6OhhmlrKN8vbdTT0c5iliuuwgMPIqbHBgxFTTDK+zbJspofhopqqYG+6Sdkkla5B+crfqq9PQYmcw0vk+a1NBNXUMdScvDinWTxIu5Qp8J4PAHXpgwYEKHj7MdMQ0zU0VNVRU0iokkCVsyxyKpJUMoaxsScOP6vdN9x3PwLd3sWO3fP8AKs5nA6/8Qlv06YMGBCmspyqkyTKqfLaCIxUtMmyNCxbaPqecGDBgQv/Z</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S26 Ultra 16GB+1TB</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAAAAQQDAQAAAAAAAAAAAAAAAAIDBAcFBggB/8QAVBAAAQIEAwEIDQcJBgQHAAAAAQIDAAQFEQYSITEHEyJBUWFxshQWFzJVc3SBkpOhsdEkNDZWcpHBI0JSVGJllNLhFSUnZHWiJkNFYzM1N0RGgsL/xAAaAQADAQEBAQAAAAAAAAAAAAAAAQMEAgUG/8QALREAAgIBAwMCBQMFAAAAAAAAAAECEQMSITEEE1EyQRQiM2FxBYGRUnKhwdH/2gAMAwEAAhEDEQA/AOkYIIIACCCCAAiBUK3TqWQJybbZUdiSbqPmGsPz8z2HTpmZtfeW1OW5bC8Vc2tS0mamFFcw9w3HDqbni6IpCGoTdG+9uVB/Xx6tfwjztzoP6+PVr+EVVWsW0yiWE9PNS5VsSrhKPmERqVjCl1pRTIT7MysbWxwF/cdsU7ceLFbLe7c6D+vj1avhB26UD9fHq1fCK3D6XUBSVXBhClc8PsoLLL7daB4QHq1fCPO3bD/hBPq1/CKxUqGlKg7KHZaXbxh3win1a/hCVY7w2lJUqpoSlO1SkKCR0kiwiqXVkI0NiSEg8lzb8Yx2FsP07EdKar9ZlG59ybUtcszMDO3Ls5iEBKDpmIF1KIuSYcen1OkdRTk6Li7o2EfD8l6wQd0bCPh+S9YIrw4Tw7b6P0r+Db/ljztTw79X6V/Bt/yxf4F+SnbZYfdHwiCP7/ktf+4IO6PhHw/JesEV2cJ4d8AUr+Db/lhJwph3wBS/4Nv+WD4F+Q7bLG7o+EPD8l6wR53SMIeH5P1kUZT10+c3Q57D7mB6a1KS6VFMz2Gm9hayjwcuVV9Laxtfarh7wDS/4Nv+WOY9Hr4ZyoWWR3SsH+H5P0487peDvrBJenFbHCuHvANL/g2/hCThbD3gGmfwjfwjv4B+Q0Fl90vB3h+T9OM3Ta1TawzvkhOMzKdvAVe3m2xS/ath/wAA0z+Eb+EYl9lvAWIKTWqEjsJh6bTLTUq3cNKzg5VBOxJuLG2hB5RE8vRyhHUmJxo6MghLagtCVDYRcQRhORUEEEABBBBABjsQEDDdRJ2djOdUxUVZqP8AZtCdm7XDEuXbctk6Rb2IPo3UfJnOqYp2pMInqcZR3vH2N7V0EWjRi4Ymc5T09MVWoLmJh3O++q5UtVhfpOwRAanZinzbU2w4tl5pWZKhoQRE7EFBqGH6g7LTTKilJ4C7EpWOI3hql0eo4inWmWmVlHe5rGwH4mI1/Iy/aHWhOUlioOaJfld/cA4lJ2nzi33RWFQ3V66uoKelXGWWArgMFsKBTznbFnUyQbpzElIWCkNy60KHEb5biNEn9x9TlQW5KT4RJKVfKpBzI5r7I0TUqVHJv+Hq2mv0CVqSUb2Xk8JF+9UNsT1KjH0mnMUalMyEv/4bKbDniSpcVXG4HjyxZNz+enrCJW50P8NqD5KOsqIC1ao+2nrCMludAnc1oHko6yoth9f7FsXJsrAZ7Ka7JzBnOM+Xba/uiRKU8VKqLl5RSktcJSVLGoA2e2wiXSaVMTSVzTQaUGgrIlSgcy7aXHJ0xmqAmly778pL74meaQkvtvCzgSb2PJbQ7NIWbqFFvTydylXBpa7NpUXCEBHfZjYJttuYwc5i+hSRIXPpcUOJlJc9oFvbDm6m/hqYnnG5R+aeqja7OtNqJl0m/CzA6BX2fPFbCUcnHd7SAhA74gbBHqdNHuwU3sdJ2rNzO6VQC5vYM8o8QEuT7LxNYxfR3wDvkyzfjelXED77WjVJKQTJpswkIJ2mwuekxPQlwbdY0dmI68m3y83LTiM8s+0+P+2oKhZjUUspUsLKbLGxWwjz7Yy0rPPt2S4S8j9rvh5+PzxxLFXAnFmVMarj5VqPTyTYCqSvWMbQhxDqLoNx7o1fH/8A5LIf6pLdYxkz/TZOXB0NLfNWvsD3QQSvzRr7CfdBHzpIdggggAIIIIAMdiD6N1LyZzqmKedWAlok2sgRbWLVqbwjU1JJB3hWoikMRrdTh+aLF99EqrLbltGjFw2Jmj4p3RGeyFykjJS80hskF19OYE/sjk54iYb3SWGZ1EvUKfLyzbhy78wm2XpHJFeKdBULpK+a9iYZm2wwEgLzKUL7LEeaJ65chR0jvgXUWFJIKS0sgjj72JvblJyFPdojszJpW8okBbgCwTzcsajh9ya7Xqde/ZIk3Am/LpaKYm3HHpl0zKiHgolec8InjFtt7xac6SBHRalw0pcYDBz02vCMj2aVb6EWurba+kZhS4qnasQpS7rb8YjrCM5ucf8AppQPJB1lRrhX+Ub8YjrCM7gWbTI7klEmFDNkkxlTykqVYRXF6y2HkzkxipvDdWYcQ3vqk6vpBtwCNnTsMahQcXT9LxU5WVJL5eS4HWyrv82oNzyKt5haIE4p2cmlZ1FZKsy1fpKhTctlAFo9ddNjSepc7M0OKZJVTpB7DSqi7UFLqrk0QtkoOoIudb8pvm80RZCVCZfNbVRJ/CJSZRZFw0o8+WFUtQmJHMNiVrQfMo/0i0PltXYCkMgCHQ1zQ8EQ4lvmjpsYylkGH0N20h1DcPoa47RNyExDSSkgg2MYHH5/uOQP7zlusY2dKI1ndDGWgSJ/eUt1jGPqHeNkZ8HQst81a+wPdBEejOKdoci4slSly7aiTxkpEEfOESbBBBAAQQQQAYTGOmDqn4hUU1MKBCARcFIBEXLjL6G1TxCoo+oTSZaUVMOGyGm8x6BGnD6WJlcYm3OFqm3JqlvNttuEqLbhtlPMYZw/ucOdlImKi82ttBvlQbgmMJWa5PV2dUta1qTqUNJOiQNdnRGPpeIJ2izqZiVeUlIPCQTdKxyERO43dAXkkJanJdtAyoQ0oAedMRpqh0qbney3pBlb+3OU6mESU8ioCUm2+8eYKwOS+WJilxq2YhVwhISkBIGgA4obUuEKXDal88MBYX+Wa8YjrCJeH3z3MsMy42Jk98V05lAfjGNSv5Qz4xHWETMHpL2BqLzSiE/cTGjpvq2y+Hlk+Tkb2J44zMvKJQBlSAeiPZaXsNkZBtqN2TJZoGFIysrVxpSVfcLxqeGs0nMLlHTwZgb6gn9O3CHnGvmjewwFIKDsIsY1N2RIsNUONnQjakjjgxTW6YVZlFS6TxWPNCN5KTrs5YlSjgmGAogBY0UOQ/CJIaB2i4jp5KAhIa0h9DUPBjKRyQ8hqJSyWIY3uNS3SE2w5Jn95S3WMbvvekabumpy4Zkz+8pbrGIZZ3Bk5rZl50P6P07yZvqCCChfR6neTNdQQR4ZnJ8EEEABBBDM3MIk5N6ZdNm2UKcUeYC590AGoVzGtGmJOq0h1amZgsuob31IyuEZk6HiJI0BtfTlinqswZ2lOy17F5ooB5yIysriBGI8U1ufnKchbq6atbaDZaGSAnU3sbi2h5TEAkFsJOosI1Y0qo5ZQM42/JzLku+lTbjZsRCEtLn32peWaus2Gg288XLV8OSFVVmmZVDyh+eDlV5+IxHp+G5OmKvKSrbB/TUcyvMNn3xz2nx7Dsk0SWMnJy0sdex2AhXSdbfdaMkpUNISllvIm/KSTck8phCnIulWwhxS4ZUuEqXzw0pcMB1tXylnxqOsIzeAW82A6Nf9XB9pjXmlfKmPGo6wjbMAN2wFQTbvpNJ9qvhFcUqn+xfByzZmGtBppE1DQhLLegiWhHHHUslmmhCW+aMbUZLJMb6BwXNvTGcSiPXJdLzRQoaH2GI9ymdJUaw2ytlwLRpzcojJM5XUhSfODtEOqlciikjZCQwpledHnHLD7/k7cbHN6uI9DcPtJ37KG0lSlGwSNt+SJIps9+pP+j/WH3V5JOlyQCiNJ3UU2wvJn95yvWMWC9KTDCAp6WdaSTYFQsLxoO6rphOUPJU5brGFKVxdHE/S6L0lEhMkylIAAQkADYNBBDVJeMzRpN9QALrCFkDYLpBgjzTIS4IIIACNX3R5/sDAdQsrKuYSmXT/APchJ9l42iKu3bKlvNLp8iFd+tcwocyU5R7V+yBAabgSRL2HcYVYjRMsJdHnOY9URjc/BHRFgYIo6ZfcOn1uAgzrT8wbaHQWT1PbFb5+AOiNWL3ORxS4aU5DanLw2pcWAUpcNlcIUuGlKgAWpcNqVCSqG1LgAeaV8qY8ajrCN7wG3/hphtzklAk+kqK9ZX8rY8ajrCLN3OW993LaAg8cmOsqEnUjR0/qNjZFwIloTEWWungkag2MTkC8RlJpm6haU6Q4EwJiSiSmnJVEw22HUKGxJ4Q83HHDkcNqPJEcaCxe2ohks3ESs3CKTdKhtSoWI80JUITO0yPJy6zUpdDay2VOAZhtHHGQn6pOKn3kNPqZbaWUAJA1txm8RUIcM0yGSEu74MhOwHn5omzTtLdmlmeQ9LTSbBwNElKjblG3ToMJNJ7kMnq3Vjc8+9PUJiZdWQW3t7WkAZVnYFdP9YrLdZ0whKn95y3WVFjz042+03LSrRZlWjcJO1R5Yrnda+h8r/qcr1jFo2os4qoMuegfRym+StdQQQ/TWUy9LlWUXyNtIQm+2wSBBGUykmCCCAAOyKC3Zagqcxe5KoN+x222AB+kbrPWT90X4dkc5sf8VbrcpcFbc1PqfI/YCiR/tSIaEy6Jinik7mL0gBbsamKbPSG9fbeOfs/AHQI6RxR9Eat5I71DHM+fgjojRh4YMcUuGlLhBXCCqLiFKVDalwlS4bUuABSlw2pUJKobKtIAH2VfK2PGo6wi19zMf4Y4e8kHWVFRMK+VseNR1hFubmR/wxw/5IOsqOXyaMHLNncbyq3wbOOHWlXj0EEWMNatLtxHYYjNe5uT9iYDD8o1NOO3k0uJVxrScqfPfQ+2IiF3ibnnk0thWdSZQp/5ehGp747YkcZPBkXnWUS+91RbMy+NiWkHMPh06Rj32ZTscvSsyVZbXZcHCFzbp98Ik5ZyacyS6RlB4Th70fEwzcKAJGsCRKMKezPBlS+0pbhaSFglwbU88TJtNEm31PmoKbUuxVkGhPLqITT2JeYmUb7MhC0OCzS0iznRywubpskZt69VZYJUTvdk8Dm2we4SknLlmPm001ptIk59cw7mAKFcSeXYIr3dZN8HSv8Aqcr1jG/1d2RlqcxKybqJl5DmdbwAvbXS46dnNFebqywvBcqoag1KVP8AuMaI3osT9DL3lPmbP2E+6CCV+aM/YT7oIyGQdggggAxGLKj/AGVhKpzgNlty68n2iLJ9pEU/uOU8TePJycIuiQlihJ/aUQkewKjed1+oiUwi1LBVlTUwkEcqUArPtCfvjG7htP3rDM9UVDhTkzlB5UoHxUYfsI3rFRthCr+Ru9QxzDm4I6I6exV9D6v5G71DHLWfQdEaMPDBjhXDalQhS4QpWkXEKUuGyrSElUIKoAFFUIKoSVQhSoAH2FfK2PGo6wi3dzRVtzPD/kg6yopyXV8sY1/5qPeIt7c1Xbc1oA/yg6yoErkXwumbmlWkCrLSQYYSvSPd812wOFmuzzfC0vKo/wBYzNGL0swZ9+YSxIEG6V674dlwOL3nkjBvEOJsTbkPJE6Soq6jSGJh2roaaZSRvZQClnU7Tca855Yzzx6eTnLJNUzMOPJqtPApTiQ03o5LgZFH4fjGKCwU6ac0OSVCQ04J+UxAzlZ75xCAUgcYJzWt0xBbmEOtBaFBSTexHHrBGK4Rxja3SMhKiQUjfJmddlnkrOXINg4jsMKcaoS1qW5VJhSlG6lEak+jEaVnZBlpSZuQMysqJCtNBppqYUuq0UbaIT50/GDRK9kzl3fuQau3SmpQKkZ1197MAUrGgTrc96OaK43R3s+CWEHaiqSw82YxY1dlZJVIZq1NC22Fr3pxpR70/hqLeeKq3QX74dQ3fbPyx+5Z+Ma4QvDJoHK4tHScr80a+wn3CCCV+aNfYT7oI8wzDsEEEAFKbuFSz1SVkgrSXlysj9pxXwR7Ysfc/pv9k4CpMsU5VlgOq6V8I++KWxs6vEm6cuUbOYTE8mVTb9FFke+8dFNNpaaS2gWSkBIHIBshsRi8WfQ+seRvdQxyrm02x1Vi36G1nyJ7qGOT82gjRh4YMWpUIKoSVQgrEXEKKoQVQgqhJVAIUVQgqhJVCSqAY8wr5Yx41PvEWzucuW3OaEP8qOsqKiYPytjxifeItLc+ctufUQf5UdYxTErkUxumbqHtI8U9bjiCH7DbCFzHPGrtmjUTlP344yNUZU/ganKl0lTKVqVMZBfha6qHGAfwjB09mYqdQRJy2QuuAkZzYaC51jZqZRMVUdajKqklNrN1NOOKKSeXZcHoiGdRjW6tb0cSlZiMCtTDmIHXMhEmhlSZhRHAVfYOQ8Z6Lxi6PUECaelUK/IlSlM9AJ/C0bXXKdjWsU9cohVOlG16KSy4oZxxgki4HRFXSU6Gp1pYUPybuU2PPlP4xbp4LNqltfhE1Jp2WVJNUyYYUqeqRlHAsgJ01FhrqOmHFyWHTtr6h6PwjXHHyL6x7KyFRqmbsGUcfCdFKFgkHkuSBeIvDXzOVIo39ybiSr09ujs0ilKU6w2vfXHlfnHX79Te/MIqXHb2ekSovtnmOsY2+vNzdLdLE9LuS7pFwlY74coI0IjRcVEu0RtZ2Nzct95Wf6xtWKMOlk4uybfsdXSnzNn7CfdBHsp8zZ+wn3QR82cDsR6hNop9NmZxzvJdpTquhIJ/CJEalumz4ksBziArKqaKJcdClcL/AGhUAFTbm0musbqko87dXYja5lf2jx+koR0MNBFPbhkjvsxWqsod8pLCD96lf/mLhhsSMPi76GVnyJ7qGOS82kdaYu+hda8ie6hjkXNpF8PDBiyqEFUJKoSVRoEKKoSVQhS7AmGy7zQAOEwkmGy5ze2Elzm4oAJDCh2Wx4xPvEWXgNzLgGii/wD7Ye8xWEubzTHjE+8RYuCHLYEo/k495jV0ivI/wNOjat/tDa3tIhretDKn+ePUWMpqJaplSFZkLUg8qVEH7xG2Uek0mcwwirT9eqEsE3S8eyClCV370XGp2bLxoK3tdsblOyEzXNzCirpTapgyKlB9hvVWaxBNuMgm/LZV4zdXGlBXVvk5bsyslRMN1KWfmJTE1TfRLjM6EvnMgcpTlvbzRUk5+RxAy2yczM28Ck84VqfOLHzmLF3PKPUZOurq07LuyUjLsLDi30lvPe2ljrYWuTs0ivJ5TT8+2+0MraJhTjY2WSc1h9xEddItOWcVLUkkIsqjN0aqSi5KcmDJz6nCpl86BQIFkniOvEbbdDE/FzlWwzhamS0gp1ptAKZh6WSb57AjXaATmMaVhzDE5ihuYeM43JyEucrj72ova9gLjYLXJPGIytWrGL9zZhhKZ2XqlKe4LD7qCpINr5b3uNNRqQeKMeTEu8owkm79L/6NuxWLJmcn9yWnzdZSpNQM4EsKcTlcWgk6kc6RfzAxW+JJct4AbmVCxmKnL5fspKgPbeN0qknXMZ4bp2J5+poWl+YMu1Jts5ES4zKCl3ubmyOPXYIwW6U2hjBsoy0nK23PSyUjkAJizah0soLm3f2+xyzo2U+Zs/YT7oIJT5mz9hPugj54Y9FVbt1QLUjTpQHgkuPq14wAlPWV90WrHPu69OqqONnpVs5i0GpVIHLbMfau3mhoTLL3I6YadudyalJKVzalzCrjXU2HsAjd4iUmTFOo8nJA37HZQ1e/6KQPwiXCGYbF/wBCq15E91DHIWbSOvcYfQit+QvdQxx9mjTh4YmKKjCSYSTCSqLiFFUJKoSTCbwCFEwm8eEx5eAB1g/KmfGJ94iwcFG+BqRrY9jj3mK8YPypnxifeI3/AAWf+CaR5OPeY29F9R/gGZhxwgkHTmiG66UnbcRPWhLibKHQeMRj5iVebJUgF1P7O37vhHtxoaYyXypQAuVKNgBqSeICNxodKxNQMU06nJm1UtyqoK75Q6jgpJIUk6FQsOi+2MRufMy05uh0xt6121LcCTpwkoJTp06+aJj2IHZTdldqdWdd7Gkpp1oJSkqLaAlSUgJ84PnvGLqZSnN4YK/lb8/ijpGcx5IYyRSnHZupt1Glt6vJlW96ygca06kgceptxiKtmJsBaE31vmiyNz+ump7q1clpdZdplRD0yplWwDMkBRT+aTmI57xUk2hLVUm0B1IabeW2g3/NSogewQ/0/VFvDJLZJ7bc+RFlYcmZLEG5nV8OqqDMjOMOmeSXjZDjabKN+MgZSDbZoYj4CxDJVGjvYPxIT/Zs580cVtYVttf80X4QOwG4OhiLhnB1Nntzyq12f33shTol5JX6ChbhW4wSbHmBtG14Qw7RqBhx+v1OWM6pS95aCgDnN7GwOmpv5hGfM8MVkW7erb+77MLMxNUcYb3OpOl9mNzZZmswcQAnMFKWoaXPLFW7pbmbCrA/z8v1jFj12RpUxQZev0mW7EQtzenWbWANyL2GgII4toMVhuiuXwyx5fL+8xnhvgnJ873+Tlvc6ZlPmbP2E+4QQSnzJn7CfdBHhnY6ogJJOgjnSjpOKd1uRUoZkvTi5tY/ZCisewAR0DVEuqpE4GElTpZWEAbSrKbe2Km3GMPvLrE/XphlSGm2xKy5WkjMdM5HRYDpJ5IaEXINkEEEIZhsY/Qit+QvdQxx1mjtOqySalR5yRWrKmZZWyTyZkkX9scb1qjT2H6s/TagwpmYYUUkKGh5COUHaDGjC+UJkImEkx5ePCY0HJ6THl484o8gA9vHl7QR5AA4yflLPjE+8Rv+DNMFUnyce8xXoUULSoalJCgOWxvG04YxJIUylNU6oPdjJYJSw8sHe3EEkgZtgUL2IPJGrpJxhk+Z1sJ8G6gx6FaxhO2vD/hqS9aIO2zD4/61JetEev3cf9S/k5pmwSsyuTn5edZyiYllhxtSk3sR+BGnQY2WrU/AWO3RP1Z2YpNSUkJdKHVIC7bNRwVdOhttiu+23D/hqS9aI9GLqAP+tSPrRGbLHHkakp017pnSbRYMirCmBqXNymEkuzE7ODK7OOKJKRr+cQNlzYAWvqY1CUpFNkiCzJtJWPz1DMr7zeMd23YfvrWpL1oj3tuw/wCGpH1oh4Y48V/PbfLsTbZYFAr9PYpszSKyw47IPrDiVt3KkK05NeIG4jzEuIJOfk5SmUlpbVPlNU5xYqVaw022Fzt1JMaB23Yf8NSPrRHnbdh/w1I+tEcdrB3O5q/ztYW6LCrNdp7mF6dSKWlxLabPP753yVa8EnjJJJuNNkVrugHNhxgbflzHvMSe2/D/AIakvWiIaEK3RsRUyg0MLmJZEwmYm5oJIbQlPITt2k32bBtMSy9rFglGMrv/AGPds6klPmbP2E+6CHEJCEJSBYAWEEfPFBRFxaGJOTl5CUblpVlDDDYyobQLBI5oIIAH4IIIACMdVcP0iuNhFUpstOBPe782FFPQdogggAwp3McGH/47JeifjB3McGfV2S9E/GCCC2AdzHBn1dkvRPxg7mODPq7JeifjBBDtgHcxwZ9XZL0T8YO5jgz6uyXon4wQQWwDuY4M+rsl6J+MJXuXYLWhSe1+VSFbcmZJ+8GCCDUwPe5fguwHa7JG3Kkn8Y97mODPq7I+gfjBBBqYB3McGfVyR9A/GDuY4M+rkj6B+MEEGpgHcwwX9XJH0D8YO5hgv6uSPoH4wQQamB53L8F/VyR9A/GDuX4L+rkj6J+MEEGpgA3L8FjZhyR9A/GM9TKNTaNL7xTZGXk2jqUsthIPTbbBBCtsCdBBBAB//9k=</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Samsung 85" Crystal UHD 4K Smart TV 85U8075</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>1000000</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Frigo Skyworth Side by Side 473L</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TV Samsung 85" Crystal UHD 4K</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TV Samsung 85" + Frigo Whirlpool 561L Combine</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TV Samsung 75" Crystal 4K UHD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TV Samsung 55" OLED S85F Vision AI</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>iPhone 17 Pro Max 512Go + Frigo TCL Cross Door 635L</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 75" Crystal UHD 4K Smart TV 75U8075</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAAAAQUBAQEAAAAAAAAAAAAAAAMEBQYHAgEI/8QAShAAAgEDAwIEAwUEBAoJBQAAAQIDBAURABIhBjEHE0FRFCJhIzJxgZEIFUKhM1KiwRYXJGJykrGz0eEYJTZDU6O00vA0N3OClP/EABsBAAIDAQEBAAAAAAAAAAAAAAAEAgMFAQYH/8QAMxEAAQQBAgQDBgYCAwAAAAAAAQACAxEEEiETMUFRBWGhFCJxgZGxIzLB0eHwQvEkM2L/2gAMAwEAAhEDEQA/APpHRo0aEI0aNGhCNGjRoQjRrxmCjJ1wruZcbfl/2aEJTRo0aEI0aNGhCNGjXLvt4HLYzjQhdaNcRMzL8wxzrvQhGjRo0IRo0aNCEaNGjQhGjXLvt4AycZ15GzMvzDH9+hC70aNGhCNGjRoQjRo0aEI1yzhB2Jz6DXMjn7qYzrnywW3Nk57A99CF4A0uGfAX6aVVcDGMD216F9T+ntpOepgplDTzRxKTjLsFGfz0ISujXgYFd2RjGc6FZW+6QfwOhC90a5Eik4DAkfXSRk8xyqsCvb5Tkg/XQhdySleFGT/LXKx85f5ifTXEbwpMIfMjM+M7dwyPy76XDKG27hu74zzoQvQPU99e65EiFdwYY986N64B3DB9c6ELrRpOaeKnUNNKkYPGXYAfz0oCCAQcg6EI0aNB4GhCZ3W60Nktk1wuVTHS0kIBklkOFXJwM/mdU3/HP0e91ekiuSPEihjVDmLJBOAe+ew7dyNSXiPJIvQN0lTb9iqOMqG5WRTyCMdtUHqHpzpyx9c1XlCCngloxPVAEyNkl1bEY7HaVPoBjJ1wkDmpsjdIdLBZV3Hib0bsMjX2Bx3yFcj/AGa4sPip03e0ps1DUk9W6xwxTKdzlsYwRx3ONY5ebJNW3SoqKVKOCnjG2OBJslEUYAPHLcZPuSdcUVynt9qpqCZJIXp7zQVYySvyeYAVI9uUYaWbkW/SQvQ5PgfDxPaI32QAXDt/pfTmjQNGml5tGvC6rjJ5PbVZ6yhvMjWg2erroA9dHDVCmVGxC2d7ncpxjA5+vrqrxXLqr992tKpL7CklfUedLFSLJD5C1DCJWAXILLg7sgBRnk6ELTd65xnnSLVIMzRI6b1xlc/MM+uPbWT2e5+INTbYlkS4rc2r4VcVdLiFYvtC2TsGFOEBKlsAg51c+glra2zfva9W6aivU7ypMJ0xIsYlby1OODhdvI799dXDfRWdI9uM8t7e2lQMfjoGPY6M/Q64ur3WCeNfTlc3XlJ1LW2hupunaeiMNRb4psS0xO7Myp69wc4PbnHB1vedZz1p4XSX3rCn6qsnUFVYbykHwjyxQLMrxnI+6exwSM/h7aEKiXO82W0/snVh6du9dcKSX/JInrMLNEXkG6MgdsDPb0PHGlPBanPS3izfOmi7BKm00dYisSfmEaFsZ+sjfpqzyeB1ok8N6Po1bpXpS09Z8dNMEUtPJgjBB4Awew9hqffoGlXxLg63hq6iKqp6T4NqZVHlyIARknvnkf6o0IXz/wBD3VrB1VP1QWYRT1d3pJGLEjKwCaMfqDq0eAtFJavEuqoWZ1km6dp6pyxJIeTy3J59fn1dajwCs9V0bPYGu9esc1za5+eEQOrMmwoOMbSNWi0eHNBZ+vqvqiGqmZ6mgjt5pio8tURUUEHvnCD9dCF8/QWGk6U6ngpeuo6+iq5br8TSdV2+bzVmP9Ryc4XPJ/iHqMc60S9SH/pWRLuO09PucZ4+7Jp2n7PVGiC2f4T3I9Niu+PFq8pMeZ2/pO+Mcdu3151Y+sfCxepOqqbqS2X6ssN2hpjSNNBGsivEc8bW7HDEZ/D20IWNWWR/+hpfX3tuFf3yc/0sWmFzZ7R03Q9LtNKxt3UVFWU5Zjk09TDvAz64YMPxOtyh8HrRT+Es3QcVbVrSTuJJanCmRn3q5OMYH3QMe2mvUfglZ+orxZrjJcq6mmtcEFPiILtnERypYEd+/bQhUzr+gouo/wBoSe232kqrrbKGwPUxUUBJbfzyigjLc+/OB7avXgbU26bwyp0tVwuNfRwTyxRvXxqkigEHbhWYbRnjn10r1n4YJ1F1TF1Jbb5cLFdxTmjkmpVVxJEc8EHseTyD7e2pvono+g6E6WhsVsad4YSztLLy8jscknHHt29tCFZN4IJHOPTSWXlOAVxweOdcEuEMgB3KfbvpwAMcDAPOMaEKt9fQeZ4cX9FGSKGVs/UKT/drJPFGCI9Q2+7UlQkxq6ON3CMG2FNoycehDL31u9xo1uNrqqJ2ZFqYmiLKOV3DGR9edZXXeCSz9RUtY1+udWZEK1c08nzsqldqgqO2N3B9ce2qpY+I2loeHZzsGcTAX0I7hUGbq65TCQYgiEhJYIpGcqyn1z/ET+ONNYqNJejr3V7w1VTGmeNM87VmVmPP0XjW10/hB0nCAGp6ufH/AIlS/wDdjRaPCbpi13GsqDb0mjlk3RRS/MsYwO2ee+7v76Xjx3B2p5tbmf49DLjnHxYtAdVn4dFekYOgYdiMjRoUBVCqMAcAe2jTq8msj8caM19d0xTCaqQPJP8AJTyFC5wnBI/E6zXqXw+IMdFbOqYaS+fL/wBXTXY+a3HYKWyG+mtt64gefq3p0wlFqI4a1oS/YSbECH/WI1k1BU9DweGDW+7pbhdvh5EuFNURg3N6455XI3li5GCOMfnpFzCZteo7UKHL5pppAj06RZvc/osqlsHW9NUyQyQXnzIsg4eTkj89SnTFV1LPTSqtsnrZIDsJk80kH3bB51qtitl+vUvUdJfeob3R1lmtNBIIqasaLy6g0pZmYDucryOxJJOdQEHVF9vRElfVGhEVrpaqLyb2lpDM8W56kgofOJfI9hjGOdMSxcVuklUh5bu1V+g6V6u6onWriqfg42kEccXxBh819pJRFJ+Y8dudWWk6Nv8AarfIsj0VbXoQi001cQ4cru2Ebs7to3AdyNW2srDT2Lw1vV6noo5Dc0lrquJgIcvDIEkJwAobg+gyTqHnqqa5eKc1xopo6min6phSOeJgyOUt7BgrDg4PHGqnYzXtDXE0OxQyR7TqHNYdW3q8zXCd5q6phbzMMkUroi84IAB4Gpay1Fwmu9OklZVOhOCHqH255+uo6vpXF2rCFztmclf6w3H+enlCzmeJadnEwOFKHDAe34D66vlb+GWt22Q1pcVMXeaot1bWTR1FT5YbbFE074YkcY54GefyOq5JfakXvzIquu+EDjMXxDt8vAPc985xp31BWJIYZ6acyy0koklkJz5j/wATfgOAPwOk6iGFamYLAHEknmb1O0YIyOD2/wCWk2udE1oed6/ZRc4OOlvRTfUjT2+o8mGvmlgnRJo6mOZgdrDg7Q3r6j0I41FW03SNqaWsrqww1I3q3nO3AYgjGfodJ4aipYopqVhMUWT7QZDKT8p+g/46e08tRDPSbQdis52Mw2hwdxCj29Pz1W6R7hWq+5/vyXWUHe6OuwT6nWvjqYp2uO+N51SD7VyrFvuhlzjbz/LUDW11c7uVq6qFg23atVJtPAGRz9M/nq4W/pqKvpklqmngoaJWnIVAQ5J9M+vpjVbrHoYrk1tiogpEzOHaQsdpHCf7P00vj5TZHuAJNeiZyonwlod1UDJX3VHUNXXBCVBG6ocZHv30/Nfcf3c83xdSwwMOtS4Kn1G3OT+Ol5IXMcMNUCxpfuK/BZc8pkcjHPB0peLP+7qSn8zZJBMpkEUTbTGSMgfjgj9R66c44JDTzSul25U9Y5jVqk0j1MwYAbfNfGcj698Z1zeI5KS9xOtTUmmZFby453GBzyefpr3plEiILAgnA3EZzx3/AB15caAJ1FcWmgaWKp2sqM5wwKnbj25zrDEzhO4ajVL0xiBjYdItRnUN6jFRTfu+5uEVcyLCWYk59STt7emmtHcJam6wo1dWPD/3pSR1IGfQBypP4EaUnorjQTQyk0VLLJysUUStsB7A5H951ovhp0Xauqqa9fvKdqeSnjjaOdCEVXcsMsMYIyBxrVjsNaxhuxsb/j9UnjYftJkyMj3Y2EXQ33rYb+e+2wVKmeWUqEqKlAmV3CocFx7kZ4PY8HSdKs9NMzSVdTURnsslRJle3rnnt6612h8LbdFdunbddY6mOorKaperVJsDfGV27Tjgc/7NNoeienK3qCG0x0ksMtTT1DQsl0jqcyIAVyEHHr37/lo0TadN+q9M1vgoNiImhd+QsXz8uyyutaomlU09TPEg3Egzv3OMDg9gB+p05SomWHyxLJycljIxb9c8DWuN4T2Wmp6apnknkioqSVroFmwUmWNHAHHA5PH4ax4EYyBjOqpuK2tZ9VoeFYnhcznPxmXXffv3+H2X034S7j4XWbfI0jbZPmYkk/av6nRrnwicSeFdmcDusn+9caNbMd6Ra+bZekTyaOVmvhajPFCqFJeen2IPzrUJkdxzEf7tZB134n3KjvmLW9GJ0QBatqZDOo7YDkbhrXvFKGKe9dPJOcR7akk5we0fbXzX4iWyS39aTKWLxThXib/NPp+usPY+KFoNHTfkU9X/AAAa6qVk8X+racqxnp97ACWXyF3T4GAHOPmABI513SeK12ro41rqC01sdN/9PHLRRsKcDttBHyj8NUStjKwxPhiz8YJxnjv+mm1MqxsCCSRznHfWsGue00sqYFpoK9VviR1BF1PV1Bqkq4qqNVqKapiEkRA527WGDjjT2HxX6i8uOkijtsFNGxECRUiKsDEEbkwPlJB7j66oUvlLM3lbljydoYjP54408pKd3CY+YsQMehHpz6HTLWhjACuMBOyl2o3rKHzXx8b5hBTcMsc/eH9XGOfTTrpyli+JZ5goZU3AnnI9P56ZUNvnrrg0FM7sNpBY8hYxySPb/nqctQhpJZIPI2M8eFLc5x2Gs3On/Dc1h96vRPQUyVgcNiVxaOj6SqqVWesSNfIMbRBfmkLEnI/UaZX+m21VPWxuheNlhaJj6DgHHsCO2u7601N1BEsaDyqhe5GNhAJ3A+mMdtRDQzVlRNN5jTsTsEjP97J5+XOQCOPz0rDC8lszn6gR9FPIYwkta3TR381I3K4vcK6erdWenCIzRgZDEDjkfw+un8dvo46meOBaiSeNIhTrGAy7T8zs2Ox7Y1HUNqnjq3RZhHtmA3CTHylScg/TIP0zqwxxT222KsUe0SyYqdrDcpA3cNns2O/P8xrha1g4bDQKIsanB/ZTdgjNVYbi8tXFDTRU7ggksQeCDt/Eemspq6Gvp6eOveB/LqJGAnYfKWGCQPc8jWhdO1HnXOoAZl+J3qTGcE7hyAccd9UW4u7y/CeYRHFIScc8k9gNJYNMke0dd1f4pZLHHspajmirPJq5BmRyqMpYgjA7/wAtIVVFU1Na1W8UkkQchpQRIPxIH5c49NOoJI7XNDFHB5rRP8xHDZyPx9NOKRPPmeaJnhmbMiyx9x/pAcEe+rXucwlwWYeXmpbpnyqpvhz80Zbkj19se2ka64CXqKWJ/mhT5FYDO4L/AMzp1Y5jDdxUSU8cUqoAQowCc/expzWpSQdWtHRFDFIoYrkFVY/eA+g1kOcBK6x0Xqscl0LLUJeqEpcErZpfNkmRdi9hGoHYasfQM6SU97tE1fFQw19MvmySKOY1b7QKT2baxI+o1D9XQTUd4jeclY5oA8StxtUHB1AxVEU9Q0XmxRbVJLykhO2cZAPJ1q4krjG1x329F6GB2JH4eY5HhlknzsOu668gt6pbkZbjYa6ovyYprefLqJxHz5nlAq3uwz/LnHOo+Z6dJbZeI62122roxPNmKmhiy4G3DKpJZcE55zn21ktmtb3qmSaF4oy4ztYE45xzga6qLLWQPUiGFaxKUZlkpiHVfp+I9QO2mjns1Fh5jzSbMHDoPbOAD/56G/3Ww+XHPLerfN1NHTR3uRTUCUxs3LtHlWU4UPGgK5zjgH31mfSXTNVfr9sghWWClYu5kOFbbyFyO+ccgemoe0UH70nPlo0sKIruYlzjP8J9iNaRQVVJbK7p6jEJDLUGTy6bBkTjGQO/J5PuM86Sys0F7YgN/t1UXZLMHHkONJr1ULqgOm3f+FpvhVLJP4a2yaU5kkad3+XbyZ5CePT8NGnfQGP8EIsdviqvH/8ATJo16hvIL56eapHjjcI7VNYKyaOSSOIVJYIccYj7/TXzP1X1VN1Jemr5EEK4CQxA58tRyB+PqdfQX7TDYsdq78rUdjj/AMP/AOY9dfMMMW58tqhmOwzmcj3qpWmd5j4N7JyZJqpwzk4C7Fz6DTmnhyxIPyqAT/frxIyYztGQOSPXUlSfCtGI3JjOPmyfp3H1+mn9mhVAFxTSooSiZV1dcjB9/wDhpWjMtRXJTxl95yu0d8kHnP66USFqmoWCnVnlPAQdvx+g1O2W2PbpdvlEzOfmkPcj2HtpGfIawGzurhTXNB6lWyw9PPF0vcpqVh8SkXLHsR6j9NRNxqIpaG2SRoFnjIDemdXnpaLZ0zWmXGwgrljkapFwiS8XN2oW2UsQBZwOMgc415TCe2V8k87uTvrtyWl4nFTo2Rj5KOv1css6wBIWaIltzuFxkDIB7ng9hpq9KKOmNfKuJEkHmdg4Xd2BHdhkY59Dz6a8tYeS60xjlZJJAziQqGAGcEgNxn8vT66l7nSx109LAzDM4IGWLEkcAnk5Pqedeiig4MQb0HNUvl4slnmnFj+GqbR8Q4YyKojBJIUMw2ZOM4UA5OpowtB0vWGWGKNXXYgyAwAZewwPTk57/kRph0pYKulqaqnqKNVFIpFQxqMqV7grx82729PXGrZcZKeot8VHtYrVxIGwxKORkjOD94DcxIHAwOdUT43BLgRfVMxSiQAg+SqNrRbfXQPHIJXBDeWqk4zjPAHbDcn01HP0tLUo9RTT0rbsyhGyhALsD+Q2/wDznXaSO8i0GyVirLFIqhcAbhg4BAIJ3Ej/AIjHlNVRRQo0ckssowIt+I9rADcH5wxIbcP4R69zpcMZ+do3KlMwSgNk6KOahuNPcVkmhMMgfCuo4UgD1/LH56sXSURfqeneSMeWxJkXHyZPr+frqHr706KwhaL5VViyAncw9s84yCQRgDHb00ra+oHoagOgQOoAkMgzk5AIyMYPfHoSD78U5cUkjSQOaWZjMa4aTy7rTur+jrdR9G1FfTqHqoDlW3YwhbsR64BxqidJWlay4qgdIg3B3DJPvjUrN1NFdenp6ZZiksoVjCW3dj3BHGleiaRZ7gm+Mkbvlx37+/56xp5HNiLdOk/VbmM3az0TfquOsuPVTUk0NCfIQRUyNSmrqGTvkIDhQTk5bGq/fbJU9LWNw+6EXBW3T+cVjOD/AEbRpwDg5ySRjtrRL9bI6fqiChhp0HxMvm/CQk/b85aWofuVHog4OnPX9kir7bSsQwjSXCRQRgySNghURCMFs55PCjJ9NaEBc3TH0FWsWaPUHv6rJ+macwVAgjrKmlh2gB/LVWkzn5gDkqPx5P01frVaEsVHLNS5ejgiaZgMFyACT+J47nVOpunYLRcBUb2ll81kqI4ZD5UbhciPzTzI4zknt6D11eLNUJWUc1FKWcTRmJyRtbaw9x+YzpHxYkOtpsHmtLw1ruBy3F1Z/tKG6cqlmvZqaSIU0dXB8Q0aLxwxP64Opnp68Wm5dSyRUdtjaKSYzJUSAJIG4J4IyeR6HIz2Gobp21SxeT8JXeStM00McnDSPGSQCM8enGfb66fQ2ZbDfKOc1kc1PWyqhEylftFwQQMnDY7EH6YxqLOFx3AO94igPh/HJVvfKQxxbTevLr/K2Pw5/wCw9Kc5+3qf/USaNc+G3/YSj/8AzVP/AKiTRr3rPyhedf8AmKyz9qVJJLb02kZIBlqN+D6bU76+enHlqVQDAXGRr6J/aeyaLptFGS8lQuPf5U188oocHaAUB2k/lxq9g2UFxBUgPubJXPO3UjHSifkygQj+Nh9wf/PbUVHTMlQQp4PdSM6mRiWmFNFHkgZ4GMn/AIarc0ncq5jgAlaO/wBPZ43hpqQSv6zF8GQfpx+GlR1rUvIW+Ei79ix1BvEZpxHGgSRuAp9BqRFvoYocVE8gkIB+QDjjtjS7sbH3LxZPxQGPe7V2U/TeJddTWaagFBTiOfILFmB59tNaXrdaam+HNt2rtIPly9/ryNQ9ZBFJHBFT1KvTx54lwrLn14769gt0DbfMrUyQPlA9Me50uPD8Pf3Kvfr+6bM2RrD7s/Jex3aneJY5jLEEwVf7zK+Mbxj1AwCOxA9CNWGnq0rlgkSKap+EcTNJHIqZI/q4JPze3HfUStnpniXbNGcttBLjJ59vb8ddzWVKcK8TATDuYsg/rnWlraRQSvBeDZVwgu1uZKoRW65SVlfGYpFeqwMnna2DwcA98bRk/TXtHcJqqORjjyo4ncMBtMsX/fSKTwikKsaFiMjJ1UIqitpUkAqDNHICkkNQuUYE889v1/np1TX8VtYI+YqsSrL5LktE7A4BIGd+xQMKSF+mpyRe0NOp26ra845FN2U1dKdbiiVIMSTSRBlwCRt25DlQCRkZAzycaSaQtf4oZKimWlqX86EzBF84SBuQuM7iGAycfdAJ00iuMlbUbxvDsZZABKrBFH3uGyR3zwfxxpHqSGkoK+nus8U9VI5jjhiRsKoVf4iMncBjg/Q8g6zMGOPXwn/L+/ZO5j3hnEZ81F1MpenZkSncwO0cixAOqjae+D8xLZxz+euoBvE8cExnaN9m1NzE4HzZUDOAxHGT349dC9L1kawrbqtdsHzzFsjBbnn8FA0hUvVOXpqSijnhkqfMiEQPyjb8x3A8EnjJ9tP5OKWVQSePk6rNqahq3wJVqEDMCxUMGCqDgcLyM4AAyMEY9daT0DIUmjqFkVI4uCc5BHHzZI5/56zKlrw9YjbqORY0MoZaksqqvcHB3AkdyPXnBHOtDt0yWvpKtllzKgpBPFKHB8zkYTgkZ4257683m4Ylpo9Fv48+kG+SvEl8pZ7m0saqCeGb+JlHYZ0rcq1LhbSkEphJ4eZPvxxn75X2baCPz1TLRVw3CBKiBkIcA4U5AOM4zqeo5dhZHAGeCPcag5mxLVZQcKKqNzoJD0va5/hRFQmoaZ4kJHls4ygIB5ATav4g++lLBJh5Ujh3qpY5xnjGc51dWeFKfCqNsQLD3HByR7HvqoWCnlgWSRJ23SgvGxPzKjDgn+R41k5jS4e8pQyez6WAJgqvbIXkpyJYUm2Ism6J/qACM9j37asK01H1NReXOjskQMkTRnD5Azx6c4xqtVtHWWq3Sy1gDR+Yq7lcHPc59+3vqx9PTQTWGVXhWOEx4J5HJ9Pfk+2kslpaQ9oo2ntOqMtduKWmeFTB/DW1sN5BM5+0Xa39PJ3HodGu/C9/M8PKB/60lQf/AD5NGvozeQXininFZh+1IQKLpnIyPOqM/wCqmvn+mlEW8hchgV5OvoP9p8M1L0wqjcTLUce/ypr55hDN8uDkH5gRyD7++rQ6ha4BZSsRLVDpGoJ25yTwPrqWo3lemNJBSCsmB3bx8ojz3BbS/TnT0t5ukVKszR00j8uBnCn0+pOO3p66tF5p6S1X392UcBhhpsJg93PcsfcnSJyRLN7O38wBKcMRhj4vc0oy3eH891tVTcKy5LEtOu4xQx5/mdMF6XoEpmL+c7N9078fyGtN6eiQdL3aRlypQjAPbjVXaBZIkXAGBrH8NfPnPk1PoNP6K3xMCAsazqFX4ej7cxVvMqBk8qHH/DU5H4bW2bpyouArqyKSLIVSVKk+meNcRU7NVKm7Cr/t1eadDB0BUFcOxbBz+OlvFsySOdscDiNwFbgAGCR8gugsJ+BrVO2OQyMBkKUIP5Htp3aaO+3aZ4aKjlmeFd7bTwBn3Pr9DzqSVRR3KSDaXHneXIjBtrqxAwfc+o9BgnV/8PLVUQXGpnkqZZKV0KxRyEj+IYZG7SJ8p78qQNb+TM2LDfkDm3p9ktBb5ms/xcs0mrrhQVUkFwgnglU4cTIQQf79N6VFlrZq5fK+yUtEW3CMMeSW2/dAXP541rFPDJW9WTpUxhlNSwZCMqR+Gqn1W9HB1RVxW74WmQkrtgAjZjkKxDH5RzxjHOMc6QxPEXzPMRbR039Uw+IFgf5kfRN7VAvxW7/JytOBh2UghW5UiTuGKl9rY2nA7cjUdfr3HcqhYYQUp6UYiDoFZ8gZY44znOPpqQ2VVwsNXHSrtn3LiGaZDIEcknkY2r8u0KffjGoF56y3p8PcqOVYWGAJFGOPY4xrRx3Nj3PNUyESO0g8kvSV8lKi7YxLE7EuyjdIo98HIOMA/hplcK2BahaqGnMn2gchU2D7uOR2ODz766pKtIqpfhYCV253PyQfdMc8acVNfHV7lmjjaTOzzF/i+p1p8UOSvBA8kwoDEbZJHTVD2+KN1lmnnbIc4wqAKM5HJx66txrDP0zW21XgFHDslEoiML1EmBlUU5DBlXd6cjn2NGlX4ST7SOOopnYO0ZPysRxnjkHVotUhaamnkZpWbBEki/0QJGAgOVXG0YAViPfSc1NbrHRWxXq0FSXSHUUMdxaISqiyAB1RGCIeMEsc5PuTtBJ49NaYlWGRfc6yO5tBauumh/eFZSq7h44YQV3OygkyevzN9O3pjV6oLkKmjjlKtGzL8yN3U+o0lPGC4OHI7puKUhtHpsrbHKgX7wweDqFg20ox8u4sVyq7eBnAx+ekVq2fCq+3TOarjLRgOd6qd3PY54/lrKkgc6ZpHn9lfxLIK9v9U89MEXayB8OCR68A/XUnbIJJelaujkY+ase5fLwG3KQQwH0xnH46rdbUoQkQi37m3O5XOCM4APp76tVAorLHVS26eOOseLKjGRsA+YD2JAOsfxD3JABtRH9+C1o6dE4nfZad4Tu0nhna3bbuZpydvbPnv20a48IefCuzn387/fPo170LxzuZWc/tPgNS9MAlQTLUYB9flTjWDwrHHUlJCN4ODx835H+/W/ftJx+bN0hHhW3VMwwxwDxHxn01Xbp4Cva1NVX9Y2i3RTSfZmoUxr2yFySMnHtoduKU2ENGpVvoioVbpTkNtCSDsMZJPOl+sdo67qGUnG9M/oNW21eDk1qvdNQ/4W2tq2ZPPigEbb5EH8QGeRx31D9bdIilo6+/wdR2+5ilqEinipgSUZjgAnOAfprLxsV0fiL5/wDEtI9Qr8jKD8RjDzBtSvTkyxdL3jceBGWx9MaqkMweHk8413R1NwSwmnSknP7zwlP9mftucfJ/W54402t1ovlWsoprRX1HkyGOTy6d22MO6nA4I9tV+DYxgMxd1d9go+LTCYs0dAnrCOKeIdy2Tq119Stu6HghHLVTcc9vUnVIhobvcbgY6O2VtTJTnbKkUDM0Z/zgBkdj31J3ypq4xTUVZDLTSQJjypEKMM+4Ost+IXZcTnctRJ+VkKuHL4cEre+wVV6odI50qtxRZlKAqgbZJjG7v3wf5HVx8M7871QtdXPK0MeBTR/eWMqpDBm/rHOfbVK6uwtjjcKC6zLtPqM57aQ6WhqluUE8MsqfDq0gCrkLhCcZHHbPf6+ut/KxBlQviPUf69VzByS1rXdj/fRaZFXJSXapqBGHJlY4zg5ydUG60LxXKZMkp8z7g2Mg9h9fT8OffU9TTF1ySd55J99EsUEjAyoshU5wfXvwfpzqUUMULiSNyB6JZuTIHV0sn6pv0vTPSxV3nn7ARhk24UNIWGMrgc4z29tWMRwVVmnLBWKg/KRnP5agkqWCQwlyYqddka54UZzxpRasbtik7W4IHrpXOxjkNqPat/oroXuM4c7lyTmPoqxXbpKsr5KLyaiBSweFinb6dv5ao9d0e8ZWWknEiE7hHL8uR7ZGtUoZvhvDq7M7HG0px7njVTgmFTbjkgtGONY3hc05LnOcS0Or4WFr+KO0OGjbZUG4WuuNQI6mnEJZQM4wgAHfI4OpSjpJRNDAs4XAKAE7CCQBnPcc/n2+urDXUs90sPlwwSTiGZWdI1zleckgd8aY2i3RmL4+sZ6eFXPydpmbHAUe3ue2Cfpr0sdzNcHEbEg9/okOLVOrf0UZ1NV0dL1ZevjYZMoEp1ZHxJlVCnaT2BwTn2P11xS3yno7VRyWZp4VXMc8M0olCnuCDgEDBPHPY40tfqWGsrKq9V0wLyzmd0kb5AWJ9e5A9vXURTw1dzpZIKf4OppNwZDHEIzC/oCcZGRnuSDjTbP+gE17qXEoMpIvdWeg61SWE/ExOGU4MkQ3A/XHfT2O5U9W6yQVCSKe+08/mNZ/Pbaygcs0MkRxg7gf5EaeWKlqamvSc7o44znzFPc+2dUnhkWNim7cOav6zu0c0cSjeync3GQvqBn1Ofz1NWKcp0VcpaaVWnjixhGwUXOG5x3APbVdhhWtZ4VnVMqCVPd+QQB9fX8tKzypS9Mz09HM0SJIPiN3JmJPAyPbGcev5a81nRNlnDB3b/f0WlFkhsenyK+gfB87vCmzH3Ex/wDOfRrjwZO7wisZ91l/3z6NeqWC7mVTf2gyBcuj2K7gs85IDbTjCdj76iPFqxdTXWlvN1udpE1DDHHDbmjqQ/w6bwWfygMl3GAT6DjVm8c+mL91DJ09LZLXLcDSPOZVjK/KGVQPvEex1VI6/wAc4ymaKvKhj8uynxtxwPy1E87U9i3Sn3UVt6gv/X3T1PSZs1fPYXRnBMix/fyu8AAFhjn0zpj1Fc6T/EDVWlbabVcLVWQQ1dMUIy+/mQE/e3Y7+4x2xpE1fj0QNsFwGPeOn51GX60eNXU9qa23egraqkdlcxkQLkqcg5GD31ZpAOpJHVpqipmx3ayw2nwujroJaiq8xhHJHWCNac+cOXXByOx7jtruoW4XXpHqWmsdSvxv+FUso2VaQnywOW3FhxkjWeWfoPqii6sW3zdOVE1dDCKh6YPGCYySobJOO4P6aXuHhJ1vUV8s8XSlVHE7blXfESP7WoNd+IW1tV359lJuoj3gtPuXUdmF06/q5Kr4ukWC3o5o6oRvIw4fY47kHvjvjGqt4mXJZuobckDxzW2KgjWhqFlMrzRd8ux53A5BB/v1VV8IevdmB0zU4HbLx8f2tKR+FXX8aYHS9Tu998fP9rSuRG47RqDw87Uou+rFWW9qd5AucOpPOCNP7JUQ2+1z0VPI7zVcaRMyMfLRMhmGCBliVH0AzzzwtL4WeIMrAt01VcDH34//AHakLd4d9bUcbCTpGudm7FZIuP7WuOfLGwhrbUIBIz3SNvsmTSGkZXk+4fXTS4XBRKGiPfg6n5Og+uJqQwSdJV7AnIPmRcf2tM6jwy60dx5PSlwCnlg8kX8sNqePLKRUzd0wG72oSOuYgtgkepGu6e4BJVkUjIII1M1Xh11y1MkNP0nWx/1mZ4yT+jabU/hd13Efn6YrSD7PH/7tMMdxWnWK/ZWscQbUve6ySDpGKFHQRVj7pM9yRzxqnQVxp3aPPB1cLj0R15X26hpP8EaxfhQQXMseWz/+2mR8MOrmpSp6QuC1GeHWWPH6btIeGwezQGN43JJ9dvRXZMplfzvZcWyXFoqpVfaNuM5xye2mAiMgKBMn3HpqXi8PuvoaX4ZOmK0xFtxBeMZP+tp0vQXWUQjaHpS5rIPv5liKn+1rgxngPLXUXGx+lqh4DgAOiod+Eo8qhUqJJsupbBxt/H8dMrPHc7ZHVRS08sPmbc7RiOUAkg+xII7j3I1frj4X9U3kbK7pK6LtO6OWGWEOh9eC2CDpWm6D6/p6NaVuma+ohhBSHzpYyyqTk/xe+nGSSCAMePe69lRbw3VW/ZVlKovGuSRxrlZBuA4AHoNP6Xozqq6T1sdB0/VSvRTeRUKjJ9nIADt7+xHb3163QXW4LqelLoM/KCIuBqEQdw6dzV7Ca3TO3Tq94gK7cbskOSAQByP01KdWtT09uelJCyJKrxrHkjawySx/kNIUnQHW6zxqekrk+GHePaP1zx+Opat6B66q6V4n6YuJaWQO7F4jnA4H3tITYz35LJANh+6bZMAKW4eCv/2esX+hL/vX0ae+FtprbH4a2m3XCmelqoVk3xPjK5kYgHHHYjRrXSxVu0YHto14SAOTjQuL3A9tGvNwzjPOk3lIJCrnnHOhCxfpe133rbxhl61qo/g7Za5Hp6YY5nC7k2r7gbiSfc4H02YR7m3M2V9Ma9jj2YyBkdgNKgc5PfQhchRjkAAdhrvjUF1jdIrP0zUVktyltoQqBNFEsj5LABQrcEntzqvUPXUdf4eVVyq7jHbqyHzUJiaOWVdjlQQpO1icD6c8catbE5zdQ5XSqdK1rtJ+Kv2BowNRM3Utno6USz3OlIyq/LKrEkkAAAH3Ok7P1VbL9VVEFBI8nkRpLv24V1ZmUFT68oRqOh1XSlrbdWprjSLOS2FwAeM9+dVLpm/3a6dX9S2qukp3itkkSReTGU4YFsnJJPoPy02g6ten8SKm2VM9R8BITTwviMwiZYw7gkfOCBnvkd9T4LrI7C1HitoHuaV2SILgkZbv+GlQoHJxnVeo+srVUXuttxqIYhTRxypM06bJ0cHlTn0IIIPOm8XXFovNsuf7vrhTVFMrKhqAIiSUJSRQ33lPcH11HhP7LvEb3Vp417xqE6Zr5p+jLVXXGqWWaelikkmKhAzMB6ficajL31JVUllJeSCiuNPPTNUwLKJPLgeoCbiSBwyg8+muCMl2kILwBZVuwNecar9f1xYrdc6OhlrFd6pgoki+eOInhd7jhckEDPfTTqPrK2U9NJQ0N0zc3CGFKQJK7ZbsNx2dlOSSMDn210RPNbc0GRovdWzjSNR80bIvGRyR3A99RfT3UKdSWGG408EkAlZkaOQgsjKxVhxweQedSiJtPPLen01AtLTRUwQ4WFjXhnab34f+IVZ0lcYhUW64q9VT1aggSFR3/HHBU+w1tIX1P5fTQEGQSMkeuutcXUaMD20aNCEaNGjQhBOBnTZH3HzG7n7o9hpr1FdWs1kmrVjSQqUT7R9iLuYLudsHCjOSfYHVNPiEJOm5rhFBC89PKYiSXWnYK+0ursBn/QzuJBAzxkQr6WLSFc89wRrqLEg3EDepKk6o8viJDC8kkNrqKhoVJlAcIq/ZtMMFsZ3RpuH+kAcHOG9T4oJbkroWtTLVUoy8bVMZJdgxUKByw4BYgfKD9NCFowGNGqHV+KEFC80VTaZ1npiUmjWaMnfzgJz868csOFyM6lLZ1mLheIrW9tqIKp2kByysgEZZZG3DuAwUe/2i/XQhTl0tNDeqCSiuNLFVU0n3o5FyD9fx+uqPX+C/R0tY1UKSoiLsMQxTFYxxjgYyB+erC/UNavVE1tWkjaGJowW37X2v/EAfvAHvj01U5vFoQXitpay3KkFDLPuaOTc7xxNIpKg4Gfs84Gc52jnTAdLByNX5pVpiyL2ujW47LpfA/o5T92uOOT/lH/LVi6X6LtHR3xstpSZRUspdZJN4UL2APfHJ751AU/itbo5ZTX0M0FN5mPPSaOQInlpIXdVO4ALIMnBH11O3nqlbN03QV0lHNmvdAYnIV4tykjdjPsAfx1GTJkc2nuNJiHFa54bE3dP7R0nR2e9V91p6qsknuJDVAlkDK5H3TjAxgcDTQ+HXTp6qqOoDTSGtqFYP9odmWXazAehIJ/XTSPreqelpZo7YjLUD5FE5LA+csQGNn+cDxpc9cKXoVSkVjVvFH/TgbGd3THbnHlkn8dVDINkh3PZMnw+Sq08vhzUL/iL6O8vYI64c5z8Rz+HbSY8C+l33fE1FyqDnCFpxlF9F7dhqx9cdXno+zwVq0gq2nnEARpNgGQTknB9tVy3eLZn+NNXaMCjmjhdqWpEy/Nuwc45Hynkav9tmB06yuN8Hc7HOUIxoHXbuBy58yrP1D0/WSdIRW3p+dKSqozC9KZeU+zIIVvocahbd0bdrxT3OfreelqJK2mWlENENixxq2/72Mlt2D9MfXXTeLNkNSnlpK1LsYyykbWRh2XbjnPPOeMalenOt7b1QksVPFPHUQwCWeN14Qn+Hd2J7fkfxxBsrmjSPr1+qUdE0mz/Cqw8EemPkC1FxjjY5kiE42ye2ePQ868j8DelPPlBeuZCAVXzgNvvzjnnSs3iTPQW03Gst0cqsIpI44nZcK7MMEkHkBc/8O+lU8W7ItOkkdNWS1M0YfyUVSE+bBy+cd8/jj66ZlnyYnaHONqiKLHlbqa0Urj05ZKGwWGmt1vRkggBVd53N3JJJ9TknUsBjWeN4s2iCnVaSirKqQE7lOyPHBPcsfp/rfQ4mb91p+6rFaq6loRVz3eVYqWGSoWBSWRpBucghflU+/PH10kSSbKbAAFBWrRrN7X4q1VfLNHP0+KZomZMx1RnU7QhJLBAAPnUfU51Z7j1lbrNFaXuIkhF1kMcJUbwp2F/mxz2HoDz+uuLqsOjVDXxdsUtDVVlPTVk9PSRvNMymIMiK7oW2M4YglGxgc68fxesqF2/d9zMCeYxmEce3ZHKsTtjfnAd1HbPPbQhX3RqM6fv1N1JaI7lRxyrTyM6qZAASVdkPAJ9VOjQhSTKGUqwyDwQdN/gKfy2jaNWiP8BUbf00aNCFxDbKWnkmaGBQ88nmyM3zZbaFzz9ABr1LXRpWyVgp0NRKixvIRklRnA/tH9dGjQhLmCJm3GNCeRkqPXv+uk1oKZa81oiHxHl+Vv8A83O7GO3fn68e2jRoQlTGhkDlQXAwGxyPz01NntxZ3FDTLI8nms4hXJf+tnHf699GjQhNqjpiz1VJNTyUMISdQkhjQRs67g20lQDgkcj108noaerwJ6eORAd2HUNzjGefx0aNC6DXJexUFLAoWGmijAO7CIBznOePrzrg2qgPeip++7+iXvnOe3vo0a5SNR52u6y30lxg8mtpYaqLO7ZMgdc++DpCnsVqpY3jp7ZRwxyYLIkCgNjtkY57nRo11d1uDdF7dl7+47VtK/u2j2kg48hMZGMenpgfoNLU1toqMk01JBASu0mONV4yTjgdskn89GjQopnT9M2enWRUt1PtlYMymMEEgkjg+xJP56V/cttB+S30oPOW8lc88H09tGjXS4uNk2uBoaKAXa2e2oMLQUo7doV9CSPT3J/U64uthtV8tf7uulupq2jyCIZowyAjsQPTGjRri6mVB0X09aqU0tvtUNHTkljFBlEJPclQcHUu1HTsYSYIyac5iJQfZ8Y+X24OOPTRo0ITKXpuyTvvms9vkYEnc1MhPJJPce5J/PS5s9tZSpt9KQwYEGFeQzBj6erAE/UZ0aNCE4p6eGlhENPEkMYJISNQoGTk8D6nOjRo0IX/2Q==</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Samsung Galaxy Tab S9 Ultra 12GB+512GB</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Infiniton Réfrigérateur Américain SBS-668 559L</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAIDAQEBAAAAAAAAAAAAAAMGBAUHAgEI/8QATRAAAQMDAQUDBQsGCwkAAAAAAQACAwQFEQYHEiExshNRYSZBc3SxFBYiMjZkcXKBkdEVUlVjkpQIFyMkN0NGgoOiwTVFhJOhs8Lh8P/EABkBAQEBAQEBAAAAAAAAAAAAAAABAgMFBP/EACQRAQACAwACAQMFAAAAAAAAAAABAgMRMRNBEhVRoRQhkbHS/9oADAMBAAIRAxEAPwD9BXO+WyzOphca2GlNVJ2MPaOx2j8E7o8cArU2zaLpC818FFQahoZ6io4QxiTBkPc3PM+AVd2tWq4XOo0oaGinqhT3XtZuyjLuzZ2TxvOxyGSOKq503eBsF0XR/kmr/Klvr6SYw9ie1g3ZnFziObcNPHwQdOqde6WpLy60zX2jFe2RsToA/ec154BpxnB8CvFVtC0lRWuG41F/oY6WokfDE8yZ7R7ThwaOZweeBwVO2VaW1BQWyerqrrX2wS3WpqJqGSkiHbAyn4Rc5u/8IY45+hVPZVpm9UO0KyTXS0VsFPSUNfh88DmtjkfVOI4kYBLTnxBQdYpdpejq2JslPqGika4yhuHHJMbA+QYxn4LSCfpXu37RtI3WuFHQ3+jnqDn4DXHIwC454cMAE8e5ci0lpq+0+2Slr5rRXRUbNQ3ed074XBgjfAwMfnucQQD51YX6Wvdxtu1ihgpZoJrtUH3E6VpY2cdkB8EngQcbueXFBf7btB0leKmSnt+obfVTRxulLI5gSWN+M4d4GDkjK82vaJpG818NFb9QUNRUz57KNsmDJ9XPxvsXMq6kuWphoykt+lrtbJLDTyuq5amkMLYgKcs7JhPx9535vgVJPpu8fxG6EpW2qrNzt1wo5XRCE9rAGyO3nEc2gA8UHbkQIgIiICIiAiIgIiICIiAq3rzVbtGaWku7KQVhZKyPsjJuZ3jjOcFWRc625DOzGo9Zg611w1i2Stbc2zbep0qbP4QlTJkjTcTWjm51YQB/kR/8ISpjwTpqIhw4EVhIP27i40wB8XZlwYQ7eBdwB83E/wD3nXx+GwtjB3zkuJA4DwC9v9Jg3rX9vn3kfrTQuqXax0tDeH0gozJI9nZB+/jddjngIq/sR/owpPTzdZReJlrFclqxyJfRXkbdDREXJoREQEREBEUNVV09FF2tVPFBGTjekeGjPdkoJkWtdqOyt53ehH/EM/FfPfLY/wBMUH7wz8UGzRav3zWL9M0H7wz8V7h1BZ6mZsMF0o5ZHnDWMnaST4DKDYosOovFtpXNbUXClhLhkCSZrcj7SoffFZf0vQfvLPxQbJFrffFZf0xQfvLPxXoX+0H/AHpRfvDPxQbBFgfl20nlc6M/47PxWVT1UFU0up5o5mg4JY4OAP2IJUREBVnaBbZbrpOWlgtzrhI6RhETS0HgfjfCIHBWZCAeaxekXrNZ9umLJOO8Xj04KNC3XcA95b844n+Q4nv+Ovr9DXQnLNEvHm5wn7vhrvGB3L7gdy876Zi+8/y9f61m+35t/pWtC2+W2aYgppbYbY9r3kwFwOMnnwJHHmisgAHmRejjpGOsUj08jJknJebz7fURFtzEREBERAVI2sDOjohz/nbPY5XdUrapg6SiHzpnsckDixjHcFG5gxyCyyxRli0yxizB5BYV1u1RYbVU3GkbGZ4WENEjct+ENw8seZxWzcxaHWDfJOu+oOoKo+aa3n6VoC8lxEeATx8wWc5g7gsbTLcaUoPRj2BRxX2gqbs+3RyONSwuBbuEDhz4rQncwZ5D7lE5g7h9yzHNUD2qohEhaN0NZgd7B+C7fsPAGlrhgAfzzzejauIlvFdv2IDyVr/XD/22rFlh0tERYbEREBERAREQEREBERAREQFStqfHS8HrTelyuqpe1HjpmD1pvS5ByJzVGW8FkuaoyxbRjubxWg1i3yTrvqt6grG5vFaDWLfJOu+q3qCD5pxvkpQeiHsCqtqMbtay7rAJGz1G87vBAwPswfvVv063yVt/oh7Aqva7bUx62lqH0krIy+f+UMZAweXHkcrTK2Y4BROasktULwqjHc3iu2bExjS1f64ehq4q5dr2KfJau9cPQ1YssddIREWGxERAREQEREBERAREQEREBUzacM6bg9Zb0uVzVO2mDOnIPWW9LkHKHN4rwQpyFG4ZWkY7gq/rQbukK8nzMb1BWN44qva5HkXcfqDqCok02M6Wt/om+wLOcwdyxNMt8lLd6FvsCz3DgqkcYr2HuKx3t4edeo9kfvgq6mujvksL5WGo7N0eWgk/F5qGLRzNKRHcuEtZ7qJz2jcbm7w4cTzypEkw8O4Fdq2K/JWu9cPQ1cWeF2vYsPJKsPzx3Q1LEOioiLDQo6ioipKaWonkbFDEwve9xwGtAySfsCkWJdaAXS0VdA6QxtqoXwl4GS0OaW5/6oPD7zb2TU8PupjpKhgkjY3Li5pOA7A5DjzPBYvvssfud04uMRhDxGHjJa9xzgMOPhn4J+LnkVpotL3SG4Ute19F28NJFRyguk3ZGRkkEAAFp+E7znn4LXR6bvdLbrTSwTsJscjTQP7ElzGiN0W68HAeNx+MjdPAHvQXyjrKa4UcVXSTx1FPM0PjkjcHNcD5wQi1ulLSLHpmjt43yYWu3i/m5xcXOPIcySceKINwiIgIiICIiAqdtL+TsHrLelyuKp20s+TsA+ct6XIOXEKMhSlRuW0Ruaq3rr5E3H6g6grK7kq1rv5E3H6jesIMnTQ8lLb6BvsCznDgsLTXyVtvoG+wLOdyVSOLFZa6GkpGOmqGRucd0AyBpwB9PJaLUdTHUVr2wuD445HBpacjjg8FhSLGeromWO9dq2LjGkav1x3Q1cVeu17GPkhVeuO6GqW4kOhoiLm2IiIGQF8yFT9W6lktlnFTT2+a61M0jm01viOHVDWHMjuYz8EOI5+bgfNW9Na4qb7qQ22jtdPRMAibHcKeR0lLLK6MSui8284MzkAZGCcjCDqqKCjqPdVKybd3S7m380jgR9hBRBOiIgIiICIiAqhtIbvafp+8VA6XK3qp7RP9gQ+sDpckDlhYQV4LCst2FGcYW0YrmFVrXbCNEXH6jetqtjsKta5AOjq8HlhnW1Ue9NsPvUtvoG+wLNewqPTwA0vbh+ob7Ast+AqzHGA9hWO9hWe/CxpMKowHsOV2rY03d0hVeuO6Wrjj8Ls+x/5I1B76t3S1ZtxY6vyIi5tiIiDlW0fSdReKOnlttoZX3u2b/uZs7iInsflrTwI3nN3845DBJ8wOg0XszNl1HTyXOxe5LZbXNqqSaaTfqZpnRhr4iGO3SO0y5vDPLjgYXcJaeKdm5LG17fHzKKG3UlO/fjhbv8t4kucPtPFAt8UkNE1soxI4ue4dxcS4j7yiyUQEREBERAREQFUdoxxp+D1gdLlblTtpbt3TtOfnLelyQS5qX8VGXKN0nFRuk4LaJXPVa1y/Gjq7+51tW9dLxVa1zJnR9d/c62qpLaaff5MW70DfYFlPetbYJMaXt3oG+wLJfLlVPT696x3vR8ix3yKoPdxXa9jxzoyb1t/S1cNdJxXcNjRzoqc/PH9LVm3FjroCIi5tiIvEz3Mhe9oyWtJA7+CCOSoLXFsUbpXDnjgB9JK8MrSHtZPC6AuOGkkFpPdkef6Vpbj2jaWL3FIZqjfG+wzmPIOCcebPLn3qO3TPuck7a2OSiy7djjMu8XN4OJOOHcpv99M/KN6WhFBQyPmoIJJPjvja4/ThFWk6IiAiIgIiICpO1J27pqnPzpvS5XZUTay7d0vTett6XKx0crdKvBlWMZD3rwZCtIyHSqt63kzpGtGfzOoLbukPeq7rSQnStYPq9QVSW3sUmNM24Z/qG+wLKfKtXZHkact4/UN9gWQ+QrTKR8qgfL4qN8hWO+RBK6Vd22KO3tDzn57J0sX5+Lzld+2HHOg5z8+k6WLNuLHXR0RFzbEREFN1hadQ1VE2nsvYmnOe0aHBkp8A48MfcVi6PsOo6OJ8F0bDFR4w1rnB8w8GkcgR3k+CviLn44+XzcPDHk8m53+HxrQxoaBgDkO5F9RdHcREQEREBERAVB2vnGlKX1tvQ5X5c92yu3dJUp+eN6HKx0lx0ycF4MigMijdJ4rppnaZ0ir2sn+S9UO/d6gtw6TxWg1e7OmqkeLeoJKNrZ3+T1B6FvsCnc9YFof5P0HoW+wKZ0niiPT3qB7uC8veoXP4Kj2Xcea/QWws50BP69L0sX53Ll+hthH9H8/r0vSxS3FjrpaIi5NiIiAiIgIiICIiAiIgIiIC5xtsdu6OpD89b0OXR1zPbs9sWhqaV7gxjK1m85xwBlrhxPm4qx1J44iZfFeDL4rCbWwP+LPG76Hgr12zD/WM/aC6ubIMnitHqt+dOzjxb1BbIyN/Pb961WpG9tYZmsIc4luADkniFJWGwtMmLBQj9UFK9/isK1yN/IlGzeG8yPdcM8Qe5SvkaDxe37wrED096ic9eHSs/PZ+0FGZo/PIz9oKiXeX6L2DHOzyX16XpYvzWamEc5ox9Lwv0psFBOzcyAZZLWSvY7zOGGjIPnGQePgs241DpiIi5NCIiAiIgIiICIiAiIgIiICx66hprlRyUtZAyeCQYdHI0OafsKyEQUODYpoGDOLC1xJyS6eTj/mWS3ZDoNvLTdKfrOefa5XNE2Kg3ZRoZvLTNCfpaT/qvQ2WaHH9mLd/ylbUTYqI2VaGbMZRpi3h5GCez/8Aa+nZZod3PTFuP+EraiCoHZRoUjHvXt32R4/1Xg7I9Bn+zFD9zvxVyRBR5djOz6bG/pik4ceDnj/yV0ggipoWxQxtjjYMNaxoaAPABSIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiD//Z</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Samsung 50 45k UHD CRISTAL</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Samsung Galaxy Tab S9 Ultra 12GB+512GB + Samsung 75" 4K UHD Crystal Smart TV 75U8000F</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Tab S10 Ultra 14.6" 12GB+256GB</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAQCAwUGBwgB/8QAURAAAQMCAgQIBwsIBwkAAAAAAQACAwQFBhEHITHREhdBVmGSk7ITIjJRVHF0FBY2RlOBgpGxweEVJCZDRXJ1gyczN0RSVaElNEJiZZTC0vD/xAAZAQEAAwEBAAAAAAAAAAAAAAAAAgMEAQX/xAAlEQEBAAMAAQQCAgMBAAAAAAAAAQIDERIEEzFRIUEUMiJCoWH/2gAMAwEAAhEDEQA/APSKIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICxl1xFbLK9rK2qEb3DMMALnZefIciya47jwl+NqprvGAa3IH9xu8rsnXK34Y+w+QCKqTI6/6l25Pf7YPSpOxduXKoaWaoYXRNBa05HWByZq4bdVNdwfBjPPLyh/9yqXjDrqPv8ArB6VJ2Ltye/7D/pUnYu3Lk0sb4X8GQcE5Z+dWi5PGHXXff8A4f8ASpOxduXzjAw96VJ2Lty5CXBUlyeMOuwcYOHvS5OxfuTjCw76XJ2Lty4+wOkkaxoBc8hoHSVnveZc/lKYfSO5d8I510HjCw76XJ2L9ycYmHPS5OxfuXPTgy5/KU3WO5UnBVz+Upuu7cngddD4xMOemSdi/cvnGNhv0yTsH7lzv3k3T5Wm653L4cEXT5Wm6x3J4HXReMbDXpsnYv3L5xkYa9Nk7B+5c5OBrr8rTdd25UnAt1P62l6ztyeB10V+kzDTTkKqZ3SIHblSNJ2Gi4A1U46TA5c6OBLqf1tL13blScB3X5Wl67tyeB10d+k7DLTqq5neqB25VcZ2F8v9+k7B+5ccFkr5LxPbI4myVUIc5zQ8AZNGZOZy5FgKu9W+hu1FbJ3z+6q0NLSxgLI+G4tZwjnmcyOQalzxjvXoLjOwt6dJ2D9yn2bGthv9V7moK9r5yOEI3scxzh0ZjWvNlwvVutdZRUdW+cT1mtvg2BzYwX8AF2vM5uB1DPVr6FsWEeFBjy0NHiuFWxpy/eyP3p4w69HoiKDomaHYvMWNbriDF+lbEFt98FdbqG0vEMUNK8tHmzyBGZJzJJUscbleQenVxvHZPv5q9vkt7jVzU4Xu/PK99u7/ANlYkwdcpHcJ+K7s93ndISfrzWnH0uz6QuUbnwj0r4XHpWkOwfcB8aLp1zvVt2E7iPjPdOud6tnpN1/SPni3kn1qknoK0N2F7iPjNdD/ADDvVt2G7kPjJc+ud67/AAt31/1z3MW/Fx8ypLlz52H7kPjHc+0O9WnWS5j4x3LtDvXf4W/6/wCnuYuicLlV83SuA1VlT2rt65dJaLqGng4iuPCy1ZyHLP61j/yfifhDhXmYDzipkKhl6Tdj/qTZj9uvm6V/ptT2rt6pN1r/AE2p7V29cqdbrqNmILh2h3qxJR3lgJF7uDh0Su3pfS7p+j3cft1o3a4em1Pau3qg3a4D+/VXau3rjrn3Uavy5cO1dvVp091H7brz/NdvUfY2fSXlHZTd7h6dVdq7eqDd7gP79Vds7euNGquo/bVf2rt6turbqP2zXds7euezs+jyjs5vFx9Pqu2dvVBvFy9Pqu2dvXGDXXbPVeK4/wA129Z62YYxhdGh4r62miOsPnmc3P1Dak07L8Q8o318r3vc9znOe45lxOZPzqglplimMcTpoM/BSujaXx57eC4jMfMsRT6ObsW/nOK63M7RHwvvcodNDXWHGctjqLjLcIH0oqGPm8ppz2fb/oo56s8J3KEyl+GwkML4ZHRRPfAS6J742udETytJGbfmWXwgf06svtUfeCwvCWXwef07svtUfeCqSj0siIqkg7F5gDeFppxz7SPtXp87F5jhGemrHftI7ynrvMpUsJ28ZrgL4WKRwVSWr1New2a0Z0asvjU0tVpzF6GGXWDOcY98SjviWRexR3s2rVjVXWOfEo741kZGKM9isGPfGrDos1Pe1WnRpxyoJhzOxfRTZ8inNiz5FIip8+Rc4jWCq7IysYS3xJeR2W31rVaunlpKh8MzCx7doP2rqkFFwstSg4mwsblanzQR51VO0uZlte3aW7ulZ9uEs7Pl3DZy8rlz1XR0FRcqyOkpYjLNIcg0fafMFQ7X8663gfDDbRbhPMz88qAHPJ2sHI3f0+pYpO1pt5FGGsD0dmYyaZramtyzMjhqZ+6OT17VtsdJnyKZBTZ5alkIaPUNSZbJj8I8tYttJq2LmOJmeC0vgZfswfaV21tFq2LjeOY/BaaQ0DL/AGU37SsXqNnljxbrnKqzWXwef06snL+dx94LC5rM4N+Hdk9rj7wWOro9NIiKlIOxeZKXXprx57SO8V6bOxeZKQf01489pHeK7Fmr+8bIQqS1XSFQQteutOyLTgrbgr7grTl6mqvM3RHkao727VKfyqw8bVvxYkN4UaQKZIFGkVsERwVIbrV1w1r40a10VRx5rI01PmRqUaFuZCzFFGCQoZZcRqVSUeeWpZunoNQICooYRq1LPU0A4I1Lz9m2xyYdcJrMJNpdLUtD4MCkaRWtbycA6wOtq+ZdNpYc8lexLbGR4np7gAOG+k8CT6pCfvV+jjzyVXl/j1qxnU2lp9mpZWGnyAVqkj1BZFjcgsGefavmPFLYWgLhWklobpwaB/lDO8V3kLg2kv8Atxb/AAhneKz5VKIeazWDfh3ZPa4+8FgwVm8G/Duye1x94JXY9OIiKlIOxeZaIZ6a8e+0jvFemjsXme2t4WmzH3RUjvFFur+8bNkqSFILFQ5i16o07EZwVp21SXjJWXjWvU0x5e6oz9hVh+0qRJsKjSL0MYxI8m1RZFJkOsqLIVbBYdtRu1UuK+NdrXXU+ny1LN0WWpYCB+RWZo5NYVOwk62mg2BbBS7AtYoJdQ1rYKWXxQvJ3NGGvrCYqq4zfqWjz8dtMZSOgv4P3L7Q8i51eMVsqtNc7WyA0zGC3tOeoubrJ6+YW/0Uo1JZfCJ4zmTZabyVMGxY2klBAWQa4ELzr8tFn4VhcG0mf24N/hDO8V3jNcG0l69N7f4QzvFRyVxBCzeDPh3ZPbI+8FhAs3g0gY7sntkfeCV2PTqIipSDsXmuzDhabdIHtI7xXpQ7F5ssZ/pu0g+0jvFTwnleJ4Xxy628sVpzVIcrL16WvUbN0RnhR5FIkOSiSv1r0teHHmZ5+VWJDrUSQq9K/pUSR+papEFqQqJI5X3lR3AlS6nIsOKpBOauFhK+tiJOxRuUiXFcLjmFlqNxzCx0UJWTpmZELPs2Rbhh1n6KQgBWsW4sZhjDktQxw92Sgx0zDyvI8r1N2/UOVYu43+isFF4erk8YjxIm+XIegffsXI8QX2rxBc3VlW7LVwY4wfFjb5h955SsNx8r1oyswn/rEmWRs3hg93hA7hcPPXnnnn6812/B+I475aI5+EBUR+JMzzO8/qO1cOcptjvtXYLk2rpTnySRk+K9vmO/kUqol49L0lUNWZWWhqAQNa53hzFNFfKUTUsvjtHjxOPjsPSPv2LZ6eu2a1i2ar8teGUrZRKCuF6SDnptb/CWd4rrsdaMtq45j6Twumdrv+lM+0rLlLEs5OdWQs3gz4d2T2uPvBYQLN4N+Hdk9rj7wSqI9OoiKlIOxeZLXUsptNuPy/PxqoZZDP8A4ivTZ2LzDb4vC6bcfdFUO8VdovNkqOX5jbn3OEDU159TVBqL9BFqcyZvSWHJS/curYrUlHm3It1L2MdvPhmuEvyxkmIKZ3+PqqLJeoHbOF9SuV1ka7N0I8G/zchWAlifC8skaWuG0FX47cnZqwZJ91iP+L6laNxiO0u+pY4qunppqudsMEZkkdsAV02WueEnwmGvgz1l3VV+n4VX/UQTSDzhmr69iztqwnBTNElUBUTbcj5DfUOX51nfc2TcgMgORUZ+oxn4i7HTlWoC11JGZj4PrIX33DIzymj61s8lP0KDPCQqfemSd1ZRhXZwtzETnnzAgfasZXXG+FhZQ0kFP/zvlD3fMNn2rPTMUCZuWatkxqu5ZT8NDrLHeKqd01Q5s0rtr3y5lQZMPXAbWR9cLfpWqDM3MJlEPloz7HWt2tZ11Hfaapu1rOstymYsfPH0LPlbE5I1uCG4UFQ2emlMEzNj2PyIW5WnSTdaRojuVJHVtH6yN3Af842H/RYKaNQpWKq5VKfj4dRpdJ9lc0eGNTAfM6PPL6iVp92vdJiDSgKyikdJELeIyS0t1gnPb61qcjVNwfSVFZjQQUsElRM6mflHG0ucdhOQCz7v6p+Vs43MBZvBvw6sntcfeCs+9m/f5Jcf+2fuWxYEwffJsY2+qnttTSU1JK2aSSeMsGTdeQz2knLYs1+HI9AIiKpI5F5qsLOHpv0hdFSO8V6VOxeYIb1bsM6dMdMvVWy3+6pw+J02Ya4Z8Lb0hwKnheXrl/LofgR5lS6BpCwvGBhHnFb+0O5fDpAwjzit/aHctM2IXBkZ6TMbFr13tYnjJaAJG+SfuU44+wifjFQdp+Cg1eNcJvaeDiCgPqk/Bate6fuq+WVq3Ac54YGkvJyDRtz8y6Hh6wNttIC8A1DxnI7/AMR0BafbsQYTGI/dc1+oGRMbwhnJtfs83zrbm6QsHNAAxHb+0/Bc9T6jk8ca16Ncv+WTPiENC+OYMlgjpEwfzkt/aHcqHaQsIEfCO39odywTJt7iy8rAoE8e1QZNIGETsxFQdodyiS47wo4asQUJ/mfgrcc0MvG/tdqI9qx0zNRVubGuGHeTfaI/T/BY+XF2HDnleqM/T/Bbde2fbLsxn6XZW5KHK1WpcVYfdsu9Kfp/gokmJrEdl1pT9Jafcws+WOyyq5WbVBmj1KqTENlOy50x+kosl9tB2XGnP0lTnlj9pzqxNHtUGaNSpbxa3bK+A/SUOS6W52ythPzrNcp9poksa3PQQMtOlv8AZZ+4VpslfQnZVRH51u2gUe6tOFLNTgyRQ0cxe5o1NHBy+0gKjdlLj+K7HrlERZEhERAWv3/AmF8U1Lai92Kir52N4Illj8fLzcIa8lsCINJ4m9HvNO3dQ7184m9HvNO39Q71u6INI4m9HvNO39Q704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHvNO39U704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHnNO39U704mtHnNO39U71u6INI4mtHnNO39U71ncP4Pw9hVkrbHaKS3eF8swxgF3rO0rNIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiIP/9k=</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Thomson Google TV 55" QLED Pro</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2× Triporteur (hors Jumia) + Samsung Tab S10 Ultra 14.6" 12GB+256GB</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 85" Crystal UHD 4K Smart TV 85U8075</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCADIAMgDASIAAhEBAxEB/8QAHAAAAgIDAQEAAAAAAAAAAAAAAAYFBwIDBAEI/8QATRAAAgEDAwIEAwUFAwUNCQAAAQIDBAURAAYhEjEHE0FRFCJhFSMycYEIJJGh0UKxwRYzUnKiFxg0U2J0goOSo7LS8DZDVISTlLTh8f/EABwBAAEFAQEBAAAAAAAAAAAAAAABAgMEBQYHCP/EADERAAEEAAQEBAQHAQEAAAAAAAEAAgMRBBIhMQUTQVEiYXGBMpGh8AYUscHR4fFCwv/aAAwDAQACEQMRAD8A+kdGjRoQjRo0aEI0aNGhCNGvGYKMnWCu5lx0/L/doQtmjRo0IRo0aNCEaNGsXfp4HLYzjQhZaNYRMzL8wxzrPQhGjRo0IRo0aNCEaNGjQhGjWLv08AZOM68jZmX5hj/HQhZ6NGjQhGjRo0IRo0aNCEaxZwg7E59BrGRz+FMZ1j5YLdTZOewPfQheANLhnwF+mtqrgYxge2vQvqf4e2tc9TBTKGnmjiUnGXYKM/roQtujXgYFerIxjOdCsrfhIP5HQhe6NYiRScBgSPrrUZPMcqrAr2+U5IP10IWckpXhRk/y1isfOX+Yn01hG8KTCHzIzPjPT1DI/TvreGUN09Q6u+M86EL0D1PfXusRIhXqDDHvnR1rgHqGD650IWWjWuaeKnUNNKkYPGXYAfz1sBBAIOQdCEaNGg8DQhcd1utDZLZNcLlUx0tJCAZJZDhVycDP6nSb/uz7Pe6vSRXJHiRQxqhzFkgnAPfPYdu5GpLxHkkXYN0lTp+5VHGVDcrIp5BGO2kHcO3NuWPfNV5Qgp4JaMT1QBMjZJdWxGOx6Sp9AMZOkJA3T2RukOVgsp3Hibs3oMjX2Bx3yFcj+7WFh8VNt3tKbNQ1JPVuscMUynqctjGCOO5xqnLzZJq26VFRSpRwU8Y6Y4EmyURRgA8ctxk+5J1hRXKe32qmoJkkhenvNBVjJK/J5gBUj25Rhqs3EW/KQuhxPA+XhPzEb7IALh2/xfTmjQNGrS5tGvC6rjJ5PbSzvKG8u1oNnq66APXRw1QpVRsQtnrc9SnGMDn6+ulaK5bqN7taVSX2FJK+o86WKkWSHyFqGESsAuQWXB6sgBRnk6EKzutc4zzrS1SDM0SOnWuMrn5hn1x7aqez3PxBqbbEsiXFbm1fCrirpcQiH7wtk9AwpwgJUtgEHOnPYS11bZvta9W6aivU7ypMs6YkWMSt5anHBwvTyO/fSpDfRM6R9OM8t7e2toGPz0cDXudIlRqhPGvblc2/KTctbaG3Nt2nojDUW+KbEtMT1ZmVPXuDnB7c44Or7zqud6eF0l93hT7qsm4Kqw3lIPhHligWZXjOR+E9jgkZ/L20ISJc7zZbT+ydWHbt3rrhSS/ukT1mFmiLyDqjIHbAz29DxxrZ4LU52t4s3zbRdglTaaOsRWJPzCNC2M/WRv4aZ5PA60P4b0ezVulelLT1nx00wRS08mCMEHgDB7D2Gp9tg0o8S4N8Q1dRFVU9J8G1MFHlyIARknvnkf8AZGhC+f8AY91awbqn3QWYRT1d3pJGLEjKwCaMfxB00eAtFJavEuqoWZ1km27T1TliSQ8nluTz6/Pp1qPAKz1WzZ7A13r1jmubXMThEDqzJ0FBxjpI00Wjw5t9n39V7ngqpmepoI7eaZlHlqiKigg984Qfx0IXz9BYaTam54KXfUdfRVct1+JpN12+bzVmP+g5OcLnk/2h6jHOrEvUh/31kS9R6Tt9zjPH4ZNdafs80aILZ/lPcTtsV3x4tXlJjzO3+c74xx27fXnTHvHwsXcm6qbclsv1ZYbtDTGkaaCNZFeI546W7HDEZ/L20IVNWWR/95pfX626hX98nP8AnYtcFzZ7Rtuh2u00rG3bioqynLMcmnqYesDPrhgw/M6vKHwes9P4SzbDirataSdxJLU4UyM/Wrk4xgfhAx7a5dx+CVn3FeLNcZLlXU01rggp8RBemcRHKlwR379tCEmb/oKLcf7Qk9tvtJVXW2UNgepiooCS3XzyigjLc+/OB7aevA2pt03hlTparhca+jgnlijevjVJFAIPThWYdIzxz6627z8ME3DumHcltvlwsV3FOaOSalVXEkRzwQex5PIPt7am9k7PoNibWhsVsad4YSztLNy8jtyScce3b20ITJ1ggkc49NasvKcArjg8c6wJbyzIAepD7d9dAAxwMA84xoQlvf0HmeHF/RRkihlbP1Ck/wCGqk8UYIjuG33akqEmNXRxu4Rg3QU6Rk49CGXvq97jRrcbXVUTsyLUxNEWUcr1AjI+vOqrrvBJZ9xUtY1+uVWZUK1c08nzsqlelQVHbHVwfXHtqKWPmNpaHDsc7AziYC+hHcJBm3dcphIMQRCQksEUjOVZT65/tE/njXLFRpLs691fWGqqY0zxpkZ6VmVmPP0XjV10/g/tOAANT1U+P+MqX/wxr20eE22LXcqyoNvSaOV+qKKX5ljGB2zz36u/vqvHh3NdmebpbmP49DLhzh8LFkDqs+nRPCMHQMOxGRo16oCqFUYAGANGrq5NUR+07VVFLQbbaCqmp+qacHy5CnV8qd8HXzx9sXMvj4+sJPb94f8Arq/v2qc/Ze2cDJ8+f/wrqkNlwmTfViMnQR8fT5U8gjzF9NNNDW1Xk+JcAutxR8vcqtOk4YGpfP8AfrVJfLmaktHdKsJnOPiXx/fr7X3heNu7MsE92udHTdCt0RxLCnXNIeyLkdz/ACAJ1AbD35Y993y4WyDbgopKGNZHaZImBy3TgADTr0pLlo1a+UKa9XSeTykr6pnY4B+Jf+utdTdrvRytG9zrOoHn96f+uvqjafiNbdxeIV421JtyjoEtYnLVZdCGEThSSOgdIOc9+Nc9m8S6bd++J7JtvaNPcKGBvvbnKyxxqnYvjoPc56RnLfT0ZfmkDB0K+YIr1cynUbnWn/5l/wCutbXi7A9bXSuVc8D4l/66e/Fhqen8VdyU60sYAnTpKjGPuk9O2ovxJ8PqnZKWhqiugq/tOBp0EUZToA6eDk8/i/lqGzmICNQoGnuFxqiBFdrhz3/eX5/nrNLrdI2Ia41eFcKeqd/66fpfDKo2nVbcWevp6r7dUNH0xFfKz0d8nn8fp7amLz4L00N7e1z70sdNdallaOllVkZs/hGM+uNQ5nlxb0TAXFxBVd1dfXSzwwRV1UhK5JFQ46v56hq+tu1JUFDda5c/hzUP/XT8nhndp/E2j2fVyw0VaI2lWfBkjZQpYMMYJBwRqbuPg3FfrpLaqDedjqLrThh8H8yv1L+IHvjH5aIuYKJSAuzabKp6S5XWZQpuld1E/wDxL/111XSW90iwTNW18cE6t5T/ABD4k6Thsc+h41qmtlTYbvU0FfF5VTSytFIhOelgcHnU7uh0bam2mIADJVc/9dp7Hu5nkgyfNKTXa7qOr7UriP8AnD/11it7uxcD7Trf/uH/AK63VkAhhU5DBhkY0z+DMdvm8XbKtwETJ1uYVl/AZwh8oH/pYx9catnROjkLwuWq254gUVq+1aqg3BBb+nrMz+aFVfc85A+p1APebpHhhdKxh65qH/rq0tl3LxLm8ZKeCuku0lRJV9NxhqOswCHPzhlPyBAucY+mNd+4rtZdobDhudisFkrzLfq+Gmnq6VZgsCuSAB6jAABOcDtpmp6qSrVSfb9dK3SK+tRMc4qHyf567Ke8V7HyzW1ZJHyk1D/11dsW0do0+5b7uN6Cio/JtNFXxUrUb1VPTvP1dcnkIQWUdI47DJOlTxJj23VbNtV8oDC1yepaL4mjtMtBT1MYHPytletTjkHkE+2mPBqrRRGtpHq4r9RWyluVRUXCKjrGZIJWnfplKnDAc+ms7lad426Oslq4rrTpQGP4lnmcCLzOU6vm46vTTLuOCpufgZsdqanlqCtdWRN5aFsOX+VTj1Ppp58TCBZPEhOOpJLQrD2PQuRqZjtACoy2tbVCfa90Hevrcf8AOH/rolut1iCk3Ktwe37w/wDXWC4I5GddflRTwCMoMg/w0t66FRh7rX1/4JzSVHg1t6WaR5JGhfLOxYn71/U6NHgmnl+DW30/0YpB/wB6+jQro2SB+1FIIrdttioYebOMH/VTVG7QjjO+tvMpwWuVPkY4H3i6+hf2hLO17Tb9GrqjE1DAsCfSMcAevOqQpbTQbV3XaJ6yWuK01XFOzCnwnSrgkjnJ4Gq754WuDCfF2UEg8Vqwtz3TcV+8Xlud+2Xf7hY7PO60FDTUzdDsrcSMSMMGI6vqAo7Zzq8FL1PSeJNzlW01lSbrL5UpjXPwgMpbqk9gO356slv2g/DtXIN3qQQe3wUv9NQm2N8+EO16+suNnrqqCauBeVpI5mDDq6jgMOOT6akIF2h48QNqrKHbV43d4tbvs9nrFpZJpawzFmIEkYmz5fHu3T/jqyfALdNDRQ1mx62kjt94pJpH/D0tU4PzBvd17f6oGOx1IWLcfhNZb/X7mtVRUivqvMNRJ0yvnrbqb5D25HtqLum6vBW97pTcc9VWx3aNkcVFPHPCepfwt8owT6Z9RpjXMvQobQNgqq/GhgfF7ca9j5y8/wDVJq2PFys2jRWza7bnsdbdX+BPktTVXk9A6U6gRnnPGqS8T71Tbg8SLzdrYXmoauVWjdkKlh5ag8Hkcg613beV53p8HT7gq1kFFEYoD5SoEQ4/0QM9h30wuygkJrn5QSrt8VZYTdvDV6ZGihdkMaM2SqlocAn1OONQPjDSVVV+0BbFp4JZjiiwEQtn7057aTrved4X77Lq6lnngsvStI/kqvlEdOM4HP4V76YKDxS8RrqJo1v6wumesikiBUf9nUJnjALnHTRNjka9xpWPdJEb9q60KrgstqbIB7fLJjW2xRbYn3Vuq8besbS7stM0/wBzNVtidjkFlHIXqOR24yPfXz+L/uSwbwbc63KR7p081UoEjN1jp5Dcfh7ccak9rbludu3FW7mS4vDcahpZGlES9MvVywx25PpjjGRqXmNyc3oldJTvdQdXLXbm3BXXKvQJWVVQ80ihekBieQB6Y7fppku+1ay6bQsQp1VvISp6gfrNrru247ZUVjVa0sr3CrPnNKI1CO55Iwvqc541LXO8xf5K25nnSnneKby4gMeYfOAIOe2Bz+ms3nvLnOaq5zkmh92qbrrVWUUjxzL+DjAOQNcKK8bq69SsDkEcEHTjTXS3qAlW8cjs56jn8I/P11pjrGse5oK+11EYqaWXrikwrgH3wcg99W24lxdThSnYHZfFus6rxM31dLR9jT7juE1LIPKMfUOuQHjpLAdTZ7YzzqJutXfKK1xbYuonpoLfK0qUc8XQ0TuMknIzyD66t/xB3xuE7O2dCayIJfaMGuaOnjVpG81RkMBlDj/RxqZqfDuy3nxIv1PcrNcb3KKtAKyS6MnlReUmesnkgHPPsQNWnOAFkqX3VHrvrc8N8prxDeaiG4UtOlLHNHhSIl7IQBhh+YOte4N4X3d9Sk99uk9fJEOmPzCAqD16VAAH8NXRcPB3as12rrrb4pWsVBBGkdObgsPxk7MckzSfgQDA9ye3146Pwm2pW7w24AogprjLPBWWtLqlU8ZWF3R0lTnpPTyD6499OokJaJG6qnb2+90bSp5aew3uooYZj1PGnSyE9s4YEA/Ua523Nep6C50Utxllhu0qT1gkIZp3U5VixGcg+x07nbuytwbI3BXWCiuVvrNvGNy9TUiYVcTOUJK4ARuCcD+eq9qKXyZlER6wy9Q/LQd6UTiW6L2miPUuex1IPA0XVUkoqd8Z1HxVYEPbscEa2wqa+sjh6mKk5xnjTo2h4pyqEvabugvsLwUbr8GtvMP7UTn/AL19Gs/BhQnhBYVHAEcg/wC9fRqT0Wq02LSh+0PXT2+isslMxSaXz4EYcEdZiHH6Z1Xa3CzrcUkr/LZammaMIV+XKA/MBjgknGn39pCemgpduvUqGzLMsf0cmMA/oM6om4JJFuWBm/zbKVX6HHbWPjImvk100Puqk41UStnqbdVIt1p2ipnBMcgAZTwSMMOCDjsDqUtFspa9akhS8YSRwWB+XgdPTj1J45412bfn+BoY7hWUbsJWdYQU6l444BznBOum5VJFL5lvpaimiZRH0EZUNnLHn39B6atOlo0dFSfO51tArVLsArKS7zZpTSPKvlFSchVPBOTqWqLJb7bRRS1EZq1Z2hkXJRkYYwR9MHIz/jop7NcbvE1O1PKXYGQSrw57evqNOO3fDepeoigrJXVGKymKZTyB/wCvpqnLjImdfFomPkNA37BVi1C8kxFO5WM9gx5xqVtm2WrGQ1VRFErgkO3JGPQ+ursuHhZQ1kMFdTBKOP5hKBHzkHvkeuuCt8OaH7NeRKmsE0JBzIFKkegxk41AzFGZuhy33TH4l8Z1bYSBa5JttCpjJMsrwnyS/wA5hJPDYB6c8HHc86zttRdaae4+S8EjHy5pnQ/P2YggEc98kfTViVOzjWUtKHiSkq41VA2AepOPlK9v7tRV02Pb4SUqWjLsch426GU+xBByB7ZGq8uLw7LZKMydhXyynO3T1VfXl5p7dUTzRxSrMVUcghFC8D3BAA98+ms6yW6y7LQRWyBKEoR5iwFS2MfMGPcHq5+un/8AyK22tKkU1dIHY9JBY4zj1PONQtDt+lpnkpNx3Gq8tpWQxJH1oqIMrKGB4QDjt/dqzgsczEsdGwfCL1G48ldfHRAvUnuqyjRly5R4pwVZHjJATA123W93i82+kpqyoWeKjDqjgAMetuo9R9edWZuHZ1if92tlunpTjBInLEkZHzAk+oPtpVqNm1UVPF5Ik4yOYyV/v0ox8TjrofMJzjy/iCR1pldenyyje/cHUpBRTTUyxUtBLUsoyfLAYDJxyRyOe356bbfRRwfJd5lqGIwihT5ignAPPZc8ZzqTtFDaIXVqWCKFZo2EjlywV+cdY6gCvBPI99PONZ/0DQ7K1Dg5ZBmaRR7pZv8AU7irotv2+42c0cdgjFMvBJb5usFxnj8J+nfVnWnxaq6W+3BK+y0brcneaqcdXTGyxgCLPqB0HP1YjUXHAGRqGWf93ibzahEk85GjQluocljgdXykYHOSO2u24bAoqy3SzW6As2DI0MvySqgAIYtySvHYZPPB9NaLaxMdxGvle2irzsmgcL1S5W+LtTcoSILNavJnPw9TaJIWkp6pTyr4zkODxkfTRRb5q7VfrfWwWC1W/wCxkkalo6WEpCnWpWQu/LsxyPXGdbDYLbU00F8tFNUxVSOj/Dwr5kfckkSH5vTgMM+mu/b1oFTdkguMMiGrkeTy5FLLErH5V7A4yxP6D31aijc12psLOfjhlyg66LLYe3Uqdq3+kol6heKaOOZJAQ4GSyuPTHUTxzwB76r6+bGv1tgmmlppHEUzQtg9RXp9ePwjjudfTO1tr0tgeOnoaqXqbLSF0z5nsM4wAPYagN07qtxiraOOgeImXy/OVxGSQMZIIOR9D31JIGk2NEj8RyIw6V399V80wwASGINnpXqb0JP6+mtXnlKyMxgjpGeOM6cp7HDPXmWImUoCclQv/wDdQNbaZIWM8DhGQ9yMgjvjVHDuLpSwnYWkjxcUovqV9Y+CuT4ObfJ7mJ8//VfRr3wWLHwdsBbHV5Umcdv86+jVtbrdgq//AGnaaWppdrxwgmQTzkYGf7KaR6DakKRC43GRjMYVpumMdaw5BHWzehxj8uT7au3xLt1JdNwbfp61OqIRVT4xkEgxdx6jXDDQU9JTeTSCHCNn5skA4x6643j3EzBKIW71+vmkI11SjdtlCqpaby5E6ooRHCUHQgz64HbsMY751EV+0II6DzZ6+oFUnDiTGVA9Ao1ZcNBCY0CvPGI2JC056EUn1xyfU+2oSphtlJUyQ1Esjv6Ozxuf1zrCilxDWC3rOmDHOsBLdmrKOmpSXhkmV3VSF9FHrxz3xpxguNMOirE8UZhAAQhgxUenUe/fOky/QWioUtHVU8cyZYYPLfTjUc17itE/k1QkqIFA6cTjDcDJ9++nNjfL4o7s9FCGOvLStNdwU1PMwrYWhppMOJjyjD8vy+mvXvNVVI72SmSvhZT0/Jhz+edVBdd7VktPELNTSU0bP0SZUM7HJwAScc4x27n6axtqXS7GskFW8SdRRkSocMuSCelWPzYyR0kcAE57a1oIJmNHOofr7q8zATSCs1Dy3Vg2++x7nmuVDdauj8sRBwIeWgcNgq7YGGB9Oex51HXS61EV1qbDfj1QOyinqo1ChGPbJHAHfg+2ue0WaOhnjVpIo43UY65AQw+Yr1Zw3Yrgkc5x31IdbUs37rLLWRCTqNNURhucYOfUDnHPOtjLDM4RublJqux/tUOI4OXDs50JzNA17jv6j9FD0tsuk9zU09TC8BfyTOZAFK56QGQ8+vf6607ltlzoKlGph8bHSiRYAyK7p3yMD8YPBz+WmCn2kt4pKla8Q2+CT5ovh5AGBzkKQeWGfr6a22VLjt40lFW1sUtskZ+oz/O1Pg4BDjlQeDzkDWsyHkOIDbvra5iGV2VrmmiPqq2ppqi30yER1FWQoqnYzYMWcgjOc9zznsfT11puviI8jiOmQJIpKqpQ5UemB7euT76tfdFooZaY1NZDHPAEPXUZ6Co45z2YfnqjbnT0dTV/C00vkhQQGVO45Iz7n041DJgY5GmSUA1r9jVdJwvikk83Je36fuoNa2aSpqJvPmZ5GyzE9JIJ/tZPr7dtdlHXVnxEipIzoMNL1Bj8oP8AaPr37/l9NRtVC0F2KoiBV4ch+svg46jj00x7PkqqS9LVUQART1SOwDqq8Z+U8EEhfpqOQMbq7ZdGC6/Dume3VsMVMvmqhiUZjSEv2YgFcf2lK5PPYnPrjUlLvWSikoaiGSSnovNmZaeI5M8i4PlZUZC4KlmPbOADqMgtS1dyqZ3EHVMDIIwuFXnLgpkAgjkL8pOGxwOYetlpblcTR0Qmq56tZIaWnqCvkzMoCxlEVR0kYyDwc8EnkmrARGLabtWpTnNEUmC0b0q7FQzV81Y1ZUMFEEMC5E3Vl3kkIXHSFz2Jyc+oI04UlzMKW+u+FmJkBdGqW6mjYn7vkkZU88+2NK6bdq3lWOqqxQS1K9Cxr1RpTwxDqcxdK/J83oSGz1ZzjJmrPTyNC1NV01ZFUVgMhFQRJJkgIWZiCo6yCwdSAc/L66nwuOMcgEl5SsbifDg+IyQ6Obr69/dMts3k9/t6pWfd1MTvBOtNMwHy54HSckntjt650n11oEkcyTgl6g/dK0mZI2B5J9D9c6mI7FQU7wRxy+WI386V0BiMoJHCkjJPsSMAd++uv4eghhZY5paicZJkKdxn1P8ADXQvjaDdLzjHY2RxBsWPmlSPaNHAiSSGokaPsxbCuw5/T+Ou6DYPxtMtdK0VPTsw6gGBC541LxL1S9MrdKk4HsOeeNSkJpoB5HXG0Up5Lhvfg8aTSiCa/hUI8XI4guP16/wnDwqplovDS10qHKwNPGD2yBM40a6PDuMRbJpYwwYJPUqCPXFRJo1WO69bhvltvegl7xRSV75YRFNLC3kVZLRnBx91qIt61lFxHXyzdI6ilQoZST/ZPr/PTVvBUfeW30k4RqesBJHA5hwf46TblcGpJpI3byWjYq2Bkk+2uf4jgopZRI8H/FgcUxUmHkzNOi4r7uK3vD0XSCvtsoyvmUo6x9PqRquZ66Fa9jTyvJCc9MkydJP6E6ZLtVJU0jiUM7N29NQNdb1pLQJh5sFS8hCLlgTj8Rb04yMfrpIeHRnwx0AqGA4tK52d4Up/lJQUlgmm+DRxChMiyDB6hjpAz+Idj6+vtqv59zXGdJUnpoZ5ZhjzGiAKkuGAU+wwMAeg1jX1VxSAwVMzujEH5/mBIJ9f+kdcUMMtSHVWLscN1H8II7dI7cZOc99W2wNjJzj+gu1grEOBwzbJ7DUrCmDyu7PLJgnzS8fdAOQfoRkYH9dPluvVPZrZRUtYvmV8jeXLUKgLNGoLZHsQAB9ODpXoqGKWSYKqCOOQpOuM9SlRgjngfQc6abPQ1Swq3VTzyRfIQqjrf5QFwRnpxnvkH+Omvh/NPDen3X36KpNj/wAlYO+1LKyXqCuuFPV1STRKYCJXjdRIrZ6RhiCQpA4wODnuDqy7HVUFoWquitTzWWs6UlcoqmIYGHbo475Bbj340s7S8PvtYTpUSp0NgvUO/U5K8HjAyB276smz7HWy1IjpKpvJUAKijjGOT+vf9dLLgXONNNEH5ehU2FxwkYXObbTp6+y7LBb7Jc6D4yg/faZ2PlyuQ4cepGfTOR+ml7clBUUtwM1LbnpkVgPMjfKt+a9tWNTUa0ESRxRKsYzgIoULk5wAPTJ1rriZEwYSR65H+OtiOx8Wq5nH8MhfGRHTK7D7K+f76twNbHTCIVVLMSzwqTHyc5GFIB9+2uO67Qpa5qd4bDXxMoBYxzdUnfuAy4PpxkauGvoaWjpq2o+zoqpvxrD+HBHYg/qdV1WXSGsMkEhmpOB8jSMPXvkg/wAtTh0TrZta5502IwuUNIJG+hSRR7Dt7ysgnqKCWOURxmpiaIjuVyfwgnJAwx9fbXTRXG12K4VNFPAizI7RztH8xcrkkgdunOP586mKpJxQSyJVsKZM4jdzPFLjkZU/rrju9ksu4LFRQ2mupxXVM3mSoqhHVcEdJA9CSBg9saxOJSQ5GxkGid6K7L8PTTzve8vuhtYOv6rVJOlyi8kQxmldTlmnXrXPyF35xjLjH+iAASARrHw68Oqu47npbo9Z8PTUZaMuZQkqSjP3YQ89eQTjsR68jSvNSXGmgqrO69Ev4ZYp4+3zZAGMdPOCMdyR3400225VNvjW4W63/D1DxGGVWw5ZlBRpC+RlypGc5AIBxkZFaGB9kM2W3iMdFEBzDqFPXLfgt9a8VjtBlZ5y6rTq0b1DJEVZwqkEqe+W6s5IOTjUzsy23k2GnfcRNTXqkCwxy9P7vTr1dKthhk+YqFgAzDCryeBWeUp4JZLaks1Q1OoPlzfMVDYVF6iele59c6sXae6xBVWG1xrDTPPPE87S1Z8wuMjoCeWwZQTwFKjPtkk3m4TSn6rLw3E+dJW3bv8AJME1NWV0XxM9XTNDIoZSqiNivcZ4BHf89ZUcFGkEpMnXk4KxksTxzzgca1Vm4II7Yoq/MqJkZkneoK9asGXIYKcHDOO3AJ6e66krTRQRVwg+aRpOpH8v5lQg85Ycev56utxAMfLcdQuO4jwqWPFF7GWx3Xer6JflqmeviWnowVzlUIzkfX9dddJVxrOaGpjZZZGwSvyleeMY+umRrTR2+tl6pA80hypm5Cr6AD6ajqCyRRblZEY1TxHzCT+FD/yj7+w0pkzNo6hZP5CRjwBV3R2+/kmvw4jMOxqSIsWKTVKkn1xUSaNbdh/+yUf/ADqq/wDyJNGkXqkYysA8kueJdbLQ7hsEsX4jDVqeM8fdarfcm4aqvjnioKB6mSlAaeoRC6wLjsccH8z2wdOXjhcXtk1lljRWklhq4lYjPQT5XzfngHGlTwqvkFgtG6KycRTFIIiIJGA87lsqM9yQf56p4hwc4R7ea0uH/h5uIdJxPFNzsblDWHYmxZPkL9zvskgW+81rQn4OunNSpeHpiY+Yo7lcDkD6aylsF9hGZbRcYwFL/NA4wo7nt2HGdXhSVVjpNy7RFsrYxboqGs6DJIB5YboIVs9j3GDzxqJirvgt6Wlq6amjt9bHU0srJeXrVwyg9R6+EGQP46rGADd33ou4i4qGt5ccDQ2iaqti7SvQeap02O5VTQIbZVymoQyRDyWPmIO7LxyOe41yoixr0qoUD0AxjX0BVbnsotV6enliWo29DJRW8Bx1SI8SKCo/tfMvp7a+fjnAAyT21DO0trxWtbhOIZKHvMQjDa2AHn+lfVdllsNFV3EzvMhd85jbJGc9u2Afz41a1ls9ssFE81XJD1yxkMsWPX2I59Ow41VsNVFBJ5ymeBygj4IKtjjnVkbTrrMLb8RLUs9ZGMBZQuD9Broo6iYGEr5r4pinTYySdvwkuIvYak+6i13vNSXKuNLDBDTuFgpopc4LK2TgD04P6kasbbW8Pj7etS/SWQDzc9hn6+3bn+moyo2ZYd0xLWIFppVQ/exoMr9fqQdclBTfYtppbSzvFKisxwyqs/SxOQVwSSOPmPA9DzqDFPjayxutfhEksjg3/mr7q0euOspVlGRkZwDjGo2R50D9ErkZ/CfmwNcViukU9tipI5BLUKhLKrDIwcHnt31quNvrJsNTyyRtgjB+vvjSxlsjA4FN4m58TjTSvJ74sUZLDz8AnCpjt30ubgvUD2tpoozFI3YFQT+eu2p2zURK0izHIX5Ys9Sg+xJ9NLl7d6eJWkjpx1csWbsffv8Ay0tG7C4/FTYg+CUUD5fuq+ut4qJ3ZOpmYegGANK1HXUq18kdRMaRvMDF40/Ge3zY5/XTRd7nFO8kQaJgWz1JGFH9TpHucCfFSrGGfrPUBKAUcngA+wHfOopRmbb22V0XBmgOoeH0VhUdVUXOrSdJg8agN1zOzDA4GAerPpkYyPqOdO9q2lRT07yyMIJ6hcztN8gP1Cgdvrnn6arc2i6WzblruXl4qJpjIsKAB1Qj5CU79JKuASB2wdOlLct11Nqd4LEekt0iYxt1Y7lee/541cwrGkZh1+ibxUyGTK/b1IXclnp6RhGtDSSooC4Eo6cZ+mf/AEdRM3hvWJUVdbagkNRVksTG/wAyITn5Cex14LPvScgpO0QJ7GVIz+o00Wyg3pbggraammjBHXKzHqx7gqdWJXtGgH6LEwkMzXFzDvvVn52q+r4brTV3XKJ6BJ5REss3EcRRmdWUjguXIP55J76Zto7sg+zo1qKhaeoSQ9CquPMbAQBF7IuQSQMZJydPEm4tr3hRFXSQ1fScpDKgZBgnDKDgnkdxzrjvOz9ubis8KfBUtJHFL1CSnQqVbPIU+ufrkaoThk8XKIrzC6eDFugl5mYO7j7/AJWV4qaippoOqKNJxKAvXHkH259Of012Wmsu6GaoudOkUKsMfd9OTnuR6j66il2terFURra62nutKpDLRXGNS2FzjokxxjJxn3Omuy19bVQuLlb4aCUMWKJL5gOeTzjtnWVFFNE2i7M3v1CnxEOFlkE0dsf1HQ/4u7YTiXaMUikMHqqpgR2OaiTRo2CQdpR9OOn4qqxjt/wiTRrTW8z4Qq5/aAY+ZYUxxic/+DVa7Y3K+2q2omFKlWk0YHlucBZFIaN/zVhnVveNO27xf3sZtdsqa9IWmE3kdJZAenHDMB6HSKuyrpTKPI2He3cf+8mlgcn/AKPVgazpIJHSlzV2UPH8JguFtgfGZHa21vrdk2PpqsqbxUemekmFrMs0FKlOxefKuVKEtgLnJ6D6+utD+JSmgjp1s6uY45Yw00oYYfHBAUAjjnP8tScdgu8lK0VX4Z1Mzf2XXyY2/wBlxqGm2NuSSRmi2NXxDPC+ZHgD8/M00sxOw1+SpRfiDhpovwbx6EH/ANDupGPxZ8muEwsqzKWViKifzHOJGkwG6eACwC/6IX1zpCSLqmLyAoGJYDPudM8NiujV8thbadfHckgFQY4/J6ugsQGJL9sgjuda5PD3d6v1Jta549MtD/g+rDYCaMhs+i5/ivHMRiYn4fAYcxMfoSTbnDtvQHfe/RQIMaMFT+7U5almEwmVEIBxho8r/A66afY+8UYPJtG4tj2kh/8APpmtFqvlCc1ew7xUA91EsGP5vqwwlmy8/l4djHkNaz3Kldr3uSipmieniR5CFDquFPBz2zn0/v1qq46xr8tXAstVBMzCeB5AnlcHhCRhkOcEEZ7410SSXZSPI8ObwgHb76D/AM+spqzcEzArsjcEB6SPu3puCfXl9OkYyU+MLQwWHx+FFAbbV/q7LF9oUkFPm3JSp8zSvLOJlGUIDRDuOfQ9wx9tTFNd6ZpAtNWu7/8AFSHHHt20tUdZuSk8wts7ctQXGAZZ4Dj9OvWxK299ZeXYV8d/9an4/L59RtibG45BorE44hiA0ubqPT9j/KmNxVdTS201dKslW2cdCg5Q49cemqqnqa24VGapfMfPUBIOB9Me2rDnvu4wq+TsC9sw9ZJIMfwD86gKmn3LPM0y7DuaSse48jj/AG86tYd4ZeZZOO4dinuzRsv79UpUmy7ldapwjCCHuT+FANTQ2jabPMEgqklq25MoXPldPJ6eM55zx2A/hPwTbthjVG2nfWCDC/8ABSP5sf79cc9Jfp5Cz+HVzLMCHdaiNC3V+IYD4wdQY3PPGY4zVq/wyGfCyCWeMuroK3/f3WzbNZ5cySQNHTCuHUs6hB5bEljwSR9Ce56fUjixeiNoH82r81ioUylgBx/q++kKOnuNMiCDw8vxCLhY5qmF0XnIwC/v6nOpilvN9hpykmwL27dOMeZT9I/2841Sw8EkEeVzr9ls4vmYqXMIq06n9v33XHX3pLLcIYaplZ5Y2dehcgAE45Pf+GuyTe89Ld6CiTEsdQ/QSU5H8NcjVt6mT77w5uhk7Flen/xY61/v81ZT1U/hvejNTHKOs8AOfcjr0CGXntdYyC9K1RFEyPDBkcREnU3YOvbpouaus0F4vNVI0dNRKsQby6d1ZycjJP55Pb6d9M+2G8+wJIySkfKsfxDh2C8DGQBjvpTh3Td6+ethsWzbkrUUvw0/T5JaNxhuknrweCDxrrpN07ngbFVsvcs+CPlEEQUEfUHWkXAjTosaDByMlBdGet1VG9uo29E81ccTRNKwYyRoGwDk4HPGPp661TmCal6YiRJ5XmAEZMiAgE/zH8dKJ3Tf5R5EWwdyKGymHWPpwRjGSeBjWJrtwxq4h2DdkZxjIaHHByBjzMYz7Y1FqVoyQW01Gc3t/qdPDrnZNMcAfvFVwO3/AAiTRrZ4f0tbR7Ko4rjTSUlWzzSPDJjqTrldgDgkdiNGnLYjFMAKZdGB7aNeEgDk40J69wPbRge2vOoZxnnWt5SCQq55xzoQqX2va77vbxhl3rVR/B2y1yPT0wxzOF6k6V9wOokn3OB9LmEfU3UzZX0xr2OPoxkDI7Aa2gc5PfQhYhRjkAAdh7az41BbxukVn2zUVktyltoQqBNFEsj5LABQrcEntzpeod9R1/h5VXKruMdurIfNQmJo5ZV6HKghSelicD6c8calbE5zcw2ulE6VrXZT6p+wPbRge2ombctno6USz3OlIyq/LKrEkkAAAH3Otdn3VbL9VVEFBI8nkRpL19OFdWZlBU+vKEabkdV0nZ23Vqa41pZyWwuAO2e/OlLbN/u103fuW1V0lO8VskiSLyYynDAtk5JJ9B+muaDdr0/iRU2ypnqPgJCaeF8RmETLGHcEj5wQM98jvp/JdZHYWm81tA9zSdkiC4JGW7/lraFA5OM6XqPeVqqL3W241EMQpo45UmadOidHB5U59CCCDzrni3xaLzbLn9n1wpqimVlQ1AERJKEpIob8SnuD66byn9kvNb3TTxr3jUJtmvmn2Zaq641SyzT0sUkkxUIGZgPT8zjUZe9yVVJZSXkgorjTz0zVMCyiTy4HqAnUSQOGUHn00gjJdlCC8AWU3YHtrzjS/X74sVuudHQy1iu9UwUSRfPHETwvW44XJBAz31ybj3lbKemkoaG6ZubhDClIEldst2HUejspySRgc+2lETzWm6DK0XqmzA9taaj5o2QcZHJHcD31F7e3Cm5LDDcaeCSASsyNHIQWRlYqw44PIPOpRE6Tzy3p9NMILTRTwQ4WFTXhnab34f8AiFWbSuMQqLdcVeqp6tQQJCo7/njgqfYaukL6n9PpoCDIJGSPXWWkSo0YHto0aEI0aNGhCCcDOuZH6j5jdz+Eew1y7iurWayTVqxpIVKJ94/Qi9TBep2wcKM5J9gdJp8QhJtua4RQQvPTymIkl1p2Cv0l1dgM/wCpnqJBAzxkQn0sWkK557gjWUWJB1EDrUlSdI8viJDC8kkNrqKhoVJlAcIq/dtMMFsZ6o06h/rAHBzjnqfFBLcldC1qZaqlGXjapjJLsGKhQOWHALED5QfpoQrGAxo0h1fihBQvNFU2mdZ6YlJo1mjJ6+cBOfnXjlhwuRnUpbN5i4XiK1vbaiCqdpAcsrIBGWWRuodwGCj3+8X66EKculpob1QSUVxpYqqmk/FHIuQfr+f10j1/gvs6WsaqFJURF2GIYpisY4xwMZA/XTC+4a1d0TW1aSNoYmjBbr6X6X/tAH8QB749NKc3i0ILxW0tZblSChln6mjk6neOJpFJUHAz93nAznPSOdWA6WDY1fmqrTFiL0ujWo7LJfA/Zyn8Ncccn94//WmLa+y7Rs742W0pMoqWUusknWFC9gD3xye+dQFP4rW6OWU19DNBTeZjz0mjkCJ5aSF3VT1ABZBk4I+up287pWzbboK6SjmzXugMTkK8XUpI6sZ9gD+emyYmRzae40rEOFa54bE3Vd9o2nR2e9V91p6qsknuJDVAlkDK5H4TjAxgcDXIfDrbp3VUbgNNIa2oVg/3h6MsvSzAehIJ/jrkj3vVPS0s0dsRlqB8iiclgfOWIDHR/wAoHjW874UvQqlIrGreKP8Az4HQzu6Y7c48sk/nqIYg2SHb6KyeHyVWXb03UL/uF7O8voEdcOc5+I5/LtrWPAva79XxNRcqg5whacZRfRe3YaY98bvOz7PBWrSCraecQBGk6AMgnJOD7aXLd4tmf401dowKOaOF2pakTL83Vg5xyPlPI1P+dmBy5ykbwdzsOcUIxkHXTuBtvuUz7h2/WSbQitu350pKqjML0pl5T7sghW+hxqFt2zbteKe5z73npaiStplpRDRDoWONW6/xYyW6sH6Y+usm8WbIalPLSVqXoYyykdLIw7L045zzznjGpXbm97buhJYqeKeOohgEs8brwhP9nq7E9v0P54Y2VzRlHz6/NVHRNJs/0lYeCO2PkC1FxjjY5kiE46ZPbPHoedeR+Bu1PPlBeuZCAVXzgOn35xzzrbN4kz0FtNxrLdHKrCKSOOJ2XCuzDBJB5AXP9O+tqeLdkWnSSOmrJamaMP5KKpCfNg5fOO+fzx9dWZZ8TE7I5xtQRRYeVuZrRScduWShsFhprdb0ZIIAVXrPU3ckkn1OSdSwGNV43izaIKdVpKKsqpAT1KeiPHBPcsfp/wBr6HEzft6fZVitVdS0Iq57vKsVLDJULApLI0g6nIIX5VPvzx9dUiSTZVsAAUE1aNVva/FWqr5Zo59vimaJmTMdUZ1PSEJJYIAB86j6nOme47yt1mitL3ESQi6yGOEqOsKegv8ANjnsPQHn+OkSph0aQ18XbFLQ1VZT01ZPT0kbzTMpiDIiu6FuhnDEEo2MDnXj+L1lQu32fczAnmMZhHH09EcqxO2OvOA7qO2ee2hCfdGozb9+ptyWiO5Uccq08jOqmQAElXZDwCfVTo0IUkyhlKsMg8EHXP8AAU/ltG0atEf7BUdP8NGjQhYQ2ylp5JmhgUPPJ5sjN82W6QuefoANepa6NK2SsFOhqJUWN5CMkqM4H+0f46NGhC3mCJm6jGhPIyVHr3/jrWtBTLXmtEQ+I8vyuv8A5OerGO3fn68e2jRoQtpjQyByoLgYDY5H665TZ7cWdxQ0yyPJ5rOIVyX/ANLOO/176NGhC5qjbFnqqSankoYQk6hJDGgjZ16g3SSoBwSOR667J6Gnq8CenjkQHqw6hucYzz+ejRoSg1svYqClgULDTRRgHqwiAc5znj686wNqoD3oqfv1f5pe+c57e+jRpKRmO9rOst9JcYPJraWGqiz1dEyB1z74OtFPYrVSxvHT2yjhjkwWRIFAbHbIxz3OjRpUudwbkvTsvfsO1dJX7No+kkHHkJjIxj09MD+A1uprbRUZJpqSCAlekmONV4yTjgdskn9dGjQmrjp9s2enWRUt1P0ysGZTGCCQSRwfYkn9dbfsW2g/Jb6UHnLeSueeD6e2jRpS4uNk2kDQ0UAs1s9tQYWgpR27Qr6EkenuT/E6wuthtV8tf2ddLdTVtHkEQzRhkBHYgemNGjSJVxUGy9vWqlNLb7VDR05JYxQZRCT3JUHB1LtR07GEmCMmnOYiUH3fGPl9uDjj00aNCFxS7bsk79c1nt8jAk9TUyE8kk9x7kn9dbzZ7aylTb6UhgwIMK8hmDH09WAJ+ozo0aELop6eGlhENPEkMYJISNQoGTk8D6nOjRo0IX//2Q==</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Infiniton Réfrigérateur Américain SBS-668 559L</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2× Triporteur (hors Jumia) + Samsung Galaxy S26 Ultra 16GB+1TB + Revolution 75" 4K UHD Smart Android TV</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
         <v>2000000</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Lave-linge LG 15kg + Seche-linge 8kg</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Apple iPhone 17 Pro Max 512Go</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TV Samsung 77" OLED + Frigo Skyworth SBS 473L</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TV Xiaomi S Mini LED 75"</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Samsung Galaxy S25 Ultra 1To Titanium</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TV LG 77" OLED + Lave-linge LG 10.5kg TurboWash</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>TV Samsung 65" QLED Q7F 4K</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TV Samsung 77" OLED Vision AI</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Galaxy S25 Ultra 1To + Galaxy Z Fold 6 512Go</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TV LG 65" 4K OLED evo C5</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Galaxy Z Fold 6 + Apple iPhone 17 Pro Max</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TV LG 83" OLED + Apple iPhone 17 Pro Max 512Go</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Frigo Whirlpool 260L Side by Side French Door</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TV LG 77" OLED + TV LG 65" OLED</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TV LG 83" OLED + Frigo Whirlpool 260L SBS</t>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Samsung Galaxy Tab S9 Ultra 12GB+512GB</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2× Triporteur (hors Jumia) + Samsung Galaxy S26 Ultra 16GB+1TB + Samsung 85" Crystal UHD 4K Smart TV 85U8075 + Samsung 50 45k UHD CRISTAL</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TV LG 77" 4K OLED evo C5</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TV LG 83" OLED + Frigo Whirlpool 260L SBS</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TV LG 83" OLED + TV LG 77" OLED</t>
+      <c r="B15" s="2" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Hisense Smart TV QLED 4K 55"</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Triporteur (hors Jumia) + Samsung Galaxy Tab S9 Ultra 12GB+512GB + Samsung 75" Crystal UHD 4K Smart TV 75U8075</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3× Triporteur (hors Jumia) + Samsung 85" Crystal UHD 4K Smart TV 85U8075 + Samsung Galaxy Tab S9+ 12GB+512GB + Samsung Tab S10 Ultra 14.6" 12GB+256GB</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAcFBQYFBAcGBgYIBwcICxILCwoKCxYPEA0SGhYbGhkWGRgcICgiHB4mHhgZIzAkJiorLS4tGyIyNTEsNSgsLSz/2wBDAQcICAsJCxULCxUsHRkdLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCwsLCz/wAARCACFAMgDASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAcCBAUGCAMB/8QAPhAAAQMDAgQEAwUFBgcAAAAAAQACAwQFEQYSByExQRMiUWEycYEIFCNCsTNykaHBFRYkUoKSFzRUc4Sy4f/EABoBAQADAQEBAAAAAAAAAAAAAAACAwQBBQb/xAApEQACAQMDAgUFAQAAAAAAAAAAAQIDBBESITEFURNBYYHBcZGh0eHx/9oADAMBAAIRAxEAPwDpFERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREAREQBERAEREARFEEepdaVs1zlpb1TQQwS1jo2S0rXeSAjln33Yz7KLlg0UqDqpvKSXfPwn2JfRQ7ozU/EXWETpKeus8AbTQVX48Djlsu/A8vcbDn5hZTUl74jaTsNTd62XTtTTU20vEccoecuDeQ+Z9VHXtnBerLVJQjOLb8t/lEnIoJZxq1kx22XTlG/BA8rZB16fmP/AM7q4Zxy1AwZl0mwgN3ZbK8cs4zzb0zyUfGgaH0e6XCT90TcihQ/aDlppTHV6WkY8EAtFTh3PpyLPdbd/wAQb+z9tw+vTf8Atua/9FJVIvgz1On16bxNJe6/Zvq0q4XGSp4uWi3tJbFSU8srufxOew9vYAK1PFCeL/mNFaki/wDELlYaO1LadXcSa2vhjqqephpwyKKZu04HlkLhzwQSB/FclJPCRKjbTgpTmtknxh8rC4ZJyJlFaecedTN93pZZthf4bC/aOpwM4WpaZ1a+76vvlFKZBTxGA0oLPKA6MkjcOXPaTgnPVZLVGqrXp6klZcIa2fMLpHR01JJLlnQkuaNrfqQoM1VxZZUWGW3aco6u307p3ymo2+G7wyNuxuM7fiwT1x065RLMkjknhNnR8M8VRH4kMrJWZI3McCMg4IyPcYVai3gHcWT6IqLe2R0go6kuYXdQyQbgPo7ePopSUpx0yaORepZCIiiSCIiAIiIAiIgCIiAsrzcobPY624zvDIqWF8ziSPygnuuTabUV5ulOYGOhkDTK93iTtgP4vxgZIyDjp2XWN5oYrlaZ6WaOOSN4BcyVu5jsEOwR3BwuNaaZsVRO98FJIJDlraiAvIGSeR7Dms1ZtNH0XR4xlComsvb17/02y1a21dpODwrbHHTx+DHDgGKYbIwQ0cyem4/NfL3xW1TqayVFouYgdTTbS9zYA13lIcOYPt6LVauaANI+4W1jvWNr2n/2wqzNQDT7YIICa2SUumk3YDYwMBjefPOSST6ABZnOWMZPoaVrRUlNw3XovIqbqK4sbtZVVO0YA8oIwO3Toe/r3yqv7z3As2vqpHDZ4eHwg4bndgcuQzzwsdgd4n/Ry+Edg2QH5qvJsa7pfYup7nLcbgKypldPKHxveS0jcGkED+WFN0P2jrc7lJYpWEdcVTT+oCharNDS2WmbTTvmrZ9xqMfDE3OA3n1ccZPYAj3VnE5u0AvePYtViqShwYq9nRusOpHj6r5Ogo/tDafJAlttY39ySN39Qo80vqLTsGprjV6kZVOo6gSPY2AvDg90m4ElhB+HPdaDK9phcC8HPLm33Xq2Bk081Q6qhZ4DmNELyd0oI57R329/mpRqObWozVLOlZ0Zugnl4Wz358uTqmi0Zp+st0FfRyXSnhnibKwi4TtIaRkHm7lyK1+p4nUWj6qrtNRVS30QOaYJ2SxlwaRkskeSAXNPcZJBGeaiKzit1Y42qmqqt4bEXeCayZkOxoAxt8w9Fjrxpi4Utz/sumomTzRbfwKMOkIBbndggHA7k9FocsLMDxLWn4tSVO9bUUs7+W6x6+hPcXFykdSQ1clmrXU0oz4lPJHNt5ZIIBBJA7DJUY8QNQUU9pjrYKNzKW5z1D6erIa2KXbK7HL4slpIPQeYZWAuulNUaK0+6tqJqGmpbiW0/g/eGyulcfMAGtBGRgkEHljqtCllut6tTqKAVU0FBvnLA5zhDucAX4HIZdt/kpRlJ8me9o2lOOaE8vP49yWOCmpZLFrGegkt7oqesiiilbG/LIZA8hrueeu7BGcrpVc6cNrK3V+qbXeprrURiMNfJSviDo5ZYsbtpyC05AdnBBXRasjPXvnJ5Tio7IIiKRwIiIAiIgCIiAIiIDwrmTSW+oZT48Z0bgzccDdg4/moD0x9nKulDJtSXdtOP+novO7/AHu5D6AroNFFxT5L6dxUpJqm8ZIpu3BeyWm01Vysraqe60cLpqZlVN4sUkjWktD245gnsuXrrqq4XGukqqqioqd8x8TZBF4bRn0bnl06Luq6wGooXNNU+lhHmldHycWAHLQfy59Rz9MdVAnFLhlb9JadrrnQGmkorpURMlpqqla+WnOSW+BLnLAAC3bg5BPNQlTj2LoX1xF5U3nggykrrlXk/dLa6do6uYDj+PRelTc6ylk/xtskpvdxIB+Wev0Umac0PUXHT4uVTXsttEG/gtxt3Dt0BPP0A6c14aq0jPZKZtPWPjrrdWD8OUDo7ng5/jz5H+tWmHY0rqV2t9f4X6I9Zc5JKOaqjo5pIYADK9rsiMEhoJ+ZICzdzvForaiKKyWG9wSNp2ySRyHxnHODvAAyGkEY+atdJ6GvN6u1ZQUNBVV9JSua2s8FwYC0+ZozzHPbnv8AyUp610jr+nvtNrvTVm/sipgpmUZpqKf7xMGNbtDix0bQW7doIAPQHspeDBo6usXaknq49CJ6qokpY2PqKGtpyRnbLAWkjHxYI6dea8am7UJ+7VEfjFvn57PkOaoZWahtc9aKyaVktZG6KZ1TE97wCckt3DynPcYWMDy9349QTjIa53ooeDFM0vrVaUcPnb7p/U2vT+sZLBdIblbp3RyRHzDYHB7e7SD2Jx/BSPpoXDVrNR3XfPDNXxvd4tKw+IZAR+G3GcN5gH2ChRkMJGW1cP8AuIP6KVeGuuKbTFrnE0kXjRse4kS9W7ge3T6j5qaio8GC4valxlzSy+3+mzauud4tGhrhHUuiruQgjdO1rvAc9m1pjaBkubzPtnPZYrgva6Vttq6mR7XNqJqbbvlaQ5rJml20Abg7rkE9DnHJa1xJ11JrHV1DUWyXdBGxsUcMZJdNn48gdSSS315e63rT0b9A8CW01ZbGw1FfVvdGyraRIZCctl29QGtaDnry7KwweZXpqhqdI8a7hSRRk08NU9+1oy4wTcxgDrglvIf5Sprh1HapqptN98ZHO47WslBYSfQZ6n26qANI326DUMV2e101E2obFUVUvN8ZkyCQe/MtJycA4wq7jQ6g0RVTXESUtwo5H/4hhjy1w3dHtyc8z1GCM5UIvSaKtTxdOVwsHSCLD6UvdJqHS9DcqJpZFLHjwycmNw5FpPsQQswrzKEREAREQBERAEREAREQHlU07KqExSZ2EgkDvg5x8uSjvjtbZq7hw6eFpcKGpjqJAOzObSfpuz8sqSVRNDHUQPhmjbJFI0texwyHA8iCO4XGsnUQNT2mi1/w5oaKkqXRTwRsjmZEAXxuaMfD1LXYB9FjtfR0+n9GW/T/AIvjVMT2nBIL2gd3Y6E4GAtvuPASmFzkqbFfp7XC8ktp3w+K2PPZrtwOPY5WS0twYoLNeGXW8XGS9VULg+FrohHExw/Ntydx+ZVWhktRnuG2lItLaRga6Esrq0NqKtx+IvLQA3/SABj5rbkRWpYWCB8cxrxhzQ4ehGVaS2e2z/trfSyfvwtP6hXiLoMNNo/TVR+209apP3qOM/0Vk/hxo179392LW13q2ma39FsyLmAa7SaA0lQyiWm05bYZQciRtO0OB+fVaxxD0rdNRT3F0NNmnobO5lCAQd8735eAPXZGG/61JKI0juTnTQfhXvRdbY2OAqXPdIGfmceoIHfBGD6citn1b4lu0TO+7lkdTUUxibETze8jGR3IHMkrYdR8HrTd7s+522tqLNVzO3S+C0Pje7/NsPQ+4IWOpOB9NLco6i+36pu1PHgmn8IRCTHQPdkuI9shVaHklqMlwRoqik4ZUsk4LRVzS1EQdyOxzsNP1xn6qQlTFEyGJkUTGxxsAa1rRgNA6ABVK1bEAiIugIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiAIiIAiIgCIiA/9k=</t>
         </is>
       </c>
     </row>
